--- a/docs/Chiraath-Summary-Aug26.xlsx
+++ b/docs/Chiraath-Summary-Aug26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anooppremachandran/Desktop/CHIRAATH/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A36F716E-4A57-0241-9B32-574C24192A96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA8A2D1C-869A-5A48-BE38-6581203DE227}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3191" uniqueCount="1266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3197" uniqueCount="1270">
   <si>
     <t>Notes:</t>
   </si>
@@ -3786,9 +3786,6 @@
     <t>Light Blue/Navy Blue, Black/Red, Red/Green, Violet/Green, Green/Red</t>
   </si>
   <si>
-    <t>Maroon/Mustard, Green/Coffee Brown, Purple/Green</t>
-  </si>
-  <si>
     <t>Brown</t>
   </si>
   <si>
@@ -3804,9 +3801,6 @@
     <t>Black, Maroon, Violet, Rani Pink, Olive Green, Navy Blue</t>
   </si>
   <si>
-    <t>Black, Blue, Wine</t>
-  </si>
-  <si>
     <t>Golden (Different Designs)</t>
   </si>
   <si>
@@ -3862,6 +3856,24 @@
   </si>
   <si>
     <t>Jiji Friend</t>
+  </si>
+  <si>
+    <t>Prabha Chidambaram - Purple/Green</t>
+  </si>
+  <si>
+    <t>Maroon/Mustard, Green/Coffee Brown</t>
+  </si>
+  <si>
+    <t>CHR-223 - Purple/Green, CHR-229 - Black</t>
+  </si>
+  <si>
+    <t>Rajan</t>
+  </si>
+  <si>
+    <t>Blue, Wine</t>
+  </si>
+  <si>
+    <t>Prabha Chidambaram - Green</t>
   </si>
 </sst>
 </file>
@@ -4427,15 +4439,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -4459,6 +4462,15 @@
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4747,7 +4759,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>305</c:v>
+                  <c:v>307</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>96</c:v>
@@ -4850,7 +4862,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>218</c:v>
+                  <c:v>216</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>54</c:v>
@@ -5183,7 +5195,7 @@
                   <c:v>57128</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>162189.19666666666</c:v>
+                  <c:v>160465.19666666666</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>1062</c:v>
@@ -6580,10 +6592,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>406</c:v>
+                  <c:v>408</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>275</c:v>
+                  <c:v>273</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7770,7 +7782,7 @@
       </c>
       <c r="B4" s="10">
         <f>SUMIFS(Sales!C:C, Sales!I:I, "Completed")</f>
-        <v>483293</v>
+        <v>485923</v>
       </c>
       <c r="E4" s="9" t="str">
         <f>PartnerShares!A3</f>
@@ -7787,7 +7799,7 @@
       </c>
       <c r="B5" s="12">
         <f>SUM(Sales!C:C)</f>
-        <v>501023</v>
+        <v>503653</v>
       </c>
       <c r="E5" s="11" t="str">
         <f>PartnerShares!A4</f>
@@ -7804,7 +7816,7 @@
       </c>
       <c r="B6" s="10">
         <f>B4-B3</f>
-        <v>-73054</v>
+        <v>-70424</v>
       </c>
       <c r="E6" s="9" t="str">
         <f>PartnerShares!A5</f>
@@ -8020,11 +8032,11 @@
       </c>
       <c r="C26" s="10">
         <f>'Cash Pool'!D4</f>
-        <v>161129.88619999998</v>
+        <v>162006.72819999998</v>
       </c>
       <c r="D26" s="10">
         <f>'Cash Pool'!E4</f>
-        <v>255009.11380000002</v>
+        <v>254132.27180000002</v>
       </c>
       <c r="E26" s="10">
         <f>'Cash Pool'!F4</f>
@@ -8032,11 +8044,11 @@
       </c>
       <c r="F26" s="13">
         <f>'Cash Pool'!G4</f>
-        <v>117699.08780000001</v>
+        <v>116822.2458</v>
       </c>
       <c r="G26" s="17" t="str">
         <f>IF(ROUND(F26,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F26),"#,##0"),IF(ROUND(F26,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F26),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹117,699</v>
+        <v>Pay ₹116,822</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="13.5" customHeight="1">
@@ -8050,11 +8062,11 @@
       </c>
       <c r="C27" s="12">
         <f>'Cash Pool'!D5</f>
-        <v>161033.22759999998</v>
+        <v>161909.5436</v>
       </c>
       <c r="D27" s="12">
         <f>'Cash Pool'!E5</f>
-        <v>-106409.22759999998</v>
+        <v>-107285.5436</v>
       </c>
       <c r="E27" s="12">
         <f>'Cash Pool'!F5</f>
@@ -8062,11 +8074,11 @@
       </c>
       <c r="F27" s="14">
         <f>'Cash Pool'!G5</f>
-        <v>-34822.185599999983</v>
+        <v>-35698.501600000003</v>
       </c>
       <c r="G27" s="18" t="str">
         <f>IF(ROUND(F27,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F27),"#,##0"),IF(ROUND(F27,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F27),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹34,822</v>
+        <v>Receive ₹35,699</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="13.5" customHeight="1">
@@ -8080,11 +8092,11 @@
       </c>
       <c r="C28" s="10">
         <f>'Cash Pool'!D6</f>
-        <v>161129.88619999998</v>
+        <v>162006.72819999998</v>
       </c>
       <c r="D28" s="10">
         <f>'Cash Pool'!E6</f>
-        <v>-148599.88619999998</v>
+        <v>-149476.72819999998</v>
       </c>
       <c r="E28" s="10">
         <f>'Cash Pool'!F6</f>
@@ -8092,11 +8104,11 @@
       </c>
       <c r="F28" s="13">
         <f>'Cash Pool'!G6</f>
-        <v>-82876.902199999968</v>
+        <v>-83753.744199999972</v>
       </c>
       <c r="G28" s="16" t="str">
         <f>IF(ROUND(F28,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F28),"#,##0"),IF(ROUND(F28,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F28),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹82,877</v>
+        <v>Receive ₹83,754</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.75" customHeight="1">
@@ -8191,16 +8203,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" customHeight="1">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="87" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
+      <c r="H1" s="87"/>
     </row>
     <row r="3" spans="1:8" ht="15" customHeight="1">
       <c r="A3" s="19" t="s">
@@ -8224,7 +8236,7 @@
       </c>
       <c r="E5" s="21">
         <f>Summary!B4</f>
-        <v>483293</v>
+        <v>485923</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
@@ -8233,14 +8245,14 @@
       </c>
       <c r="B6" s="21">
         <f>Summary!B6</f>
-        <v>-73054</v>
+        <v>-70424</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>71</v>
       </c>
       <c r="E6" s="21">
         <f>SUMIFS(INVENTORY!K:K, INVENTORY!N:N, "&lt;&gt;Sold Out")</f>
-        <v>210758.39666666667</v>
+        <v>209034.39666666667</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1">
@@ -8292,7 +8304,7 @@
       </c>
       <c r="G10" s="21">
         <f>SUM(INVENTORY!F:F)</f>
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1">
@@ -8316,7 +8328,7 @@
       </c>
       <c r="G11" s="27">
         <f>SUM(INVENTORY!G:G)</f>
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
@@ -8512,11 +8524,11 @@
       </c>
       <c r="G47" s="30">
         <f>SUMIF(INVENTORY!C:C, F47, INVENTORY!F:F)</f>
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="H47" s="30">
         <f>SUMIF(INVENTORY!C:C, F47, INVENTORY!G:G)</f>
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="J47" s="30" t="s">
         <v>96</v>
@@ -8543,7 +8555,7 @@
       </c>
       <c r="K48" s="31">
         <f t="array" ref="K48">SUMPRODUCT((INVENTORY!$C$2:$C$477=J48)*(INVENTORY!$D$2:$D$477)*(INVENTORY!$G$2:$G$477))</f>
-        <v>162189.19666666666</v>
+        <v>160465.19666666666</v>
       </c>
     </row>
     <row r="49" spans="5:12" ht="15" customHeight="1">
@@ -12201,8 +12213,8 @@
     <col min="10" max="16384" width="8.83203125" style="42"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="84" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A1" s="83" t="s">
+    <row r="1" spans="1:9" s="81" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A1" s="80" t="s">
         <v>98</v>
       </c>
       <c r="B1" s="43" t="s">
@@ -12231,13 +12243,13 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="14">
-      <c r="A2" s="85">
+      <c r="A2" s="82">
         <v>45900</v>
       </c>
       <c r="B2" s="44" t="s">
         <v>146</v>
       </c>
-      <c r="C2" s="86">
+      <c r="C2" s="83">
         <v>1250</v>
       </c>
       <c r="D2" s="44" t="s">
@@ -12254,13 +12266,13 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="14">
-      <c r="A3" s="87">
+      <c r="A3" s="84">
         <v>45900</v>
       </c>
       <c r="B3" s="45" t="s">
         <v>149</v>
       </c>
-      <c r="C3" s="88">
+      <c r="C3" s="85">
         <v>1600</v>
       </c>
       <c r="D3" s="45" t="s">
@@ -12277,13 +12289,13 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="14">
-      <c r="A4" s="85">
+      <c r="A4" s="82">
         <v>45900</v>
       </c>
       <c r="B4" s="44" t="s">
         <v>151</v>
       </c>
-      <c r="C4" s="86">
+      <c r="C4" s="83">
         <v>1800</v>
       </c>
       <c r="D4" s="44" t="s">
@@ -12300,13 +12312,13 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="14">
-      <c r="A5" s="87">
+      <c r="A5" s="84">
         <v>45900</v>
       </c>
       <c r="B5" s="45" t="s">
         <v>152</v>
       </c>
-      <c r="C5" s="88">
+      <c r="C5" s="85">
         <v>2000</v>
       </c>
       <c r="D5" s="45" t="s">
@@ -12323,13 +12335,13 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="14">
-      <c r="A6" s="85">
+      <c r="A6" s="82">
         <v>45900</v>
       </c>
       <c r="B6" s="44" t="s">
         <v>153</v>
       </c>
-      <c r="C6" s="86">
+      <c r="C6" s="83">
         <v>1600</v>
       </c>
       <c r="D6" s="44" t="s">
@@ -12346,13 +12358,13 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="14">
-      <c r="A7" s="87">
+      <c r="A7" s="84">
         <v>45900</v>
       </c>
       <c r="B7" s="45" t="s">
         <v>154</v>
       </c>
-      <c r="C7" s="88">
+      <c r="C7" s="85">
         <v>750</v>
       </c>
       <c r="D7" s="45" t="s">
@@ -12369,13 +12381,13 @@
       </c>
     </row>
     <row r="8" spans="1:9" ht="14">
-      <c r="A8" s="85">
+      <c r="A8" s="82">
         <v>45900</v>
       </c>
       <c r="B8" s="44" t="s">
         <v>155</v>
       </c>
-      <c r="C8" s="86">
+      <c r="C8" s="83">
         <v>3600</v>
       </c>
       <c r="D8" s="44" t="s">
@@ -12392,13 +12404,13 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="14">
-      <c r="A9" s="87">
+      <c r="A9" s="84">
         <v>45901</v>
       </c>
       <c r="B9" s="45" t="s">
         <v>155</v>
       </c>
-      <c r="C9" s="88">
+      <c r="C9" s="85">
         <v>1000</v>
       </c>
       <c r="D9" s="45" t="s">
@@ -12415,13 +12427,13 @@
       </c>
     </row>
     <row r="10" spans="1:9" ht="14">
-      <c r="A10" s="85">
+      <c r="A10" s="82">
         <v>45902</v>
       </c>
       <c r="B10" s="44" t="s">
         <v>156</v>
       </c>
-      <c r="C10" s="86">
+      <c r="C10" s="83">
         <v>2000</v>
       </c>
       <c r="D10" s="44" t="s">
@@ -12438,13 +12450,13 @@
       </c>
     </row>
     <row r="11" spans="1:9" ht="14">
-      <c r="A11" s="87">
+      <c r="A11" s="84">
         <v>45903</v>
       </c>
       <c r="B11" s="45" t="s">
         <v>157</v>
       </c>
-      <c r="C11" s="88">
+      <c r="C11" s="85">
         <v>3400</v>
       </c>
       <c r="D11" s="45" t="s">
@@ -12461,13 +12473,13 @@
       </c>
     </row>
     <row r="12" spans="1:9" ht="14">
-      <c r="A12" s="85">
+      <c r="A12" s="82">
         <v>45904</v>
       </c>
       <c r="B12" s="44" t="s">
         <v>158</v>
       </c>
-      <c r="C12" s="86">
+      <c r="C12" s="83">
         <v>2500</v>
       </c>
       <c r="D12" s="44" t="s">
@@ -12484,13 +12496,13 @@
       </c>
     </row>
     <row r="13" spans="1:9" ht="14">
-      <c r="A13" s="87">
+      <c r="A13" s="84">
         <v>45905</v>
       </c>
       <c r="B13" s="45" t="s">
         <v>160</v>
       </c>
-      <c r="C13" s="88">
+      <c r="C13" s="85">
         <v>4000</v>
       </c>
       <c r="D13" s="45" t="s">
@@ -12507,13 +12519,13 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="14">
-      <c r="A14" s="85">
+      <c r="A14" s="82">
         <v>45906</v>
       </c>
       <c r="B14" s="44" t="s">
         <v>161</v>
       </c>
-      <c r="C14" s="86">
+      <c r="C14" s="83">
         <v>8000</v>
       </c>
       <c r="D14" s="44" t="s">
@@ -12530,13 +12542,13 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="14">
-      <c r="A15" s="87">
+      <c r="A15" s="84">
         <v>45907</v>
       </c>
       <c r="B15" s="45" t="s">
         <v>152</v>
       </c>
-      <c r="C15" s="88">
+      <c r="C15" s="85">
         <v>1300</v>
       </c>
       <c r="D15" s="45" t="s">
@@ -12553,13 +12565,13 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="14">
-      <c r="A16" s="85">
+      <c r="A16" s="82">
         <v>45908</v>
       </c>
       <c r="B16" s="44" t="s">
         <v>163</v>
       </c>
-      <c r="C16" s="86">
+      <c r="C16" s="83">
         <v>900</v>
       </c>
       <c r="D16" s="44" t="s">
@@ -12576,13 +12588,13 @@
       </c>
     </row>
     <row r="17" spans="1:9" ht="14">
-      <c r="A17" s="87">
+      <c r="A17" s="84">
         <v>45909</v>
       </c>
       <c r="B17" s="45" t="s">
         <v>164</v>
       </c>
-      <c r="C17" s="88">
+      <c r="C17" s="85">
         <v>750</v>
       </c>
       <c r="D17" s="45" t="s">
@@ -12599,13 +12611,13 @@
       </c>
     </row>
     <row r="18" spans="1:9" ht="14">
-      <c r="A18" s="85">
+      <c r="A18" s="82">
         <v>45910</v>
       </c>
       <c r="B18" s="44" t="s">
         <v>165</v>
       </c>
-      <c r="C18" s="86">
+      <c r="C18" s="83">
         <v>700</v>
       </c>
       <c r="D18" s="44" t="s">
@@ -12622,13 +12634,13 @@
       </c>
     </row>
     <row r="19" spans="1:9" ht="14">
-      <c r="A19" s="87">
+      <c r="A19" s="84">
         <v>45911</v>
       </c>
       <c r="B19" s="45" t="s">
         <v>166</v>
       </c>
-      <c r="C19" s="88">
+      <c r="C19" s="85">
         <v>2900</v>
       </c>
       <c r="D19" s="45" t="s">
@@ -12645,13 +12657,13 @@
       </c>
     </row>
     <row r="20" spans="1:9" ht="14">
-      <c r="A20" s="85">
+      <c r="A20" s="82">
         <v>45912</v>
       </c>
       <c r="B20" s="44" t="s">
         <v>167</v>
       </c>
-      <c r="C20" s="86">
+      <c r="C20" s="83">
         <v>2600</v>
       </c>
       <c r="D20" s="44" t="s">
@@ -12668,13 +12680,13 @@
       </c>
     </row>
     <row r="21" spans="1:9" ht="14">
-      <c r="A21" s="87">
+      <c r="A21" s="84">
         <v>45913</v>
       </c>
       <c r="B21" s="45" t="s">
         <v>168</v>
       </c>
-      <c r="C21" s="88">
+      <c r="C21" s="85">
         <v>900</v>
       </c>
       <c r="D21" s="45" t="s">
@@ -12691,13 +12703,13 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="14">
-      <c r="A22" s="85">
+      <c r="A22" s="82">
         <v>45914</v>
       </c>
       <c r="B22" s="44" t="s">
         <v>169</v>
       </c>
-      <c r="C22" s="86">
+      <c r="C22" s="83">
         <v>1000</v>
       </c>
       <c r="D22" s="44" t="s">
@@ -12714,13 +12726,13 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="14">
-      <c r="A23" s="87">
+      <c r="A23" s="84">
         <v>45915</v>
       </c>
       <c r="B23" s="45" t="s">
         <v>170</v>
       </c>
-      <c r="C23" s="88">
+      <c r="C23" s="85">
         <v>1800</v>
       </c>
       <c r="D23" s="45" t="s">
@@ -12737,13 +12749,13 @@
       </c>
     </row>
     <row r="24" spans="1:9" ht="14">
-      <c r="A24" s="85">
+      <c r="A24" s="82">
         <v>45916</v>
       </c>
       <c r="B24" s="44" t="s">
         <v>171</v>
       </c>
-      <c r="C24" s="86">
+      <c r="C24" s="83">
         <v>1600</v>
       </c>
       <c r="D24" s="44" t="s">
@@ -12760,13 +12772,13 @@
       </c>
     </row>
     <row r="25" spans="1:9" ht="14">
-      <c r="A25" s="87">
+      <c r="A25" s="84">
         <v>45917</v>
       </c>
       <c r="B25" s="45" t="s">
         <v>172</v>
       </c>
-      <c r="C25" s="88">
+      <c r="C25" s="85">
         <v>800</v>
       </c>
       <c r="D25" s="45" t="s">
@@ -12783,13 +12795,13 @@
       </c>
     </row>
     <row r="26" spans="1:9" ht="14">
-      <c r="A26" s="85">
+      <c r="A26" s="82">
         <v>45917</v>
       </c>
       <c r="B26" s="44" t="s">
         <v>172</v>
       </c>
-      <c r="C26" s="86">
+      <c r="C26" s="83">
         <v>1300</v>
       </c>
       <c r="D26" s="44" t="s">
@@ -12806,13 +12818,13 @@
       </c>
     </row>
     <row r="27" spans="1:9" ht="14">
-      <c r="A27" s="87">
+      <c r="A27" s="84">
         <v>45918</v>
       </c>
       <c r="B27" s="45" t="s">
         <v>173</v>
       </c>
-      <c r="C27" s="88">
+      <c r="C27" s="85">
         <v>1500</v>
       </c>
       <c r="D27" s="45" t="s">
@@ -12829,13 +12841,13 @@
       </c>
     </row>
     <row r="28" spans="1:9" ht="14">
-      <c r="A28" s="85">
+      <c r="A28" s="82">
         <v>45919</v>
       </c>
       <c r="B28" s="44" t="s">
         <v>174</v>
       </c>
-      <c r="C28" s="86">
+      <c r="C28" s="83">
         <v>1400</v>
       </c>
       <c r="D28" s="44" t="s">
@@ -12852,13 +12864,13 @@
       </c>
     </row>
     <row r="29" spans="1:9" ht="14">
-      <c r="A29" s="87">
+      <c r="A29" s="84">
         <v>45920</v>
       </c>
       <c r="B29" s="45" t="s">
         <v>175</v>
       </c>
-      <c r="C29" s="88">
+      <c r="C29" s="85">
         <v>3500</v>
       </c>
       <c r="D29" s="45" t="s">
@@ -12875,13 +12887,13 @@
       </c>
     </row>
     <row r="30" spans="1:9" ht="14">
-      <c r="A30" s="85">
+      <c r="A30" s="82">
         <v>45921</v>
       </c>
       <c r="B30" s="44" t="s">
         <v>176</v>
       </c>
-      <c r="C30" s="86">
+      <c r="C30" s="83">
         <v>2400</v>
       </c>
       <c r="D30" s="44" t="s">
@@ -12898,13 +12910,13 @@
       </c>
     </row>
     <row r="31" spans="1:9" ht="14">
-      <c r="A31" s="87">
+      <c r="A31" s="84">
         <v>45922</v>
       </c>
       <c r="B31" s="45" t="s">
         <v>177</v>
       </c>
-      <c r="C31" s="88">
+      <c r="C31" s="85">
         <v>1000</v>
       </c>
       <c r="D31" s="45" t="s">
@@ -12921,13 +12933,13 @@
       </c>
     </row>
     <row r="32" spans="1:9" ht="14">
-      <c r="A32" s="85">
+      <c r="A32" s="82">
         <v>45924</v>
       </c>
       <c r="B32" s="44" t="s">
         <v>178</v>
       </c>
-      <c r="C32" s="86">
+      <c r="C32" s="83">
         <v>2500</v>
       </c>
       <c r="D32" s="44" t="s">
@@ -12944,13 +12956,13 @@
       </c>
     </row>
     <row r="33" spans="1:9" ht="14">
-      <c r="A33" s="87">
+      <c r="A33" s="84">
         <v>45924</v>
       </c>
       <c r="B33" s="45" t="s">
         <v>179</v>
       </c>
-      <c r="C33" s="88">
+      <c r="C33" s="85">
         <v>9250</v>
       </c>
       <c r="D33" s="45" t="s">
@@ -12967,13 +12979,13 @@
       </c>
     </row>
     <row r="34" spans="1:9" ht="14">
-      <c r="A34" s="85">
+      <c r="A34" s="82">
         <v>45930</v>
       </c>
       <c r="B34" s="44" t="s">
         <v>169</v>
       </c>
-      <c r="C34" s="86">
+      <c r="C34" s="83">
         <v>3800</v>
       </c>
       <c r="D34" s="44" t="s">
@@ -12990,13 +13002,13 @@
       </c>
     </row>
     <row r="35" spans="1:9" ht="14">
-      <c r="A35" s="87">
+      <c r="A35" s="84">
         <v>45933.931944444397</v>
       </c>
       <c r="B35" s="45" t="s">
         <v>181</v>
       </c>
-      <c r="C35" s="88">
+      <c r="C35" s="85">
         <v>800</v>
       </c>
       <c r="D35" s="45" t="s">
@@ -13013,13 +13025,13 @@
       </c>
     </row>
     <row r="36" spans="1:9" ht="14">
-      <c r="A36" s="85">
+      <c r="A36" s="82">
         <v>45934.931944386597</v>
       </c>
       <c r="B36" s="44" t="s">
         <v>182</v>
       </c>
-      <c r="C36" s="86">
+      <c r="C36" s="83">
         <v>1600</v>
       </c>
       <c r="D36" s="44" t="s">
@@ -13036,13 +13048,13 @@
       </c>
     </row>
     <row r="37" spans="1:9" ht="14">
-      <c r="A37" s="87">
+      <c r="A37" s="84">
         <v>45935.931944386597</v>
       </c>
       <c r="B37" s="45" t="s">
         <v>183</v>
       </c>
-      <c r="C37" s="88">
+      <c r="C37" s="85">
         <v>5900</v>
       </c>
       <c r="D37" s="45" t="s">
@@ -13059,13 +13071,13 @@
       </c>
     </row>
     <row r="38" spans="1:9" ht="14">
-      <c r="A38" s="85">
+      <c r="A38" s="82">
         <v>45939.931944444397</v>
       </c>
       <c r="B38" s="44" t="s">
         <v>175</v>
       </c>
-      <c r="C38" s="86">
+      <c r="C38" s="83">
         <v>3000</v>
       </c>
       <c r="D38" s="44" t="s">
@@ -13082,13 +13094,13 @@
       </c>
     </row>
     <row r="39" spans="1:9" ht="14">
-      <c r="A39" s="87">
+      <c r="A39" s="84">
         <v>45939.931944444397</v>
       </c>
       <c r="B39" s="45" t="s">
         <v>184</v>
       </c>
-      <c r="C39" s="88">
+      <c r="C39" s="85">
         <v>800</v>
       </c>
       <c r="D39" s="45" t="s">
@@ -13105,13 +13117,13 @@
       </c>
     </row>
     <row r="40" spans="1:9" ht="14">
-      <c r="A40" s="85">
+      <c r="A40" s="82">
         <v>45945</v>
       </c>
       <c r="B40" s="44" t="s">
         <v>185</v>
       </c>
-      <c r="C40" s="86">
+      <c r="C40" s="83">
         <v>1560</v>
       </c>
       <c r="D40" s="44" t="s">
@@ -13128,13 +13140,13 @@
       </c>
     </row>
     <row r="41" spans="1:9" ht="14">
-      <c r="A41" s="87">
+      <c r="A41" s="84">
         <v>45946</v>
       </c>
       <c r="B41" s="45" t="s">
         <v>186</v>
       </c>
-      <c r="C41" s="88">
+      <c r="C41" s="85">
         <v>1400</v>
       </c>
       <c r="D41" s="45" t="s">
@@ -13151,13 +13163,13 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="14">
-      <c r="A42" s="85">
+      <c r="A42" s="82">
         <v>45946</v>
       </c>
       <c r="B42" s="44" t="s">
         <v>151</v>
       </c>
-      <c r="C42" s="86">
+      <c r="C42" s="83">
         <v>3000</v>
       </c>
       <c r="D42" s="44" t="s">
@@ -13174,13 +13186,13 @@
       </c>
     </row>
     <row r="43" spans="1:9" ht="14">
-      <c r="A43" s="87">
+      <c r="A43" s="84">
         <v>45947</v>
       </c>
       <c r="B43" s="45" t="s">
         <v>187</v>
       </c>
-      <c r="C43" s="88">
+      <c r="C43" s="85">
         <v>1799</v>
       </c>
       <c r="D43" s="45" t="s">
@@ -13197,13 +13209,13 @@
       </c>
     </row>
     <row r="44" spans="1:9" ht="14">
-      <c r="A44" s="85">
+      <c r="A44" s="82">
         <v>45948</v>
       </c>
       <c r="B44" s="44" t="s">
         <v>158</v>
       </c>
-      <c r="C44" s="86">
+      <c r="C44" s="83">
         <v>1400</v>
       </c>
       <c r="D44" s="44" t="s">
@@ -13220,13 +13232,13 @@
       </c>
     </row>
     <row r="45" spans="1:9" ht="14">
-      <c r="A45" s="87">
+      <c r="A45" s="84">
         <v>45949</v>
       </c>
       <c r="B45" s="45" t="s">
         <v>188</v>
       </c>
-      <c r="C45" s="88">
+      <c r="C45" s="85">
         <v>1400</v>
       </c>
       <c r="D45" s="45" t="s">
@@ -13243,13 +13255,13 @@
       </c>
     </row>
     <row r="46" spans="1:9" ht="14">
-      <c r="A46" s="85">
+      <c r="A46" s="82">
         <v>45950</v>
       </c>
       <c r="B46" s="44" t="s">
         <v>189</v>
       </c>
-      <c r="C46" s="86">
+      <c r="C46" s="83">
         <v>600</v>
       </c>
       <c r="D46" s="44" t="s">
@@ -13266,13 +13278,13 @@
       </c>
     </row>
     <row r="47" spans="1:9" ht="14">
-      <c r="A47" s="87">
+      <c r="A47" s="84">
         <v>45951</v>
       </c>
       <c r="B47" s="45" t="s">
         <v>190</v>
       </c>
-      <c r="C47" s="88">
+      <c r="C47" s="85">
         <v>1000</v>
       </c>
       <c r="D47" s="45" t="s">
@@ -13289,13 +13301,13 @@
       </c>
     </row>
     <row r="48" spans="1:9" ht="14">
-      <c r="A48" s="85">
+      <c r="A48" s="82">
         <v>45964</v>
       </c>
       <c r="B48" s="44" t="s">
         <v>189</v>
       </c>
-      <c r="C48" s="86">
+      <c r="C48" s="83">
         <v>1500</v>
       </c>
       <c r="D48" s="44" t="s">
@@ -13312,13 +13324,13 @@
       </c>
     </row>
     <row r="49" spans="1:9" ht="14">
-      <c r="A49" s="87">
+      <c r="A49" s="84">
         <v>45963</v>
       </c>
       <c r="B49" s="45" t="s">
         <v>189</v>
       </c>
-      <c r="C49" s="88">
+      <c r="C49" s="85">
         <v>1600</v>
       </c>
       <c r="D49" s="45" t="s">
@@ -13335,13 +13347,13 @@
       </c>
     </row>
     <row r="50" spans="1:9" ht="14">
-      <c r="A50" s="85">
+      <c r="A50" s="82">
         <v>45982</v>
       </c>
       <c r="B50" s="44" t="s">
         <v>191</v>
       </c>
-      <c r="C50" s="86">
+      <c r="C50" s="83">
         <v>1600</v>
       </c>
       <c r="D50" s="44" t="s">
@@ -13358,13 +13370,13 @@
       </c>
     </row>
     <row r="51" spans="1:9" ht="14">
-      <c r="A51" s="87">
+      <c r="A51" s="84">
         <v>45983</v>
       </c>
       <c r="B51" s="45" t="s">
         <v>192</v>
       </c>
-      <c r="C51" s="88">
+      <c r="C51" s="85">
         <v>1400</v>
       </c>
       <c r="D51" s="45" t="s">
@@ -13381,13 +13393,13 @@
       </c>
     </row>
     <row r="52" spans="1:9" ht="14">
-      <c r="A52" s="85">
+      <c r="A52" s="82">
         <v>45984</v>
       </c>
       <c r="B52" s="44" t="s">
         <v>193</v>
       </c>
-      <c r="C52" s="86">
+      <c r="C52" s="83">
         <v>1600</v>
       </c>
       <c r="D52" s="44" t="s">
@@ -13404,13 +13416,13 @@
       </c>
     </row>
     <row r="53" spans="1:9" ht="14">
-      <c r="A53" s="87">
+      <c r="A53" s="84">
         <v>45985</v>
       </c>
       <c r="B53" s="45" t="s">
         <v>191</v>
       </c>
-      <c r="C53" s="88">
+      <c r="C53" s="85">
         <v>1600</v>
       </c>
       <c r="D53" s="45" t="s">
@@ -13427,13 +13439,13 @@
       </c>
     </row>
     <row r="54" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A54" s="85">
+      <c r="A54" s="82">
         <v>45986</v>
       </c>
       <c r="B54" s="44" t="s">
         <v>194</v>
       </c>
-      <c r="C54" s="86">
+      <c r="C54" s="83">
         <v>4900</v>
       </c>
       <c r="D54" s="44" t="s">
@@ -13452,13 +13464,13 @@
       </c>
     </row>
     <row r="55" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A55" s="87">
+      <c r="A55" s="84">
         <v>45992</v>
       </c>
       <c r="B55" s="45" t="s">
         <v>196</v>
       </c>
-      <c r="C55" s="88">
+      <c r="C55" s="85">
         <v>4500</v>
       </c>
       <c r="D55" s="45" t="s">
@@ -13477,13 +13489,13 @@
       </c>
     </row>
     <row r="56" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A56" s="85">
+      <c r="A56" s="82">
         <v>45992</v>
       </c>
       <c r="B56" s="44" t="s">
         <v>197</v>
       </c>
-      <c r="C56" s="86">
+      <c r="C56" s="83">
         <v>1600</v>
       </c>
       <c r="D56" s="44" t="s">
@@ -13502,13 +13514,13 @@
       </c>
     </row>
     <row r="57" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A57" s="87">
+      <c r="A57" s="84">
         <v>45996</v>
       </c>
       <c r="B57" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="C57" s="88">
+      <c r="C57" s="85">
         <v>1500</v>
       </c>
       <c r="D57" s="45" t="s">
@@ -13527,13 +13539,13 @@
       </c>
     </row>
     <row r="58" spans="1:9" ht="42" customHeight="1">
-      <c r="A58" s="85">
+      <c r="A58" s="82">
         <v>45996</v>
       </c>
       <c r="B58" s="44" t="s">
         <v>201</v>
       </c>
-      <c r="C58" s="86">
+      <c r="C58" s="83">
         <v>7500</v>
       </c>
       <c r="D58" s="44" t="s">
@@ -13552,13 +13564,13 @@
       </c>
     </row>
     <row r="59" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A59" s="87">
+      <c r="A59" s="84">
         <v>45996</v>
       </c>
       <c r="B59" s="45" t="s">
         <v>173</v>
       </c>
-      <c r="C59" s="88">
+      <c r="C59" s="85">
         <v>1400</v>
       </c>
       <c r="D59" s="45" t="s">
@@ -13577,13 +13589,13 @@
       </c>
     </row>
     <row r="60" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A60" s="85">
+      <c r="A60" s="82">
         <v>46007</v>
       </c>
       <c r="B60" s="44" t="s">
         <v>204</v>
       </c>
-      <c r="C60" s="86">
+      <c r="C60" s="83">
         <v>699</v>
       </c>
       <c r="D60" s="44" t="s">
@@ -13602,13 +13614,13 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A61" s="87">
+      <c r="A61" s="84">
         <v>46008</v>
       </c>
       <c r="B61" s="45" t="s">
         <v>151</v>
       </c>
-      <c r="C61" s="88">
+      <c r="C61" s="85">
         <v>1400</v>
       </c>
       <c r="D61" s="45" t="s">
@@ -13629,13 +13641,13 @@
       </c>
     </row>
     <row r="62" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A62" s="85">
+      <c r="A62" s="82">
         <v>46008</v>
       </c>
       <c r="B62" s="44" t="s">
         <v>209</v>
       </c>
-      <c r="C62" s="86">
+      <c r="C62" s="83">
         <v>1380</v>
       </c>
       <c r="D62" s="44" t="s">
@@ -13654,13 +13666,13 @@
       </c>
     </row>
     <row r="63" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A63" s="87">
+      <c r="A63" s="84">
         <v>46008</v>
       </c>
       <c r="B63" s="45" t="s">
         <v>191</v>
       </c>
-      <c r="C63" s="88">
+      <c r="C63" s="85">
         <v>1380</v>
       </c>
       <c r="D63" s="45" t="s">
@@ -13679,13 +13691,13 @@
       </c>
     </row>
     <row r="64" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A64" s="87">
+      <c r="A64" s="84">
         <v>46008</v>
       </c>
       <c r="B64" s="45" t="s">
         <v>173</v>
       </c>
-      <c r="C64" s="88">
+      <c r="C64" s="85">
         <v>700</v>
       </c>
       <c r="D64" s="45" t="s">
@@ -13704,13 +13716,13 @@
       </c>
     </row>
     <row r="65" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A65" s="85">
+      <c r="A65" s="82">
         <v>46009</v>
       </c>
       <c r="B65" s="44" t="s">
         <v>177</v>
       </c>
-      <c r="C65" s="86">
+      <c r="C65" s="83">
         <v>2100</v>
       </c>
       <c r="D65" s="44" t="s">
@@ -13729,13 +13741,13 @@
       </c>
     </row>
     <row r="66" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A66" s="87">
+      <c r="A66" s="84">
         <v>46010</v>
       </c>
       <c r="B66" s="45" t="s">
         <v>214</v>
       </c>
-      <c r="C66" s="88">
+      <c r="C66" s="85">
         <v>1380</v>
       </c>
       <c r="D66" s="45" t="s">
@@ -13754,13 +13766,13 @@
       </c>
     </row>
     <row r="67" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A67" s="85">
+      <c r="A67" s="82">
         <v>46010</v>
       </c>
       <c r="B67" s="44" t="s">
         <v>215</v>
       </c>
-      <c r="C67" s="86">
+      <c r="C67" s="83">
         <v>1000</v>
       </c>
       <c r="D67" s="44" t="s">
@@ -13781,13 +13793,13 @@
       </c>
     </row>
     <row r="68" spans="1:9" ht="31.5" customHeight="1">
-      <c r="A68" s="87">
+      <c r="A68" s="84">
         <v>46011</v>
       </c>
       <c r="B68" s="45" t="s">
         <v>218</v>
       </c>
-      <c r="C68" s="88">
+      <c r="C68" s="85">
         <v>3900</v>
       </c>
       <c r="D68" s="45" t="s">
@@ -13806,13 +13818,13 @@
       </c>
     </row>
     <row r="69" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A69" s="85">
+      <c r="A69" s="82">
         <v>46011</v>
       </c>
       <c r="B69" s="44" t="s">
         <v>220</v>
       </c>
-      <c r="C69" s="86">
+      <c r="C69" s="83">
         <v>1400</v>
       </c>
       <c r="D69" s="44" t="s">
@@ -13831,13 +13843,13 @@
       </c>
     </row>
     <row r="70" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A70" s="85">
+      <c r="A70" s="82">
         <v>46011</v>
       </c>
       <c r="B70" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="C70" s="86">
+      <c r="C70" s="83">
         <v>1400</v>
       </c>
       <c r="D70" s="44" t="s">
@@ -13856,13 +13868,13 @@
       </c>
     </row>
     <row r="71" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A71" s="87">
+      <c r="A71" s="84">
         <v>46011</v>
       </c>
       <c r="B71" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="C71" s="88">
+      <c r="C71" s="85">
         <v>1400</v>
       </c>
       <c r="D71" s="45" t="s">
@@ -13881,13 +13893,13 @@
       </c>
     </row>
     <row r="72" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A72" s="85">
+      <c r="A72" s="82">
         <v>46011</v>
       </c>
       <c r="B72" s="44" t="s">
         <v>224</v>
       </c>
-      <c r="C72" s="86">
+      <c r="C72" s="83">
         <v>3700</v>
       </c>
       <c r="D72" s="44" t="s">
@@ -13906,13 +13918,13 @@
       </c>
     </row>
     <row r="73" spans="1:9" ht="31.5" customHeight="1">
-      <c r="A73" s="87">
+      <c r="A73" s="84">
         <v>46011</v>
       </c>
       <c r="B73" s="45" t="s">
         <v>226</v>
       </c>
-      <c r="C73" s="88">
+      <c r="C73" s="85">
         <v>4529</v>
       </c>
       <c r="D73" s="45" t="s">
@@ -13931,13 +13943,13 @@
       </c>
     </row>
     <row r="74" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A74" s="85">
+      <c r="A74" s="82">
         <v>46013</v>
       </c>
       <c r="B74" s="44" t="s">
         <v>228</v>
       </c>
-      <c r="C74" s="86">
+      <c r="C74" s="83">
         <v>580</v>
       </c>
       <c r="D74" s="44" t="s">
@@ -13958,13 +13970,13 @@
       </c>
     </row>
     <row r="75" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A75" s="87">
+      <c r="A75" s="84">
         <v>46013</v>
       </c>
       <c r="B75" s="45" t="s">
         <v>231</v>
       </c>
-      <c r="C75" s="88">
+      <c r="C75" s="85">
         <v>1380</v>
       </c>
       <c r="D75" s="45" t="s">
@@ -13983,13 +13995,13 @@
       </c>
     </row>
     <row r="76" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A76" s="87">
+      <c r="A76" s="84">
         <v>46017</v>
       </c>
       <c r="B76" s="45" t="s">
         <v>232</v>
       </c>
-      <c r="C76" s="88">
+      <c r="C76" s="85">
         <v>1380</v>
       </c>
       <c r="D76" s="45" t="s">
@@ -14008,13 +14020,13 @@
       </c>
     </row>
     <row r="77" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A77" s="85">
+      <c r="A77" s="82">
         <v>46017</v>
       </c>
       <c r="B77" s="44" t="s">
         <v>234</v>
       </c>
-      <c r="C77" s="86">
+      <c r="C77" s="83">
         <v>1380</v>
       </c>
       <c r="D77" s="44" t="s">
@@ -14033,13 +14045,13 @@
       </c>
     </row>
     <row r="78" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A78" s="87">
+      <c r="A78" s="84">
         <v>46017</v>
       </c>
       <c r="B78" s="45" t="s">
         <v>189</v>
       </c>
-      <c r="C78" s="88">
+      <c r="C78" s="85">
         <v>690</v>
       </c>
       <c r="D78" s="45" t="s">
@@ -14058,13 +14070,13 @@
       </c>
     </row>
     <row r="79" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A79" s="85">
+      <c r="A79" s="82">
         <v>46017</v>
       </c>
       <c r="B79" s="44" t="s">
         <v>189</v>
       </c>
-      <c r="C79" s="86">
+      <c r="C79" s="83">
         <v>690</v>
       </c>
       <c r="D79" s="44" t="s">
@@ -14083,13 +14095,13 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A80" s="87">
+      <c r="A80" s="84">
         <v>46020</v>
       </c>
       <c r="B80" s="45" t="s">
         <v>161</v>
       </c>
-      <c r="C80" s="88">
+      <c r="C80" s="85">
         <v>3200</v>
       </c>
       <c r="D80" s="45" t="s">
@@ -14108,13 +14120,13 @@
       </c>
     </row>
     <row r="81" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A81" s="85">
+      <c r="A81" s="82">
         <v>46024</v>
       </c>
       <c r="B81" s="44" t="s">
         <v>238</v>
       </c>
-      <c r="C81" s="86">
+      <c r="C81" s="83">
         <v>2750</v>
       </c>
       <c r="D81" s="44" t="s">
@@ -14133,13 +14145,13 @@
       </c>
     </row>
     <row r="82" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A82" s="87">
+      <c r="A82" s="84">
         <v>46024</v>
       </c>
       <c r="B82" s="45" t="s">
         <v>240</v>
       </c>
-      <c r="C82" s="88">
+      <c r="C82" s="85">
         <v>1400</v>
       </c>
       <c r="D82" s="45" t="s">
@@ -14158,13 +14170,13 @@
       </c>
     </row>
     <row r="83" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A83" s="85">
+      <c r="A83" s="82">
         <v>46024</v>
       </c>
       <c r="B83" s="44" t="s">
         <v>242</v>
       </c>
-      <c r="C83" s="86">
+      <c r="C83" s="83">
         <v>1600</v>
       </c>
       <c r="D83" s="44" t="s">
@@ -14183,13 +14195,13 @@
       </c>
     </row>
     <row r="84" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A84" s="87">
+      <c r="A84" s="84">
         <v>46024</v>
       </c>
       <c r="B84" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="C84" s="88">
+      <c r="C84" s="85">
         <v>1200</v>
       </c>
       <c r="D84" s="45" t="s">
@@ -14208,13 +14220,13 @@
       </c>
     </row>
     <row r="85" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A85" s="85">
+      <c r="A85" s="82">
         <v>46027</v>
       </c>
       <c r="B85" s="44" t="s">
         <v>245</v>
       </c>
-      <c r="C85" s="86">
+      <c r="C85" s="83">
         <v>1250</v>
       </c>
       <c r="D85" s="44" t="s">
@@ -14233,13 +14245,13 @@
       </c>
     </row>
     <row r="86" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A86" s="85">
+      <c r="A86" s="82">
         <v>46028</v>
       </c>
       <c r="B86" s="44" t="s">
         <v>247</v>
       </c>
-      <c r="C86" s="86">
+      <c r="C86" s="83">
         <v>1380</v>
       </c>
       <c r="D86" s="44" t="s">
@@ -14258,13 +14270,13 @@
       </c>
     </row>
     <row r="87" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A87" s="87">
+      <c r="A87" s="84">
         <v>46029</v>
       </c>
       <c r="B87" s="45" t="s">
         <v>249</v>
       </c>
-      <c r="C87" s="88">
+      <c r="C87" s="85">
         <v>1380</v>
       </c>
       <c r="D87" s="45" t="s">
@@ -14283,13 +14295,13 @@
       </c>
     </row>
     <row r="88" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A88" s="85">
+      <c r="A88" s="82">
         <v>46032</v>
       </c>
       <c r="B88" s="44" t="s">
         <v>250</v>
       </c>
-      <c r="C88" s="86">
+      <c r="C88" s="83">
         <v>1100</v>
       </c>
       <c r="D88" s="44" t="s">
@@ -14308,13 +14320,13 @@
       </c>
     </row>
     <row r="89" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A89" s="87">
+      <c r="A89" s="84">
         <v>46033</v>
       </c>
       <c r="B89" s="45" t="s">
         <v>252</v>
       </c>
-      <c r="C89" s="88">
+      <c r="C89" s="85">
         <v>1380</v>
       </c>
       <c r="D89" s="45" t="s">
@@ -14333,13 +14345,13 @@
       </c>
     </row>
     <row r="90" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A90" s="85">
+      <c r="A90" s="82">
         <v>46033</v>
       </c>
       <c r="B90" s="44" t="s">
         <v>253</v>
       </c>
-      <c r="C90" s="86">
+      <c r="C90" s="83">
         <v>1100</v>
       </c>
       <c r="D90" s="44" t="s">
@@ -14358,13 +14370,13 @@
       </c>
     </row>
     <row r="91" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A91" s="87">
+      <c r="A91" s="84">
         <v>46034</v>
       </c>
       <c r="B91" s="45" t="s">
         <v>254</v>
       </c>
-      <c r="C91" s="88">
+      <c r="C91" s="85">
         <v>1100</v>
       </c>
       <c r="D91" s="45" t="s">
@@ -14383,13 +14395,13 @@
       </c>
     </row>
     <row r="92" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A92" s="85">
+      <c r="A92" s="82">
         <v>46034</v>
       </c>
       <c r="B92" s="44" t="s">
         <v>255</v>
       </c>
-      <c r="C92" s="86">
+      <c r="C92" s="83">
         <v>3000</v>
       </c>
       <c r="D92" s="44" t="s">
@@ -14408,13 +14420,13 @@
       </c>
     </row>
     <row r="93" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A93" s="87">
+      <c r="A93" s="84">
         <v>46035</v>
       </c>
       <c r="B93" s="45" t="s">
         <v>257</v>
       </c>
-      <c r="C93" s="88">
+      <c r="C93" s="85">
         <v>1450</v>
       </c>
       <c r="D93" s="45" t="s">
@@ -14433,13 +14445,13 @@
       </c>
     </row>
     <row r="94" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A94" s="85">
+      <c r="A94" s="82">
         <v>46036</v>
       </c>
       <c r="B94" s="44" t="s">
         <v>259</v>
       </c>
-      <c r="C94" s="86">
+      <c r="C94" s="83">
         <v>1599</v>
       </c>
       <c r="D94" s="44" t="s">
@@ -14458,13 +14470,13 @@
       </c>
     </row>
     <row r="95" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A95" s="87">
+      <c r="A95" s="84">
         <v>46038</v>
       </c>
       <c r="B95" s="45" t="s">
         <v>261</v>
       </c>
-      <c r="C95" s="88">
+      <c r="C95" s="85">
         <v>1100</v>
       </c>
       <c r="D95" s="45" t="s">
@@ -14483,13 +14495,13 @@
       </c>
     </row>
     <row r="96" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A96" s="85">
+      <c r="A96" s="82">
         <v>46038</v>
       </c>
       <c r="B96" s="44" t="s">
         <v>262</v>
       </c>
-      <c r="C96" s="86">
+      <c r="C96" s="83">
         <v>1650</v>
       </c>
       <c r="D96" s="44" t="s">
@@ -14508,13 +14520,13 @@
       </c>
     </row>
     <row r="97" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A97" s="87">
+      <c r="A97" s="84">
         <v>46039</v>
       </c>
       <c r="B97" s="45" t="s">
         <v>264</v>
       </c>
-      <c r="C97" s="88">
+      <c r="C97" s="85">
         <v>2300</v>
       </c>
       <c r="D97" s="45" t="s">
@@ -14533,13 +14545,13 @@
       </c>
     </row>
     <row r="98" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A98" s="85">
+      <c r="A98" s="82">
         <v>46040</v>
       </c>
       <c r="B98" s="44" t="s">
         <v>266</v>
       </c>
-      <c r="C98" s="86">
+      <c r="C98" s="83">
         <v>1399</v>
       </c>
       <c r="D98" s="44" t="s">
@@ -14558,13 +14570,13 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A99" s="87">
+      <c r="A99" s="84">
         <v>46041</v>
       </c>
       <c r="B99" s="45" t="s">
         <v>268</v>
       </c>
-      <c r="C99" s="88">
+      <c r="C99" s="85">
         <v>1100</v>
       </c>
       <c r="D99" s="45" t="s">
@@ -14583,13 +14595,13 @@
       </c>
     </row>
     <row r="100" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A100" s="85">
+      <c r="A100" s="82">
         <v>46042</v>
       </c>
       <c r="B100" s="44" t="s">
         <v>269</v>
       </c>
-      <c r="C100" s="86">
+      <c r="C100" s="83">
         <v>1250</v>
       </c>
       <c r="D100" s="44" t="s">
@@ -14608,13 +14620,13 @@
       </c>
     </row>
     <row r="101" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A101" s="87">
+      <c r="A101" s="84">
         <v>46043</v>
       </c>
       <c r="B101" s="45" t="s">
         <v>271</v>
       </c>
-      <c r="C101" s="88">
+      <c r="C101" s="85">
         <v>1380</v>
       </c>
       <c r="D101" s="45" t="s">
@@ -14633,13 +14645,13 @@
       </c>
     </row>
     <row r="102" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A102" s="85">
+      <c r="A102" s="82">
         <v>46046</v>
       </c>
       <c r="B102" s="44" t="s">
         <v>273</v>
       </c>
-      <c r="C102" s="86">
+      <c r="C102" s="83">
         <v>950</v>
       </c>
       <c r="D102" s="44" t="s">
@@ -14658,13 +14670,13 @@
       </c>
     </row>
     <row r="103" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A103" s="87">
+      <c r="A103" s="84">
         <v>46048</v>
       </c>
       <c r="B103" s="45" t="s">
         <v>275</v>
       </c>
-      <c r="C103" s="88">
+      <c r="C103" s="85">
         <v>1380</v>
       </c>
       <c r="D103" s="45" t="s">
@@ -14683,13 +14695,13 @@
       </c>
     </row>
     <row r="104" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A104" s="85">
+      <c r="A104" s="82">
         <v>46048</v>
       </c>
       <c r="B104" s="44" t="s">
         <v>276</v>
       </c>
-      <c r="C104" s="86">
+      <c r="C104" s="83">
         <v>2700</v>
       </c>
       <c r="D104" s="44" t="s">
@@ -14708,13 +14720,13 @@
       </c>
     </row>
     <row r="105" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A105" s="87">
+      <c r="A105" s="84">
         <v>46049</v>
       </c>
       <c r="B105" s="45" t="s">
         <v>278</v>
       </c>
-      <c r="C105" s="88">
+      <c r="C105" s="85">
         <v>1380</v>
       </c>
       <c r="D105" s="45" t="s">
@@ -14733,13 +14745,13 @@
       </c>
     </row>
     <row r="106" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A106" s="85">
+      <c r="A106" s="82">
         <v>46049</v>
       </c>
       <c r="B106" s="44" t="s">
         <v>279</v>
       </c>
-      <c r="C106" s="86">
+      <c r="C106" s="83">
         <v>1380</v>
       </c>
       <c r="D106" s="44" t="s">
@@ -14758,13 +14770,13 @@
       </c>
     </row>
     <row r="107" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A107" s="87">
+      <c r="A107" s="84">
         <v>46049</v>
       </c>
       <c r="B107" s="45" t="s">
         <v>281</v>
       </c>
-      <c r="C107" s="88">
+      <c r="C107" s="85">
         <v>1200</v>
       </c>
       <c r="D107" s="45" t="s">
@@ -14783,13 +14795,13 @@
       </c>
     </row>
     <row r="108" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A108" s="85">
+      <c r="A108" s="82">
         <v>46050</v>
       </c>
       <c r="B108" s="44" t="s">
         <v>283</v>
       </c>
-      <c r="C108" s="86">
+      <c r="C108" s="83">
         <v>1250</v>
       </c>
       <c r="D108" s="44" t="s">
@@ -14808,13 +14820,13 @@
       </c>
     </row>
     <row r="109" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A109" s="87">
+      <c r="A109" s="84">
         <v>46051</v>
       </c>
       <c r="B109" s="45" t="s">
         <v>285</v>
       </c>
-      <c r="C109" s="88">
+      <c r="C109" s="85">
         <v>1380</v>
       </c>
       <c r="D109" s="45" t="s">
@@ -14833,13 +14845,13 @@
       </c>
     </row>
     <row r="110" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A110" s="85">
+      <c r="A110" s="82">
         <v>46051</v>
       </c>
       <c r="B110" s="44" t="s">
         <v>286</v>
       </c>
-      <c r="C110" s="86">
+      <c r="C110" s="83">
         <v>1380</v>
       </c>
       <c r="D110" s="44" t="s">
@@ -14858,13 +14870,13 @@
       </c>
     </row>
     <row r="111" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A111" s="87">
+      <c r="A111" s="84">
         <v>46051</v>
       </c>
       <c r="B111" s="45" t="s">
         <v>264</v>
       </c>
-      <c r="C111" s="88">
+      <c r="C111" s="85">
         <v>580</v>
       </c>
       <c r="D111" s="45" t="s">
@@ -14883,13 +14895,13 @@
       </c>
     </row>
     <row r="112" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A112" s="85">
+      <c r="A112" s="82">
         <v>46054</v>
       </c>
       <c r="B112" s="44" t="s">
         <v>289</v>
       </c>
-      <c r="C112" s="86">
+      <c r="C112" s="83">
         <v>1800</v>
       </c>
       <c r="D112" s="44" t="s">
@@ -14908,13 +14920,13 @@
       </c>
     </row>
     <row r="113" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A113" s="87">
+      <c r="A113" s="84">
         <v>46054</v>
       </c>
       <c r="B113" s="45" t="s">
         <v>291</v>
       </c>
-      <c r="C113" s="88">
+      <c r="C113" s="85">
         <v>1550</v>
       </c>
       <c r="D113" s="45" t="s">
@@ -14933,13 +14945,13 @@
       </c>
     </row>
     <row r="114" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A114" s="85">
+      <c r="A114" s="82">
         <v>46055</v>
       </c>
       <c r="B114" s="44" t="s">
         <v>157</v>
       </c>
-      <c r="C114" s="86">
+      <c r="C114" s="83">
         <v>1380</v>
       </c>
       <c r="D114" s="44" t="s">
@@ -14958,13 +14970,13 @@
       </c>
     </row>
     <row r="115" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A115" s="87">
+      <c r="A115" s="84">
         <v>46055</v>
       </c>
       <c r="B115" s="45" t="s">
         <v>170</v>
       </c>
-      <c r="C115" s="88">
+      <c r="C115" s="85">
         <v>1380</v>
       </c>
       <c r="D115" s="45" t="s">
@@ -14983,13 +14995,13 @@
       </c>
     </row>
     <row r="116" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A116" s="85">
+      <c r="A116" s="82">
         <v>46060</v>
       </c>
       <c r="B116" s="44" t="s">
         <v>293</v>
       </c>
-      <c r="C116" s="86">
+      <c r="C116" s="83">
         <v>1050</v>
       </c>
       <c r="D116" s="44" t="s">
@@ -15008,13 +15020,13 @@
       </c>
     </row>
     <row r="117" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A117" s="87">
+      <c r="A117" s="84">
         <v>46062</v>
       </c>
       <c r="B117" s="45" t="s">
         <v>295</v>
       </c>
-      <c r="C117" s="88">
+      <c r="C117" s="85">
         <v>1000</v>
       </c>
       <c r="D117" s="45" t="s">
@@ -15033,13 +15045,13 @@
       </c>
     </row>
     <row r="118" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A118" s="85">
+      <c r="A118" s="82">
         <v>46065</v>
       </c>
       <c r="B118" s="44" t="s">
         <v>297</v>
       </c>
-      <c r="C118" s="86">
+      <c r="C118" s="83">
         <v>799</v>
       </c>
       <c r="D118" s="44" t="s">
@@ -15058,13 +15070,13 @@
       </c>
     </row>
     <row r="119" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A119" s="87">
+      <c r="A119" s="84">
         <v>46055</v>
       </c>
       <c r="B119" s="45" t="s">
         <v>299</v>
       </c>
-      <c r="C119" s="88">
+      <c r="C119" s="85">
         <v>500</v>
       </c>
       <c r="D119" s="45" t="s">
@@ -15083,13 +15095,13 @@
       </c>
     </row>
     <row r="120" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A120" s="85">
+      <c r="A120" s="82">
         <v>46070</v>
       </c>
       <c r="B120" s="44" t="s">
         <v>300</v>
       </c>
-      <c r="C120" s="86">
+      <c r="C120" s="83">
         <v>1450</v>
       </c>
       <c r="D120" s="44" t="s">
@@ -15108,13 +15120,13 @@
       </c>
     </row>
     <row r="121" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A121" s="87">
+      <c r="A121" s="84">
         <v>46073</v>
       </c>
       <c r="B121" s="45" t="s">
         <v>183</v>
       </c>
-      <c r="C121" s="88">
+      <c r="C121" s="85">
         <v>1200</v>
       </c>
       <c r="D121" s="45" t="s">
@@ -15133,13 +15145,13 @@
       </c>
     </row>
     <row r="122" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A122" s="85">
+      <c r="A122" s="82">
         <v>46074</v>
       </c>
       <c r="B122" s="44" t="s">
         <v>304</v>
       </c>
-      <c r="C122" s="86">
+      <c r="C122" s="83">
         <v>1200</v>
       </c>
       <c r="D122" s="44" t="s">
@@ -15158,13 +15170,13 @@
       </c>
     </row>
     <row r="123" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A123" s="87">
+      <c r="A123" s="84">
         <v>46075</v>
       </c>
       <c r="B123" s="45" t="s">
         <v>306</v>
       </c>
-      <c r="C123" s="88">
+      <c r="C123" s="85">
         <v>1380</v>
       </c>
       <c r="D123" s="45" t="s">
@@ -15183,13 +15195,13 @@
       </c>
     </row>
     <row r="124" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A124" s="85">
+      <c r="A124" s="82">
         <v>46075</v>
       </c>
       <c r="B124" s="44" t="s">
         <v>307</v>
       </c>
-      <c r="C124" s="86">
+      <c r="C124" s="83">
         <v>2550</v>
       </c>
       <c r="D124" s="44" t="s">
@@ -15208,13 +15220,13 @@
       </c>
     </row>
     <row r="125" spans="1:9" ht="31.5" customHeight="1">
-      <c r="A125" s="87">
+      <c r="A125" s="84">
         <v>46079</v>
       </c>
       <c r="B125" s="45" t="s">
         <v>153</v>
       </c>
-      <c r="C125" s="88">
+      <c r="C125" s="85">
         <v>1350</v>
       </c>
       <c r="D125" s="45" t="s">
@@ -15233,13 +15245,13 @@
       </c>
     </row>
     <row r="126" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A126" s="85">
+      <c r="A126" s="82">
         <v>46079</v>
       </c>
       <c r="B126" s="44" t="s">
         <v>310</v>
       </c>
-      <c r="C126" s="86">
+      <c r="C126" s="83">
         <v>500</v>
       </c>
       <c r="D126" s="44" t="s">
@@ -15258,13 +15270,13 @@
       </c>
     </row>
     <row r="127" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A127" s="87">
+      <c r="A127" s="84">
         <v>46090</v>
       </c>
       <c r="B127" s="45" t="s">
         <v>312</v>
       </c>
-      <c r="C127" s="88">
+      <c r="C127" s="85">
         <v>850</v>
       </c>
       <c r="D127" s="45" t="s">
@@ -15283,13 +15295,13 @@
       </c>
     </row>
     <row r="128" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A128" s="85">
+      <c r="A128" s="82">
         <v>46090</v>
       </c>
       <c r="B128" s="44" t="s">
         <v>314</v>
       </c>
-      <c r="C128" s="86">
+      <c r="C128" s="83">
         <v>1100</v>
       </c>
       <c r="D128" s="44" t="s">
@@ -15308,13 +15320,13 @@
       </c>
     </row>
     <row r="129" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A129" s="85">
+      <c r="A129" s="82">
         <v>46090</v>
       </c>
       <c r="B129" s="44" t="s">
         <v>316</v>
       </c>
-      <c r="C129" s="86">
+      <c r="C129" s="83">
         <v>800</v>
       </c>
       <c r="D129" s="44" t="s">
@@ -15333,13 +15345,13 @@
       </c>
     </row>
     <row r="130" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A130" s="87">
+      <c r="A130" s="84">
         <v>46091</v>
       </c>
       <c r="B130" s="45" t="s">
         <v>318</v>
       </c>
-      <c r="C130" s="88">
+      <c r="C130" s="85">
         <v>1099</v>
       </c>
       <c r="D130" s="45" t="s">
@@ -15358,13 +15370,13 @@
       </c>
     </row>
     <row r="131" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A131" s="85">
+      <c r="A131" s="82">
         <v>46092</v>
       </c>
       <c r="B131" s="44" t="s">
         <v>307</v>
       </c>
-      <c r="C131" s="86">
+      <c r="C131" s="83">
         <v>1200</v>
       </c>
       <c r="D131" s="44" t="s">
@@ -15383,13 +15395,13 @@
       </c>
     </row>
     <row r="132" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A132" s="87">
+      <c r="A132" s="84">
         <v>46092</v>
       </c>
       <c r="B132" s="45" t="s">
         <v>321</v>
       </c>
-      <c r="C132" s="88">
+      <c r="C132" s="85">
         <v>1099</v>
       </c>
       <c r="D132" s="45" t="s">
@@ -15408,13 +15420,13 @@
       </c>
     </row>
     <row r="133" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A133" s="85">
+      <c r="A133" s="82">
         <v>46093</v>
       </c>
       <c r="B133" s="44" t="s">
         <v>215</v>
       </c>
-      <c r="C133" s="86">
+      <c r="C133" s="83">
         <v>550</v>
       </c>
       <c r="D133" s="44" t="s">
@@ -15433,13 +15445,13 @@
       </c>
     </row>
     <row r="134" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A134" s="87">
+      <c r="A134" s="84">
         <v>46093</v>
       </c>
       <c r="B134" s="45" t="s">
         <v>201</v>
       </c>
-      <c r="C134" s="88">
+      <c r="C134" s="85">
         <v>650</v>
       </c>
       <c r="D134" s="45" t="s">
@@ -15458,13 +15470,13 @@
       </c>
     </row>
     <row r="135" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A135" s="85">
+      <c r="A135" s="82">
         <v>46097</v>
       </c>
       <c r="B135" s="44" t="s">
         <v>325</v>
       </c>
-      <c r="C135" s="86">
+      <c r="C135" s="83">
         <v>1550</v>
       </c>
       <c r="D135" s="44" t="s">
@@ -15483,13 +15495,13 @@
       </c>
     </row>
     <row r="136" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A136" s="87">
+      <c r="A136" s="84">
         <v>46097</v>
       </c>
       <c r="B136" s="45" t="s">
         <v>327</v>
       </c>
-      <c r="C136" s="88">
+      <c r="C136" s="85">
         <v>850</v>
       </c>
       <c r="D136" s="45" t="s">
@@ -15508,13 +15520,13 @@
       </c>
     </row>
     <row r="137" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A137" s="85">
+      <c r="A137" s="82">
         <v>46100</v>
       </c>
       <c r="B137" s="44" t="s">
         <v>329</v>
       </c>
-      <c r="C137" s="86">
+      <c r="C137" s="83">
         <v>1200</v>
       </c>
       <c r="D137" s="44" t="s">
@@ -15533,13 +15545,13 @@
       </c>
     </row>
     <row r="138" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A138" s="87">
+      <c r="A138" s="84">
         <v>46104</v>
       </c>
       <c r="B138" s="45" t="s">
         <v>226</v>
       </c>
-      <c r="C138" s="88">
+      <c r="C138" s="85">
         <v>1800</v>
       </c>
       <c r="D138" s="45" t="s">
@@ -15558,13 +15570,13 @@
       </c>
     </row>
     <row r="139" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A139" s="85">
+      <c r="A139" s="82">
         <v>46105</v>
       </c>
       <c r="B139" s="44" t="s">
         <v>146</v>
       </c>
-      <c r="C139" s="86">
+      <c r="C139" s="83">
         <v>3500</v>
       </c>
       <c r="D139" s="44" t="s">
@@ -15583,13 +15595,13 @@
       </c>
     </row>
     <row r="140" spans="1:9" ht="31.5" customHeight="1">
-      <c r="A140" s="87">
+      <c r="A140" s="84">
         <v>46113</v>
       </c>
       <c r="B140" s="45" t="s">
         <v>332</v>
       </c>
-      <c r="C140" s="88">
+      <c r="C140" s="85">
         <v>3000</v>
       </c>
       <c r="D140" s="45" t="s">
@@ -15608,13 +15620,13 @@
       </c>
     </row>
     <row r="141" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A141" s="85">
+      <c r="A141" s="82">
         <v>46118</v>
       </c>
       <c r="B141" s="44" t="s">
         <v>146</v>
       </c>
-      <c r="C141" s="86">
+      <c r="C141" s="83">
         <v>1450</v>
       </c>
       <c r="D141" s="44" t="s">
@@ -15633,13 +15645,13 @@
       </c>
     </row>
     <row r="142" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A142" s="87">
+      <c r="A142" s="84">
         <v>46119</v>
       </c>
       <c r="B142" s="45" t="s">
         <v>335</v>
       </c>
-      <c r="C142" s="88">
+      <c r="C142" s="85">
         <v>1200</v>
       </c>
       <c r="D142" s="45" t="s">
@@ -15658,13 +15670,13 @@
       </c>
     </row>
     <row r="143" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A143" s="85">
+      <c r="A143" s="82">
         <v>46120</v>
       </c>
       <c r="B143" s="44" t="s">
         <v>337</v>
       </c>
-      <c r="C143" s="86">
+      <c r="C143" s="83">
         <v>1200</v>
       </c>
       <c r="D143" s="44" t="s">
@@ -15683,13 +15695,13 @@
       </c>
     </row>
     <row r="144" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A144" s="87">
+      <c r="A144" s="84">
         <v>46120</v>
       </c>
       <c r="B144" s="45" t="s">
         <v>339</v>
       </c>
-      <c r="C144" s="88">
+      <c r="C144" s="85">
         <v>1500</v>
       </c>
       <c r="D144" s="45" t="s">
@@ -15708,13 +15720,13 @@
       </c>
     </row>
     <row r="145" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A145" s="85">
+      <c r="A145" s="82">
         <v>46120</v>
       </c>
       <c r="B145" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="C145" s="86">
+      <c r="C145" s="83">
         <v>730</v>
       </c>
       <c r="D145" s="44" t="s">
@@ -15733,13 +15745,13 @@
       </c>
     </row>
     <row r="146" spans="1:9" ht="31.5" customHeight="1">
-      <c r="A146" s="87">
+      <c r="A146" s="84">
         <v>46122</v>
       </c>
       <c r="B146" s="45" t="s">
         <v>307</v>
       </c>
-      <c r="C146" s="88">
+      <c r="C146" s="85">
         <v>950</v>
       </c>
       <c r="D146" s="45" t="s">
@@ -15758,13 +15770,13 @@
       </c>
     </row>
     <row r="147" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A147" s="85">
+      <c r="A147" s="82">
         <v>46122</v>
       </c>
       <c r="B147" s="44" t="s">
         <v>343</v>
       </c>
-      <c r="C147" s="86">
+      <c r="C147" s="83">
         <v>650</v>
       </c>
       <c r="D147" s="44" t="s">
@@ -15783,13 +15795,13 @@
       </c>
     </row>
     <row r="148" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A148" s="87">
+      <c r="A148" s="84">
         <v>46122</v>
       </c>
       <c r="B148" s="45" t="s">
         <v>345</v>
       </c>
-      <c r="C148" s="88">
+      <c r="C148" s="85">
         <v>500</v>
       </c>
       <c r="D148" s="45" t="s">
@@ -15808,13 +15820,13 @@
       </c>
     </row>
     <row r="149" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A149" s="85">
+      <c r="A149" s="82">
         <v>46122</v>
       </c>
       <c r="B149" s="44" t="s">
         <v>153</v>
       </c>
-      <c r="C149" s="86">
+      <c r="C149" s="83">
         <v>1200</v>
       </c>
       <c r="D149" s="44" t="s">
@@ -15833,13 +15845,13 @@
       </c>
     </row>
     <row r="150" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A150" s="87">
+      <c r="A150" s="84">
         <v>46125</v>
       </c>
       <c r="B150" s="45" t="s">
         <v>218</v>
       </c>
-      <c r="C150" s="88">
+      <c r="C150" s="85">
         <v>1100</v>
       </c>
       <c r="D150" s="45" t="s">
@@ -15858,13 +15870,13 @@
       </c>
     </row>
     <row r="151" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A151" s="85">
+      <c r="A151" s="82">
         <v>46125</v>
       </c>
       <c r="B151" s="44" t="s">
         <v>349</v>
       </c>
-      <c r="C151" s="86">
+      <c r="C151" s="83">
         <v>1200</v>
       </c>
       <c r="D151" s="44" t="s">
@@ -15883,13 +15895,13 @@
       </c>
     </row>
     <row r="152" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A152" s="87">
+      <c r="A152" s="84">
         <v>46125</v>
       </c>
       <c r="B152" s="45" t="s">
         <v>173</v>
       </c>
-      <c r="C152" s="88">
+      <c r="C152" s="85">
         <v>980</v>
       </c>
       <c r="D152" s="45" t="s">
@@ -15908,13 +15920,13 @@
       </c>
     </row>
     <row r="153" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A153" s="85">
+      <c r="A153" s="82">
         <v>46125</v>
       </c>
       <c r="B153" s="44" t="s">
         <v>186</v>
       </c>
-      <c r="C153" s="86">
+      <c r="C153" s="83">
         <v>980</v>
       </c>
       <c r="D153" s="44" t="s">
@@ -15933,13 +15945,13 @@
       </c>
     </row>
     <row r="154" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A154" s="87">
+      <c r="A154" s="84">
         <v>46126</v>
       </c>
       <c r="B154" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="C154" s="88">
+      <c r="C154" s="85">
         <v>2000</v>
       </c>
       <c r="D154" s="45" t="s">
@@ -15958,13 +15970,13 @@
       </c>
     </row>
     <row r="155" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A155" s="85">
+      <c r="A155" s="82">
         <v>46127</v>
       </c>
       <c r="B155" s="44" t="s">
         <v>352</v>
       </c>
-      <c r="C155" s="86">
+      <c r="C155" s="83">
         <v>1299</v>
       </c>
       <c r="D155" s="44" t="s">
@@ -15983,13 +15995,13 @@
       </c>
     </row>
     <row r="156" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A156" s="87">
+      <c r="A156" s="84">
         <v>46129</v>
       </c>
       <c r="B156" s="45" t="s">
         <v>354</v>
       </c>
-      <c r="C156" s="88">
+      <c r="C156" s="85">
         <v>980</v>
       </c>
       <c r="D156" s="45" t="s">
@@ -16008,13 +16020,13 @@
       </c>
     </row>
     <row r="157" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A157" s="85">
+      <c r="A157" s="82">
         <v>46129</v>
       </c>
       <c r="B157" s="44" t="s">
         <v>355</v>
       </c>
-      <c r="C157" s="86">
+      <c r="C157" s="83">
         <v>980</v>
       </c>
       <c r="D157" s="44" t="s">
@@ -16033,13 +16045,13 @@
       </c>
     </row>
     <row r="158" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A158" s="87">
+      <c r="A158" s="84">
         <v>46129</v>
       </c>
       <c r="B158" s="45" t="s">
         <v>187</v>
       </c>
-      <c r="C158" s="88">
+      <c r="C158" s="85">
         <v>980</v>
       </c>
       <c r="D158" s="45" t="s">
@@ -16058,13 +16070,13 @@
       </c>
     </row>
     <row r="159" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A159" s="85">
+      <c r="A159" s="82">
         <v>46130</v>
       </c>
       <c r="B159" s="44" t="s">
         <v>357</v>
       </c>
-      <c r="C159" s="86">
+      <c r="C159" s="83">
         <v>1280</v>
       </c>
       <c r="D159" s="44" t="s">
@@ -16083,13 +16095,13 @@
       </c>
     </row>
     <row r="160" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A160" s="87">
+      <c r="A160" s="84">
         <v>46131</v>
       </c>
       <c r="B160" s="45" t="s">
         <v>359</v>
       </c>
-      <c r="C160" s="88">
+      <c r="C160" s="85">
         <v>1000</v>
       </c>
       <c r="D160" s="45" t="s">
@@ -16108,13 +16120,13 @@
       </c>
     </row>
     <row r="161" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A161" s="85">
+      <c r="A161" s="82">
         <v>46132</v>
       </c>
       <c r="B161" s="44" t="s">
         <v>361</v>
       </c>
-      <c r="C161" s="86">
+      <c r="C161" s="83">
         <v>1100</v>
       </c>
       <c r="D161" s="44" t="s">
@@ -16133,13 +16145,13 @@
       </c>
     </row>
     <row r="162" spans="1:9" ht="42" customHeight="1">
-      <c r="A162" s="87">
+      <c r="A162" s="84">
         <v>46132</v>
       </c>
       <c r="B162" s="45" t="s">
         <v>161</v>
       </c>
-      <c r="C162" s="88">
+      <c r="C162" s="85">
         <v>5880</v>
       </c>
       <c r="D162" s="45" t="s">
@@ -16158,13 +16170,13 @@
       </c>
     </row>
     <row r="163" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A163" s="85">
+      <c r="A163" s="82">
         <v>46133</v>
       </c>
       <c r="B163" s="44" t="s">
         <v>364</v>
       </c>
-      <c r="C163" s="86">
+      <c r="C163" s="83">
         <v>1350</v>
       </c>
       <c r="D163" s="44" t="s">
@@ -16183,13 +16195,13 @@
       </c>
     </row>
     <row r="164" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A164" s="87">
+      <c r="A164" s="84">
         <v>46133</v>
       </c>
       <c r="B164" s="45" t="s">
         <v>215</v>
       </c>
-      <c r="C164" s="88">
+      <c r="C164" s="85">
         <v>1000</v>
       </c>
       <c r="D164" s="45" t="s">
@@ -16208,13 +16220,13 @@
       </c>
     </row>
     <row r="165" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A165" s="85">
+      <c r="A165" s="82">
         <v>46133</v>
       </c>
       <c r="B165" s="44" t="s">
         <v>164</v>
       </c>
-      <c r="C165" s="86">
+      <c r="C165" s="83">
         <v>1200</v>
       </c>
       <c r="D165" s="44" t="s">
@@ -16233,13 +16245,13 @@
       </c>
     </row>
     <row r="166" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A166" s="87">
+      <c r="A166" s="84">
         <v>46134</v>
       </c>
       <c r="B166" s="45" t="s">
         <v>368</v>
       </c>
-      <c r="C166" s="88">
+      <c r="C166" s="85">
         <v>1280</v>
       </c>
       <c r="D166" s="45" t="s">
@@ -16258,13 +16270,13 @@
       </c>
     </row>
     <row r="167" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A167" s="85">
+      <c r="A167" s="82">
         <v>46134</v>
       </c>
       <c r="B167" s="44" t="s">
         <v>191</v>
       </c>
-      <c r="C167" s="86">
+      <c r="C167" s="83">
         <v>1100</v>
       </c>
       <c r="D167" s="44" t="s">
@@ -16283,13 +16295,13 @@
       </c>
     </row>
     <row r="168" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A168" s="85">
+      <c r="A168" s="82">
         <v>46134</v>
       </c>
       <c r="B168" s="44" t="s">
         <v>355</v>
       </c>
-      <c r="C168" s="86">
+      <c r="C168" s="83">
         <v>950</v>
       </c>
       <c r="D168" s="44" t="s">
@@ -16308,13 +16320,13 @@
       </c>
     </row>
     <row r="169" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A169" s="87">
+      <c r="A169" s="84">
         <v>46134</v>
       </c>
       <c r="B169" s="45" t="s">
         <v>177</v>
       </c>
-      <c r="C169" s="88">
+      <c r="C169" s="85">
         <v>650</v>
       </c>
       <c r="D169" s="45" t="s">
@@ -16333,13 +16345,13 @@
       </c>
     </row>
     <row r="170" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A170" s="85">
+      <c r="A170" s="82">
         <v>46134</v>
       </c>
       <c r="B170" s="44" t="s">
         <v>373</v>
       </c>
-      <c r="C170" s="86">
+      <c r="C170" s="83">
         <v>650</v>
       </c>
       <c r="D170" s="44" t="s">
@@ -16358,13 +16370,13 @@
       </c>
     </row>
     <row r="171" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A171" s="87">
+      <c r="A171" s="84">
         <v>46136</v>
       </c>
       <c r="B171" s="45" t="s">
         <v>214</v>
       </c>
-      <c r="C171" s="88">
+      <c r="C171" s="85">
         <v>680</v>
       </c>
       <c r="D171" s="45" t="s">
@@ -16383,13 +16395,13 @@
       </c>
     </row>
     <row r="172" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A172" s="85">
+      <c r="A172" s="82">
         <v>46138</v>
       </c>
       <c r="B172" s="44" t="s">
         <v>375</v>
       </c>
-      <c r="C172" s="86">
+      <c r="C172" s="83">
         <v>690</v>
       </c>
       <c r="D172" s="44" t="s">
@@ -16408,13 +16420,13 @@
       </c>
     </row>
     <row r="173" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A173" s="87">
+      <c r="A173" s="84">
         <v>46138</v>
       </c>
       <c r="B173" s="45" t="s">
         <v>377</v>
       </c>
-      <c r="C173" s="88">
+      <c r="C173" s="85">
         <v>1099</v>
       </c>
       <c r="D173" s="45" t="s">
@@ -16433,13 +16445,13 @@
       </c>
     </row>
     <row r="174" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A174" s="85">
+      <c r="A174" s="82">
         <v>46139</v>
       </c>
       <c r="B174" s="44" t="s">
         <v>379</v>
       </c>
-      <c r="C174" s="86">
+      <c r="C174" s="83">
         <v>690</v>
       </c>
       <c r="D174" s="44" t="s">
@@ -16458,13 +16470,13 @@
       </c>
     </row>
     <row r="175" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A175" s="87">
+      <c r="A175" s="84">
         <v>46139</v>
       </c>
       <c r="B175" s="45" t="s">
         <v>381</v>
       </c>
-      <c r="C175" s="88">
+      <c r="C175" s="85">
         <v>690</v>
       </c>
       <c r="D175" s="45" t="s">
@@ -16483,13 +16495,13 @@
       </c>
     </row>
     <row r="176" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A176" s="85">
+      <c r="A176" s="82">
         <v>46139</v>
       </c>
       <c r="B176" s="44" t="s">
         <v>382</v>
       </c>
-      <c r="C176" s="86">
+      <c r="C176" s="83">
         <v>690</v>
       </c>
       <c r="D176" s="44" t="s">
@@ -16508,13 +16520,13 @@
       </c>
     </row>
     <row r="177" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A177" s="87">
+      <c r="A177" s="84">
         <v>46140</v>
       </c>
       <c r="B177" s="45" t="s">
         <v>384</v>
       </c>
-      <c r="C177" s="88">
+      <c r="C177" s="85">
         <v>1380</v>
       </c>
       <c r="D177" s="45" t="s">
@@ -16533,13 +16545,13 @@
       </c>
     </row>
     <row r="178" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A178" s="85">
+      <c r="A178" s="82">
         <v>46140</v>
       </c>
       <c r="B178" s="44" t="s">
         <v>186</v>
       </c>
-      <c r="C178" s="86">
+      <c r="C178" s="83">
         <v>1480</v>
       </c>
       <c r="D178" s="44" t="s">
@@ -16558,13 +16570,13 @@
       </c>
     </row>
     <row r="179" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A179" s="87">
+      <c r="A179" s="84">
         <v>46140</v>
       </c>
       <c r="B179" s="45" t="s">
         <v>387</v>
       </c>
-      <c r="C179" s="88">
+      <c r="C179" s="85">
         <v>1200</v>
       </c>
       <c r="D179" s="45" t="s">
@@ -16583,13 +16595,13 @@
       </c>
     </row>
     <row r="180" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A180" s="85">
+      <c r="A180" s="82">
         <v>46140</v>
       </c>
       <c r="B180" s="44" t="s">
         <v>389</v>
       </c>
-      <c r="C180" s="86">
+      <c r="C180" s="83">
         <v>1200</v>
       </c>
       <c r="D180" s="44" t="s">
@@ -16608,13 +16620,13 @@
       </c>
     </row>
     <row r="181" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A181" s="87">
+      <c r="A181" s="84">
         <v>46141</v>
       </c>
       <c r="B181" s="45" t="s">
         <v>391</v>
       </c>
-      <c r="C181" s="88">
+      <c r="C181" s="85">
         <v>1380</v>
       </c>
       <c r="D181" s="45" t="s">
@@ -16633,13 +16645,13 @@
       </c>
     </row>
     <row r="182" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A182" s="85">
+      <c r="A182" s="82">
         <v>46141</v>
       </c>
       <c r="B182" s="44" t="s">
         <v>393</v>
       </c>
-      <c r="C182" s="86">
+      <c r="C182" s="83">
         <v>690</v>
       </c>
       <c r="D182" s="44" t="s">
@@ -16658,13 +16670,13 @@
       </c>
     </row>
     <row r="183" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A183" s="87">
+      <c r="A183" s="84">
         <v>46142</v>
       </c>
       <c r="B183" s="45" t="s">
         <v>394</v>
       </c>
-      <c r="C183" s="88">
+      <c r="C183" s="85">
         <v>690</v>
       </c>
       <c r="D183" s="45" t="s">
@@ -16683,13 +16695,13 @@
       </c>
     </row>
     <row r="184" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A184" s="85">
+      <c r="A184" s="82">
         <v>46142</v>
       </c>
       <c r="B184" s="44" t="s">
         <v>396</v>
       </c>
-      <c r="C184" s="86">
+      <c r="C184" s="83">
         <v>690</v>
       </c>
       <c r="D184" s="44" t="s">
@@ -16708,13 +16720,13 @@
       </c>
     </row>
     <row r="185" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A185" s="87">
+      <c r="A185" s="84">
         <v>46142</v>
       </c>
       <c r="B185" s="45" t="s">
         <v>397</v>
       </c>
-      <c r="C185" s="88">
+      <c r="C185" s="85">
         <v>609</v>
       </c>
       <c r="D185" s="45" t="s">
@@ -16733,13 +16745,13 @@
       </c>
     </row>
     <row r="186" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A186" s="87">
+      <c r="A186" s="84">
         <v>46144</v>
       </c>
       <c r="B186" s="45" t="s">
         <v>399</v>
       </c>
-      <c r="C186" s="88">
+      <c r="C186" s="85">
         <v>699</v>
       </c>
       <c r="D186" s="45" t="s">
@@ -16758,13 +16770,13 @@
       </c>
     </row>
     <row r="187" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A187" s="85">
+      <c r="A187" s="82">
         <v>46144</v>
       </c>
       <c r="B187" s="44" t="s">
         <v>401</v>
       </c>
-      <c r="C187" s="86">
+      <c r="C187" s="83">
         <v>690</v>
       </c>
       <c r="D187" s="44" t="s">
@@ -16783,13 +16795,13 @@
       </c>
     </row>
     <row r="188" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A188" s="87">
+      <c r="A188" s="84">
         <v>46145</v>
       </c>
       <c r="B188" s="45" t="s">
         <v>403</v>
       </c>
-      <c r="C188" s="88">
+      <c r="C188" s="85">
         <v>1200</v>
       </c>
       <c r="D188" s="45" t="s">
@@ -16808,13 +16820,13 @@
       </c>
     </row>
     <row r="189" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A189" s="85">
+      <c r="A189" s="82">
         <v>46145</v>
       </c>
       <c r="B189" s="44" t="s">
         <v>405</v>
       </c>
-      <c r="C189" s="86">
+      <c r="C189" s="83">
         <v>1200</v>
       </c>
       <c r="D189" s="44" t="s">
@@ -16833,13 +16845,13 @@
       </c>
     </row>
     <row r="190" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A190" s="87">
+      <c r="A190" s="84">
         <v>46145</v>
       </c>
       <c r="B190" s="45" t="s">
         <v>161</v>
       </c>
-      <c r="C190" s="88">
+      <c r="C190" s="85">
         <v>600</v>
       </c>
       <c r="D190" s="45" t="s">
@@ -16858,13 +16870,13 @@
       </c>
     </row>
     <row r="191" spans="1:9" ht="42" customHeight="1">
-      <c r="A191" s="85">
+      <c r="A191" s="82">
         <v>46151</v>
       </c>
       <c r="B191" s="44" t="s">
         <v>408</v>
       </c>
-      <c r="C191" s="86">
+      <c r="C191" s="83">
         <v>5600</v>
       </c>
       <c r="D191" s="44" t="s">
@@ -16883,13 +16895,13 @@
       </c>
     </row>
     <row r="192" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A192" s="87">
+      <c r="A192" s="84">
         <v>46152</v>
       </c>
       <c r="B192" s="45" t="s">
         <v>410</v>
       </c>
-      <c r="C192" s="88">
+      <c r="C192" s="85">
         <v>5600</v>
       </c>
       <c r="D192" s="45" t="s">
@@ -16908,13 +16920,13 @@
       </c>
     </row>
     <row r="193" spans="1:9" ht="42" customHeight="1">
-      <c r="A193" s="85">
+      <c r="A193" s="82">
         <v>46152</v>
       </c>
       <c r="B193" s="44" t="s">
         <v>412</v>
       </c>
-      <c r="C193" s="86">
+      <c r="C193" s="83">
         <v>5600</v>
       </c>
       <c r="D193" s="44" t="s">
@@ -16933,13 +16945,13 @@
       </c>
     </row>
     <row r="194" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A194" s="87">
+      <c r="A194" s="84">
         <v>46151</v>
       </c>
       <c r="B194" s="45" t="s">
         <v>414</v>
       </c>
-      <c r="C194" s="88">
+      <c r="C194" s="85">
         <v>3100</v>
       </c>
       <c r="D194" s="45" t="s">
@@ -16958,13 +16970,13 @@
       </c>
     </row>
     <row r="195" spans="1:9" ht="42" customHeight="1">
-      <c r="A195" s="85">
+      <c r="A195" s="82">
         <v>46155</v>
       </c>
       <c r="B195" s="44" t="s">
         <v>416</v>
       </c>
-      <c r="C195" s="86">
+      <c r="C195" s="83">
         <v>5400</v>
       </c>
       <c r="D195" s="44" t="s">
@@ -16983,13 +16995,13 @@
       </c>
     </row>
     <row r="196" spans="1:9" ht="42" customHeight="1">
-      <c r="A196" s="87">
+      <c r="A196" s="84">
         <v>46155</v>
       </c>
       <c r="B196" s="45" t="s">
         <v>418</v>
       </c>
-      <c r="C196" s="88">
+      <c r="C196" s="85">
         <v>5750</v>
       </c>
       <c r="D196" s="45" t="s">
@@ -17008,13 +17020,13 @@
       </c>
     </row>
     <row r="197" spans="1:9" ht="42" customHeight="1">
-      <c r="A197" s="85">
+      <c r="A197" s="82">
         <v>46155</v>
       </c>
       <c r="B197" s="44" t="s">
         <v>183</v>
       </c>
-      <c r="C197" s="86">
+      <c r="C197" s="83">
         <v>4000</v>
       </c>
       <c r="D197" s="44" t="s">
@@ -17033,13 +17045,13 @@
       </c>
     </row>
     <row r="198" spans="1:9" ht="42" customHeight="1">
-      <c r="A198" s="87">
+      <c r="A198" s="84">
         <v>46168</v>
       </c>
       <c r="B198" s="45" t="s">
         <v>421</v>
       </c>
-      <c r="C198" s="88">
+      <c r="C198" s="85">
         <v>5200</v>
       </c>
       <c r="D198" s="45" t="s">
@@ -17058,13 +17070,13 @@
       </c>
     </row>
     <row r="199" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A199" s="85">
+      <c r="A199" s="82">
         <v>46172</v>
       </c>
       <c r="B199" s="44" t="s">
         <v>423</v>
       </c>
-      <c r="C199" s="86">
+      <c r="C199" s="83">
         <v>1425</v>
       </c>
       <c r="D199" s="44" t="s">
@@ -17083,13 +17095,13 @@
       </c>
     </row>
     <row r="200" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A200" s="87">
+      <c r="A200" s="84">
         <v>46173</v>
       </c>
       <c r="B200" s="45" t="s">
         <v>425</v>
       </c>
-      <c r="C200" s="88">
+      <c r="C200" s="85">
         <v>2850</v>
       </c>
       <c r="D200" s="45" t="s">
@@ -17108,13 +17120,13 @@
       </c>
     </row>
     <row r="201" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A201" s="85">
+      <c r="A201" s="82">
         <v>46173</v>
       </c>
       <c r="B201" s="44" t="s">
         <v>427</v>
       </c>
-      <c r="C201" s="86">
+      <c r="C201" s="83">
         <v>3850</v>
       </c>
       <c r="D201" s="44" t="s">
@@ -17133,13 +17145,13 @@
       </c>
     </row>
     <row r="202" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A202" s="87">
+      <c r="A202" s="84">
         <v>46173</v>
       </c>
       <c r="B202" s="45" t="s">
         <v>429</v>
       </c>
-      <c r="C202" s="88">
+      <c r="C202" s="85">
         <v>930</v>
       </c>
       <c r="D202" s="45" t="s">
@@ -17158,13 +17170,13 @@
       </c>
     </row>
     <row r="203" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A203" s="85">
+      <c r="A203" s="82">
         <v>46173</v>
       </c>
       <c r="B203" s="44" t="s">
         <v>431</v>
       </c>
-      <c r="C203" s="86">
+      <c r="C203" s="83">
         <v>930</v>
       </c>
       <c r="D203" s="44" t="s">
@@ -17183,13 +17195,13 @@
       </c>
     </row>
     <row r="204" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A204" s="87">
+      <c r="A204" s="84">
         <v>46175</v>
       </c>
       <c r="B204" s="45" t="s">
         <v>433</v>
       </c>
-      <c r="C204" s="88">
+      <c r="C204" s="85">
         <v>699</v>
       </c>
       <c r="D204" s="45" t="s">
@@ -17208,13 +17220,13 @@
       </c>
     </row>
     <row r="205" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A205" s="85">
+      <c r="A205" s="82">
         <v>46175</v>
       </c>
       <c r="B205" s="44" t="s">
         <v>434</v>
       </c>
-      <c r="C205" s="86">
+      <c r="C205" s="83">
         <v>700</v>
       </c>
       <c r="D205" s="44" t="s">
@@ -17233,13 +17245,13 @@
       </c>
     </row>
     <row r="206" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A206" s="87">
+      <c r="A206" s="84">
         <v>46175</v>
       </c>
       <c r="B206" s="45" t="s">
         <v>436</v>
       </c>
-      <c r="C206" s="88">
+      <c r="C206" s="85">
         <v>1350</v>
       </c>
       <c r="D206" s="45" t="s">
@@ -17258,13 +17270,13 @@
       </c>
     </row>
     <row r="207" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A207" s="85">
+      <c r="A207" s="82">
         <v>46175</v>
       </c>
       <c r="B207" s="44" t="s">
         <v>438</v>
       </c>
-      <c r="C207" s="86">
+      <c r="C207" s="83">
         <v>699</v>
       </c>
       <c r="D207" s="44" t="s">
@@ -17283,13 +17295,13 @@
       </c>
     </row>
     <row r="208" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A208" s="87">
+      <c r="A208" s="84">
         <v>46175</v>
       </c>
       <c r="B208" s="45" t="s">
         <v>440</v>
       </c>
-      <c r="C208" s="88">
+      <c r="C208" s="85">
         <v>699</v>
       </c>
       <c r="D208" s="45" t="s">
@@ -17308,13 +17320,13 @@
       </c>
     </row>
     <row r="209" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A209" s="85">
+      <c r="A209" s="82">
         <v>46176</v>
       </c>
       <c r="B209" s="44" t="s">
         <v>442</v>
       </c>
-      <c r="C209" s="86">
+      <c r="C209" s="83">
         <v>699</v>
       </c>
       <c r="D209" s="44" t="s">
@@ -17333,13 +17345,13 @@
       </c>
     </row>
     <row r="210" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A210" s="87">
+      <c r="A210" s="84">
         <v>46176</v>
       </c>
       <c r="B210" s="45" t="s">
         <v>443</v>
       </c>
-      <c r="C210" s="88">
+      <c r="C210" s="85">
         <v>2200</v>
       </c>
       <c r="D210" s="45" t="s">
@@ -17358,13 +17370,13 @@
       </c>
     </row>
     <row r="211" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A211" s="85">
+      <c r="A211" s="82">
         <v>46176</v>
       </c>
       <c r="B211" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="C211" s="86">
+      <c r="C211" s="83">
         <v>699</v>
       </c>
       <c r="D211" s="44" t="s">
@@ -17383,13 +17395,13 @@
       </c>
     </row>
     <row r="212" spans="1:9" ht="14">
-      <c r="A212" s="87">
+      <c r="A212" s="84">
         <v>46176</v>
       </c>
       <c r="B212" s="45" t="s">
         <v>447</v>
       </c>
-      <c r="C212" s="88">
+      <c r="C212" s="85">
         <v>699</v>
       </c>
       <c r="D212" s="45" t="s">
@@ -17408,13 +17420,13 @@
       </c>
     </row>
     <row r="213" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A213" s="85">
+      <c r="A213" s="82">
         <v>46176</v>
       </c>
       <c r="B213" s="44" t="s">
         <v>448</v>
       </c>
-      <c r="C213" s="86">
+      <c r="C213" s="83">
         <v>700</v>
       </c>
       <c r="D213" s="44" t="s">
@@ -17433,13 +17445,13 @@
       </c>
     </row>
     <row r="214" spans="1:9" ht="14">
-      <c r="A214" s="87">
+      <c r="A214" s="84">
         <v>46177</v>
       </c>
       <c r="B214" s="45" t="s">
         <v>449</v>
       </c>
-      <c r="C214" s="88">
+      <c r="C214" s="85">
         <v>699</v>
       </c>
       <c r="D214" s="45" t="s">
@@ -17458,13 +17470,13 @@
       </c>
     </row>
     <row r="215" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A215" s="85">
+      <c r="A215" s="82">
         <v>46187</v>
       </c>
       <c r="B215" s="44" t="s">
         <v>450</v>
       </c>
-      <c r="C215" s="86">
+      <c r="C215" s="83">
         <v>1380</v>
       </c>
       <c r="D215" s="44" t="s">
@@ -17483,13 +17495,13 @@
       </c>
     </row>
     <row r="216" spans="1:9" ht="55.5" customHeight="1">
-      <c r="A216" s="87">
+      <c r="A216" s="84">
         <v>46188</v>
       </c>
       <c r="B216" s="45" t="s">
         <v>451</v>
       </c>
-      <c r="C216" s="88">
+      <c r="C216" s="85">
         <v>5000</v>
       </c>
       <c r="D216" s="45" t="s">
@@ -17508,13 +17520,13 @@
       </c>
     </row>
     <row r="217" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A217" s="87">
+      <c r="A217" s="84">
         <v>46191</v>
       </c>
       <c r="B217" s="45" t="s">
         <v>452</v>
       </c>
-      <c r="C217" s="88">
+      <c r="C217" s="85">
         <v>1380</v>
       </c>
       <c r="D217" s="45" t="s">
@@ -17533,13 +17545,13 @@
       </c>
     </row>
     <row r="218" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A218" s="85">
+      <c r="A218" s="82">
         <v>46191</v>
       </c>
       <c r="B218" s="44" t="s">
         <v>454</v>
       </c>
-      <c r="C218" s="86">
+      <c r="C218" s="83">
         <v>1380</v>
       </c>
       <c r="D218" s="44" t="s">
@@ -17558,13 +17570,13 @@
       </c>
     </row>
     <row r="219" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A219" s="87">
+      <c r="A219" s="84">
         <v>46191</v>
       </c>
       <c r="B219" s="45" t="s">
         <v>455</v>
       </c>
-      <c r="C219" s="88">
+      <c r="C219" s="85">
         <v>1380</v>
       </c>
       <c r="D219" s="45" t="s">
@@ -17583,13 +17595,13 @@
       </c>
     </row>
     <row r="220" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A220" s="85">
+      <c r="A220" s="82">
         <v>46191</v>
       </c>
       <c r="B220" s="44" t="s">
         <v>373</v>
       </c>
-      <c r="C220" s="86">
+      <c r="C220" s="83">
         <v>1380</v>
       </c>
       <c r="D220" s="44" t="s">
@@ -17608,13 +17620,13 @@
       </c>
     </row>
     <row r="221" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A221" s="87">
+      <c r="A221" s="84">
         <v>46191</v>
       </c>
       <c r="B221" s="45" t="s">
         <v>456</v>
       </c>
-      <c r="C221" s="88">
+      <c r="C221" s="85">
         <v>1380</v>
       </c>
       <c r="D221" s="45" t="s">
@@ -17633,13 +17645,13 @@
       </c>
     </row>
     <row r="222" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A222" s="85">
+      <c r="A222" s="82">
         <v>46191</v>
       </c>
       <c r="B222" s="44" t="s">
         <v>457</v>
       </c>
-      <c r="C222" s="86">
+      <c r="C222" s="83">
         <v>1380</v>
       </c>
       <c r="D222" s="44" t="s">
@@ -17658,13 +17670,13 @@
       </c>
     </row>
     <row r="223" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A223" s="87">
+      <c r="A223" s="84">
         <v>46191</v>
       </c>
       <c r="B223" s="45" t="s">
         <v>458</v>
       </c>
-      <c r="C223" s="88">
+      <c r="C223" s="85">
         <v>1380</v>
       </c>
       <c r="D223" s="45" t="s">
@@ -17683,13 +17695,13 @@
       </c>
     </row>
     <row r="224" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A224" s="85">
+      <c r="A224" s="82">
         <v>46192</v>
       </c>
       <c r="B224" s="44" t="s">
         <v>459</v>
       </c>
-      <c r="C224" s="86">
+      <c r="C224" s="83">
         <v>1380</v>
       </c>
       <c r="D224" s="44" t="s">
@@ -17708,13 +17720,13 @@
       </c>
     </row>
     <row r="225" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A225" s="87">
+      <c r="A225" s="84">
         <v>46192</v>
       </c>
       <c r="B225" s="45" t="s">
         <v>460</v>
       </c>
-      <c r="C225" s="88">
+      <c r="C225" s="85">
         <v>1440</v>
       </c>
       <c r="D225" s="45" t="s">
@@ -17733,13 +17745,13 @@
       </c>
     </row>
     <row r="226" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A226" s="85">
+      <c r="A226" s="82">
         <v>46192</v>
       </c>
       <c r="B226" s="44" t="s">
         <v>461</v>
       </c>
-      <c r="C226" s="86">
+      <c r="C226" s="83">
         <v>1380</v>
       </c>
       <c r="D226" s="44" t="s">
@@ -17758,13 +17770,13 @@
       </c>
     </row>
     <row r="227" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A227" s="87">
+      <c r="A227" s="84">
         <v>46192</v>
       </c>
       <c r="B227" s="45" t="s">
         <v>462</v>
       </c>
-      <c r="C227" s="88">
+      <c r="C227" s="85">
         <v>1380</v>
       </c>
       <c r="D227" s="45" t="s">
@@ -17783,13 +17795,13 @@
       </c>
     </row>
     <row r="228" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A228" s="85">
+      <c r="A228" s="82">
         <v>46193</v>
       </c>
       <c r="B228" s="44" t="s">
         <v>463</v>
       </c>
-      <c r="C228" s="86">
+      <c r="C228" s="83">
         <v>699</v>
       </c>
       <c r="D228" s="44" t="s">
@@ -17808,13 +17820,13 @@
       </c>
     </row>
     <row r="229" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A229" s="87">
+      <c r="A229" s="84">
         <v>46193</v>
       </c>
       <c r="B229" s="45" t="s">
         <v>465</v>
       </c>
-      <c r="C229" s="88">
+      <c r="C229" s="85">
         <v>699</v>
       </c>
       <c r="D229" s="45" t="s">
@@ -17833,13 +17845,13 @@
       </c>
     </row>
     <row r="230" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A230" s="85">
+      <c r="A230" s="82">
         <v>46193</v>
       </c>
       <c r="B230" s="44" t="s">
         <v>467</v>
       </c>
-      <c r="C230" s="86">
+      <c r="C230" s="83">
         <v>1380</v>
       </c>
       <c r="D230" s="44" t="s">
@@ -17858,13 +17870,13 @@
       </c>
     </row>
     <row r="231" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A231" s="87">
+      <c r="A231" s="84">
         <v>46193</v>
       </c>
       <c r="B231" s="45" t="s">
         <v>468</v>
       </c>
-      <c r="C231" s="88">
+      <c r="C231" s="85">
         <v>699</v>
       </c>
       <c r="D231" s="45" t="s">
@@ -17883,13 +17895,13 @@
       </c>
     </row>
     <row r="232" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A232" s="85">
+      <c r="A232" s="82">
         <v>46193</v>
       </c>
       <c r="B232" s="44" t="s">
         <v>469</v>
       </c>
-      <c r="C232" s="86">
+      <c r="C232" s="83">
         <v>1380</v>
       </c>
       <c r="D232" s="44" t="s">
@@ -17908,13 +17920,13 @@
       </c>
     </row>
     <row r="233" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A233" s="87">
+      <c r="A233" s="84">
         <v>46193</v>
       </c>
       <c r="B233" s="45" t="s">
         <v>167</v>
       </c>
-      <c r="C233" s="88">
+      <c r="C233" s="85">
         <v>2400</v>
       </c>
       <c r="D233" s="45" t="s">
@@ -17933,13 +17945,13 @@
       </c>
     </row>
     <row r="234" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A234" s="85">
+      <c r="A234" s="82">
         <v>46193</v>
       </c>
       <c r="B234" s="44" t="s">
         <v>153</v>
       </c>
-      <c r="C234" s="86">
+      <c r="C234" s="83">
         <v>4000</v>
       </c>
       <c r="D234" s="44" t="s">
@@ -17958,13 +17970,13 @@
       </c>
     </row>
     <row r="235" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A235" s="87">
+      <c r="A235" s="84">
         <v>46194</v>
       </c>
       <c r="B235" s="45" t="s">
         <v>472</v>
       </c>
-      <c r="C235" s="88">
+      <c r="C235" s="85">
         <v>700</v>
       </c>
       <c r="D235" s="45" t="s">
@@ -17983,13 +17995,13 @@
       </c>
     </row>
     <row r="236" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A236" s="85">
+      <c r="A236" s="82">
         <v>46194</v>
       </c>
       <c r="B236" s="44" t="s">
         <v>472</v>
       </c>
-      <c r="C236" s="86">
+      <c r="C236" s="83">
         <v>2480</v>
       </c>
       <c r="D236" s="44" t="s">
@@ -18008,13 +18020,13 @@
       </c>
     </row>
     <row r="237" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A237" s="87">
+      <c r="A237" s="84">
         <v>46196</v>
       </c>
       <c r="B237" s="45" t="s">
         <v>472</v>
       </c>
-      <c r="C237" s="88">
+      <c r="C237" s="85">
         <v>700</v>
       </c>
       <c r="D237" s="45" t="s">
@@ -18033,13 +18045,13 @@
       </c>
     </row>
     <row r="238" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A238" s="85">
+      <c r="A238" s="82">
         <v>46196</v>
       </c>
       <c r="B238" s="44" t="s">
         <v>476</v>
       </c>
-      <c r="C238" s="86">
+      <c r="C238" s="83">
         <v>1380</v>
       </c>
       <c r="D238" s="44" t="s">
@@ -18058,13 +18070,13 @@
       </c>
     </row>
     <row r="239" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A239" s="87">
+      <c r="A239" s="84">
         <v>46196</v>
       </c>
       <c r="B239" s="45" t="s">
         <v>478</v>
       </c>
-      <c r="C239" s="88">
+      <c r="C239" s="85">
         <v>699</v>
       </c>
       <c r="D239" s="45" t="s">
@@ -18083,13 +18095,13 @@
       </c>
     </row>
     <row r="240" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A240" s="85">
+      <c r="A240" s="82">
         <v>46196</v>
       </c>
       <c r="B240" s="44" t="s">
         <v>304</v>
       </c>
-      <c r="C240" s="86">
+      <c r="C240" s="83">
         <v>5000</v>
       </c>
       <c r="D240" s="44" t="s">
@@ -18108,13 +18120,13 @@
       </c>
     </row>
     <row r="241" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A241" s="87">
+      <c r="A241" s="84">
         <v>46197</v>
       </c>
       <c r="B241" s="45" t="s">
         <v>481</v>
       </c>
-      <c r="C241" s="88">
+      <c r="C241" s="85">
         <v>1380</v>
       </c>
       <c r="D241" s="45" t="s">
@@ -18133,13 +18145,13 @@
       </c>
     </row>
     <row r="242" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A242" s="85">
+      <c r="A242" s="82">
         <v>46197</v>
       </c>
       <c r="B242" s="44" t="s">
         <v>482</v>
       </c>
-      <c r="C242" s="86">
+      <c r="C242" s="83">
         <v>1380</v>
       </c>
       <c r="D242" s="44" t="s">
@@ -18158,13 +18170,13 @@
       </c>
     </row>
     <row r="243" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A243" s="87">
+      <c r="A243" s="84">
         <v>46197</v>
       </c>
       <c r="B243" s="45" t="s">
         <v>484</v>
       </c>
-      <c r="C243" s="88">
+      <c r="C243" s="85">
         <v>1380</v>
       </c>
       <c r="D243" s="45" t="s">
@@ -18183,13 +18195,13 @@
       </c>
     </row>
     <row r="244" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A244" s="85">
+      <c r="A244" s="82">
         <v>46197</v>
       </c>
       <c r="B244" s="44" t="s">
         <v>165</v>
       </c>
-      <c r="C244" s="86">
+      <c r="C244" s="83">
         <v>699</v>
       </c>
       <c r="D244" s="44" t="s">
@@ -18208,13 +18220,13 @@
       </c>
     </row>
     <row r="245" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A245" s="87">
+      <c r="A245" s="84">
         <v>46198</v>
       </c>
       <c r="B245" s="45" t="s">
         <v>486</v>
       </c>
-      <c r="C245" s="88">
+      <c r="C245" s="85">
         <v>1380</v>
       </c>
       <c r="D245" s="45" t="s">
@@ -18233,13 +18245,13 @@
       </c>
     </row>
     <row r="246" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A246" s="85">
+      <c r="A246" s="82">
         <v>46199</v>
       </c>
       <c r="B246" s="44" t="s">
         <v>487</v>
       </c>
-      <c r="C246" s="86">
+      <c r="C246" s="83">
         <v>1380</v>
       </c>
       <c r="D246" s="44" t="s">
@@ -18258,13 +18270,13 @@
       </c>
     </row>
     <row r="247" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A247" s="87">
+      <c r="A247" s="84">
         <v>46199</v>
       </c>
       <c r="B247" s="45" t="s">
         <v>488</v>
       </c>
-      <c r="C247" s="88">
+      <c r="C247" s="85">
         <v>1380</v>
       </c>
       <c r="D247" s="45" t="s">
@@ -18283,13 +18295,13 @@
       </c>
     </row>
     <row r="248" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A248" s="85">
+      <c r="A248" s="82">
         <v>46199</v>
       </c>
       <c r="B248" s="44" t="s">
         <v>332</v>
       </c>
-      <c r="C248" s="86">
+      <c r="C248" s="83">
         <v>1000</v>
       </c>
       <c r="D248" s="44" t="s">
@@ -18308,13 +18320,13 @@
       </c>
     </row>
     <row r="249" spans="1:9" ht="14">
-      <c r="A249" s="87">
+      <c r="A249" s="84">
         <v>46200</v>
       </c>
       <c r="B249" s="45" t="s">
         <v>153</v>
       </c>
-      <c r="C249" s="88">
+      <c r="C249" s="85">
         <v>1200</v>
       </c>
       <c r="D249" s="45" t="s">
@@ -18333,13 +18345,13 @@
       </c>
     </row>
     <row r="250" spans="1:9" ht="14">
-      <c r="A250" s="85">
+      <c r="A250" s="82">
         <v>46200</v>
       </c>
       <c r="B250" s="44" t="s">
         <v>164</v>
       </c>
-      <c r="C250" s="86">
+      <c r="C250" s="83">
         <v>950</v>
       </c>
       <c r="D250" s="44"/>
@@ -18354,13 +18366,13 @@
       </c>
     </row>
     <row r="251" spans="1:9" ht="14">
-      <c r="A251" s="87">
+      <c r="A251" s="84">
         <v>46201</v>
       </c>
       <c r="B251" s="45" t="s">
         <v>1093</v>
       </c>
-      <c r="C251" s="88">
+      <c r="C251" s="85">
         <v>1380</v>
       </c>
       <c r="D251" s="45" t="s">
@@ -18379,13 +18391,13 @@
       </c>
     </row>
     <row r="252" spans="1:9" ht="14">
-      <c r="A252" s="85">
+      <c r="A252" s="82">
         <v>46201</v>
       </c>
       <c r="B252" s="44" t="s">
         <v>1079</v>
       </c>
-      <c r="C252" s="86">
+      <c r="C252" s="83">
         <v>699</v>
       </c>
       <c r="D252" s="44" t="s">
@@ -18404,13 +18416,13 @@
       </c>
     </row>
     <row r="253" spans="1:9" ht="14">
-      <c r="A253" s="87">
+      <c r="A253" s="84">
         <v>46201</v>
       </c>
       <c r="B253" s="45" t="s">
         <v>1081</v>
       </c>
-      <c r="C253" s="88">
+      <c r="C253" s="85">
         <v>699</v>
       </c>
       <c r="D253" s="45" t="s">
@@ -18429,13 +18441,13 @@
       </c>
     </row>
     <row r="254" spans="1:9" ht="14">
-      <c r="A254" s="85">
+      <c r="A254" s="82">
         <v>46201</v>
       </c>
       <c r="B254" s="44" t="s">
         <v>1083</v>
       </c>
-      <c r="C254" s="86">
+      <c r="C254" s="83">
         <v>699</v>
       </c>
       <c r="D254" s="44" t="s">
@@ -18454,13 +18466,13 @@
       </c>
     </row>
     <row r="255" spans="1:9" ht="14">
-      <c r="A255" s="87">
+      <c r="A255" s="84">
         <v>46201</v>
       </c>
       <c r="B255" s="45" t="s">
         <v>472</v>
       </c>
-      <c r="C255" s="88">
+      <c r="C255" s="85">
         <v>2650</v>
       </c>
       <c r="D255" s="45" t="s">
@@ -18479,13 +18491,13 @@
       </c>
     </row>
     <row r="256" spans="1:9" ht="14">
-      <c r="A256" s="85">
+      <c r="A256" s="82">
         <v>46203</v>
       </c>
       <c r="B256" s="44" t="s">
         <v>1094</v>
       </c>
-      <c r="C256" s="86">
+      <c r="C256" s="83">
         <v>950</v>
       </c>
       <c r="D256" s="44" t="s">
@@ -18504,13 +18516,13 @@
       </c>
     </row>
     <row r="257" spans="1:9" ht="14">
-      <c r="A257" s="87">
+      <c r="A257" s="84">
         <v>46204</v>
       </c>
       <c r="B257" s="45" t="s">
         <v>1098</v>
       </c>
-      <c r="C257" s="88">
+      <c r="C257" s="85">
         <v>699</v>
       </c>
       <c r="D257" s="45" t="s">
@@ -18529,13 +18541,13 @@
       </c>
     </row>
     <row r="258" spans="1:9" ht="14">
-      <c r="A258" s="85">
+      <c r="A258" s="82">
         <v>46205</v>
       </c>
       <c r="B258" s="44" t="s">
         <v>1100</v>
       </c>
-      <c r="C258" s="86">
+      <c r="C258" s="83">
         <v>1500</v>
       </c>
       <c r="D258" s="44" t="s">
@@ -18554,13 +18566,13 @@
       </c>
     </row>
     <row r="259" spans="1:9" ht="14">
-      <c r="A259" s="87">
+      <c r="A259" s="84">
         <v>46205</v>
       </c>
       <c r="B259" s="45" t="s">
         <v>1100</v>
       </c>
-      <c r="C259" s="88">
+      <c r="C259" s="85">
         <v>1200</v>
       </c>
       <c r="D259" s="45" t="s">
@@ -18579,13 +18591,13 @@
       </c>
     </row>
     <row r="260" spans="1:9" ht="14">
-      <c r="A260" s="85">
+      <c r="A260" s="82">
         <v>46205</v>
       </c>
       <c r="B260" s="44" t="s">
         <v>1106</v>
       </c>
-      <c r="C260" s="86">
+      <c r="C260" s="83">
         <v>1500</v>
       </c>
       <c r="D260" s="44" t="s">
@@ -18604,13 +18616,13 @@
       </c>
     </row>
     <row r="261" spans="1:9" ht="14">
-      <c r="A261" s="87">
+      <c r="A261" s="84">
         <v>46205</v>
       </c>
       <c r="B261" s="45" t="s">
         <v>1109</v>
       </c>
-      <c r="C261" s="88">
+      <c r="C261" s="85">
         <v>2600</v>
       </c>
       <c r="D261" s="45" t="s">
@@ -18629,13 +18641,13 @@
       </c>
     </row>
     <row r="262" spans="1:9" ht="14">
-      <c r="A262" s="85">
+      <c r="A262" s="82">
         <v>46206</v>
       </c>
       <c r="B262" s="44" t="s">
         <v>1113</v>
       </c>
-      <c r="C262" s="86">
+      <c r="C262" s="83">
         <v>1380</v>
       </c>
       <c r="D262" s="44" t="s">
@@ -18654,13 +18666,13 @@
       </c>
     </row>
     <row r="263" spans="1:9" ht="14">
-      <c r="A263" s="87">
+      <c r="A263" s="84">
         <v>46206</v>
       </c>
       <c r="B263" s="45" t="s">
         <v>1114</v>
       </c>
-      <c r="C263" s="88">
+      <c r="C263" s="85">
         <v>1380</v>
       </c>
       <c r="D263" s="45" t="s">
@@ -18679,13 +18691,13 @@
       </c>
     </row>
     <row r="264" spans="1:9" ht="14">
-      <c r="A264" s="85">
+      <c r="A264" s="82">
         <v>46206</v>
       </c>
       <c r="B264" s="44" t="s">
         <v>1125</v>
       </c>
-      <c r="C264" s="86">
+      <c r="C264" s="83">
         <v>2500</v>
       </c>
       <c r="D264" s="44" t="s">
@@ -18704,13 +18716,13 @@
       </c>
     </row>
     <row r="265" spans="1:9" ht="14">
-      <c r="A265" s="87">
+      <c r="A265" s="84">
         <v>46206</v>
       </c>
       <c r="B265" s="45" t="s">
         <v>1117</v>
       </c>
-      <c r="C265" s="88">
+      <c r="C265" s="85">
         <v>1300</v>
       </c>
       <c r="D265" s="45" t="s">
@@ -18729,13 +18741,13 @@
       </c>
     </row>
     <row r="266" spans="1:9" ht="14">
-      <c r="A266" s="85">
+      <c r="A266" s="82">
         <v>46206</v>
       </c>
       <c r="B266" s="44" t="s">
         <v>1106</v>
       </c>
-      <c r="C266" s="86">
+      <c r="C266" s="83">
         <v>1380</v>
       </c>
       <c r="D266" s="44" t="s">
@@ -18754,13 +18766,13 @@
       </c>
     </row>
     <row r="267" spans="1:9" ht="14">
-      <c r="A267" s="87">
+      <c r="A267" s="84">
         <v>46207</v>
       </c>
       <c r="B267" s="45" t="s">
         <v>173</v>
       </c>
-      <c r="C267" s="88">
+      <c r="C267" s="85">
         <v>1250</v>
       </c>
       <c r="D267" s="45" t="s">
@@ -18779,13 +18791,13 @@
       </c>
     </row>
     <row r="268" spans="1:9" ht="28">
-      <c r="A268" s="85">
+      <c r="A268" s="82">
         <v>46208</v>
       </c>
       <c r="B268" s="44" t="s">
         <v>1124</v>
       </c>
-      <c r="C268" s="86">
+      <c r="C268" s="83">
         <v>2350</v>
       </c>
       <c r="D268" s="44"/>
@@ -18800,13 +18812,13 @@
       </c>
     </row>
     <row r="269" spans="1:9" ht="14">
-      <c r="A269" s="87">
+      <c r="A269" s="84">
         <v>46209</v>
       </c>
       <c r="B269" s="45" t="s">
         <v>1122</v>
       </c>
-      <c r="C269" s="88">
+      <c r="C269" s="85">
         <v>1100</v>
       </c>
       <c r="D269" s="45" t="s">
@@ -18825,13 +18837,13 @@
       </c>
     </row>
     <row r="270" spans="1:9" ht="14">
-      <c r="A270" s="85">
+      <c r="A270" s="82">
         <v>46210</v>
       </c>
       <c r="B270" s="44" t="s">
-        <v>1258</v>
-      </c>
-      <c r="C270" s="86">
+        <v>1256</v>
+      </c>
+      <c r="C270" s="83">
         <v>3200</v>
       </c>
       <c r="D270" s="44" t="s">
@@ -18850,13 +18862,13 @@
       </c>
     </row>
     <row r="271" spans="1:9" ht="14">
-      <c r="A271" s="87">
+      <c r="A271" s="84">
         <v>46211</v>
       </c>
       <c r="B271" s="45" t="s">
         <v>1130</v>
       </c>
-      <c r="C271" s="88">
+      <c r="C271" s="85">
         <v>1380</v>
       </c>
       <c r="D271" s="45" t="s">
@@ -18875,13 +18887,13 @@
       </c>
     </row>
     <row r="272" spans="1:9" ht="14">
-      <c r="A272" s="85">
+      <c r="A272" s="82">
         <v>46215</v>
       </c>
       <c r="B272" s="44" t="s">
         <v>1135</v>
       </c>
-      <c r="C272" s="86">
+      <c r="C272" s="83">
         <v>1380</v>
       </c>
       <c r="D272" s="44" t="s">
@@ -18900,13 +18912,13 @@
       </c>
     </row>
     <row r="273" spans="1:9" ht="14">
-      <c r="A273" s="87">
+      <c r="A273" s="84">
         <v>46215</v>
       </c>
       <c r="B273" s="45" t="s">
         <v>1136</v>
       </c>
-      <c r="C273" s="88">
+      <c r="C273" s="85">
         <v>699</v>
       </c>
       <c r="D273" s="45" t="s">
@@ -18925,13 +18937,13 @@
       </c>
     </row>
     <row r="274" spans="1:9" ht="14">
-      <c r="A274" s="85">
+      <c r="A274" s="82">
         <v>46215</v>
       </c>
       <c r="B274" s="44" t="s">
         <v>197</v>
       </c>
-      <c r="C274" s="86">
+      <c r="C274" s="83">
         <v>1350</v>
       </c>
       <c r="D274" s="44" t="s">
@@ -18950,13 +18962,13 @@
       </c>
     </row>
     <row r="275" spans="1:9" ht="14">
-      <c r="A275" s="87">
+      <c r="A275" s="84">
         <v>46216</v>
       </c>
       <c r="B275" s="45" t="s">
         <v>1139</v>
       </c>
-      <c r="C275" s="88">
+      <c r="C275" s="85">
         <v>699</v>
       </c>
       <c r="D275" s="45" t="s">
@@ -18975,13 +18987,13 @@
       </c>
     </row>
     <row r="276" spans="1:9" ht="14">
-      <c r="A276" s="85">
+      <c r="A276" s="82">
         <v>46216</v>
       </c>
       <c r="B276" s="44" t="s">
         <v>1141</v>
       </c>
-      <c r="C276" s="86">
+      <c r="C276" s="83">
         <v>3000</v>
       </c>
       <c r="D276" s="44" t="s">
@@ -19000,13 +19012,13 @@
       </c>
     </row>
     <row r="277" spans="1:9" ht="14">
-      <c r="A277" s="87">
+      <c r="A277" s="84">
         <v>46219</v>
       </c>
       <c r="B277" s="45" t="s">
         <v>1142</v>
       </c>
-      <c r="C277" s="88">
+      <c r="C277" s="85">
         <v>1380</v>
       </c>
       <c r="D277" s="45" t="s">
@@ -19025,13 +19037,13 @@
       </c>
     </row>
     <row r="278" spans="1:9" ht="14">
-      <c r="A278" s="85">
+      <c r="A278" s="82">
         <v>46219</v>
       </c>
       <c r="B278" s="44" t="s">
         <v>482</v>
       </c>
-      <c r="C278" s="86">
+      <c r="C278" s="83">
         <v>1380</v>
       </c>
       <c r="D278" s="44" t="s">
@@ -19050,13 +19062,13 @@
       </c>
     </row>
     <row r="279" spans="1:9" ht="14">
-      <c r="A279" s="87">
+      <c r="A279" s="84">
         <v>46219</v>
       </c>
       <c r="B279" s="45" t="s">
         <v>224</v>
       </c>
-      <c r="C279" s="88">
+      <c r="C279" s="85">
         <v>1200</v>
       </c>
       <c r="D279" s="45" t="s">
@@ -19075,13 +19087,13 @@
       </c>
     </row>
     <row r="280" spans="1:9" ht="14">
-      <c r="A280" s="85">
+      <c r="A280" s="82">
         <v>46219</v>
       </c>
       <c r="B280" s="44" t="s">
         <v>220</v>
       </c>
-      <c r="C280" s="86">
+      <c r="C280" s="83">
         <v>2500</v>
       </c>
       <c r="D280" s="44" t="s">
@@ -19100,13 +19112,13 @@
       </c>
     </row>
     <row r="281" spans="1:9" ht="14">
-      <c r="A281" s="87">
+      <c r="A281" s="84">
         <v>46219</v>
       </c>
       <c r="B281" s="45" t="s">
         <v>153</v>
       </c>
-      <c r="C281" s="88">
+      <c r="C281" s="85">
         <v>3200</v>
       </c>
       <c r="D281" s="45" t="s">
@@ -19125,13 +19137,13 @@
       </c>
     </row>
     <row r="282" spans="1:9" ht="14">
-      <c r="A282" s="85">
+      <c r="A282" s="82">
         <v>46220</v>
       </c>
       <c r="B282" s="44" t="s">
         <v>1167</v>
       </c>
-      <c r="C282" s="86">
+      <c r="C282" s="83">
         <v>1500</v>
       </c>
       <c r="D282" s="44" t="s">
@@ -19150,13 +19162,13 @@
       </c>
     </row>
     <row r="283" spans="1:9" ht="14">
-      <c r="A283" s="87">
+      <c r="A283" s="84">
         <v>46221</v>
       </c>
       <c r="B283" s="45" t="s">
         <v>1171</v>
       </c>
-      <c r="C283" s="88">
+      <c r="C283" s="85">
         <v>1100</v>
       </c>
       <c r="D283" s="45" t="s">
@@ -19175,13 +19187,13 @@
       </c>
     </row>
     <row r="284" spans="1:9" ht="14">
-      <c r="A284" s="85">
+      <c r="A284" s="82">
         <v>46222</v>
       </c>
       <c r="B284" s="44" t="s">
         <v>1173</v>
       </c>
-      <c r="C284" s="86">
+      <c r="C284" s="83">
         <v>850</v>
       </c>
       <c r="D284" s="44" t="s">
@@ -19200,13 +19212,13 @@
       </c>
     </row>
     <row r="285" spans="1:9" ht="14">
-      <c r="A285" s="87">
+      <c r="A285" s="84">
         <v>46222</v>
       </c>
       <c r="B285" s="45" t="s">
         <v>1175</v>
       </c>
-      <c r="C285" s="88">
+      <c r="C285" s="85">
         <v>1250</v>
       </c>
       <c r="D285" s="45" t="s">
@@ -19225,13 +19237,13 @@
       </c>
     </row>
     <row r="286" spans="1:9" ht="14">
-      <c r="A286" s="85">
+      <c r="A286" s="82">
         <v>46222</v>
       </c>
       <c r="B286" s="44" t="s">
         <v>1178</v>
       </c>
-      <c r="C286" s="86">
+      <c r="C286" s="83">
         <v>700</v>
       </c>
       <c r="D286" s="44" t="s">
@@ -19250,13 +19262,13 @@
       </c>
     </row>
     <row r="287" spans="1:9" ht="14">
-      <c r="A287" s="87">
+      <c r="A287" s="84">
         <v>46222</v>
       </c>
       <c r="B287" s="45" t="s">
         <v>1179</v>
       </c>
-      <c r="C287" s="88">
+      <c r="C287" s="85">
         <v>699</v>
       </c>
       <c r="D287" s="45" t="s">
@@ -19275,13 +19287,13 @@
       </c>
     </row>
     <row r="288" spans="1:9" ht="14">
-      <c r="A288" s="85">
+      <c r="A288" s="82">
         <v>46223</v>
       </c>
       <c r="B288" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="C288" s="86">
+      <c r="C288" s="83">
         <v>1380</v>
       </c>
       <c r="D288" s="44" t="s">
@@ -19300,13 +19312,13 @@
       </c>
     </row>
     <row r="289" spans="1:9" ht="14">
-      <c r="A289" s="87">
+      <c r="A289" s="84">
         <v>46224</v>
       </c>
       <c r="B289" s="45" t="s">
         <v>1185</v>
       </c>
-      <c r="C289" s="88">
+      <c r="C289" s="85">
         <v>1380</v>
       </c>
       <c r="D289" s="45" t="s">
@@ -19325,13 +19337,13 @@
       </c>
     </row>
     <row r="290" spans="1:9" ht="14">
-      <c r="A290" s="85">
+      <c r="A290" s="82">
         <v>46224</v>
       </c>
       <c r="B290" s="44" t="s">
         <v>1184</v>
       </c>
-      <c r="C290" s="86">
+      <c r="C290" s="83">
         <v>1380</v>
       </c>
       <c r="D290" s="44" t="s">
@@ -19350,13 +19362,13 @@
       </c>
     </row>
     <row r="291" spans="1:9" ht="14">
-      <c r="A291" s="85">
+      <c r="A291" s="82">
         <v>46228</v>
       </c>
       <c r="B291" s="44" t="s">
         <v>186</v>
       </c>
-      <c r="C291" s="86">
+      <c r="C291" s="83">
         <v>1250</v>
       </c>
       <c r="D291" s="44" t="s">
@@ -19375,13 +19387,13 @@
       </c>
     </row>
     <row r="292" spans="1:9" ht="42">
-      <c r="A292" s="87">
+      <c r="A292" s="84">
         <v>46229</v>
       </c>
       <c r="B292" s="45" t="s">
         <v>1195</v>
       </c>
-      <c r="C292" s="88">
+      <c r="C292" s="85">
         <v>1900</v>
       </c>
       <c r="D292" s="45"/>
@@ -19389,20 +19401,20 @@
       <c r="F292" s="46"/>
       <c r="G292" s="46"/>
       <c r="H292" s="46" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="I292" s="45" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="293" spans="1:9" ht="28">
-      <c r="A293" s="85">
+      <c r="A293" s="82">
         <v>46229</v>
       </c>
       <c r="B293" s="44" t="s">
         <v>293</v>
       </c>
-      <c r="C293" s="86">
+      <c r="C293" s="83">
         <v>3000</v>
       </c>
       <c r="D293" s="44"/>
@@ -19410,20 +19422,20 @@
       <c r="F293" s="44"/>
       <c r="G293" s="44"/>
       <c r="H293" s="44" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="I293" s="44" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="294" spans="1:9" ht="28">
-      <c r="A294" s="87">
+      <c r="A294" s="84">
         <v>46229</v>
       </c>
       <c r="B294" s="45" t="s">
         <v>1109</v>
       </c>
-      <c r="C294" s="88">
+      <c r="C294" s="85">
         <v>3250</v>
       </c>
       <c r="D294" s="45"/>
@@ -19438,13 +19450,13 @@
       </c>
     </row>
     <row r="295" spans="1:9" ht="14">
-      <c r="A295" s="85">
+      <c r="A295" s="82">
         <v>46229</v>
       </c>
       <c r="B295" s="44" t="s">
         <v>1207</v>
       </c>
-      <c r="C295" s="86">
+      <c r="C295" s="83">
         <v>1550</v>
       </c>
       <c r="D295" s="44"/>
@@ -19459,13 +19471,13 @@
       </c>
     </row>
     <row r="296" spans="1:9" ht="14">
-      <c r="A296" s="87">
+      <c r="A296" s="84">
         <v>46235</v>
       </c>
       <c r="B296" s="45" t="s">
-        <v>1262</v>
-      </c>
-      <c r="C296" s="88">
+        <v>1260</v>
+      </c>
+      <c r="C296" s="85">
         <v>1450</v>
       </c>
       <c r="D296" s="45" t="s">
@@ -19477,20 +19489,20 @@
       <c r="F296" s="46"/>
       <c r="G296" s="46"/>
       <c r="H296" s="46" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="I296" s="45" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="297" spans="1:9" ht="28">
-      <c r="A297" s="85">
+      <c r="A297" s="82">
         <v>46236</v>
       </c>
       <c r="B297" s="44" t="s">
-        <v>1259</v>
-      </c>
-      <c r="C297" s="86">
+        <v>1257</v>
+      </c>
+      <c r="C297" s="83">
         <v>6900</v>
       </c>
       <c r="D297" s="44" t="s">
@@ -19502,20 +19514,20 @@
       <c r="F297" s="44"/>
       <c r="G297" s="44"/>
       <c r="H297" s="44" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="I297" s="44" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="298" spans="1:9" ht="14">
-      <c r="A298" s="87">
+      <c r="A298" s="84">
         <v>46236</v>
       </c>
       <c r="B298" s="45" t="s">
-        <v>1265</v>
-      </c>
-      <c r="C298" s="88">
+        <v>1263</v>
+      </c>
+      <c r="C298" s="85">
         <v>1479</v>
       </c>
       <c r="D298" s="45" t="s">
@@ -19527,27 +19539,37 @@
       <c r="F298" s="46"/>
       <c r="G298" s="46"/>
       <c r="H298" s="46" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="I298" s="45" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="299" spans="1:9">
-      <c r="A299" s="85"/>
+    <row r="299" spans="1:9" ht="14">
+      <c r="A299" s="82"/>
       <c r="B299" s="44"/>
-      <c r="C299" s="86"/>
-      <c r="D299" s="44"/>
-      <c r="E299" s="44"/>
+      <c r="C299" s="83">
+        <v>2630</v>
+      </c>
+      <c r="D299" s="44" t="s">
+        <v>162</v>
+      </c>
+      <c r="E299" s="44" t="s">
+        <v>1267</v>
+      </c>
       <c r="F299" s="44"/>
       <c r="G299" s="44"/>
-      <c r="H299" s="44"/>
-      <c r="I299" s="44"/>
+      <c r="H299" s="44" t="s">
+        <v>1266</v>
+      </c>
+      <c r="I299" s="44" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="300" spans="1:9">
-      <c r="A300" s="87"/>
+      <c r="A300" s="84"/>
       <c r="B300" s="45"/>
-      <c r="C300" s="88"/>
+      <c r="C300" s="85"/>
       <c r="D300" s="45"/>
       <c r="E300" s="45"/>
       <c r="F300" s="46"/>
@@ -19556,9 +19578,9 @@
       <c r="I300" s="45"/>
     </row>
     <row r="301" spans="1:9">
-      <c r="A301" s="85"/>
+      <c r="A301" s="82"/>
       <c r="B301" s="44"/>
-      <c r="C301" s="86"/>
+      <c r="C301" s="83"/>
       <c r="D301" s="44"/>
       <c r="E301" s="44"/>
       <c r="F301" s="44"/>
@@ -19567,9 +19589,9 @@
       <c r="I301" s="44"/>
     </row>
     <row r="302" spans="1:9">
-      <c r="A302" s="87"/>
+      <c r="A302" s="84"/>
       <c r="B302" s="45"/>
-      <c r="C302" s="88"/>
+      <c r="C302" s="85"/>
       <c r="D302" s="45"/>
       <c r="E302" s="45"/>
       <c r="F302" s="46"/>
@@ -19578,9 +19600,9 @@
       <c r="I302" s="45"/>
     </row>
     <row r="303" spans="1:9">
-      <c r="A303" s="85"/>
+      <c r="A303" s="82"/>
       <c r="B303" s="44"/>
-      <c r="C303" s="86"/>
+      <c r="C303" s="83"/>
       <c r="D303" s="44"/>
       <c r="E303" s="44"/>
       <c r="F303" s="44"/>
@@ -19589,9 +19611,9 @@
       <c r="I303" s="44"/>
     </row>
     <row r="304" spans="1:9">
-      <c r="A304" s="87"/>
+      <c r="A304" s="84"/>
       <c r="B304" s="45"/>
-      <c r="C304" s="88"/>
+      <c r="C304" s="85"/>
       <c r="D304" s="45"/>
       <c r="E304" s="45"/>
       <c r="F304" s="46"/>
@@ -19600,9 +19622,9 @@
       <c r="I304" s="45"/>
     </row>
     <row r="305" spans="1:9">
-      <c r="A305" s="85"/>
+      <c r="A305" s="82"/>
       <c r="B305" s="44"/>
-      <c r="C305" s="86"/>
+      <c r="C305" s="83"/>
       <c r="D305" s="44"/>
       <c r="E305" s="44"/>
       <c r="F305" s="44"/>
@@ -19611,9 +19633,9 @@
       <c r="I305" s="44"/>
     </row>
     <row r="306" spans="1:9">
-      <c r="A306" s="87"/>
+      <c r="A306" s="84"/>
       <c r="B306" s="45"/>
-      <c r="C306" s="88"/>
+      <c r="C306" s="85"/>
       <c r="D306" s="45"/>
       <c r="E306" s="45"/>
       <c r="F306" s="46"/>
@@ -19622,9 +19644,9 @@
       <c r="I306" s="45"/>
     </row>
     <row r="307" spans="1:9">
-      <c r="A307" s="85"/>
+      <c r="A307" s="82"/>
       <c r="B307" s="44"/>
-      <c r="C307" s="86"/>
+      <c r="C307" s="83"/>
       <c r="D307" s="44"/>
       <c r="E307" s="44"/>
       <c r="F307" s="44"/>
@@ -19633,9 +19655,9 @@
       <c r="I307" s="44"/>
     </row>
     <row r="308" spans="1:9">
-      <c r="A308" s="87"/>
+      <c r="A308" s="84"/>
       <c r="B308" s="45"/>
-      <c r="C308" s="88"/>
+      <c r="C308" s="85"/>
       <c r="D308" s="45"/>
       <c r="E308" s="45"/>
       <c r="F308" s="46"/>
@@ -19644,9 +19666,9 @@
       <c r="I308" s="45"/>
     </row>
     <row r="309" spans="1:9">
-      <c r="A309" s="85"/>
+      <c r="A309" s="82"/>
       <c r="B309" s="44"/>
-      <c r="C309" s="86"/>
+      <c r="C309" s="83"/>
       <c r="D309" s="44"/>
       <c r="E309" s="44"/>
       <c r="F309" s="44"/>
@@ -19655,9 +19677,9 @@
       <c r="I309" s="44"/>
     </row>
     <row r="310" spans="1:9">
-      <c r="A310" s="87"/>
+      <c r="A310" s="84"/>
       <c r="B310" s="45"/>
-      <c r="C310" s="88"/>
+      <c r="C310" s="85"/>
       <c r="D310" s="45"/>
       <c r="E310" s="45"/>
       <c r="F310" s="46"/>
@@ -19666,9 +19688,9 @@
       <c r="I310" s="45"/>
     </row>
     <row r="311" spans="1:9">
-      <c r="A311" s="85"/>
+      <c r="A311" s="82"/>
       <c r="B311" s="44"/>
-      <c r="C311" s="86"/>
+      <c r="C311" s="83"/>
       <c r="D311" s="44"/>
       <c r="E311" s="44"/>
       <c r="F311" s="44"/>
@@ -19677,9 +19699,9 @@
       <c r="I311" s="44"/>
     </row>
     <row r="312" spans="1:9">
-      <c r="A312" s="87"/>
+      <c r="A312" s="84"/>
       <c r="B312" s="45"/>
-      <c r="C312" s="88"/>
+      <c r="C312" s="85"/>
       <c r="D312" s="45"/>
       <c r="E312" s="45"/>
       <c r="F312" s="46"/>
@@ -19688,9 +19710,9 @@
       <c r="I312" s="45"/>
     </row>
     <row r="313" spans="1:9">
-      <c r="A313" s="85"/>
+      <c r="A313" s="82"/>
       <c r="B313" s="44"/>
-      <c r="C313" s="86"/>
+      <c r="C313" s="83"/>
       <c r="D313" s="44"/>
       <c r="E313" s="44"/>
       <c r="F313" s="44"/>
@@ -19699,9 +19721,9 @@
       <c r="I313" s="44"/>
     </row>
     <row r="314" spans="1:9">
-      <c r="A314" s="87"/>
+      <c r="A314" s="84"/>
       <c r="B314" s="45"/>
-      <c r="C314" s="88"/>
+      <c r="C314" s="85"/>
       <c r="D314" s="45"/>
       <c r="E314" s="45"/>
       <c r="F314" s="46"/>
@@ -19710,9 +19732,9 @@
       <c r="I314" s="45"/>
     </row>
     <row r="315" spans="1:9">
-      <c r="A315" s="85"/>
+      <c r="A315" s="82"/>
       <c r="B315" s="44"/>
-      <c r="C315" s="86"/>
+      <c r="C315" s="83"/>
       <c r="D315" s="44"/>
       <c r="E315" s="44"/>
       <c r="F315" s="44"/>
@@ -19721,9 +19743,9 @@
       <c r="I315" s="44"/>
     </row>
     <row r="316" spans="1:9">
-      <c r="A316" s="87"/>
+      <c r="A316" s="84"/>
       <c r="B316" s="45"/>
-      <c r="C316" s="88"/>
+      <c r="C316" s="85"/>
       <c r="D316" s="45"/>
       <c r="E316" s="45"/>
       <c r="F316" s="46"/>
@@ -19732,9 +19754,9 @@
       <c r="I316" s="45"/>
     </row>
     <row r="317" spans="1:9">
-      <c r="A317" s="85"/>
+      <c r="A317" s="82"/>
       <c r="B317" s="44"/>
-      <c r="C317" s="86"/>
+      <c r="C317" s="83"/>
       <c r="D317" s="44"/>
       <c r="E317" s="44"/>
       <c r="F317" s="44"/>
@@ -19743,9 +19765,9 @@
       <c r="I317" s="44"/>
     </row>
     <row r="318" spans="1:9">
-      <c r="A318" s="87"/>
+      <c r="A318" s="84"/>
       <c r="B318" s="45"/>
-      <c r="C318" s="88"/>
+      <c r="C318" s="85"/>
       <c r="D318" s="45"/>
       <c r="E318" s="45"/>
       <c r="F318" s="46"/>
@@ -19754,9 +19776,9 @@
       <c r="I318" s="45"/>
     </row>
     <row r="319" spans="1:9">
-      <c r="A319" s="85"/>
+      <c r="A319" s="82"/>
       <c r="B319" s="44"/>
-      <c r="C319" s="86"/>
+      <c r="C319" s="83"/>
       <c r="D319" s="44"/>
       <c r="E319" s="44"/>
       <c r="F319" s="44"/>
@@ -19765,9 +19787,9 @@
       <c r="I319" s="44"/>
     </row>
     <row r="320" spans="1:9">
-      <c r="A320" s="87"/>
+      <c r="A320" s="84"/>
       <c r="B320" s="45"/>
-      <c r="C320" s="88"/>
+      <c r="C320" s="85"/>
       <c r="D320" s="45"/>
       <c r="E320" s="45"/>
       <c r="F320" s="46"/>
@@ -19776,9 +19798,9 @@
       <c r="I320" s="45"/>
     </row>
     <row r="321" spans="1:9">
-      <c r="A321" s="85"/>
+      <c r="A321" s="82"/>
       <c r="B321" s="44"/>
-      <c r="C321" s="86"/>
+      <c r="C321" s="83"/>
       <c r="D321" s="44"/>
       <c r="E321" s="44"/>
       <c r="F321" s="44"/>
@@ -19787,9 +19809,9 @@
       <c r="I321" s="44"/>
     </row>
     <row r="322" spans="1:9">
-      <c r="A322" s="87"/>
+      <c r="A322" s="84"/>
       <c r="B322" s="45"/>
-      <c r="C322" s="88"/>
+      <c r="C322" s="85"/>
       <c r="D322" s="45"/>
       <c r="E322" s="45"/>
       <c r="F322" s="46"/>
@@ -19798,9 +19820,9 @@
       <c r="I322" s="45"/>
     </row>
     <row r="323" spans="1:9">
-      <c r="A323" s="85"/>
+      <c r="A323" s="82"/>
       <c r="B323" s="44"/>
-      <c r="C323" s="86"/>
+      <c r="C323" s="83"/>
       <c r="D323" s="44"/>
       <c r="E323" s="44"/>
       <c r="F323" s="44"/>
@@ -19809,9 +19831,9 @@
       <c r="I323" s="44"/>
     </row>
     <row r="324" spans="1:9">
-      <c r="A324" s="87"/>
+      <c r="A324" s="84"/>
       <c r="B324" s="45"/>
-      <c r="C324" s="88"/>
+      <c r="C324" s="85"/>
       <c r="D324" s="45"/>
       <c r="E324" s="45"/>
       <c r="F324" s="46"/>
@@ -19820,9 +19842,9 @@
       <c r="I324" s="45"/>
     </row>
     <row r="325" spans="1:9">
-      <c r="A325" s="85"/>
+      <c r="A325" s="82"/>
       <c r="B325" s="44"/>
-      <c r="C325" s="86"/>
+      <c r="C325" s="83"/>
       <c r="D325" s="44"/>
       <c r="E325" s="44"/>
       <c r="F325" s="44"/>
@@ -19831,9 +19853,9 @@
       <c r="I325" s="44"/>
     </row>
     <row r="326" spans="1:9">
-      <c r="A326" s="87"/>
+      <c r="A326" s="84"/>
       <c r="B326" s="45"/>
-      <c r="C326" s="88"/>
+      <c r="C326" s="85"/>
       <c r="D326" s="45"/>
       <c r="E326" s="45"/>
       <c r="F326" s="46"/>
@@ -19842,9 +19864,9 @@
       <c r="I326" s="45"/>
     </row>
     <row r="327" spans="1:9">
-      <c r="A327" s="85"/>
+      <c r="A327" s="82"/>
       <c r="B327" s="44"/>
-      <c r="C327" s="86"/>
+      <c r="C327" s="83"/>
       <c r="D327" s="44"/>
       <c r="E327" s="44"/>
       <c r="F327" s="44"/>
@@ -19853,9 +19875,9 @@
       <c r="I327" s="44"/>
     </row>
     <row r="328" spans="1:9">
-      <c r="A328" s="87"/>
+      <c r="A328" s="84"/>
       <c r="B328" s="45"/>
-      <c r="C328" s="88"/>
+      <c r="C328" s="85"/>
       <c r="D328" s="45"/>
       <c r="E328" s="45"/>
       <c r="F328" s="46"/>
@@ -19864,9 +19886,9 @@
       <c r="I328" s="45"/>
     </row>
     <row r="329" spans="1:9">
-      <c r="A329" s="85"/>
+      <c r="A329" s="82"/>
       <c r="B329" s="44"/>
-      <c r="C329" s="86"/>
+      <c r="C329" s="83"/>
       <c r="D329" s="44"/>
       <c r="E329" s="44"/>
       <c r="F329" s="44"/>
@@ -29487,7 +29509,7 @@
         <v>504</v>
       </c>
       <c r="O115" s="55"/>
-      <c r="P115" s="82"/>
+      <c r="P115" s="79"/>
       <c r="Q115" s="55"/>
       <c r="R115" s="55"/>
       <c r="S115" s="55"/>
@@ -35208,7 +35230,7 @@
         <v>23179</v>
       </c>
       <c r="L212" s="52" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="M212" s="52"/>
       <c r="N212" s="47" t="s">
@@ -35356,7 +35378,7 @@
         <v>2976</v>
       </c>
       <c r="L215" s="55" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="M215" s="55"/>
       <c r="N215" s="47" t="s">
@@ -35570,7 +35592,7 @@
       <c r="S219" s="47"/>
       <c r="T219" s="47"/>
     </row>
-    <row r="220" spans="1:20" ht="30">
+    <row r="220" spans="1:20" ht="15">
       <c r="A220" s="52" t="s">
         <v>1043</v>
       </c>
@@ -35713,7 +35735,7 @@
       <c r="N222" s="47" t="s">
         <v>678</v>
       </c>
-      <c r="P222" s="89" t="s">
+      <c r="P222" s="86" t="s">
         <v>1238</v>
       </c>
       <c r="S222" s="47"/>
@@ -35762,7 +35784,7 @@
       <c r="N223" s="47" t="s">
         <v>678</v>
       </c>
-      <c r="P223" s="89" t="s">
+      <c r="P223" s="86" t="s">
         <v>1239</v>
       </c>
       <c r="S223" s="47"/>
@@ -35785,10 +35807,10 @@
         <v>1380</v>
       </c>
       <c r="F224" s="66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G224" s="66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H224" s="65">
         <f t="shared" si="12"/>
@@ -35800,19 +35822,21 @@
       </c>
       <c r="J224" s="65">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>942</v>
       </c>
       <c r="K224" s="65">
         <f t="shared" si="14"/>
-        <v>2826</v>
-      </c>
-      <c r="L224" s="52"/>
+        <v>1884</v>
+      </c>
+      <c r="L224" s="52" t="s">
+        <v>1264</v>
+      </c>
       <c r="M224" s="52"/>
       <c r="N224" s="47" t="s">
-        <v>678</v>
-      </c>
-      <c r="P224" s="89" t="s">
-        <v>1240</v>
+        <v>589</v>
+      </c>
+      <c r="P224" s="86" t="s">
+        <v>1265</v>
       </c>
       <c r="S224" s="47"/>
       <c r="T224" s="47"/>
@@ -35860,8 +35884,8 @@
       <c r="N225" s="47" t="s">
         <v>678</v>
       </c>
-      <c r="P225" s="89" t="s">
-        <v>1241</v>
+      <c r="P225" s="86" t="s">
+        <v>1240</v>
       </c>
       <c r="S225" s="47"/>
       <c r="T225" s="47"/>
@@ -35909,8 +35933,8 @@
       <c r="N226" s="47" t="s">
         <v>678</v>
       </c>
-      <c r="P226" s="89" t="s">
-        <v>1242</v>
+      <c r="P226" s="86" t="s">
+        <v>1241</v>
       </c>
       <c r="S226" s="47"/>
       <c r="T226" s="47"/>
@@ -35958,8 +35982,8 @@
       <c r="N227" s="47" t="s">
         <v>678</v>
       </c>
-      <c r="P227" s="89" t="s">
-        <v>1243</v>
+      <c r="P227" s="86" t="s">
+        <v>1242</v>
       </c>
       <c r="S227" s="47"/>
       <c r="T227" s="47"/>
@@ -36007,8 +36031,8 @@
       <c r="N228" s="47" t="s">
         <v>678</v>
       </c>
-      <c r="P228" s="89" t="s">
-        <v>1244</v>
+      <c r="P228" s="86" t="s">
+        <v>1243</v>
       </c>
       <c r="S228" s="47"/>
       <c r="T228" s="47"/>
@@ -36056,8 +36080,8 @@
       <c r="N229" s="47" t="s">
         <v>678</v>
       </c>
-      <c r="P229" s="89" t="s">
-        <v>1245</v>
+      <c r="P229" s="86" t="s">
+        <v>1244</v>
       </c>
       <c r="S229" s="47"/>
       <c r="T229" s="47"/>
@@ -36079,10 +36103,10 @@
         <v>1250</v>
       </c>
       <c r="F230" s="66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G230" s="66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H230" s="65">
         <f t="shared" si="15"/>
@@ -36094,19 +36118,21 @@
       </c>
       <c r="J230" s="65">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>782</v>
       </c>
       <c r="K230" s="65">
         <f t="shared" si="17"/>
-        <v>2346</v>
-      </c>
-      <c r="L230" s="52"/>
+        <v>1564</v>
+      </c>
+      <c r="L230" s="52" t="s">
+        <v>1269</v>
+      </c>
       <c r="M230" s="52"/>
       <c r="N230" s="47" t="s">
-        <v>678</v>
-      </c>
-      <c r="P230" s="89" t="s">
-        <v>1246</v>
+        <v>589</v>
+      </c>
+      <c r="P230" s="86" t="s">
+        <v>1268</v>
       </c>
       <c r="S230" s="47"/>
       <c r="T230" s="47"/>
@@ -36154,8 +36180,8 @@
       <c r="N231" s="47" t="s">
         <v>678</v>
       </c>
-      <c r="P231" s="89" t="s">
-        <v>1247</v>
+      <c r="P231" s="86" t="s">
+        <v>1245</v>
       </c>
       <c r="S231" s="47"/>
       <c r="T231" s="47"/>
@@ -36203,7 +36229,7 @@
       <c r="N232" s="47" t="s">
         <v>678</v>
       </c>
-      <c r="P232" s="89" t="s">
+      <c r="P232" s="86" t="s">
         <v>1191</v>
       </c>
       <c r="S232" s="47"/>
@@ -36248,14 +36274,14 @@
         <v>0</v>
       </c>
       <c r="L233" s="55" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="M233" s="55"/>
       <c r="N233" s="47" t="s">
         <v>504</v>
       </c>
-      <c r="P233" s="89" t="s">
-        <v>1248</v>
+      <c r="P233" s="86" t="s">
+        <v>1246</v>
       </c>
       <c r="S233" s="47"/>
       <c r="T233" s="47"/>
@@ -36303,8 +36329,8 @@
       <c r="N234" s="47" t="s">
         <v>678</v>
       </c>
-      <c r="P234" s="89" t="s">
-        <v>1249</v>
+      <c r="P234" s="86" t="s">
+        <v>1247</v>
       </c>
       <c r="S234" s="47"/>
       <c r="T234" s="47"/>
@@ -36352,8 +36378,8 @@
       <c r="N235" s="47" t="s">
         <v>678</v>
       </c>
-      <c r="P235" s="89" t="s">
-        <v>1250</v>
+      <c r="P235" s="86" t="s">
+        <v>1248</v>
       </c>
       <c r="S235" s="47"/>
       <c r="T235" s="47"/>
@@ -36401,8 +36427,8 @@
       <c r="N236" s="47" t="s">
         <v>678</v>
       </c>
-      <c r="P236" s="89" t="s">
-        <v>1251</v>
+      <c r="P236" s="86" t="s">
+        <v>1249</v>
       </c>
       <c r="S236" s="47"/>
       <c r="T236" s="47"/>
@@ -36450,8 +36476,8 @@
       <c r="N237" s="47" t="s">
         <v>678</v>
       </c>
-      <c r="P237" s="89" t="s">
-        <v>1252</v>
+      <c r="P237" s="86" t="s">
+        <v>1250</v>
       </c>
       <c r="S237" s="47"/>
       <c r="T237" s="47"/>
@@ -36499,8 +36525,8 @@
       <c r="N238" s="47" t="s">
         <v>678</v>
       </c>
-      <c r="P238" s="89" t="s">
-        <v>1253</v>
+      <c r="P238" s="86" t="s">
+        <v>1251</v>
       </c>
       <c r="S238" s="47"/>
       <c r="T238" s="47"/>
@@ -40353,10 +40379,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" customHeight="1">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="88" t="s">
         <v>1050</v>
       </c>
-      <c r="B1" s="80"/>
+      <c r="B1" s="88"/>
     </row>
     <row r="2" spans="1:8" ht="13.5" customHeight="1">
       <c r="A2" s="8" t="s">
@@ -40516,14 +40542,14 @@
       </c>
     </row>
     <row r="12" spans="1:8" s="75" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A12" s="81" t="s">
+      <c r="A12" s="89" t="s">
         <v>1059</v>
       </c>
-      <c r="B12" s="81"/>
-      <c r="C12" s="81"/>
-      <c r="D12" s="81"/>
-      <c r="E12" s="81"/>
-      <c r="F12" s="81"/>
+      <c r="B12" s="89"/>
+      <c r="C12" s="89"/>
+      <c r="D12" s="89"/>
+      <c r="E12" s="89"/>
+      <c r="F12" s="89"/>
     </row>
     <row r="13" spans="1:8" s="72" customFormat="1" ht="13.5" customHeight="1">
       <c r="A13" s="71" t="s">
@@ -40937,11 +40963,11 @@
       </c>
       <c r="D4" s="9">
         <f>Summary!$B$4*C4</f>
-        <v>161129.88619999998</v>
+        <v>162006.72819999998</v>
       </c>
       <c r="E4" s="9">
         <f>B4-D4</f>
-        <v>255009.11380000002</v>
+        <v>254132.27180000002</v>
       </c>
       <c r="F4" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -40949,7 +40975,7 @@
       </c>
       <c r="G4" s="73">
         <f>E4+F4</f>
-        <v>117699.08780000001</v>
+        <v>116822.2458</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5" customHeight="1">
@@ -40966,11 +40992,11 @@
       </c>
       <c r="D5" s="11">
         <f>Summary!$B$4*C5</f>
-        <v>161033.22759999998</v>
+        <v>161909.5436</v>
       </c>
       <c r="E5" s="11">
         <f>B5-D5</f>
-        <v>-106409.22759999998</v>
+        <v>-107285.5436</v>
       </c>
       <c r="F5" s="11">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -40978,7 +41004,7 @@
       </c>
       <c r="G5" s="74">
         <f>E5+F5</f>
-        <v>-34822.185599999983</v>
+        <v>-35698.501600000003</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1">
@@ -40995,11 +41021,11 @@
       </c>
       <c r="D6" s="9">
         <f>Summary!$B$4*C6</f>
-        <v>161129.88619999998</v>
+        <v>162006.72819999998</v>
       </c>
       <c r="E6" s="9">
         <f>B6-D6</f>
-        <v>-148599.88619999998</v>
+        <v>-149476.72819999998</v>
       </c>
       <c r="F6" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -41007,7 +41033,7 @@
       </c>
       <c r="G6" s="73">
         <f>E6+F6</f>
-        <v>-82876.902199999968</v>
+        <v>-83753.744199999972</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="13.5" customHeight="1">

--- a/docs/Chiraath-Summary-Aug26.xlsx
+++ b/docs/Chiraath-Summary-Aug26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anooppremachandran/Desktop/CHIRAATH/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA8A2D1C-869A-5A48-BE38-6581203DE227}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88CB7011-580A-8F42-9B00-0A7BBA060129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">INVENTORY!$A$1:$T$188</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Purchases!$A$1:$D$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Sales!$A$1:$I$296</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Sales!$A$1:$I$301</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3197" uniqueCount="1270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3211" uniqueCount="1272">
   <si>
     <t>Notes:</t>
   </si>
@@ -3466,9 +3466,6 @@
     <t>CHR-87 Red Salwar with Elephant print, CHR-58 Wine Red Salwar (1000 advance, 1350 balance)</t>
   </si>
   <si>
-    <t>Renju, Jisha bank</t>
-  </si>
-  <si>
     <t>Urmila</t>
   </si>
   <si>
@@ -3491,9 +3488,6 @@
   </si>
   <si>
     <t>Gincy Jibi</t>
-  </si>
-  <si>
-    <t>Sheeba George, Soji Thomas, Jessy Joseph, Jeeja Anil ,Sanam, Geetha, Sushama Bhaskar, Divya Jacob, Baby Johny, Jayasree, Navya, Bindu Saji, Vanajakshi, Dison Jose, Akshitha, Bahuleyan, Urmila, Gincy Jibi, Razia Salim</t>
   </si>
   <si>
     <t>Green/maroon - Rajitha Teacher,  chikku green - Razia Salim, Rust Orange/Coffee Brown - Nishida, Chikku Maroon(1200) - Nishida, Komalavalli - Red/green, peacock blue/navy - returned, mustard/blue - girija(1200)</t>
@@ -3678,9 +3672,6 @@
     <t>CHR-111 white cotton salwar, Banarasi golden yellow blue</t>
   </si>
   <si>
-    <t>CHR-212 - Red, CHR-214 - Yellow/Blue Chanderi Silk, CHR-95 Chinon Silk</t>
-  </si>
-  <si>
     <t>Teena mathew - Paeach</t>
   </si>
   <si>
@@ -3843,9 +3834,6 @@
     <t>Parrot Green Banarasi - 6 pieces from bulk</t>
   </si>
   <si>
-    <t>1250 X 6</t>
-  </si>
-  <si>
     <t>Asha Sandran</t>
   </si>
   <si>
@@ -3861,19 +3849,37 @@
     <t>Prabha Chidambaram - Purple/Green</t>
   </si>
   <si>
-    <t>Maroon/Mustard, Green/Coffee Brown</t>
-  </si>
-  <si>
     <t>CHR-223 - Purple/Green, CHR-229 - Black</t>
   </si>
   <si>
-    <t>Rajan</t>
-  </si>
-  <si>
     <t>Blue, Wine</t>
   </si>
   <si>
     <t>Prabha Chidambaram - Green</t>
+  </si>
+  <si>
+    <t>Green/Coffee Brown</t>
+  </si>
+  <si>
+    <t>Prabha Chithambaram</t>
+  </si>
+  <si>
+    <t>Sheeba George, Soji Thomas, Jessy Joseph, Jeeja Anil ,Sanam, Geetha, Sushama Bhaskar, Divya Jacob, Baby Johny, Jayasree, Navya, Bindu Saji, Vanajakshi, Dison Jose, Akshitha, Bahuleyan, Urmila, Gincy Jibi, Razia Salim, Komalavalli</t>
+  </si>
+  <si>
+    <t>Asha Sharath (Haritha Karma Sena Bulk - 11 pieces)</t>
+  </si>
+  <si>
+    <t>Parrot Green Banarasi - 11 pieces from bulk</t>
+  </si>
+  <si>
+    <t>1250 X 6, 1250 X 11</t>
+  </si>
+  <si>
+    <t>Renju</t>
+  </si>
+  <si>
+    <t>CHR-212 - Red, CHR-214 - Yellow/Blue Chanderi Silk - 1380 advance for the returned saree, 920 pending</t>
   </si>
 </sst>
 </file>
@@ -4759,7 +4765,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>307</c:v>
+                  <c:v>317</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>96</c:v>
@@ -4862,7 +4868,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>216</c:v>
+                  <c:v>204</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>54</c:v>
@@ -5195,7 +5201,7 @@
                   <c:v>57128</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>160465.19666666666</c:v>
+                  <c:v>150163.43666666665</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>1062</c:v>
@@ -5531,7 +5537,7 @@
                   <c:v>102200</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>9387</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -5688,10 +5694,10 @@
                   <c:v>72885</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>62696</c:v>
+                  <c:v>61746</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>9829</c:v>
+                  <c:v>26489</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -6128,10 +6134,10 @@
                   <c:v>-26158</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-39504</c:v>
+                  <c:v>-40454</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>9829</c:v>
+                  <c:v>17102</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -6592,10 +6598,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>408</c:v>
+                  <c:v>418</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>273</c:v>
+                  <c:v>261</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7767,7 +7773,7 @@
       </c>
       <c r="B3" s="8">
         <f>SUM(Purchases!C:C)</f>
-        <v>556347</v>
+        <v>565734</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>42</v>
@@ -7782,7 +7788,7 @@
       </c>
       <c r="B4" s="10">
         <f>SUMIFS(Sales!C:C, Sales!I:I, "Completed")</f>
-        <v>485923</v>
+        <v>499953</v>
       </c>
       <c r="E4" s="9" t="str">
         <f>PartnerShares!A3</f>
@@ -7799,7 +7805,7 @@
       </c>
       <c r="B5" s="12">
         <f>SUM(Sales!C:C)</f>
-        <v>503653</v>
+        <v>516733</v>
       </c>
       <c r="E5" s="11" t="str">
         <f>PartnerShares!A4</f>
@@ -7816,7 +7822,7 @@
       </c>
       <c r="B6" s="10">
         <f>B4-B3</f>
-        <v>-70424</v>
+        <v>-65781</v>
       </c>
       <c r="E6" s="9" t="str">
         <f>PartnerShares!A5</f>
@@ -7851,7 +7857,7 @@
       </c>
       <c r="B10" s="13">
         <f>PartnerShares!H8</f>
-        <v>48677.66</v>
+        <v>54935.66</v>
       </c>
       <c r="C10" s="9"/>
     </row>
@@ -7861,7 +7867,7 @@
       </c>
       <c r="B11" s="14">
         <f>PartnerShares!H9</f>
-        <v>44228.67</v>
+        <v>41099.67</v>
       </c>
       <c r="C11" s="11"/>
     </row>
@@ -7871,7 +7877,7 @@
       </c>
       <c r="B12" s="13">
         <f>PartnerShares!H10</f>
-        <v>-92906.33</v>
+        <v>-96035.33</v>
       </c>
       <c r="C12" s="9"/>
     </row>
@@ -7910,15 +7916,15 @@
       </c>
       <c r="B18" s="10">
         <f>PartnerShares!B8</f>
-        <v>252430</v>
+        <v>261817</v>
       </c>
       <c r="C18" s="10">
         <f>PartnerShares!C8</f>
-        <v>185449</v>
+        <v>188578</v>
       </c>
       <c r="D18" s="10">
         <f>PartnerShares!D8</f>
-        <v>66981</v>
+        <v>73239</v>
       </c>
       <c r="E18" s="10">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A18,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A18,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -7926,11 +7932,11 @@
       </c>
       <c r="F18" s="13">
         <f>D18-E18</f>
-        <v>48677.66</v>
+        <v>54935.66</v>
       </c>
       <c r="G18" s="16" t="str">
         <f>IF(ROUND(F18,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F18),"#,##0"),IF(ROUND(F18,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F18),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹48,678</v>
+        <v>Receive ₹54,936</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="13.5" customHeight="1">
@@ -7944,11 +7950,11 @@
       </c>
       <c r="C19" s="12">
         <f>PartnerShares!C9</f>
-        <v>185449</v>
+        <v>188578</v>
       </c>
       <c r="D19" s="12">
         <f>PartnerShares!D9</f>
-        <v>85868</v>
+        <v>82739</v>
       </c>
       <c r="E19" s="12">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A19,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A19,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -7956,11 +7962,11 @@
       </c>
       <c r="F19" s="14">
         <f>D19-E19</f>
-        <v>44228.67</v>
+        <v>41099.67</v>
       </c>
       <c r="G19" s="17" t="str">
         <f>IF(ROUND(F19,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F19),"#,##0"),IF(ROUND(F19,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F19),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹44,229</v>
+        <v>Receive ₹41,100</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="13.5" customHeight="1">
@@ -7974,11 +7980,11 @@
       </c>
       <c r="C20" s="10">
         <f>PartnerShares!C10</f>
-        <v>185449</v>
+        <v>188578</v>
       </c>
       <c r="D20" s="10">
         <f>PartnerShares!D10</f>
-        <v>-152849</v>
+        <v>-155978</v>
       </c>
       <c r="E20" s="10">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A20,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A20,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -7986,11 +7992,11 @@
       </c>
       <c r="F20" s="13">
         <f>D20-E20</f>
-        <v>-92906.33</v>
+        <v>-96035.33</v>
       </c>
       <c r="G20" s="17" t="str">
         <f>IF(ROUND(F20,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F20),"#,##0"),IF(ROUND(F20,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F20),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹92,906</v>
+        <v>Pay ₹96,035</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.75" customHeight="1">
@@ -8028,15 +8034,15 @@
       </c>
       <c r="B26" s="10">
         <f>'Cash Pool'!B4</f>
-        <v>416139</v>
+        <v>432799</v>
       </c>
       <c r="C26" s="10">
         <f>'Cash Pool'!D4</f>
-        <v>162006.72819999998</v>
+        <v>166684.3302</v>
       </c>
       <c r="D26" s="10">
         <f>'Cash Pool'!E4</f>
-        <v>254132.27180000002</v>
+        <v>266114.66980000003</v>
       </c>
       <c r="E26" s="10">
         <f>'Cash Pool'!F4</f>
@@ -8044,11 +8050,11 @@
       </c>
       <c r="F26" s="13">
         <f>'Cash Pool'!G4</f>
-        <v>116822.2458</v>
+        <v>128804.64380000002</v>
       </c>
       <c r="G26" s="17" t="str">
         <f>IF(ROUND(F26,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F26),"#,##0"),IF(ROUND(F26,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F26),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹116,822</v>
+        <v>Pay ₹128,805</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="13.5" customHeight="1">
@@ -8062,11 +8068,11 @@
       </c>
       <c r="C27" s="12">
         <f>'Cash Pool'!D5</f>
-        <v>161909.5436</v>
+        <v>166584.33960000001</v>
       </c>
       <c r="D27" s="12">
         <f>'Cash Pool'!E5</f>
-        <v>-107285.5436</v>
+        <v>-111960.33960000001</v>
       </c>
       <c r="E27" s="12">
         <f>'Cash Pool'!F5</f>
@@ -8074,11 +8080,11 @@
       </c>
       <c r="F27" s="14">
         <f>'Cash Pool'!G5</f>
-        <v>-35698.501600000003</v>
+        <v>-40373.297600000005</v>
       </c>
       <c r="G27" s="18" t="str">
         <f>IF(ROUND(F27,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F27),"#,##0"),IF(ROUND(F27,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F27),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹35,699</v>
+        <v>Receive ₹40,373</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="13.5" customHeight="1">
@@ -8092,11 +8098,11 @@
       </c>
       <c r="C28" s="10">
         <f>'Cash Pool'!D6</f>
-        <v>162006.72819999998</v>
+        <v>166684.3302</v>
       </c>
       <c r="D28" s="10">
         <f>'Cash Pool'!E6</f>
-        <v>-149476.72819999998</v>
+        <v>-154154.3302</v>
       </c>
       <c r="E28" s="10">
         <f>'Cash Pool'!F6</f>
@@ -8104,11 +8110,11 @@
       </c>
       <c r="F28" s="13">
         <f>'Cash Pool'!G6</f>
-        <v>-83753.744199999972</v>
+        <v>-88431.346199999985</v>
       </c>
       <c r="G28" s="16" t="str">
         <f>IF(ROUND(F28,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F28),"#,##0"),IF(ROUND(F28,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F28),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹83,754</v>
+        <v>Receive ₹88,431</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.75" customHeight="1">
@@ -8220,7 +8226,7 @@
       </c>
       <c r="B3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46236</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1">
@@ -8229,14 +8235,14 @@
       </c>
       <c r="B5" s="21">
         <f>Summary!B3</f>
-        <v>556347</v>
+        <v>565734</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>69</v>
       </c>
       <c r="E5" s="21">
         <f>Summary!B4</f>
-        <v>485923</v>
+        <v>499953</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
@@ -8245,14 +8251,14 @@
       </c>
       <c r="B6" s="21">
         <f>Summary!B6</f>
-        <v>-70424</v>
+        <v>-65781</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>71</v>
       </c>
       <c r="E6" s="21">
         <f>SUMIFS(INVENTORY!K:K, INVENTORY!N:N, "&lt;&gt;Sold Out")</f>
-        <v>209034.39666666667</v>
+        <v>197482.63666666666</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1">
@@ -8304,7 +8310,7 @@
       </c>
       <c r="G10" s="21">
         <f>SUM(INVENTORY!F:F)</f>
-        <v>408</v>
+        <v>418</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1">
@@ -8328,7 +8334,7 @@
       </c>
       <c r="G11" s="27">
         <f>SUM(INVENTORY!G:G)</f>
-        <v>273</v>
+        <v>261</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
@@ -8409,11 +8415,11 @@
       </c>
       <c r="C16" s="21">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$994,"MMM")=$A16)*(YEAR(Sales!$A$2:$A$994)=$B$7)*Sales!$C$2:$C$994),0)</f>
-        <v>62696</v>
+        <v>61746</v>
       </c>
       <c r="D16" s="21">
         <f t="shared" si="0"/>
-        <v>-39504</v>
+        <v>-40454</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1">
@@ -8422,15 +8428,15 @@
       </c>
       <c r="B17" s="27">
         <f>IFERROR(SUMPRODUCT((TEXT(Purchases!$A$2:$A$998,"MMM")=$A17)*(YEAR(Purchases!$A$2:$A$998)=$B$7)*Purchases!$C$2:$C$998),0)</f>
-        <v>0</v>
+        <v>9387</v>
       </c>
       <c r="C17" s="27">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$994,"MMM")=$A17)*(YEAR(Sales!$A$2:$A$994)=$B$7)*Sales!$C$2:$C$994),0)</f>
-        <v>9829</v>
+        <v>26489</v>
       </c>
       <c r="D17" s="27">
         <f t="shared" si="0"/>
-        <v>9829</v>
+        <v>17102</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1">
@@ -8524,11 +8530,11 @@
       </c>
       <c r="G47" s="30">
         <f>SUMIF(INVENTORY!C:C, F47, INVENTORY!F:F)</f>
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="H47" s="30">
         <f>SUMIF(INVENTORY!C:C, F47, INVENTORY!G:G)</f>
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="J47" s="30" t="s">
         <v>96</v>
@@ -8555,7 +8561,7 @@
       </c>
       <c r="K48" s="31">
         <f t="array" ref="K48">SUMPRODUCT((INVENTORY!$C$2:$C$477=J48)*(INVENTORY!$D$2:$D$477)*(INVENTORY!$G$2:$G$477))</f>
-        <v>160465.19666666666</v>
+        <v>150163.43666666665</v>
       </c>
     </row>
     <row r="49" spans="5:12" ht="15" customHeight="1">
@@ -9998,7 +10004,7 @@
         <v>70</v>
       </c>
       <c r="D96" s="36" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="15" customHeight="1">
@@ -10012,7 +10018,7 @@
         <v>1375</v>
       </c>
       <c r="D97" s="39" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="15" customHeight="1">
@@ -10026,7 +10032,7 @@
         <v>189</v>
       </c>
       <c r="D98" s="36" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="15" customHeight="1">
@@ -10114,16 +10120,32 @@
       </c>
     </row>
     <row r="105" spans="1:4" ht="15" customHeight="1">
-      <c r="A105" s="38"/>
-      <c r="B105" s="39"/>
-      <c r="C105" s="40"/>
-      <c r="D105" s="39"/>
+      <c r="A105" s="38">
+        <v>46238</v>
+      </c>
+      <c r="B105" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="C105" s="40">
+        <v>757</v>
+      </c>
+      <c r="D105" s="39" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="106" spans="1:4" ht="15" customHeight="1">
-      <c r="A106" s="35"/>
-      <c r="B106" s="36"/>
-      <c r="C106" s="37"/>
-      <c r="D106" s="36"/>
+      <c r="A106" s="35">
+        <v>46239</v>
+      </c>
+      <c r="B106" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="C106" s="37">
+        <v>8630</v>
+      </c>
+      <c r="D106" s="36" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="107" spans="1:4" ht="15" customHeight="1">
       <c r="A107" s="38"/>
@@ -12198,6 +12220,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:I329"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13"/>
   <cols>
@@ -12242,7 +12265,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="14">
+    <row r="2" spans="1:9" ht="14" hidden="1">
       <c r="A2" s="82">
         <v>45900</v>
       </c>
@@ -12265,7 +12288,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="14">
+    <row r="3" spans="1:9" ht="14" hidden="1">
       <c r="A3" s="84">
         <v>45900</v>
       </c>
@@ -12288,7 +12311,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="14">
+    <row r="4" spans="1:9" ht="14" hidden="1">
       <c r="A4" s="82">
         <v>45900</v>
       </c>
@@ -12311,7 +12334,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="14">
+    <row r="5" spans="1:9" ht="14" hidden="1">
       <c r="A5" s="84">
         <v>45900</v>
       </c>
@@ -12334,7 +12357,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="14">
+    <row r="6" spans="1:9" ht="14" hidden="1">
       <c r="A6" s="82">
         <v>45900</v>
       </c>
@@ -12357,7 +12380,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="14">
+    <row r="7" spans="1:9" ht="14" hidden="1">
       <c r="A7" s="84">
         <v>45900</v>
       </c>
@@ -12380,7 +12403,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="14">
+    <row r="8" spans="1:9" ht="14" hidden="1">
       <c r="A8" s="82">
         <v>45900</v>
       </c>
@@ -12403,7 +12426,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="14">
+    <row r="9" spans="1:9" ht="14" hidden="1">
       <c r="A9" s="84">
         <v>45901</v>
       </c>
@@ -12426,7 +12449,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="14">
+    <row r="10" spans="1:9" ht="14" hidden="1">
       <c r="A10" s="82">
         <v>45902</v>
       </c>
@@ -12449,7 +12472,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="14">
+    <row r="11" spans="1:9" ht="14" hidden="1">
       <c r="A11" s="84">
         <v>45903</v>
       </c>
@@ -12472,7 +12495,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="14">
+    <row r="12" spans="1:9" ht="14" hidden="1">
       <c r="A12" s="82">
         <v>45904</v>
       </c>
@@ -12495,7 +12518,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="14">
+    <row r="13" spans="1:9" ht="14" hidden="1">
       <c r="A13" s="84">
         <v>45905</v>
       </c>
@@ -12518,7 +12541,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="14">
+    <row r="14" spans="1:9" ht="14" hidden="1">
       <c r="A14" s="82">
         <v>45906</v>
       </c>
@@ -12541,7 +12564,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="14">
+    <row r="15" spans="1:9" ht="14" hidden="1">
       <c r="A15" s="84">
         <v>45907</v>
       </c>
@@ -12564,7 +12587,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="14">
+    <row r="16" spans="1:9" ht="14" hidden="1">
       <c r="A16" s="82">
         <v>45908</v>
       </c>
@@ -12587,7 +12610,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="14">
+    <row r="17" spans="1:9" ht="14" hidden="1">
       <c r="A17" s="84">
         <v>45909</v>
       </c>
@@ -12610,7 +12633,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="14">
+    <row r="18" spans="1:9" ht="14" hidden="1">
       <c r="A18" s="82">
         <v>45910</v>
       </c>
@@ -12633,7 +12656,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="14">
+    <row r="19" spans="1:9" ht="14" hidden="1">
       <c r="A19" s="84">
         <v>45911</v>
       </c>
@@ -12656,7 +12679,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="14">
+    <row r="20" spans="1:9" ht="14" hidden="1">
       <c r="A20" s="82">
         <v>45912</v>
       </c>
@@ -12679,7 +12702,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="14">
+    <row r="21" spans="1:9" ht="14" hidden="1">
       <c r="A21" s="84">
         <v>45913</v>
       </c>
@@ -12702,7 +12725,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="14">
+    <row r="22" spans="1:9" ht="14" hidden="1">
       <c r="A22" s="82">
         <v>45914</v>
       </c>
@@ -12725,7 +12748,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="14">
+    <row r="23" spans="1:9" ht="14" hidden="1">
       <c r="A23" s="84">
         <v>45915</v>
       </c>
@@ -12748,7 +12771,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="14">
+    <row r="24" spans="1:9" ht="14" hidden="1">
       <c r="A24" s="82">
         <v>45916</v>
       </c>
@@ -12771,7 +12794,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="14">
+    <row r="25" spans="1:9" ht="14" hidden="1">
       <c r="A25" s="84">
         <v>45917</v>
       </c>
@@ -12794,7 +12817,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="14">
+    <row r="26" spans="1:9" ht="14" hidden="1">
       <c r="A26" s="82">
         <v>45917</v>
       </c>
@@ -12817,7 +12840,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="14">
+    <row r="27" spans="1:9" ht="14" hidden="1">
       <c r="A27" s="84">
         <v>45918</v>
       </c>
@@ -12840,7 +12863,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="14">
+    <row r="28" spans="1:9" ht="14" hidden="1">
       <c r="A28" s="82">
         <v>45919</v>
       </c>
@@ -12863,7 +12886,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="14">
+    <row r="29" spans="1:9" ht="14" hidden="1">
       <c r="A29" s="84">
         <v>45920</v>
       </c>
@@ -12886,7 +12909,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="14">
+    <row r="30" spans="1:9" ht="14" hidden="1">
       <c r="A30" s="82">
         <v>45921</v>
       </c>
@@ -12909,7 +12932,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="14">
+    <row r="31" spans="1:9" ht="14" hidden="1">
       <c r="A31" s="84">
         <v>45922</v>
       </c>
@@ -12932,7 +12955,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="14">
+    <row r="32" spans="1:9" ht="14" hidden="1">
       <c r="A32" s="82">
         <v>45924</v>
       </c>
@@ -12955,7 +12978,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="14">
+    <row r="33" spans="1:9" ht="14" hidden="1">
       <c r="A33" s="84">
         <v>45924</v>
       </c>
@@ -12978,7 +13001,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="14">
+    <row r="34" spans="1:9" ht="14" hidden="1">
       <c r="A34" s="82">
         <v>45930</v>
       </c>
@@ -13001,7 +13024,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="14">
+    <row r="35" spans="1:9" ht="14" hidden="1">
       <c r="A35" s="84">
         <v>45933.931944444397</v>
       </c>
@@ -13024,7 +13047,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="14">
+    <row r="36" spans="1:9" ht="14" hidden="1">
       <c r="A36" s="82">
         <v>45934.931944386597</v>
       </c>
@@ -13047,7 +13070,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="14">
+    <row r="37" spans="1:9" ht="14" hidden="1">
       <c r="A37" s="84">
         <v>45935.931944386597</v>
       </c>
@@ -13070,7 +13093,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="14">
+    <row r="38" spans="1:9" ht="14" hidden="1">
       <c r="A38" s="82">
         <v>45939.931944444397</v>
       </c>
@@ -13093,7 +13116,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="14">
+    <row r="39" spans="1:9" ht="14" hidden="1">
       <c r="A39" s="84">
         <v>45939.931944444397</v>
       </c>
@@ -13116,7 +13139,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="14">
+    <row r="40" spans="1:9" ht="14" hidden="1">
       <c r="A40" s="82">
         <v>45945</v>
       </c>
@@ -13139,7 +13162,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="14">
+    <row r="41" spans="1:9" ht="14" hidden="1">
       <c r="A41" s="84">
         <v>45946</v>
       </c>
@@ -13162,7 +13185,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="14">
+    <row r="42" spans="1:9" ht="14" hidden="1">
       <c r="A42" s="82">
         <v>45946</v>
       </c>
@@ -13185,7 +13208,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="14">
+    <row r="43" spans="1:9" ht="14" hidden="1">
       <c r="A43" s="84">
         <v>45947</v>
       </c>
@@ -13208,7 +13231,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="14">
+    <row r="44" spans="1:9" ht="14" hidden="1">
       <c r="A44" s="82">
         <v>45948</v>
       </c>
@@ -13231,7 +13254,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="14">
+    <row r="45" spans="1:9" ht="14" hidden="1">
       <c r="A45" s="84">
         <v>45949</v>
       </c>
@@ -13254,7 +13277,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="14">
+    <row r="46" spans="1:9" ht="14" hidden="1">
       <c r="A46" s="82">
         <v>45950</v>
       </c>
@@ -13277,7 +13300,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="14">
+    <row r="47" spans="1:9" ht="14" hidden="1">
       <c r="A47" s="84">
         <v>45951</v>
       </c>
@@ -13300,7 +13323,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="14">
+    <row r="48" spans="1:9" ht="14" hidden="1">
       <c r="A48" s="82">
         <v>45964</v>
       </c>
@@ -13323,7 +13346,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="14">
+    <row r="49" spans="1:9" ht="14" hidden="1">
       <c r="A49" s="84">
         <v>45963</v>
       </c>
@@ -13346,7 +13369,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="14">
+    <row r="50" spans="1:9" ht="14" hidden="1">
       <c r="A50" s="82">
         <v>45982</v>
       </c>
@@ -13369,7 +13392,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="14">
+    <row r="51" spans="1:9" ht="14" hidden="1">
       <c r="A51" s="84">
         <v>45983</v>
       </c>
@@ -13392,7 +13415,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="14">
+    <row r="52" spans="1:9" ht="14" hidden="1">
       <c r="A52" s="82">
         <v>45984</v>
       </c>
@@ -13415,7 +13438,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="14">
+    <row r="53" spans="1:9" ht="14" hidden="1">
       <c r="A53" s="84">
         <v>45985</v>
       </c>
@@ -13438,7 +13461,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="13.5" customHeight="1">
+    <row r="54" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A54" s="82">
         <v>45986</v>
       </c>
@@ -13463,7 +13486,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="15.75" customHeight="1">
+    <row r="55" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A55" s="84">
         <v>45992</v>
       </c>
@@ -13488,7 +13511,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="13.5" customHeight="1">
+    <row r="56" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A56" s="82">
         <v>45992</v>
       </c>
@@ -13513,7 +13536,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="15.75" customHeight="1">
+    <row r="57" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A57" s="84">
         <v>45996</v>
       </c>
@@ -13538,7 +13561,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="42" customHeight="1">
+    <row r="58" spans="1:9" ht="42" hidden="1" customHeight="1">
       <c r="A58" s="82">
         <v>45996</v>
       </c>
@@ -13563,7 +13586,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="15.75" customHeight="1">
+    <row r="59" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A59" s="84">
         <v>45996</v>
       </c>
@@ -13588,7 +13611,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="13.5" customHeight="1">
+    <row r="60" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A60" s="82">
         <v>46007</v>
       </c>
@@ -13613,7 +13636,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="15.75" customHeight="1">
+    <row r="61" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A61" s="84">
         <v>46008</v>
       </c>
@@ -13640,7 +13663,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="13.5" customHeight="1">
+    <row r="62" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A62" s="82">
         <v>46008</v>
       </c>
@@ -13665,7 +13688,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="15.75" customHeight="1">
+    <row r="63" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A63" s="84">
         <v>46008</v>
       </c>
@@ -13690,7 +13713,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="15.75" customHeight="1">
+    <row r="64" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A64" s="84">
         <v>46008</v>
       </c>
@@ -13715,7 +13738,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="13.5" customHeight="1">
+    <row r="65" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A65" s="82">
         <v>46009</v>
       </c>
@@ -13740,7 +13763,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="15.75" customHeight="1">
+    <row r="66" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A66" s="84">
         <v>46010</v>
       </c>
@@ -13765,7 +13788,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="13.5" customHeight="1">
+    <row r="67" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A67" s="82">
         <v>46010</v>
       </c>
@@ -13792,7 +13815,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="31.5" customHeight="1">
+    <row r="68" spans="1:9" ht="31.5" hidden="1" customHeight="1">
       <c r="A68" s="84">
         <v>46011</v>
       </c>
@@ -13817,7 +13840,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="13.5" customHeight="1">
+    <row r="69" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A69" s="82">
         <v>46011</v>
       </c>
@@ -13842,7 +13865,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="13.5" customHeight="1">
+    <row r="70" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A70" s="82">
         <v>46011</v>
       </c>
@@ -13867,7 +13890,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="15.75" customHeight="1">
+    <row r="71" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A71" s="84">
         <v>46011</v>
       </c>
@@ -13892,7 +13915,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="27.75" customHeight="1">
+    <row r="72" spans="1:9" ht="27.75" hidden="1" customHeight="1">
       <c r="A72" s="82">
         <v>46011</v>
       </c>
@@ -13917,7 +13940,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="31.5" customHeight="1">
+    <row r="73" spans="1:9" ht="31.5" hidden="1" customHeight="1">
       <c r="A73" s="84">
         <v>46011</v>
       </c>
@@ -13942,7 +13965,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="13.5" customHeight="1">
+    <row r="74" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A74" s="82">
         <v>46013</v>
       </c>
@@ -13969,7 +13992,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="15.75" customHeight="1">
+    <row r="75" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A75" s="84">
         <v>46013</v>
       </c>
@@ -13994,7 +14017,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="15.75" customHeight="1">
+    <row r="76" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A76" s="84">
         <v>46017</v>
       </c>
@@ -14019,7 +14042,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="13.5" customHeight="1">
+    <row r="77" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A77" s="82">
         <v>46017</v>
       </c>
@@ -14044,7 +14067,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="15.75" customHeight="1">
+    <row r="78" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A78" s="84">
         <v>46017</v>
       </c>
@@ -14069,7 +14092,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="13.5" customHeight="1">
+    <row r="79" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A79" s="82">
         <v>46017</v>
       </c>
@@ -14094,7 +14117,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="15.75" customHeight="1">
+    <row r="80" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A80" s="84">
         <v>46020</v>
       </c>
@@ -14119,7 +14142,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="13.5" customHeight="1">
+    <row r="81" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A81" s="82">
         <v>46024</v>
       </c>
@@ -14144,7 +14167,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="15.75" customHeight="1">
+    <row r="82" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A82" s="84">
         <v>46024</v>
       </c>
@@ -14169,7 +14192,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="13.5" customHeight="1">
+    <row r="83" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A83" s="82">
         <v>46024</v>
       </c>
@@ -14194,7 +14217,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="15.75" customHeight="1">
+    <row r="84" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A84" s="84">
         <v>46024</v>
       </c>
@@ -14219,7 +14242,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="13.5" customHeight="1">
+    <row r="85" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A85" s="82">
         <v>46027</v>
       </c>
@@ -14244,7 +14267,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="13.5" customHeight="1">
+    <row r="86" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A86" s="82">
         <v>46028</v>
       </c>
@@ -14269,7 +14292,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="15.75" customHeight="1">
+    <row r="87" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A87" s="84">
         <v>46029</v>
       </c>
@@ -14294,7 +14317,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="13.5" customHeight="1">
+    <row r="88" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A88" s="82">
         <v>46032</v>
       </c>
@@ -14319,7 +14342,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="15.75" customHeight="1">
+    <row r="89" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A89" s="84">
         <v>46033</v>
       </c>
@@ -14344,7 +14367,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="13.5" customHeight="1">
+    <row r="90" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A90" s="82">
         <v>46033</v>
       </c>
@@ -14369,7 +14392,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="15.75" customHeight="1">
+    <row r="91" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A91" s="84">
         <v>46034</v>
       </c>
@@ -14394,7 +14417,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="27.75" customHeight="1">
+    <row r="92" spans="1:9" ht="27.75" hidden="1" customHeight="1">
       <c r="A92" s="82">
         <v>46034</v>
       </c>
@@ -14419,7 +14442,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="15.75" customHeight="1">
+    <row r="93" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A93" s="84">
         <v>46035</v>
       </c>
@@ -14444,7 +14467,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="13.5" customHeight="1">
+    <row r="94" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A94" s="82">
         <v>46036</v>
       </c>
@@ -14469,7 +14492,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="15.75" customHeight="1">
+    <row r="95" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A95" s="84">
         <v>46038</v>
       </c>
@@ -14494,7 +14517,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="13.5" customHeight="1">
+    <row r="96" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A96" s="82">
         <v>46038</v>
       </c>
@@ -14519,7 +14542,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="15.75" customHeight="1">
+    <row r="97" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A97" s="84">
         <v>46039</v>
       </c>
@@ -14544,7 +14567,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="13.5" customHeight="1">
+    <row r="98" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A98" s="82">
         <v>46040</v>
       </c>
@@ -14569,7 +14592,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="15.75" customHeight="1">
+    <row r="99" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A99" s="84">
         <v>46041</v>
       </c>
@@ -14594,7 +14617,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="13.5" customHeight="1">
+    <row r="100" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A100" s="82">
         <v>46042</v>
       </c>
@@ -14619,7 +14642,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="15.75" customHeight="1">
+    <row r="101" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A101" s="84">
         <v>46043</v>
       </c>
@@ -14644,7 +14667,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="13.5" customHeight="1">
+    <row r="102" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A102" s="82">
         <v>46046</v>
       </c>
@@ -14669,7 +14692,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="13.5" customHeight="1">
+    <row r="103" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A103" s="84">
         <v>46048</v>
       </c>
@@ -14694,7 +14717,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="13.5" customHeight="1">
+    <row r="104" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A104" s="82">
         <v>46048</v>
       </c>
@@ -14719,7 +14742,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="15.75" customHeight="1">
+    <row r="105" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A105" s="84">
         <v>46049</v>
       </c>
@@ -14744,7 +14767,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="13.5" customHeight="1">
+    <row r="106" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A106" s="82">
         <v>46049</v>
       </c>
@@ -14769,7 +14792,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="15.75" customHeight="1">
+    <row r="107" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A107" s="84">
         <v>46049</v>
       </c>
@@ -14794,7 +14817,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="13.5" customHeight="1">
+    <row r="108" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A108" s="82">
         <v>46050</v>
       </c>
@@ -14819,7 +14842,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="15.75" customHeight="1">
+    <row r="109" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A109" s="84">
         <v>46051</v>
       </c>
@@ -14844,7 +14867,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="13.5" customHeight="1">
+    <row r="110" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A110" s="82">
         <v>46051</v>
       </c>
@@ -14869,7 +14892,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="15.75" customHeight="1">
+    <row r="111" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A111" s="84">
         <v>46051</v>
       </c>
@@ -14894,7 +14917,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="27.75" customHeight="1">
+    <row r="112" spans="1:9" ht="27.75" hidden="1" customHeight="1">
       <c r="A112" s="82">
         <v>46054</v>
       </c>
@@ -14919,7 +14942,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="15.75" customHeight="1">
+    <row r="113" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A113" s="84">
         <v>46054</v>
       </c>
@@ -14944,7 +14967,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="13.5" customHeight="1">
+    <row r="114" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A114" s="82">
         <v>46055</v>
       </c>
@@ -14969,7 +14992,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="15.75" customHeight="1">
+    <row r="115" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A115" s="84">
         <v>46055</v>
       </c>
@@ -14994,7 +15017,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="13.5" customHeight="1">
+    <row r="116" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A116" s="82">
         <v>46060</v>
       </c>
@@ -15019,7 +15042,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="15.75" customHeight="1">
+    <row r="117" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A117" s="84">
         <v>46062</v>
       </c>
@@ -15044,7 +15067,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="118" spans="1:9" ht="13.5" customHeight="1">
+    <row r="118" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A118" s="82">
         <v>46065</v>
       </c>
@@ -15069,7 +15092,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="119" spans="1:9" ht="15.75" customHeight="1">
+    <row r="119" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A119" s="84">
         <v>46055</v>
       </c>
@@ -15094,7 +15117,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="27.75" customHeight="1">
+    <row r="120" spans="1:9" ht="27.75" hidden="1" customHeight="1">
       <c r="A120" s="82">
         <v>46070</v>
       </c>
@@ -15119,7 +15142,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="15.75" customHeight="1">
+    <row r="121" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A121" s="84">
         <v>46073</v>
       </c>
@@ -15144,7 +15167,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="13.5" customHeight="1">
+    <row r="122" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A122" s="82">
         <v>46074</v>
       </c>
@@ -15169,7 +15192,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="15.75" customHeight="1">
+    <row r="123" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A123" s="84">
         <v>46075</v>
       </c>
@@ -15194,7 +15217,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="124" spans="1:9" ht="13.5" customHeight="1">
+    <row r="124" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A124" s="82">
         <v>46075</v>
       </c>
@@ -15219,7 +15242,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="125" spans="1:9" ht="31.5" customHeight="1">
+    <row r="125" spans="1:9" ht="31.5" hidden="1" customHeight="1">
       <c r="A125" s="84">
         <v>46079</v>
       </c>
@@ -15244,7 +15267,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="126" spans="1:9" ht="13.5" customHeight="1">
+    <row r="126" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A126" s="82">
         <v>46079</v>
       </c>
@@ -15269,7 +15292,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="127" spans="1:9" ht="13.5" customHeight="1">
+    <row r="127" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A127" s="84">
         <v>46090</v>
       </c>
@@ -15294,7 +15317,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="128" spans="1:9" ht="13.5" customHeight="1">
+    <row r="128" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A128" s="82">
         <v>46090</v>
       </c>
@@ -15319,7 +15342,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="129" spans="1:9" ht="13.5" customHeight="1">
+    <row r="129" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A129" s="82">
         <v>46090</v>
       </c>
@@ -15344,7 +15367,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="130" spans="1:9" ht="15.75" customHeight="1">
+    <row r="130" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A130" s="84">
         <v>46091</v>
       </c>
@@ -15369,7 +15392,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="131" spans="1:9" ht="13.5" customHeight="1">
+    <row r="131" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A131" s="82">
         <v>46092</v>
       </c>
@@ -15394,7 +15417,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="132" spans="1:9" ht="15.75" customHeight="1">
+    <row r="132" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A132" s="84">
         <v>46092</v>
       </c>
@@ -15419,7 +15442,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="133" spans="1:9" ht="27.75" customHeight="1">
+    <row r="133" spans="1:9" ht="27.75" hidden="1" customHeight="1">
       <c r="A133" s="82">
         <v>46093</v>
       </c>
@@ -15444,7 +15467,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="134" spans="1:9" ht="15.75" customHeight="1">
+    <row r="134" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A134" s="84">
         <v>46093</v>
       </c>
@@ -15469,7 +15492,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="135" spans="1:9" ht="13.5" customHeight="1">
+    <row r="135" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A135" s="82">
         <v>46097</v>
       </c>
@@ -15494,7 +15517,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="136" spans="1:9" ht="15.75" customHeight="1">
+    <row r="136" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A136" s="84">
         <v>46097</v>
       </c>
@@ -15519,7 +15542,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="137" spans="1:9" ht="13.5" customHeight="1">
+    <row r="137" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A137" s="82">
         <v>46100</v>
       </c>
@@ -15544,7 +15567,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="138" spans="1:9" ht="15.75" customHeight="1">
+    <row r="138" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A138" s="84">
         <v>46104</v>
       </c>
@@ -15569,7 +15592,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="139" spans="1:9" ht="27.75" customHeight="1">
+    <row r="139" spans="1:9" ht="27.75" hidden="1" customHeight="1">
       <c r="A139" s="82">
         <v>46105</v>
       </c>
@@ -15594,7 +15617,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="140" spans="1:9" ht="31.5" customHeight="1">
+    <row r="140" spans="1:9" ht="31.5" hidden="1" customHeight="1">
       <c r="A140" s="84">
         <v>46113</v>
       </c>
@@ -15619,7 +15642,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="141" spans="1:9" ht="13.5" customHeight="1">
+    <row r="141" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A141" s="82">
         <v>46118</v>
       </c>
@@ -15644,7 +15667,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="142" spans="1:9" ht="15.75" customHeight="1">
+    <row r="142" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A142" s="84">
         <v>46119</v>
       </c>
@@ -15669,7 +15692,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="143" spans="1:9" ht="13.5" customHeight="1">
+    <row r="143" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A143" s="82">
         <v>46120</v>
       </c>
@@ -15694,7 +15717,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="144" spans="1:9" ht="15.75" customHeight="1">
+    <row r="144" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A144" s="84">
         <v>46120</v>
       </c>
@@ -15719,7 +15742,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="145" spans="1:9" ht="13.5" customHeight="1">
+    <row r="145" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A145" s="82">
         <v>46120</v>
       </c>
@@ -15744,7 +15767,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="146" spans="1:9" ht="31.5" customHeight="1">
+    <row r="146" spans="1:9" ht="31.5" hidden="1" customHeight="1">
       <c r="A146" s="84">
         <v>46122</v>
       </c>
@@ -15769,7 +15792,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="147" spans="1:9" ht="13.5" customHeight="1">
+    <row r="147" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A147" s="82">
         <v>46122</v>
       </c>
@@ -15794,7 +15817,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="148" spans="1:9" ht="15.75" customHeight="1">
+    <row r="148" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A148" s="84">
         <v>46122</v>
       </c>
@@ -15819,7 +15842,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="149" spans="1:9" ht="13.5" customHeight="1">
+    <row r="149" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A149" s="82">
         <v>46122</v>
       </c>
@@ -15844,7 +15867,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="150" spans="1:9" ht="15.75" customHeight="1">
+    <row r="150" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A150" s="84">
         <v>46125</v>
       </c>
@@ -15869,7 +15892,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="151" spans="1:9" ht="13.5" customHeight="1">
+    <row r="151" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A151" s="82">
         <v>46125</v>
       </c>
@@ -15894,7 +15917,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="152" spans="1:9" ht="15.75" customHeight="1">
+    <row r="152" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A152" s="84">
         <v>46125</v>
       </c>
@@ -15919,7 +15942,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="153" spans="1:9" ht="13.5" customHeight="1">
+    <row r="153" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A153" s="82">
         <v>46125</v>
       </c>
@@ -15944,7 +15967,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="154" spans="1:9" ht="15.75" customHeight="1">
+    <row r="154" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A154" s="84">
         <v>46126</v>
       </c>
@@ -15969,7 +15992,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="155" spans="1:9" ht="13.5" customHeight="1">
+    <row r="155" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A155" s="82">
         <v>46127</v>
       </c>
@@ -15994,7 +16017,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="156" spans="1:9" ht="15.75" customHeight="1">
+    <row r="156" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A156" s="84">
         <v>46129</v>
       </c>
@@ -16019,7 +16042,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="157" spans="1:9" ht="13.5" customHeight="1">
+    <row r="157" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A157" s="82">
         <v>46129</v>
       </c>
@@ -16044,7 +16067,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="158" spans="1:9" ht="15.75" customHeight="1">
+    <row r="158" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A158" s="84">
         <v>46129</v>
       </c>
@@ -16069,7 +16092,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="159" spans="1:9" ht="13.5" customHeight="1">
+    <row r="159" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A159" s="82">
         <v>46130</v>
       </c>
@@ -16094,7 +16117,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="160" spans="1:9" ht="15.75" customHeight="1">
+    <row r="160" spans="1:9" ht="15.75" hidden="1" customHeight="1">
       <c r="A160" s="84">
         <v>46131</v>
       </c>
@@ -16119,7 +16142,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="161" spans="1:9" ht="13.5" customHeight="1">
+    <row r="161" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A161" s="82">
         <v>46132</v>
       </c>
@@ -16144,7 +16167,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="162" spans="1:9" ht="42" customHeight="1">
+    <row r="162" spans="1:9" ht="42" hidden="1" customHeight="1">
       <c r="A162" s="84">
         <v>46132</v>
       </c>
@@ -16169,7 +16192,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="163" spans="1:9" ht="13.5" customHeight="1">
+    <row r="163" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A163" s="82">
         <v>46133</v>
       </c>
@@ -16194,7 +16217,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="164" spans="1:9" ht="13.5" customHeight="1">
+    <row r="164" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A164" s="84">
         <v>46133</v>
       </c>
@@ -16219,7 +16242,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="165" spans="1:9" ht="13.5" customHeight="1">
+    <row r="165" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A165" s="82">
         <v>46133</v>
       </c>
@@ -16244,7 +16267,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="166" spans="1:9" ht="13.5" customHeight="1">
+    <row r="166" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A166" s="84">
         <v>46134</v>
       </c>
@@ -16269,7 +16292,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="167" spans="1:9" ht="13.5" customHeight="1">
+    <row r="167" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A167" s="82">
         <v>46134</v>
       </c>
@@ -16294,7 +16317,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="168" spans="1:9" ht="13.5" customHeight="1">
+    <row r="168" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A168" s="82">
         <v>46134</v>
       </c>
@@ -16319,7 +16342,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="169" spans="1:9" ht="13.5" customHeight="1">
+    <row r="169" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A169" s="84">
         <v>46134</v>
       </c>
@@ -16344,7 +16367,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="170" spans="1:9" ht="13.5" customHeight="1">
+    <row r="170" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A170" s="82">
         <v>46134</v>
       </c>
@@ -16369,7 +16392,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="171" spans="1:9" ht="13.5" customHeight="1">
+    <row r="171" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A171" s="84">
         <v>46136</v>
       </c>
@@ -16394,7 +16417,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="172" spans="1:9" ht="13.5" customHeight="1">
+    <row r="172" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A172" s="82">
         <v>46138</v>
       </c>
@@ -16419,7 +16442,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="173" spans="1:9" ht="13.5" customHeight="1">
+    <row r="173" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A173" s="84">
         <v>46138</v>
       </c>
@@ -16444,7 +16467,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="174" spans="1:9" ht="13.5" customHeight="1">
+    <row r="174" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A174" s="82">
         <v>46139</v>
       </c>
@@ -16469,7 +16492,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="175" spans="1:9" ht="13.5" customHeight="1">
+    <row r="175" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A175" s="84">
         <v>46139</v>
       </c>
@@ -16494,7 +16517,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="176" spans="1:9" ht="13.5" customHeight="1">
+    <row r="176" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A176" s="82">
         <v>46139</v>
       </c>
@@ -16519,7 +16542,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="177" spans="1:9" ht="13.5" customHeight="1">
+    <row r="177" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A177" s="84">
         <v>46140</v>
       </c>
@@ -16544,7 +16567,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="178" spans="1:9" ht="13.5" customHeight="1">
+    <row r="178" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A178" s="82">
         <v>46140</v>
       </c>
@@ -16569,7 +16592,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="179" spans="1:9" ht="13.5" customHeight="1">
+    <row r="179" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A179" s="84">
         <v>46140</v>
       </c>
@@ -16594,7 +16617,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="180" spans="1:9" ht="13.5" customHeight="1">
+    <row r="180" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A180" s="82">
         <v>46140</v>
       </c>
@@ -16619,7 +16642,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="181" spans="1:9" ht="13.5" customHeight="1">
+    <row r="181" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A181" s="84">
         <v>46141</v>
       </c>
@@ -16644,7 +16667,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="182" spans="1:9" ht="13.5" customHeight="1">
+    <row r="182" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A182" s="82">
         <v>46141</v>
       </c>
@@ -16669,7 +16692,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="183" spans="1:9" ht="13.5" customHeight="1">
+    <row r="183" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A183" s="84">
         <v>46142</v>
       </c>
@@ -16694,7 +16717,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="184" spans="1:9" ht="13.5" customHeight="1">
+    <row r="184" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A184" s="82">
         <v>46142</v>
       </c>
@@ -16719,7 +16742,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="185" spans="1:9" ht="13.5" customHeight="1">
+    <row r="185" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A185" s="84">
         <v>46142</v>
       </c>
@@ -16744,7 +16767,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="186" spans="1:9" ht="13.5" customHeight="1">
+    <row r="186" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A186" s="84">
         <v>46144</v>
       </c>
@@ -16769,7 +16792,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="187" spans="1:9" ht="13.5" customHeight="1">
+    <row r="187" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A187" s="82">
         <v>46144</v>
       </c>
@@ -16794,7 +16817,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="188" spans="1:9" ht="13.5" customHeight="1">
+    <row r="188" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A188" s="84">
         <v>46145</v>
       </c>
@@ -16819,7 +16842,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="189" spans="1:9" ht="13.5" customHeight="1">
+    <row r="189" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A189" s="82">
         <v>46145</v>
       </c>
@@ -16844,7 +16867,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="190" spans="1:9" ht="13.5" customHeight="1">
+    <row r="190" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A190" s="84">
         <v>46145</v>
       </c>
@@ -16869,7 +16892,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="191" spans="1:9" ht="42" customHeight="1">
+    <row r="191" spans="1:9" ht="42" hidden="1" customHeight="1">
       <c r="A191" s="82">
         <v>46151</v>
       </c>
@@ -16894,7 +16917,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="192" spans="1:9" ht="27.75" customHeight="1">
+    <row r="192" spans="1:9" ht="27.75" hidden="1" customHeight="1">
       <c r="A192" s="84">
         <v>46152</v>
       </c>
@@ -16919,7 +16942,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="193" spans="1:9" ht="42" customHeight="1">
+    <row r="193" spans="1:9" ht="42" hidden="1" customHeight="1">
       <c r="A193" s="82">
         <v>46152</v>
       </c>
@@ -16944,7 +16967,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="194" spans="1:9" ht="27.75" customHeight="1">
+    <row r="194" spans="1:9" ht="27.75" hidden="1" customHeight="1">
       <c r="A194" s="84">
         <v>46151</v>
       </c>
@@ -16969,7 +16992,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="195" spans="1:9" ht="42" customHeight="1">
+    <row r="195" spans="1:9" ht="42" hidden="1" customHeight="1">
       <c r="A195" s="82">
         <v>46155</v>
       </c>
@@ -16994,7 +17017,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="196" spans="1:9" ht="42" customHeight="1">
+    <row r="196" spans="1:9" ht="42" hidden="1" customHeight="1">
       <c r="A196" s="84">
         <v>46155</v>
       </c>
@@ -17019,7 +17042,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="197" spans="1:9" ht="42" customHeight="1">
+    <row r="197" spans="1:9" ht="42" hidden="1" customHeight="1">
       <c r="A197" s="82">
         <v>46155</v>
       </c>
@@ -17044,7 +17067,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="198" spans="1:9" ht="42" customHeight="1">
+    <row r="198" spans="1:9" ht="42" hidden="1" customHeight="1">
       <c r="A198" s="84">
         <v>46168</v>
       </c>
@@ -17069,7 +17092,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="199" spans="1:9" ht="13.5" customHeight="1">
+    <row r="199" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A199" s="82">
         <v>46172</v>
       </c>
@@ -17094,7 +17117,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="200" spans="1:9" ht="27.75" customHeight="1">
+    <row r="200" spans="1:9" ht="27.75" hidden="1" customHeight="1">
       <c r="A200" s="84">
         <v>46173</v>
       </c>
@@ -17119,7 +17142,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="201" spans="1:9" ht="27.75" customHeight="1">
+    <row r="201" spans="1:9" ht="27.75" hidden="1" customHeight="1">
       <c r="A201" s="82">
         <v>46173</v>
       </c>
@@ -17144,7 +17167,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="202" spans="1:9" ht="13.5" customHeight="1">
+    <row r="202" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A202" s="84">
         <v>46173</v>
       </c>
@@ -17194,7 +17217,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="204" spans="1:9" ht="13.5" customHeight="1">
+    <row r="204" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A204" s="84">
         <v>46175</v>
       </c>
@@ -17219,7 +17242,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="205" spans="1:9" ht="13.5" customHeight="1">
+    <row r="205" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A205" s="82">
         <v>46175</v>
       </c>
@@ -17244,7 +17267,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="206" spans="1:9" ht="13.5" customHeight="1">
+    <row r="206" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A206" s="84">
         <v>46175</v>
       </c>
@@ -17269,7 +17292,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="207" spans="1:9" ht="13.5" customHeight="1">
+    <row r="207" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A207" s="82">
         <v>46175</v>
       </c>
@@ -17294,7 +17317,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="208" spans="1:9" ht="13.5" customHeight="1">
+    <row r="208" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A208" s="84">
         <v>46175</v>
       </c>
@@ -17319,7 +17342,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="209" spans="1:9" ht="13.5" customHeight="1">
+    <row r="209" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A209" s="82">
         <v>46176</v>
       </c>
@@ -17344,7 +17367,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="210" spans="1:9" ht="27.75" customHeight="1">
+    <row r="210" spans="1:9" ht="27.75" hidden="1" customHeight="1">
       <c r="A210" s="84">
         <v>46176</v>
       </c>
@@ -17369,7 +17392,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="211" spans="1:9" ht="13.5" customHeight="1">
+    <row r="211" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A211" s="82">
         <v>46176</v>
       </c>
@@ -17394,7 +17417,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="212" spans="1:9" ht="14">
+    <row r="212" spans="1:9" ht="14" hidden="1">
       <c r="A212" s="84">
         <v>46176</v>
       </c>
@@ -17419,7 +17442,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="213" spans="1:9" ht="13.5" customHeight="1">
+    <row r="213" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A213" s="82">
         <v>46176</v>
       </c>
@@ -17444,7 +17467,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="214" spans="1:9" ht="14">
+    <row r="214" spans="1:9" ht="14" hidden="1">
       <c r="A214" s="84">
         <v>46177</v>
       </c>
@@ -17469,7 +17492,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="215" spans="1:9" ht="13.5" customHeight="1">
+    <row r="215" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A215" s="82">
         <v>46187</v>
       </c>
@@ -17494,7 +17517,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="216" spans="1:9" ht="55.5" customHeight="1">
+    <row r="216" spans="1:9" ht="55.5" hidden="1" customHeight="1">
       <c r="A216" s="84">
         <v>46188</v>
       </c>
@@ -17519,7 +17542,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="217" spans="1:9" ht="13.5" customHeight="1">
+    <row r="217" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A217" s="84">
         <v>46191</v>
       </c>
@@ -17544,7 +17567,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="218" spans="1:9" ht="13.5" customHeight="1">
+    <row r="218" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A218" s="82">
         <v>46191</v>
       </c>
@@ -17569,7 +17592,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="219" spans="1:9" ht="13.5" customHeight="1">
+    <row r="219" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A219" s="84">
         <v>46191</v>
       </c>
@@ -17594,7 +17617,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="220" spans="1:9" ht="13.5" customHeight="1">
+    <row r="220" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A220" s="82">
         <v>46191</v>
       </c>
@@ -17619,7 +17642,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="221" spans="1:9" ht="13.5" customHeight="1">
+    <row r="221" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A221" s="84">
         <v>46191</v>
       </c>
@@ -17644,7 +17667,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="222" spans="1:9" ht="13.5" customHeight="1">
+    <row r="222" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A222" s="82">
         <v>46191</v>
       </c>
@@ -17669,7 +17692,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="223" spans="1:9" ht="13.5" customHeight="1">
+    <row r="223" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A223" s="84">
         <v>46191</v>
       </c>
@@ -17694,7 +17717,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="224" spans="1:9" ht="13.5" customHeight="1">
+    <row r="224" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A224" s="82">
         <v>46192</v>
       </c>
@@ -17719,7 +17742,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="225" spans="1:9" ht="13.5" customHeight="1">
+    <row r="225" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A225" s="84">
         <v>46192</v>
       </c>
@@ -17744,7 +17767,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="226" spans="1:9" ht="13.5" customHeight="1">
+    <row r="226" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A226" s="82">
         <v>46192</v>
       </c>
@@ -17769,7 +17792,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="227" spans="1:9" ht="13.5" customHeight="1">
+    <row r="227" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A227" s="84">
         <v>46192</v>
       </c>
@@ -17794,7 +17817,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="228" spans="1:9" ht="13.5" customHeight="1">
+    <row r="228" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A228" s="82">
         <v>46193</v>
       </c>
@@ -17819,7 +17842,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="229" spans="1:9" ht="13.5" customHeight="1">
+    <row r="229" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A229" s="84">
         <v>46193</v>
       </c>
@@ -17844,7 +17867,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="230" spans="1:9" ht="13.5" customHeight="1">
+    <row r="230" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A230" s="82">
         <v>46193</v>
       </c>
@@ -17869,7 +17892,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="231" spans="1:9" ht="13.5" customHeight="1">
+    <row r="231" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A231" s="84">
         <v>46193</v>
       </c>
@@ -17894,7 +17917,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="232" spans="1:9" ht="13.5" customHeight="1">
+    <row r="232" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A232" s="82">
         <v>46193</v>
       </c>
@@ -17919,7 +17942,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="233" spans="1:9" ht="13.5" customHeight="1">
+    <row r="233" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A233" s="84">
         <v>46193</v>
       </c>
@@ -17944,7 +17967,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="234" spans="1:9" ht="27.75" customHeight="1">
+    <row r="234" spans="1:9" ht="27.75" hidden="1" customHeight="1">
       <c r="A234" s="82">
         <v>46193</v>
       </c>
@@ -17969,7 +17992,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="235" spans="1:9" ht="13.5" customHeight="1">
+    <row r="235" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A235" s="84">
         <v>46194</v>
       </c>
@@ -17994,7 +18017,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="236" spans="1:9" ht="27.75" customHeight="1">
+    <row r="236" spans="1:9" ht="27.75" hidden="1" customHeight="1">
       <c r="A236" s="82">
         <v>46194</v>
       </c>
@@ -18019,7 +18042,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="237" spans="1:9" ht="13.5" customHeight="1">
+    <row r="237" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A237" s="84">
         <v>46196</v>
       </c>
@@ -18044,7 +18067,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="238" spans="1:9" ht="13.5" customHeight="1">
+    <row r="238" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A238" s="82">
         <v>46196</v>
       </c>
@@ -18069,7 +18092,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="239" spans="1:9" ht="13.5" customHeight="1">
+    <row r="239" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A239" s="84">
         <v>46196</v>
       </c>
@@ -18094,7 +18117,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="240" spans="1:9" ht="27.75" customHeight="1">
+    <row r="240" spans="1:9" ht="27.75" hidden="1" customHeight="1">
       <c r="A240" s="82">
         <v>46196</v>
       </c>
@@ -18119,7 +18142,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="241" spans="1:9" ht="13.5" customHeight="1">
+    <row r="241" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A241" s="84">
         <v>46197</v>
       </c>
@@ -18144,7 +18167,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="242" spans="1:9" ht="13.5" customHeight="1">
+    <row r="242" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A242" s="82">
         <v>46197</v>
       </c>
@@ -18169,7 +18192,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="243" spans="1:9" ht="13.5" customHeight="1">
+    <row r="243" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A243" s="84">
         <v>46197</v>
       </c>
@@ -18194,7 +18217,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="244" spans="1:9" ht="13.5" customHeight="1">
+    <row r="244" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A244" s="82">
         <v>46197</v>
       </c>
@@ -18219,7 +18242,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="245" spans="1:9" ht="13.5" customHeight="1">
+    <row r="245" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A245" s="84">
         <v>46198</v>
       </c>
@@ -18244,7 +18267,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="246" spans="1:9" ht="13.5" customHeight="1">
+    <row r="246" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A246" s="82">
         <v>46199</v>
       </c>
@@ -18269,7 +18292,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="247" spans="1:9" ht="13.5" customHeight="1">
+    <row r="247" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A247" s="84">
         <v>46199</v>
       </c>
@@ -18294,7 +18317,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="248" spans="1:9" ht="13.5" customHeight="1">
+    <row r="248" spans="1:9" ht="13.5" hidden="1" customHeight="1">
       <c r="A248" s="82">
         <v>46199</v>
       </c>
@@ -18319,7 +18342,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="249" spans="1:9" ht="14">
+    <row r="249" spans="1:9" ht="14" hidden="1">
       <c r="A249" s="84">
         <v>46200</v>
       </c>
@@ -18365,7 +18388,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="251" spans="1:9" ht="14">
+    <row r="251" spans="1:9" ht="14" hidden="1">
       <c r="A251" s="84">
         <v>46201</v>
       </c>
@@ -18390,7 +18413,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="252" spans="1:9" ht="14">
+    <row r="252" spans="1:9" ht="14" hidden="1">
       <c r="A252" s="82">
         <v>46201</v>
       </c>
@@ -18415,7 +18438,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="253" spans="1:9" ht="14">
+    <row r="253" spans="1:9" ht="14" hidden="1">
       <c r="A253" s="84">
         <v>46201</v>
       </c>
@@ -18440,7 +18463,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="254" spans="1:9" ht="14">
+    <row r="254" spans="1:9" ht="14" hidden="1">
       <c r="A254" s="82">
         <v>46201</v>
       </c>
@@ -18465,7 +18488,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="255" spans="1:9" ht="14">
+    <row r="255" spans="1:9" ht="14" hidden="1">
       <c r="A255" s="84">
         <v>46201</v>
       </c>
@@ -18490,7 +18513,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="256" spans="1:9" ht="14">
+    <row r="256" spans="1:9" ht="14" hidden="1">
       <c r="A256" s="82">
         <v>46203</v>
       </c>
@@ -18515,7 +18538,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="257" spans="1:9" ht="14">
+    <row r="257" spans="1:9" ht="14" hidden="1">
       <c r="A257" s="84">
         <v>46204</v>
       </c>
@@ -18540,7 +18563,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="258" spans="1:9" ht="14">
+    <row r="258" spans="1:9" ht="14" hidden="1">
       <c r="A258" s="82">
         <v>46205</v>
       </c>
@@ -18565,7 +18588,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="259" spans="1:9" ht="14">
+    <row r="259" spans="1:9" ht="14" hidden="1">
       <c r="A259" s="84">
         <v>46205</v>
       </c>
@@ -18590,7 +18613,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="260" spans="1:9" ht="14">
+    <row r="260" spans="1:9" ht="14" hidden="1">
       <c r="A260" s="82">
         <v>46205</v>
       </c>
@@ -18615,7 +18638,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="261" spans="1:9" ht="14">
+    <row r="261" spans="1:9" ht="14" hidden="1">
       <c r="A261" s="84">
         <v>46205</v>
       </c>
@@ -18634,13 +18657,13 @@
       <c r="F261" s="46"/>
       <c r="G261" s="46"/>
       <c r="H261" s="46" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="I261" s="45" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="262" spans="1:9" ht="14">
+    <row r="262" spans="1:9" ht="14" hidden="1">
       <c r="A262" s="82">
         <v>46206</v>
       </c>
@@ -18665,7 +18688,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="263" spans="1:9" ht="14">
+    <row r="263" spans="1:9" ht="14" hidden="1">
       <c r="A263" s="84">
         <v>46206</v>
       </c>
@@ -18740,7 +18763,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="266" spans="1:9" ht="14">
+    <row r="266" spans="1:9" ht="14" hidden="1">
       <c r="A266" s="82">
         <v>46206</v>
       </c>
@@ -18765,7 +18788,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="267" spans="1:9" ht="14">
+    <row r="267" spans="1:9" ht="14" hidden="1">
       <c r="A267" s="84">
         <v>46207</v>
       </c>
@@ -18811,7 +18834,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="269" spans="1:9" ht="14">
+    <row r="269" spans="1:9" ht="14" hidden="1">
       <c r="A269" s="84">
         <v>46209</v>
       </c>
@@ -18836,12 +18859,12 @@
         <v>148</v>
       </c>
     </row>
-    <row r="270" spans="1:9" ht="14">
+    <row r="270" spans="1:9" ht="14" hidden="1">
       <c r="A270" s="82">
         <v>46210</v>
       </c>
       <c r="B270" s="44" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="C270" s="83">
         <v>3200</v>
@@ -18861,7 +18884,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="271" spans="1:9" ht="14">
+    <row r="271" spans="1:9" ht="14" hidden="1">
       <c r="A271" s="84">
         <v>46211</v>
       </c>
@@ -18886,12 +18909,12 @@
         <v>148</v>
       </c>
     </row>
-    <row r="272" spans="1:9" ht="14">
+    <row r="272" spans="1:9" ht="14" hidden="1">
       <c r="A272" s="82">
         <v>46215</v>
       </c>
       <c r="B272" s="44" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="C272" s="83">
         <v>1380</v>
@@ -18911,12 +18934,12 @@
         <v>148</v>
       </c>
     </row>
-    <row r="273" spans="1:9" ht="14">
+    <row r="273" spans="1:9" ht="14" hidden="1">
       <c r="A273" s="84">
         <v>46215</v>
       </c>
       <c r="B273" s="45" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="C273" s="85">
         <v>699</v>
@@ -18936,7 +18959,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="274" spans="1:9" ht="14">
+    <row r="274" spans="1:9" ht="14" hidden="1">
       <c r="A274" s="82">
         <v>46215</v>
       </c>
@@ -18955,18 +18978,18 @@
       <c r="F274" s="44"/>
       <c r="G274" s="44"/>
       <c r="H274" s="44" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="I274" s="44" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="275" spans="1:9" ht="14">
+    <row r="275" spans="1:9" ht="14" hidden="1">
       <c r="A275" s="84">
         <v>46216</v>
       </c>
       <c r="B275" s="45" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="C275" s="85">
         <v>699</v>
@@ -18986,12 +19009,12 @@
         <v>148</v>
       </c>
     </row>
-    <row r="276" spans="1:9" ht="14">
+    <row r="276" spans="1:9" ht="14" hidden="1">
       <c r="A276" s="82">
         <v>46216</v>
       </c>
       <c r="B276" s="44" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="C276" s="83">
         <v>3000</v>
@@ -19005,18 +19028,18 @@
       <c r="F276" s="44"/>
       <c r="G276" s="44"/>
       <c r="H276" s="44" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="I276" s="44" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="277" spans="1:9" ht="14">
+    <row r="277" spans="1:9" ht="14" hidden="1">
       <c r="A277" s="84">
         <v>46219</v>
       </c>
       <c r="B277" s="45" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="C277" s="85">
         <v>1380</v>
@@ -19036,7 +19059,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="278" spans="1:9" ht="14">
+    <row r="278" spans="1:9" ht="14" hidden="1">
       <c r="A278" s="82">
         <v>46219</v>
       </c>
@@ -19061,7 +19084,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="279" spans="1:9" ht="14">
+    <row r="279" spans="1:9" ht="14" hidden="1">
       <c r="A279" s="84">
         <v>46219</v>
       </c>
@@ -19080,13 +19103,13 @@
       <c r="F279" s="46"/>
       <c r="G279" s="46"/>
       <c r="H279" s="46" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="I279" s="45" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="280" spans="1:9" ht="14">
+    <row r="280" spans="1:9" ht="14" hidden="1">
       <c r="A280" s="82">
         <v>46219</v>
       </c>
@@ -19105,13 +19128,13 @@
       <c r="F280" s="44"/>
       <c r="G280" s="44"/>
       <c r="H280" s="44" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="I280" s="44" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="281" spans="1:9" ht="14">
+    <row r="281" spans="1:9" ht="14" hidden="1">
       <c r="A281" s="84">
         <v>46219</v>
       </c>
@@ -19130,18 +19153,18 @@
       <c r="F281" s="46"/>
       <c r="G281" s="46"/>
       <c r="H281" s="46" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="I281" s="45" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="282" spans="1:9" ht="14">
+    <row r="282" spans="1:9" ht="14" hidden="1">
       <c r="A282" s="82">
         <v>46220</v>
       </c>
       <c r="B282" s="44" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="C282" s="83">
         <v>1500</v>
@@ -19155,18 +19178,18 @@
       <c r="F282" s="44"/>
       <c r="G282" s="44"/>
       <c r="H282" s="44" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="I282" s="44" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="283" spans="1:9" ht="14">
+    <row r="283" spans="1:9" ht="14" hidden="1">
       <c r="A283" s="84">
         <v>46221</v>
       </c>
       <c r="B283" s="45" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="C283" s="85">
         <v>1100</v>
@@ -19180,18 +19203,18 @@
       <c r="F283" s="46"/>
       <c r="G283" s="46"/>
       <c r="H283" s="46" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="I283" s="45" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="284" spans="1:9" ht="14">
+    <row r="284" spans="1:9" ht="14" hidden="1">
       <c r="A284" s="82">
         <v>46222</v>
       </c>
       <c r="B284" s="44" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="C284" s="83">
         <v>850</v>
@@ -19205,18 +19228,18 @@
       <c r="F284" s="44"/>
       <c r="G284" s="44"/>
       <c r="H284" s="44" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="I284" s="44" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="285" spans="1:9" ht="14">
+    <row r="285" spans="1:9" ht="14" hidden="1">
       <c r="A285" s="84">
         <v>46222</v>
       </c>
       <c r="B285" s="45" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="C285" s="85">
         <v>1250</v>
@@ -19230,18 +19253,18 @@
       <c r="F285" s="46"/>
       <c r="G285" s="46"/>
       <c r="H285" s="46" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="I285" s="45" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="286" spans="1:9" ht="14">
+    <row r="286" spans="1:9" ht="14" hidden="1">
       <c r="A286" s="82">
         <v>46222</v>
       </c>
       <c r="B286" s="44" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="C286" s="83">
         <v>700</v>
@@ -19261,12 +19284,12 @@
         <v>148</v>
       </c>
     </row>
-    <row r="287" spans="1:9" ht="14">
+    <row r="287" spans="1:9" ht="14" hidden="1">
       <c r="A287" s="84">
         <v>46222</v>
       </c>
       <c r="B287" s="45" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="C287" s="85">
         <v>699</v>
@@ -19286,12 +19309,12 @@
         <v>148</v>
       </c>
     </row>
-    <row r="288" spans="1:9" ht="14">
+    <row r="288" spans="1:9" ht="14" hidden="1">
       <c r="A288" s="82">
         <v>46223</v>
       </c>
       <c r="B288" s="44" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="C288" s="83">
         <v>1380</v>
@@ -19305,18 +19328,18 @@
       <c r="F288" s="44"/>
       <c r="G288" s="44"/>
       <c r="H288" s="44" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="I288" s="44" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="289" spans="1:9" ht="14">
+    <row r="289" spans="1:9" ht="14" hidden="1">
       <c r="A289" s="84">
         <v>46224</v>
       </c>
       <c r="B289" s="45" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="C289" s="85">
         <v>1380</v>
@@ -19330,18 +19353,18 @@
       <c r="F289" s="46"/>
       <c r="G289" s="46"/>
       <c r="H289" s="46" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="I289" s="45" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="290" spans="1:9" ht="14">
+    <row r="290" spans="1:9" ht="14" hidden="1">
       <c r="A290" s="82">
         <v>46224</v>
       </c>
       <c r="B290" s="44" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="C290" s="83">
         <v>1380</v>
@@ -19355,13 +19378,13 @@
       <c r="F290" s="44"/>
       <c r="G290" s="44"/>
       <c r="H290" s="44" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="I290" s="44" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="291" spans="1:9" ht="14">
+    <row r="291" spans="1:9" ht="14" hidden="1">
       <c r="A291" s="82">
         <v>46228</v>
       </c>
@@ -19380,7 +19403,7 @@
       <c r="F291" s="44"/>
       <c r="G291" s="44"/>
       <c r="H291" s="44" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="I291" s="44" t="s">
         <v>148</v>
@@ -19391,7 +19414,7 @@
         <v>46229</v>
       </c>
       <c r="B292" s="45" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="C292" s="85">
         <v>1900</v>
@@ -19401,7 +19424,7 @@
       <c r="F292" s="46"/>
       <c r="G292" s="46"/>
       <c r="H292" s="46" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="I292" s="45" t="s">
         <v>356</v>
@@ -19422,7 +19445,7 @@
       <c r="F293" s="44"/>
       <c r="G293" s="44"/>
       <c r="H293" s="44" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="I293" s="44" t="s">
         <v>356</v>
@@ -19436,14 +19459,14 @@
         <v>1109</v>
       </c>
       <c r="C294" s="85">
-        <v>3250</v>
+        <v>2300</v>
       </c>
       <c r="D294" s="45"/>
       <c r="E294" s="45"/>
       <c r="F294" s="46"/>
       <c r="G294" s="46"/>
       <c r="H294" s="46" t="s">
-        <v>1204</v>
+        <v>1271</v>
       </c>
       <c r="I294" s="45" t="s">
         <v>356</v>
@@ -19454,7 +19477,7 @@
         <v>46229</v>
       </c>
       <c r="B295" s="44" t="s">
-        <v>1207</v>
+        <v>1204</v>
       </c>
       <c r="C295" s="83">
         <v>1550</v>
@@ -19464,18 +19487,18 @@
       <c r="F295" s="44"/>
       <c r="G295" s="44"/>
       <c r="H295" s="44" t="s">
-        <v>1208</v>
+        <v>1205</v>
       </c>
       <c r="I295" s="44" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="296" spans="1:9" ht="14">
+    <row r="296" spans="1:9" ht="14" hidden="1">
       <c r="A296" s="84">
         <v>46235</v>
       </c>
       <c r="B296" s="45" t="s">
-        <v>1260</v>
+        <v>1256</v>
       </c>
       <c r="C296" s="85">
         <v>1450</v>
@@ -19489,18 +19512,18 @@
       <c r="F296" s="46"/>
       <c r="G296" s="46"/>
       <c r="H296" s="46" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="I296" s="45" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="297" spans="1:9" ht="28">
+    <row r="297" spans="1:9" ht="28" hidden="1">
       <c r="A297" s="82">
         <v>46236</v>
       </c>
       <c r="B297" s="44" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="C297" s="83">
         <v>6900</v>
@@ -19514,18 +19537,18 @@
       <c r="F297" s="44"/>
       <c r="G297" s="44"/>
       <c r="H297" s="44" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="I297" s="44" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="298" spans="1:9" ht="14">
+    <row r="298" spans="1:9" ht="14" hidden="1">
       <c r="A298" s="84">
         <v>46236</v>
       </c>
       <c r="B298" s="45" t="s">
-        <v>1263</v>
+        <v>1259</v>
       </c>
       <c r="C298" s="85">
         <v>1479</v>
@@ -19539,15 +19562,19 @@
       <c r="F298" s="46"/>
       <c r="G298" s="46"/>
       <c r="H298" s="46" t="s">
-        <v>1262</v>
+        <v>1258</v>
       </c>
       <c r="I298" s="45" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="299" spans="1:9" ht="14">
-      <c r="A299" s="82"/>
-      <c r="B299" s="44"/>
+    <row r="299" spans="1:9" ht="14" hidden="1">
+      <c r="A299" s="82">
+        <v>46236</v>
+      </c>
+      <c r="B299" s="44" t="s">
+        <v>1265</v>
+      </c>
       <c r="C299" s="83">
         <v>2630</v>
       </c>
@@ -19555,38 +19582,66 @@
         <v>162</v>
       </c>
       <c r="E299" s="44" t="s">
-        <v>1267</v>
+        <v>49</v>
       </c>
       <c r="F299" s="44"/>
       <c r="G299" s="44"/>
       <c r="H299" s="44" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
       <c r="I299" s="44" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="300" spans="1:9">
-      <c r="A300" s="84"/>
-      <c r="B300" s="45"/>
-      <c r="C300" s="85"/>
-      <c r="D300" s="45"/>
-      <c r="E300" s="45"/>
+    <row r="300" spans="1:9" ht="14" hidden="1">
+      <c r="A300" s="84">
+        <v>46238</v>
+      </c>
+      <c r="B300" s="45" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C300" s="85">
+        <v>1380</v>
+      </c>
+      <c r="D300" s="45" t="s">
+        <v>162</v>
+      </c>
+      <c r="E300" s="45" t="s">
+        <v>49</v>
+      </c>
       <c r="F300" s="46"/>
       <c r="G300" s="46"/>
-      <c r="H300" s="46"/>
-      <c r="I300" s="45"/>
-    </row>
-    <row r="301" spans="1:9">
-      <c r="A301" s="82"/>
-      <c r="B301" s="44"/>
-      <c r="C301" s="83"/>
-      <c r="D301" s="44"/>
-      <c r="E301" s="44"/>
+      <c r="H300" s="46" t="s">
+        <v>272</v>
+      </c>
+      <c r="I300" s="45" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="301" spans="1:9" ht="28" hidden="1">
+      <c r="A301" s="82">
+        <v>46238</v>
+      </c>
+      <c r="B301" s="44" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C301" s="83">
+        <v>12650</v>
+      </c>
+      <c r="D301" s="44" t="s">
+        <v>162</v>
+      </c>
+      <c r="E301" s="44" t="s">
+        <v>49</v>
+      </c>
       <c r="F301" s="44"/>
       <c r="G301" s="44"/>
-      <c r="H301" s="44"/>
-      <c r="I301" s="44"/>
+      <c r="H301" s="44" t="s">
+        <v>1268</v>
+      </c>
+      <c r="I301" s="44" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="302" spans="1:9">
       <c r="A302" s="84"/>
@@ -19897,7 +19952,13 @@
       <c r="I329" s="44"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I296" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <autoFilter ref="A1:I301" xr:uid="{00000000-0009-0000-0000-000004000000}">
+    <filterColumn colId="8">
+      <filters>
+        <filter val="Pending"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1258" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"Ordered,Pending,Completed,Cancelled"</formula1>
@@ -28324,7 +28385,7 @@
         <v>472</v>
       </c>
       <c r="L93" s="55" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="M93" s="55"/>
       <c r="N93" s="52" t="s">
@@ -28460,10 +28521,10 @@
         <v>1450</v>
       </c>
       <c r="F96" s="53">
+        <v>0</v>
+      </c>
+      <c r="G96" s="53">
         <v>1</v>
-      </c>
-      <c r="G96" s="53">
-        <v>0</v>
       </c>
       <c r="H96" s="52">
         <f t="shared" si="4"/>
@@ -28475,15 +28536,13 @@
       </c>
       <c r="J96" s="52">
         <f t="shared" si="5"/>
-        <v>1250</v>
+        <v>0</v>
       </c>
       <c r="K96" s="52">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="L96" s="52" t="s">
-        <v>1109</v>
-      </c>
+        <v>1250</v>
+      </c>
+      <c r="L96" s="52"/>
       <c r="M96" s="52"/>
       <c r="N96" s="52" t="s">
         <v>504</v>
@@ -29764,7 +29823,7 @@
         <v>3351.6266666666638</v>
       </c>
       <c r="L120" s="52" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="M120" s="52" t="s">
         <v>49</v>
@@ -29774,7 +29833,7 @@
       </c>
       <c r="O120" s="52"/>
       <c r="P120" s="52" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="Q120" s="52"/>
       <c r="R120" s="52"/>
@@ -31854,7 +31913,7 @@
         <v>0</v>
       </c>
       <c r="L147" s="55" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="M147" s="55"/>
       <c r="N147" s="55" t="s">
@@ -31906,7 +31965,7 @@
         <v>1004</v>
       </c>
       <c r="L148" s="52" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="M148" s="52"/>
       <c r="N148" s="52" t="s">
@@ -31958,7 +32017,7 @@
         <v>0</v>
       </c>
       <c r="L149" s="55" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="M149" s="55"/>
       <c r="N149" s="55" t="s">
@@ -32280,7 +32339,7 @@
         <v>949</v>
       </c>
       <c r="L155" s="55" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="M155" s="55"/>
       <c r="N155" s="55" t="s">
@@ -32756,7 +32815,7 @@
         <v>0</v>
       </c>
       <c r="L164" s="52" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="M164" s="52"/>
       <c r="N164" s="52" t="s">
@@ -33215,11 +33274,11 @@
         <v>1</v>
       </c>
       <c r="G173" s="64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H173" s="63">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I173" s="63">
         <f>IF(D173&lt;&gt;"",D173,IFERROR(E173/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
@@ -33231,14 +33290,14 @@
       </c>
       <c r="K173" s="63">
         <f t="shared" si="10"/>
-        <v>803.26</v>
+        <v>0</v>
       </c>
       <c r="L173" s="55" t="s">
         <v>416</v>
       </c>
       <c r="M173" s="55"/>
       <c r="N173" s="55" t="s">
-        <v>589</v>
+        <v>504</v>
       </c>
       <c r="O173" s="55"/>
       <c r="P173" s="55"/>
@@ -33765,7 +33824,7 @@
         <v>1676</v>
       </c>
       <c r="L183" s="55" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="M183" s="55"/>
       <c r="N183" s="55" t="s">
@@ -33795,10 +33854,10 @@
         <v>1380</v>
       </c>
       <c r="F184" s="66">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G184" s="66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H184" s="65">
         <f t="shared" ref="H184:H226" si="12">F184+IF(LEN(G184)=0,0,G184)</f>
@@ -33810,18 +33869,18 @@
       </c>
       <c r="J184" s="65">
         <f t="shared" si="9"/>
-        <v>16929</v>
+        <v>17820</v>
       </c>
       <c r="K184" s="65">
         <f t="shared" si="10"/>
-        <v>891</v>
+        <v>0</v>
       </c>
       <c r="L184" s="52" t="s">
-        <v>1143</v>
+        <v>1266</v>
       </c>
       <c r="M184" s="52"/>
       <c r="N184" s="52" t="s">
-        <v>589</v>
+        <v>504</v>
       </c>
       <c r="O184" s="52"/>
       <c r="P184" s="52"/>
@@ -33999,10 +34058,10 @@
         <v>1380</v>
       </c>
       <c r="F188" s="66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G188" s="66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H188" s="65">
         <f t="shared" si="12"/>
@@ -34014,18 +34073,18 @@
       </c>
       <c r="J188" s="65">
         <f t="shared" si="9"/>
-        <v>1782</v>
+        <v>891</v>
       </c>
       <c r="K188" s="65">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>891</v>
       </c>
       <c r="L188" s="52" t="s">
-        <v>1134</v>
+        <v>1270</v>
       </c>
       <c r="M188" s="52"/>
       <c r="N188" s="52" t="s">
-        <v>504</v>
+        <v>589</v>
       </c>
       <c r="O188" s="52"/>
       <c r="P188" s="52"/>
@@ -34073,7 +34132,7 @@
         <v>1782</v>
       </c>
       <c r="L189" s="55" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="M189" s="55"/>
       <c r="N189" s="55" t="s">
@@ -34081,7 +34140,7 @@
       </c>
       <c r="O189" s="55"/>
       <c r="P189" s="55" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="Q189" s="55"/>
       <c r="R189" s="55"/>
@@ -34127,7 +34186,7 @@
         <v>0</v>
       </c>
       <c r="L190" s="52" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="M190" s="52"/>
       <c r="N190" s="47" t="s">
@@ -34424,14 +34483,14 @@
         <v>3985</v>
       </c>
       <c r="L196" s="52" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="M196" s="52"/>
       <c r="N196" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P196" s="47" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="S196" s="47"/>
       <c r="T196" s="47"/>
@@ -34573,14 +34632,14 @@
         <v>1401</v>
       </c>
       <c r="L199" s="55" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="M199" s="55"/>
       <c r="N199" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P199" s="47" t="s">
-        <v>1206</v>
+        <v>1203</v>
       </c>
       <c r="S199" s="47"/>
       <c r="T199" s="47"/>
@@ -34726,14 +34785,14 @@
         <v>940</v>
       </c>
       <c r="L202" s="52" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="M202" s="52"/>
       <c r="N202" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P202" s="47" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="S202" s="47"/>
       <c r="T202" s="47"/>
@@ -35208,10 +35267,10 @@
         <v>1380</v>
       </c>
       <c r="F212" s="66">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="G212" s="66">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="H212" s="65">
         <f t="shared" si="12"/>
@@ -35223,14 +35282,14 @@
       </c>
       <c r="J212" s="65">
         <f t="shared" si="13"/>
-        <v>5349</v>
+        <v>15155.5</v>
       </c>
       <c r="K212" s="65">
         <f t="shared" si="14"/>
-        <v>23179</v>
+        <v>13372.5</v>
       </c>
       <c r="L212" s="52" t="s">
-        <v>1259</v>
+        <v>1269</v>
       </c>
       <c r="M212" s="52"/>
       <c r="N212" s="47" t="s">
@@ -35244,7 +35303,7 @@
         <v>1036</v>
       </c>
       <c r="B213" s="52" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="C213" s="52" t="s">
         <v>95</v>
@@ -35278,14 +35337,14 @@
         <v>3330</v>
       </c>
       <c r="L213" s="55" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="M213" s="55"/>
       <c r="N213" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P213" s="47" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="S213" s="47"/>
       <c r="T213" s="47"/>
@@ -35295,7 +35354,7 @@
         <v>1037</v>
       </c>
       <c r="B214" s="52" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="C214" s="52" t="s">
         <v>95</v>
@@ -35334,7 +35393,7 @@
         <v>678</v>
       </c>
       <c r="P214" s="47" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="S214" s="47"/>
       <c r="T214" s="47"/>
@@ -35344,7 +35403,7 @@
         <v>1038</v>
       </c>
       <c r="B215" s="55" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="C215" s="55" t="s">
         <v>95</v>
@@ -35378,14 +35437,14 @@
         <v>2976</v>
       </c>
       <c r="L215" s="55" t="s">
-        <v>1261</v>
+        <v>1257</v>
       </c>
       <c r="M215" s="55"/>
       <c r="N215" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P215" s="47" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="S215" s="47"/>
       <c r="T215" s="47"/>
@@ -35429,14 +35488,14 @@
         <v>2880</v>
       </c>
       <c r="L216" s="52" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="M216" s="52"/>
       <c r="N216" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P216" s="47" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="S216" s="47"/>
       <c r="T216" s="47"/>
@@ -35446,7 +35505,7 @@
         <v>1040</v>
       </c>
       <c r="B217" s="55" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="C217" s="55" t="s">
         <v>95</v>
@@ -35485,7 +35544,7 @@
         <v>678</v>
       </c>
       <c r="P217" s="47" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="S217" s="47"/>
       <c r="T217" s="47"/>
@@ -35495,7 +35554,7 @@
         <v>1041</v>
       </c>
       <c r="B218" s="52" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="C218" s="52" t="s">
         <v>95</v>
@@ -35529,14 +35588,14 @@
         <v>828</v>
       </c>
       <c r="L218" s="52" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="M218" s="52"/>
       <c r="N218" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P218" s="47" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="S218" s="47"/>
       <c r="T218" s="47"/>
@@ -35546,7 +35605,7 @@
         <v>1042</v>
       </c>
       <c r="B219" s="55" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="C219" s="55" t="s">
         <v>95</v>
@@ -35580,14 +35639,14 @@
         <v>2283</v>
       </c>
       <c r="L219" s="55" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="M219" s="55"/>
       <c r="N219" s="47" t="s">
         <v>678</v>
       </c>
       <c r="P219" s="47" t="s">
-        <v>1209</v>
+        <v>1206</v>
       </c>
       <c r="S219" s="47"/>
       <c r="T219" s="47"/>
@@ -35597,7 +35656,7 @@
         <v>1043</v>
       </c>
       <c r="B220" s="52" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="C220" s="52" t="s">
         <v>95</v>
@@ -35631,14 +35690,14 @@
         <v>3805</v>
       </c>
       <c r="L220" s="52" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="M220" s="52"/>
       <c r="N220" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P220" s="47" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="S220" s="47"/>
       <c r="T220" s="47"/>
@@ -35648,7 +35707,7 @@
         <v>1044</v>
       </c>
       <c r="B221" s="55" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="C221" s="55" t="s">
         <v>95</v>
@@ -35687,7 +35746,7 @@
         <v>678</v>
       </c>
       <c r="P221" s="47" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="S221" s="47"/>
       <c r="T221" s="47"/>
@@ -35697,7 +35756,7 @@
         <v>1045</v>
       </c>
       <c r="B222" s="52" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="C222" s="52" t="s">
         <v>96</v>
@@ -35736,7 +35795,7 @@
         <v>678</v>
       </c>
       <c r="P222" s="86" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="S222" s="47"/>
       <c r="T222" s="47"/>
@@ -35746,7 +35805,7 @@
         <v>1046</v>
       </c>
       <c r="B223" s="55" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="C223" s="55" t="s">
         <v>95</v>
@@ -35785,7 +35844,7 @@
         <v>678</v>
       </c>
       <c r="P223" s="86" t="s">
-        <v>1239</v>
+        <v>1236</v>
       </c>
       <c r="S223" s="47"/>
       <c r="T223" s="47"/>
@@ -35795,7 +35854,7 @@
         <v>1047</v>
       </c>
       <c r="B224" s="52" t="s">
-        <v>1213</v>
+        <v>1210</v>
       </c>
       <c r="C224" s="52" t="s">
         <v>95</v>
@@ -35810,11 +35869,11 @@
         <v>1</v>
       </c>
       <c r="G224" s="66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H224" s="65">
         <f t="shared" si="12"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I224" s="65">
         <f>IF(D224&lt;&gt;"",D224,IFERROR(E224/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
@@ -35826,17 +35885,17 @@
       </c>
       <c r="K224" s="65">
         <f t="shared" si="14"/>
-        <v>1884</v>
+        <v>942</v>
       </c>
       <c r="L224" s="52" t="s">
-        <v>1264</v>
+        <v>1260</v>
       </c>
       <c r="M224" s="52"/>
       <c r="N224" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P224" s="86" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="S224" s="47"/>
       <c r="T224" s="47"/>
@@ -35846,7 +35905,7 @@
         <v>1048</v>
       </c>
       <c r="B225" s="55" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="C225" s="55" t="s">
         <v>95</v>
@@ -35885,7 +35944,7 @@
         <v>678</v>
       </c>
       <c r="P225" s="86" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
       <c r="S225" s="47"/>
       <c r="T225" s="47"/>
@@ -35895,7 +35954,7 @@
         <v>1049</v>
       </c>
       <c r="B226" s="52" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="C226" s="52" t="s">
         <v>95</v>
@@ -35934,17 +35993,17 @@
         <v>678</v>
       </c>
       <c r="P226" s="86" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="S226" s="47"/>
       <c r="T226" s="47"/>
     </row>
     <row r="227" spans="1:20" ht="17">
       <c r="A227" s="52" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="B227" s="55" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="C227" s="55" t="s">
         <v>95</v>
@@ -35983,17 +36042,17 @@
         <v>678</v>
       </c>
       <c r="P227" s="86" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
       <c r="S227" s="47"/>
       <c r="T227" s="47"/>
     </row>
     <row r="228" spans="1:20" ht="17">
       <c r="A228" s="55" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
       <c r="B228" s="52" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="C228" s="52" t="s">
         <v>95</v>
@@ -36032,17 +36091,17 @@
         <v>678</v>
       </c>
       <c r="P228" s="86" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="S228" s="47"/>
       <c r="T228" s="47"/>
     </row>
     <row r="229" spans="1:20" ht="17">
       <c r="A229" s="52" t="s">
-        <v>1228</v>
+        <v>1225</v>
       </c>
       <c r="B229" s="55" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
       <c r="C229" s="55" t="s">
         <v>95</v>
@@ -36081,17 +36140,17 @@
         <v>678</v>
       </c>
       <c r="P229" s="86" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="S229" s="47"/>
       <c r="T229" s="47"/>
     </row>
     <row r="230" spans="1:20" ht="17">
       <c r="A230" s="55" t="s">
-        <v>1229</v>
+        <v>1226</v>
       </c>
       <c r="B230" s="52" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="C230" s="52" t="s">
         <v>95</v>
@@ -36125,24 +36184,24 @@
         <v>1564</v>
       </c>
       <c r="L230" s="52" t="s">
-        <v>1269</v>
+        <v>1263</v>
       </c>
       <c r="M230" s="52"/>
       <c r="N230" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P230" s="86" t="s">
-        <v>1268</v>
+        <v>1262</v>
       </c>
       <c r="S230" s="47"/>
       <c r="T230" s="47"/>
     </row>
     <row r="231" spans="1:20" ht="17">
       <c r="A231" s="52" t="s">
-        <v>1230</v>
+        <v>1227</v>
       </c>
       <c r="B231" s="55" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
       <c r="C231" s="55" t="s">
         <v>95</v>
@@ -36181,17 +36240,17 @@
         <v>678</v>
       </c>
       <c r="P231" s="86" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
       <c r="S231" s="47"/>
       <c r="T231" s="47"/>
     </row>
     <row r="232" spans="1:20" ht="17">
       <c r="A232" s="52" t="s">
-        <v>1231</v>
+        <v>1228</v>
       </c>
       <c r="B232" s="52" t="s">
-        <v>1220</v>
+        <v>1217</v>
       </c>
       <c r="C232" s="52" t="s">
         <v>95</v>
@@ -36230,17 +36289,17 @@
         <v>678</v>
       </c>
       <c r="P232" s="86" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="S232" s="47"/>
       <c r="T232" s="47"/>
     </row>
     <row r="233" spans="1:20" ht="17">
       <c r="A233" s="55" t="s">
-        <v>1232</v>
+        <v>1229</v>
       </c>
       <c r="B233" s="55" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
       <c r="C233" s="55" t="s">
         <v>95</v>
@@ -36274,24 +36333,24 @@
         <v>0</v>
       </c>
       <c r="L233" s="55" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
       <c r="M233" s="55"/>
       <c r="N233" s="47" t="s">
         <v>504</v>
       </c>
       <c r="P233" s="86" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="S233" s="47"/>
       <c r="T233" s="47"/>
     </row>
     <row r="234" spans="1:20" ht="17">
       <c r="A234" s="52" t="s">
-        <v>1233</v>
+        <v>1230</v>
       </c>
       <c r="B234" s="52" t="s">
-        <v>1222</v>
+        <v>1219</v>
       </c>
       <c r="C234" s="52" t="s">
         <v>95</v>
@@ -36309,8 +36368,7 @@
         <v>5</v>
       </c>
       <c r="H234" s="65">
-        <f t="shared" si="15"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I234" s="65">
         <f>IF(D234&lt;&gt;"",D234,IFERROR(E234/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
@@ -36330,17 +36388,17 @@
         <v>678</v>
       </c>
       <c r="P234" s="86" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="S234" s="47"/>
       <c r="T234" s="47"/>
     </row>
     <row r="235" spans="1:20" ht="17">
       <c r="A235" s="55" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="B235" s="55" t="s">
-        <v>1223</v>
+        <v>1220</v>
       </c>
       <c r="C235" s="55" t="s">
         <v>95</v>
@@ -36379,14 +36437,14 @@
         <v>678</v>
       </c>
       <c r="P235" s="86" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="S235" s="47"/>
       <c r="T235" s="47"/>
     </row>
     <row r="236" spans="1:20" ht="17">
       <c r="A236" s="52" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
       <c r="B236" s="52" t="s">
         <v>510</v>
@@ -36428,17 +36486,17 @@
         <v>678</v>
       </c>
       <c r="P236" s="86" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
       <c r="S236" s="47"/>
       <c r="T236" s="47"/>
     </row>
     <row r="237" spans="1:20" ht="17">
       <c r="A237" s="52" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
       <c r="B237" s="55" t="s">
-        <v>1224</v>
+        <v>1221</v>
       </c>
       <c r="C237" s="55" t="s">
         <v>95</v>
@@ -36477,17 +36535,17 @@
         <v>678</v>
       </c>
       <c r="P237" s="86" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="S237" s="47"/>
       <c r="T237" s="47"/>
     </row>
     <row r="238" spans="1:20" ht="17">
       <c r="A238" s="55" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="B238" s="52" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="C238" s="52" t="s">
         <v>95</v>
@@ -36526,7 +36584,7 @@
         <v>678</v>
       </c>
       <c r="P238" s="86" t="s">
-        <v>1251</v>
+        <v>1248</v>
       </c>
       <c r="S238" s="47"/>
       <c r="T238" s="47"/>
@@ -40448,15 +40506,15 @@
       </c>
       <c r="B8" s="9">
         <f>IFERROR(SUMIF(Purchases!$B:$B,$A8,Purchases!$C:$C),0)</f>
-        <v>252430</v>
+        <v>261817</v>
       </c>
       <c r="C8" s="9">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>185449</v>
+        <v>188578</v>
       </c>
       <c r="D8" s="9">
         <f>B8-C8</f>
-        <v>66981</v>
+        <v>73239</v>
       </c>
       <c r="E8" s="9">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A8,$A$3:$B$5,2,FALSE()),0)</f>
@@ -40464,7 +40522,7 @@
       </c>
       <c r="F8" s="9">
         <f>D8+E8</f>
-        <v>66981</v>
+        <v>73239</v>
       </c>
       <c r="G8" s="9">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A8,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A8,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A8,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A8,$B$13:$B$499,"Profit"),0)</f>
@@ -40472,7 +40530,7 @@
       </c>
       <c r="H8" s="73">
         <f>F8-G8</f>
-        <v>48677.66</v>
+        <v>54935.66</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="13.5" customHeight="1">
@@ -40485,11 +40543,11 @@
       </c>
       <c r="C9" s="11">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>185449</v>
+        <v>188578</v>
       </c>
       <c r="D9" s="11">
         <f>B9-C9</f>
-        <v>85868</v>
+        <v>82739</v>
       </c>
       <c r="E9" s="11">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A9,$A$3:$B$5,2,FALSE()),0)</f>
@@ -40497,7 +40555,7 @@
       </c>
       <c r="F9" s="11">
         <f>D9+E9</f>
-        <v>85868</v>
+        <v>82739</v>
       </c>
       <c r="G9" s="11">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A9,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A9,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A9,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A9,$B$13:$B$499,"Profit"),0)</f>
@@ -40505,7 +40563,7 @@
       </c>
       <c r="H9" s="74">
         <f>F9-G9</f>
-        <v>44228.67</v>
+        <v>41099.67</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="13.5" customHeight="1">
@@ -40518,11 +40576,11 @@
       </c>
       <c r="C10" s="9">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>185449</v>
+        <v>188578</v>
       </c>
       <c r="D10" s="9">
         <f>B10-C10</f>
-        <v>-152849</v>
+        <v>-155978</v>
       </c>
       <c r="E10" s="9">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A10,$A$3:$B$5,2,FALSE()),0)</f>
@@ -40530,7 +40588,7 @@
       </c>
       <c r="F10" s="9">
         <f>D10+E10</f>
-        <v>-152849</v>
+        <v>-155978</v>
       </c>
       <c r="G10" s="9">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A10,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A10,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A10,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A10,$B$13:$B$499,"Profit"),0)</f>
@@ -40538,7 +40596,7 @@
       </c>
       <c r="H10" s="73">
         <f>F10-G10</f>
-        <v>-92906.33</v>
+        <v>-96035.33</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="75" customFormat="1" ht="15.75" customHeight="1">
@@ -40955,7 +41013,7 @@
       </c>
       <c r="B4" s="9">
         <f>IFERROR(SUMIFS(Sales!$C:$C,Sales!$E:$E,$A4,Sales!$I:$I,"Completed"),0)</f>
-        <v>416139</v>
+        <v>432799</v>
       </c>
       <c r="C4" s="9">
         <f>VLOOKUP($A4,PartnerShares!$A$3:$B$5,2,FALSE())</f>
@@ -40963,11 +41021,11 @@
       </c>
       <c r="D4" s="9">
         <f>Summary!$B$4*C4</f>
-        <v>162006.72819999998</v>
+        <v>166684.3302</v>
       </c>
       <c r="E4" s="9">
         <f>B4-D4</f>
-        <v>254132.27180000002</v>
+        <v>266114.66980000003</v>
       </c>
       <c r="F4" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -40975,7 +41033,7 @@
       </c>
       <c r="G4" s="73">
         <f>E4+F4</f>
-        <v>116822.2458</v>
+        <v>128804.64380000002</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5" customHeight="1">
@@ -40992,11 +41050,11 @@
       </c>
       <c r="D5" s="11">
         <f>Summary!$B$4*C5</f>
-        <v>161909.5436</v>
+        <v>166584.33960000001</v>
       </c>
       <c r="E5" s="11">
         <f>B5-D5</f>
-        <v>-107285.5436</v>
+        <v>-111960.33960000001</v>
       </c>
       <c r="F5" s="11">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -41004,7 +41062,7 @@
       </c>
       <c r="G5" s="74">
         <f>E5+F5</f>
-        <v>-35698.501600000003</v>
+        <v>-40373.297600000005</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1">
@@ -41021,11 +41079,11 @@
       </c>
       <c r="D6" s="9">
         <f>Summary!$B$4*C6</f>
-        <v>162006.72819999998</v>
+        <v>166684.3302</v>
       </c>
       <c r="E6" s="9">
         <f>B6-D6</f>
-        <v>-149476.72819999998</v>
+        <v>-154154.3302</v>
       </c>
       <c r="F6" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -41033,7 +41091,7 @@
       </c>
       <c r="G6" s="73">
         <f>E6+F6</f>
-        <v>-83753.744199999972</v>
+        <v>-88431.346199999985</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="13.5" customHeight="1">

--- a/docs/Chiraath-Summary-Aug26.xlsx
+++ b/docs/Chiraath-Summary-Aug26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anooppremachandran/Desktop/CHIRAATH/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7C75C7A-EEE0-084B-9EE7-9AB4653532A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ECEDE02-61C1-EF40-ACB7-5D1A4391069E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3279" uniqueCount="1308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3282" uniqueCount="1310">
   <si>
     <t>Notes:</t>
   </si>
@@ -3988,6 +3988,12 @@
   </si>
   <si>
     <t>CHR-153 (XXL)-Cotton whine 3 piece salwar, CHR-155 (XXL) -Cotton black 3 piece salwar, CHR-51(XXL)-Mul cotton floral salwar  - 1000 advance, 1500 pending</t>
+  </si>
+  <si>
+    <t>Sumesh Hyderabad</t>
+  </si>
+  <si>
+    <t>CHR-188 - Red/Green banarasi (Advance - 700)</t>
   </si>
 </sst>
 </file>
@@ -5805,7 +5811,7 @@
                   <c:v>63646</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>32239</c:v>
+                  <c:v>33619</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -6245,7 +6251,7 @@
                   <c:v>-38554</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>22852</c:v>
+                  <c:v>24232</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -7913,7 +7919,7 @@
       </c>
       <c r="B5" s="12">
         <f>SUM(Sales!C:C)</f>
-        <v>524383</v>
+        <v>525763</v>
       </c>
       <c r="E5" s="11" t="str">
         <f>PartnerShares!A4</f>
@@ -8540,11 +8546,11 @@
       </c>
       <c r="C17" s="27">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$994,"MMM")=$A17)*(YEAR(Sales!$A$2:$A$994)=$B$7)*Sales!$C$2:$C$994),0)</f>
-        <v>32239</v>
+        <v>33619</v>
       </c>
       <c r="D17" s="27">
         <f t="shared" si="0"/>
-        <v>22852</v>
+        <v>24232</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1">
@@ -19792,16 +19798,26 @@
         <v>356</v>
       </c>
     </row>
-    <row r="304" spans="1:9">
-      <c r="A304" s="84"/>
-      <c r="B304" s="45"/>
-      <c r="C304" s="85"/>
+    <row r="304" spans="1:9" ht="14">
+      <c r="A304" s="84">
+        <v>46243</v>
+      </c>
+      <c r="B304" s="45" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C304" s="85">
+        <v>1380</v>
+      </c>
       <c r="D304" s="45"/>
       <c r="E304" s="45"/>
       <c r="F304" s="46"/>
       <c r="G304" s="46"/>
-      <c r="H304" s="46"/>
-      <c r="I304" s="45"/>
+      <c r="H304" s="46" t="s">
+        <v>1309</v>
+      </c>
+      <c r="I304" s="45" t="s">
+        <v>356</v>
+      </c>
     </row>
     <row r="305" spans="1:9">
       <c r="A305" s="82"/>

--- a/docs/Chiraath-Summary-Aug26.xlsx
+++ b/docs/Chiraath-Summary-Aug26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anooppremachandran/Desktop/CHIRAATH/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ECEDE02-61C1-EF40-ACB7-5D1A4391069E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABC88D0A-F7CD-8844-87D4-99D4D4BD461E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3282" uniqueCount="1310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3300" uniqueCount="1318">
   <si>
     <t>Notes:</t>
   </si>
@@ -3364,14 +3364,6 @@
     <t>CHR-180 - Cotton Salwar (XXL)</t>
   </si>
   <si>
-    <t>Peacok Blue/Maroon - 1,
-Navy Blue/Maroon - 2,
-Grey/Blue - 1, Purple/Green - 1</t>
-  </si>
-  <si>
-    <t>Sherin - Maroon/navy blue(1099), Lakshmi - Navy Blue &amp; Maroon, Jaimy - Peacok Blue/Maroon, Shinoob Cousin - Lavender/Violet, Shinoob friend - Peacok Blue/Maroon(1200)</t>
-  </si>
-  <si>
     <t>CHR-174 Matka new design Peacok Blue/Maroon</t>
   </si>
   <si>
@@ -3783,9 +3775,6 @@
     <t>Blue, Beige/Green, Orange/Maroon</t>
   </si>
   <si>
-    <t>Pink with Silver Butas, Black/Red, Wine/Green, Yellow/Black</t>
-  </si>
-  <si>
     <t>1479 - Jiji Fried</t>
   </si>
   <si>
@@ -3795,12 +3784,6 @@
     <t>CHR-182 (Yellow Linen Saree with Lotus, CHR-217 cream/gold with stars and paisley &amp; cream/gold with flowers - 1000 advance, 900 - pending</t>
   </si>
   <si>
-    <t>Asha Sharath (Haritha Karma Sena Bulk Order)</t>
-  </si>
-  <si>
-    <t>Asha Sharath (Haritha Karma Sena Bulk - 6 pieces)</t>
-  </si>
-  <si>
     <t>Parrot Green Banarasi - 6 pieces from bulk</t>
   </si>
   <si>
@@ -3831,9 +3814,6 @@
     <t>Sheeba George, Soji Thomas, Jessy Joseph, Jeeja Anil ,Sanam, Geetha, Sushama Bhaskar, Divya Jacob, Baby Johny, Jayasree, Navya, Bindu Saji, Vanajakshi, Dison Jose, Akshitha, Bahuleyan, Urmila, Gincy Jibi, Razia Salim, Komalavalli</t>
   </si>
   <si>
-    <t>Asha Sharath (Haritha Karma Sena Bulk - 11 pieces)</t>
-  </si>
-  <si>
     <t>Parrot Green Banarasi - 11 pieces from bulk</t>
   </si>
   <si>
@@ -3994,6 +3974,50 @@
   </si>
   <si>
     <t>CHR-188 - Red/Green banarasi (Advance - 700)</t>
+  </si>
+  <si>
+    <t>Dr.Rehna S</t>
+  </si>
+  <si>
+    <t>CHR-235-Silk Saree - Yellow/Black</t>
+  </si>
+  <si>
+    <t>Dr.Reshna - Yellow/Black</t>
+  </si>
+  <si>
+    <t>Pink with Silver Butas, Black/Red, Wine/Green</t>
+  </si>
+  <si>
+    <t>Nisha Shaju</t>
+  </si>
+  <si>
+    <t>CHR-174 Matka Peacock blue/maroon</t>
+  </si>
+  <si>
+    <t>Purple/Green - 1,
+Navy Blue/Maroon - 2,
+Grey/Blue - 1</t>
+  </si>
+  <si>
+    <t>Sherin - Maroon/navy blue(1099), Lakshmi - Navy Blue &amp; Maroon, Jaimy - Peacok Blue/Maroon, Shinoob Cousin - Lavender/Violet, Shinoob friend - Peacok Blue/Maroon(1200), Nisha Shaji - Peacok Blue/Maroon(1250)</t>
+  </si>
+  <si>
+    <t>DTDC parcel charges</t>
+  </si>
+  <si>
+    <t>Asha Binu (Haritha Karma Sena Bulk Order)</t>
+  </si>
+  <si>
+    <t>Asha Binu (Haritha Karma Sena Bulk - 6 pieces)</t>
+  </si>
+  <si>
+    <t>Asha Binu (Haritha Karma Sena Bulk - 11 pieces)</t>
+  </si>
+  <si>
+    <t>Asha Binu (Advance for Bulk 5 saree)</t>
+  </si>
+  <si>
+    <t>Parrot Green Banarasi - advance</t>
   </si>
 </sst>
 </file>
@@ -4879,7 +4903,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>323</c:v>
+                  <c:v>325</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>98</c:v>
@@ -4982,7 +5006,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>206</c:v>
+                  <c:v>204</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>52</c:v>
@@ -5315,7 +5339,7 @@
                   <c:v>54964</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>149497.89666666664</c:v>
+                  <c:v>147887.64666666664</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>1062</c:v>
@@ -5651,7 +5675,7 @@
                   <c:v>102200</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>9387</c:v>
+                  <c:v>9957</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -5811,7 +5835,7 @@
                   <c:v>63646</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>33619</c:v>
+                  <c:v>41999</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -6251,7 +6275,7 @@
                   <c:v>-38554</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>24232</c:v>
+                  <c:v>32042</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -6712,10 +6736,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>426</c:v>
+                  <c:v>428</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>303</c:v>
+                  <c:v>301</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7887,7 +7911,7 @@
       </c>
       <c r="B3" s="8">
         <f>SUM(Purchases!C:C)</f>
-        <v>565734</v>
+        <v>566304</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>42</v>
@@ -7902,7 +7926,7 @@
       </c>
       <c r="B4" s="10">
         <f>SUMIFS(Sales!C:C, Sales!I:I, "Completed")</f>
-        <v>500953</v>
+        <v>509333</v>
       </c>
       <c r="E4" s="9" t="str">
         <f>PartnerShares!A3</f>
@@ -7919,7 +7943,7 @@
       </c>
       <c r="B5" s="12">
         <f>SUM(Sales!C:C)</f>
-        <v>525763</v>
+        <v>534143</v>
       </c>
       <c r="E5" s="11" t="str">
         <f>PartnerShares!A4</f>
@@ -7936,7 +7960,7 @@
       </c>
       <c r="B6" s="10">
         <f>B4-B3</f>
-        <v>-64781</v>
+        <v>-56971</v>
       </c>
       <c r="E6" s="9" t="str">
         <f>PartnerShares!A5</f>
@@ -7971,7 +7995,7 @@
       </c>
       <c r="B10" s="13">
         <f>PartnerShares!H8</f>
-        <v>54935.66</v>
+        <v>55315.66</v>
       </c>
       <c r="C10" s="9"/>
     </row>
@@ -7981,7 +8005,7 @@
       </c>
       <c r="B11" s="14">
         <f>PartnerShares!H9</f>
-        <v>41099.67</v>
+        <v>40909.67</v>
       </c>
       <c r="C11" s="11"/>
     </row>
@@ -7991,7 +8015,7 @@
       </c>
       <c r="B12" s="13">
         <f>PartnerShares!H10</f>
-        <v>-96035.33</v>
+        <v>-96225.33</v>
       </c>
       <c r="C12" s="9"/>
     </row>
@@ -8030,15 +8054,15 @@
       </c>
       <c r="B18" s="10">
         <f>PartnerShares!B8</f>
-        <v>261817</v>
+        <v>262387</v>
       </c>
       <c r="C18" s="10">
         <f>PartnerShares!C8</f>
-        <v>188578</v>
+        <v>188768</v>
       </c>
       <c r="D18" s="10">
         <f>PartnerShares!D8</f>
-        <v>73239</v>
+        <v>73619</v>
       </c>
       <c r="E18" s="10">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A18,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A18,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -8046,11 +8070,11 @@
       </c>
       <c r="F18" s="13">
         <f>D18-E18</f>
-        <v>54935.66</v>
+        <v>55315.66</v>
       </c>
       <c r="G18" s="16" t="str">
         <f>IF(ROUND(F18,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F18),"#,##0"),IF(ROUND(F18,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F18),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹54,936</v>
+        <v>Receive ₹55,316</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="13.5" customHeight="1">
@@ -8064,11 +8088,11 @@
       </c>
       <c r="C19" s="12">
         <f>PartnerShares!C9</f>
-        <v>188578</v>
+        <v>188768</v>
       </c>
       <c r="D19" s="12">
         <f>PartnerShares!D9</f>
-        <v>82739</v>
+        <v>82549</v>
       </c>
       <c r="E19" s="12">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A19,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A19,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -8076,11 +8100,11 @@
       </c>
       <c r="F19" s="14">
         <f>D19-E19</f>
-        <v>41099.67</v>
+        <v>40909.67</v>
       </c>
       <c r="G19" s="17" t="str">
         <f>IF(ROUND(F19,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F19),"#,##0"),IF(ROUND(F19,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F19),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹41,100</v>
+        <v>Receive ₹40,910</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="13.5" customHeight="1">
@@ -8094,11 +8118,11 @@
       </c>
       <c r="C20" s="10">
         <f>PartnerShares!C10</f>
-        <v>188578</v>
+        <v>188768</v>
       </c>
       <c r="D20" s="10">
         <f>PartnerShares!D10</f>
-        <v>-155978</v>
+        <v>-156168</v>
       </c>
       <c r="E20" s="10">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A20,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A20,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -8106,11 +8130,11 @@
       </c>
       <c r="F20" s="13">
         <f>D20-E20</f>
-        <v>-96035.33</v>
+        <v>-96225.33</v>
       </c>
       <c r="G20" s="17" t="str">
         <f>IF(ROUND(F20,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F20),"#,##0"),IF(ROUND(F20,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F20),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹96,035</v>
+        <v>Pay ₹96,225</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.75" customHeight="1">
@@ -8148,15 +8172,15 @@
       </c>
       <c r="B26" s="10">
         <f>'Cash Pool'!B4</f>
-        <v>432799</v>
+        <v>441179</v>
       </c>
       <c r="C26" s="10">
         <f>'Cash Pool'!D4</f>
-        <v>167017.73019999999</v>
+        <v>169811.62219999998</v>
       </c>
       <c r="D26" s="10">
         <f>'Cash Pool'!E4</f>
-        <v>265781.26980000001</v>
+        <v>271367.37780000002</v>
       </c>
       <c r="E26" s="10">
         <f>'Cash Pool'!F4</f>
@@ -8164,11 +8188,11 @@
       </c>
       <c r="F26" s="13">
         <f>'Cash Pool'!G4</f>
-        <v>128471.2438</v>
+        <v>134057.3518</v>
       </c>
       <c r="G26" s="17" t="str">
         <f>IF(ROUND(F26,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F26),"#,##0"),IF(ROUND(F26,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F26),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹128,471</v>
+        <v>Pay ₹134,057</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="13.5" customHeight="1">
@@ -8182,11 +8206,11 @@
       </c>
       <c r="C27" s="12">
         <f>'Cash Pool'!D5</f>
-        <v>166917.53959999999</v>
+        <v>169709.7556</v>
       </c>
       <c r="D27" s="12">
         <f>'Cash Pool'!E5</f>
-        <v>-112293.53959999999</v>
+        <v>-115085.7556</v>
       </c>
       <c r="E27" s="12">
         <f>'Cash Pool'!F5</f>
@@ -8194,11 +8218,11 @@
       </c>
       <c r="F27" s="14">
         <f>'Cash Pool'!G5</f>
-        <v>-40706.497599999988</v>
+        <v>-43498.713600000003</v>
       </c>
       <c r="G27" s="18" t="str">
         <f>IF(ROUND(F27,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F27),"#,##0"),IF(ROUND(F27,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F27),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹40,706</v>
+        <v>Receive ₹43,499</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="13.5" customHeight="1">
@@ -8212,11 +8236,11 @@
       </c>
       <c r="C28" s="10">
         <f>'Cash Pool'!D6</f>
-        <v>167017.73019999999</v>
+        <v>169811.62219999998</v>
       </c>
       <c r="D28" s="10">
         <f>'Cash Pool'!E6</f>
-        <v>-154487.73019999999</v>
+        <v>-157281.62219999998</v>
       </c>
       <c r="E28" s="10">
         <f>'Cash Pool'!F6</f>
@@ -8224,11 +8248,11 @@
       </c>
       <c r="F28" s="13">
         <f>'Cash Pool'!G6</f>
-        <v>-88764.74619999998</v>
+        <v>-91558.638199999972</v>
       </c>
       <c r="G28" s="16" t="str">
         <f>IF(ROUND(F28,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F28),"#,##0"),IF(ROUND(F28,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F28),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹88,765</v>
+        <v>Receive ₹91,559</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.75" customHeight="1">
@@ -8349,14 +8373,14 @@
       </c>
       <c r="B5" s="21">
         <f>Summary!B3</f>
-        <v>565734</v>
+        <v>566304</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>69</v>
       </c>
       <c r="E5" s="21">
         <f>Summary!B4</f>
-        <v>500953</v>
+        <v>509333</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
@@ -8365,14 +8389,14 @@
       </c>
       <c r="B6" s="21">
         <f>Summary!B6</f>
-        <v>-64781</v>
+        <v>-56971</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>71</v>
       </c>
       <c r="E6" s="21">
         <f>SUMIFS(INVENTORY!K:K, INVENTORY!N:N, "&lt;&gt;Sold Out")</f>
-        <v>194653.09666666665</v>
+        <v>193042.84666666665</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1">
@@ -8424,7 +8448,7 @@
       </c>
       <c r="G10" s="21">
         <f>SUM(INVENTORY!F:F)</f>
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1">
@@ -8448,7 +8472,7 @@
       </c>
       <c r="G11" s="27">
         <f>SUM(INVENTORY!G:G)</f>
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
@@ -8542,15 +8566,15 @@
       </c>
       <c r="B17" s="27">
         <f>IFERROR(SUMPRODUCT((TEXT(Purchases!$A$2:$A$998,"MMM")=$A17)*(YEAR(Purchases!$A$2:$A$998)=$B$7)*Purchases!$C$2:$C$998),0)</f>
-        <v>9387</v>
+        <v>9957</v>
       </c>
       <c r="C17" s="27">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$994,"MMM")=$A17)*(YEAR(Sales!$A$2:$A$994)=$B$7)*Sales!$C$2:$C$994),0)</f>
-        <v>33619</v>
+        <v>41999</v>
       </c>
       <c r="D17" s="27">
         <f t="shared" si="0"/>
-        <v>24232</v>
+        <v>32042</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1">
@@ -8644,11 +8668,11 @@
       </c>
       <c r="G47" s="30">
         <f>SUMIF(INVENTORY!C:C, F47, INVENTORY!F:F)</f>
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H47" s="30">
         <f>SUMIF(INVENTORY!C:C, F47, INVENTORY!G:G)</f>
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="J47" s="30" t="s">
         <v>96</v>
@@ -8675,7 +8699,7 @@
       </c>
       <c r="K48" s="31">
         <f t="array" ref="K48">SUMPRODUCT((INVENTORY!$C$2:$C$477=J48)*(INVENTORY!$D$2:$D$477)*(INVENTORY!$G$2:$G$477))</f>
-        <v>149497.89666666664</v>
+        <v>147887.64666666664</v>
       </c>
     </row>
     <row r="49" spans="5:12" ht="15" customHeight="1">
@@ -10048,7 +10072,7 @@
         <v>28526</v>
       </c>
       <c r="D91" s="39" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="15" customHeight="1">
@@ -10118,7 +10142,7 @@
         <v>70</v>
       </c>
       <c r="D96" s="36" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="15" customHeight="1">
@@ -10132,7 +10156,7 @@
         <v>1375</v>
       </c>
       <c r="D97" s="39" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="15" customHeight="1">
@@ -10146,7 +10170,7 @@
         <v>189</v>
       </c>
       <c r="D98" s="36" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="15" customHeight="1">
@@ -10262,10 +10286,18 @@
       </c>
     </row>
     <row r="107" spans="1:4" ht="15" customHeight="1">
-      <c r="A107" s="38"/>
-      <c r="B107" s="39"/>
-      <c r="C107" s="40"/>
-      <c r="D107" s="39"/>
+      <c r="A107" s="38">
+        <v>46241</v>
+      </c>
+      <c r="B107" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="C107" s="40">
+        <v>570</v>
+      </c>
+      <c r="D107" s="39" t="s">
+        <v>1312</v>
+      </c>
     </row>
     <row r="108" spans="1:4" ht="15" customHeight="1">
       <c r="A108" s="35"/>
@@ -18720,7 +18752,7 @@
       <c r="F259" s="46"/>
       <c r="G259" s="46"/>
       <c r="H259" s="46" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="I259" s="45" t="s">
         <v>148</v>
@@ -18731,7 +18763,7 @@
         <v>46205</v>
       </c>
       <c r="B260" s="44" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="C260" s="83">
         <v>1500</v>
@@ -18745,7 +18777,7 @@
       <c r="F260" s="44"/>
       <c r="G260" s="44"/>
       <c r="H260" s="44" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="I260" s="44" t="s">
         <v>148</v>
@@ -18756,7 +18788,7 @@
         <v>46205</v>
       </c>
       <c r="B261" s="45" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="C261" s="85">
         <v>2600</v>
@@ -18770,7 +18802,7 @@
       <c r="F261" s="46"/>
       <c r="G261" s="46"/>
       <c r="H261" s="46" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="I261" s="45" t="s">
         <v>148</v>
@@ -18781,7 +18813,7 @@
         <v>46206</v>
       </c>
       <c r="B262" s="44" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="C262" s="83">
         <v>1380</v>
@@ -18806,7 +18838,7 @@
         <v>46206</v>
       </c>
       <c r="B263" s="45" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="C263" s="85">
         <v>1380</v>
@@ -18831,7 +18863,7 @@
         <v>46206</v>
       </c>
       <c r="B264" s="44" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="C264" s="83">
         <v>2500</v>
@@ -18845,7 +18877,7 @@
       <c r="F264" s="44"/>
       <c r="G264" s="44"/>
       <c r="H264" s="44" t="s">
-        <v>1307</v>
+        <v>1301</v>
       </c>
       <c r="I264" s="44" t="s">
         <v>356</v>
@@ -18856,7 +18888,7 @@
         <v>46206</v>
       </c>
       <c r="B265" s="45" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="C265" s="85">
         <v>1300</v>
@@ -18870,7 +18902,7 @@
       <c r="F265" s="46"/>
       <c r="G265" s="46"/>
       <c r="H265" s="46" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="I265" s="45" t="s">
         <v>356</v>
@@ -18881,7 +18913,7 @@
         <v>46206</v>
       </c>
       <c r="B266" s="44" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="C266" s="83">
         <v>1380</v>
@@ -18895,7 +18927,7 @@
       <c r="F266" s="44"/>
       <c r="G266" s="44"/>
       <c r="H266" s="44" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="I266" s="44" t="s">
         <v>148</v>
@@ -18920,7 +18952,7 @@
       <c r="F267" s="46"/>
       <c r="G267" s="46"/>
       <c r="H267" s="46" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="I267" s="45" t="s">
         <v>148</v>
@@ -18931,7 +18963,7 @@
         <v>46208</v>
       </c>
       <c r="B268" s="44" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="C268" s="83">
         <v>2350</v>
@@ -18941,7 +18973,7 @@
       <c r="F268" s="44"/>
       <c r="G268" s="44"/>
       <c r="H268" s="44" t="s">
-        <v>1263</v>
+        <v>1257</v>
       </c>
       <c r="I268" s="44" t="s">
         <v>356</v>
@@ -18952,7 +18984,7 @@
         <v>46209</v>
       </c>
       <c r="B269" s="45" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="C269" s="85">
         <v>1100</v>
@@ -18966,7 +18998,7 @@
       <c r="F269" s="46"/>
       <c r="G269" s="46"/>
       <c r="H269" s="46" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="I269" s="45" t="s">
         <v>148</v>
@@ -18977,7 +19009,7 @@
         <v>46210</v>
       </c>
       <c r="B270" s="44" t="s">
-        <v>1243</v>
+        <v>1313</v>
       </c>
       <c r="C270" s="83">
         <v>3200</v>
@@ -18991,7 +19023,7 @@
       <c r="F270" s="44"/>
       <c r="G270" s="44"/>
       <c r="H270" s="44" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="I270" s="44" t="s">
         <v>148</v>
@@ -19002,7 +19034,7 @@
         <v>46211</v>
       </c>
       <c r="B271" s="45" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="C271" s="85">
         <v>1380</v>
@@ -19016,7 +19048,7 @@
       <c r="F271" s="46"/>
       <c r="G271" s="46"/>
       <c r="H271" s="46" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="I271" s="45" t="s">
         <v>148</v>
@@ -19027,7 +19059,7 @@
         <v>46215</v>
       </c>
       <c r="B272" s="44" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="C272" s="83">
         <v>1380</v>
@@ -19052,7 +19084,7 @@
         <v>46215</v>
       </c>
       <c r="B273" s="45" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="C273" s="85">
         <v>699</v>
@@ -19091,7 +19123,7 @@
       <c r="F274" s="44"/>
       <c r="G274" s="44"/>
       <c r="H274" s="44" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="I274" s="44" t="s">
         <v>148</v>
@@ -19102,7 +19134,7 @@
         <v>46216</v>
       </c>
       <c r="B275" s="45" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="C275" s="85">
         <v>699</v>
@@ -19127,7 +19159,7 @@
         <v>46216</v>
       </c>
       <c r="B276" s="44" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="C276" s="83">
         <v>3000</v>
@@ -19141,7 +19173,7 @@
       <c r="F276" s="44"/>
       <c r="G276" s="44"/>
       <c r="H276" s="44" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="I276" s="44" t="s">
         <v>148</v>
@@ -19152,7 +19184,7 @@
         <v>46219</v>
       </c>
       <c r="B277" s="45" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="C277" s="85">
         <v>1380</v>
@@ -19216,7 +19248,7 @@
       <c r="F279" s="46"/>
       <c r="G279" s="46"/>
       <c r="H279" s="46" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="I279" s="45" t="s">
         <v>148</v>
@@ -19241,7 +19273,7 @@
       <c r="F280" s="44"/>
       <c r="G280" s="44"/>
       <c r="H280" s="44" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="I280" s="44" t="s">
         <v>148</v>
@@ -19266,7 +19298,7 @@
       <c r="F281" s="46"/>
       <c r="G281" s="46"/>
       <c r="H281" s="46" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="I281" s="45" t="s">
         <v>148</v>
@@ -19277,7 +19309,7 @@
         <v>46220</v>
       </c>
       <c r="B282" s="44" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="C282" s="83">
         <v>1500</v>
@@ -19291,7 +19323,7 @@
       <c r="F282" s="44"/>
       <c r="G282" s="44"/>
       <c r="H282" s="44" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="I282" s="44" t="s">
         <v>148</v>
@@ -19302,7 +19334,7 @@
         <v>46221</v>
       </c>
       <c r="B283" s="45" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="C283" s="85">
         <v>1100</v>
@@ -19316,7 +19348,7 @@
       <c r="F283" s="46"/>
       <c r="G283" s="46"/>
       <c r="H283" s="46" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="I283" s="45" t="s">
         <v>148</v>
@@ -19327,7 +19359,7 @@
         <v>46222</v>
       </c>
       <c r="B284" s="44" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="C284" s="83">
         <v>850</v>
@@ -19341,7 +19373,7 @@
       <c r="F284" s="44"/>
       <c r="G284" s="44"/>
       <c r="H284" s="44" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="I284" s="44" t="s">
         <v>148</v>
@@ -19352,7 +19384,7 @@
         <v>46222</v>
       </c>
       <c r="B285" s="45" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="C285" s="85">
         <v>1250</v>
@@ -19366,7 +19398,7 @@
       <c r="F285" s="46"/>
       <c r="G285" s="46"/>
       <c r="H285" s="46" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="I285" s="45" t="s">
         <v>148</v>
@@ -19377,7 +19409,7 @@
         <v>46222</v>
       </c>
       <c r="B286" s="44" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="C286" s="83">
         <v>700</v>
@@ -19402,7 +19434,7 @@
         <v>46222</v>
       </c>
       <c r="B287" s="45" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="C287" s="85">
         <v>699</v>
@@ -19427,7 +19459,7 @@
         <v>46223</v>
       </c>
       <c r="B288" s="44" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="C288" s="83">
         <v>1380</v>
@@ -19441,7 +19473,7 @@
       <c r="F288" s="44"/>
       <c r="G288" s="44"/>
       <c r="H288" s="44" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="I288" s="44" t="s">
         <v>148</v>
@@ -19452,7 +19484,7 @@
         <v>46224</v>
       </c>
       <c r="B289" s="45" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="C289" s="85">
         <v>1380</v>
@@ -19466,7 +19498,7 @@
       <c r="F289" s="46"/>
       <c r="G289" s="46"/>
       <c r="H289" s="46" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="I289" s="45" t="s">
         <v>148</v>
@@ -19477,7 +19509,7 @@
         <v>46224</v>
       </c>
       <c r="B290" s="44" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="C290" s="83">
         <v>1380</v>
@@ -19491,7 +19523,7 @@
       <c r="F290" s="44"/>
       <c r="G290" s="44"/>
       <c r="H290" s="44" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="I290" s="44" t="s">
         <v>148</v>
@@ -19516,7 +19548,7 @@
       <c r="F291" s="44"/>
       <c r="G291" s="44"/>
       <c r="H291" s="44" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="I291" s="44" t="s">
         <v>148</v>
@@ -19527,7 +19559,7 @@
         <v>46229</v>
       </c>
       <c r="B292" s="45" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="C292" s="85">
         <v>1900</v>
@@ -19537,7 +19569,7 @@
       <c r="F292" s="46"/>
       <c r="G292" s="46"/>
       <c r="H292" s="46" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
       <c r="I292" s="45" t="s">
         <v>356</v>
@@ -19558,7 +19590,7 @@
       <c r="F293" s="44"/>
       <c r="G293" s="44"/>
       <c r="H293" s="44" t="s">
-        <v>1306</v>
+        <v>1300</v>
       </c>
       <c r="I293" s="44" t="s">
         <v>356</v>
@@ -19569,7 +19601,7 @@
         <v>46229</v>
       </c>
       <c r="B294" s="45" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="C294" s="85">
         <v>2300</v>
@@ -19579,7 +19611,7 @@
       <c r="F294" s="46"/>
       <c r="G294" s="46"/>
       <c r="H294" s="46" t="s">
-        <v>1259</v>
+        <v>1253</v>
       </c>
       <c r="I294" s="45" t="s">
         <v>356</v>
@@ -19590,7 +19622,7 @@
         <v>46229</v>
       </c>
       <c r="B295" s="44" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="C295" s="83">
         <v>4700</v>
@@ -19600,7 +19632,7 @@
       <c r="F295" s="44"/>
       <c r="G295" s="44"/>
       <c r="H295" s="44" t="s">
-        <v>1305</v>
+        <v>1299</v>
       </c>
       <c r="I295" s="44" t="s">
         <v>356</v>
@@ -19611,7 +19643,7 @@
         <v>46235</v>
       </c>
       <c r="B296" s="45" t="s">
-        <v>1246</v>
+        <v>1241</v>
       </c>
       <c r="C296" s="85">
         <v>1450</v>
@@ -19625,7 +19657,7 @@
       <c r="F296" s="46"/>
       <c r="G296" s="46"/>
       <c r="H296" s="46" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="I296" s="45" t="s">
         <v>148</v>
@@ -19636,7 +19668,7 @@
         <v>46236</v>
       </c>
       <c r="B297" s="44" t="s">
-        <v>1244</v>
+        <v>1314</v>
       </c>
       <c r="C297" s="83">
         <v>6900</v>
@@ -19650,7 +19682,7 @@
       <c r="F297" s="44"/>
       <c r="G297" s="44"/>
       <c r="H297" s="44" t="s">
-        <v>1245</v>
+        <v>1240</v>
       </c>
       <c r="I297" s="44" t="s">
         <v>148</v>
@@ -19661,7 +19693,7 @@
         <v>46236</v>
       </c>
       <c r="B298" s="45" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="C298" s="85">
         <v>1479</v>
@@ -19675,7 +19707,7 @@
       <c r="F298" s="46"/>
       <c r="G298" s="46"/>
       <c r="H298" s="46" t="s">
-        <v>1248</v>
+        <v>1243</v>
       </c>
       <c r="I298" s="45" t="s">
         <v>148</v>
@@ -19686,7 +19718,7 @@
         <v>46236</v>
       </c>
       <c r="B299" s="44" t="s">
-        <v>1253</v>
+        <v>1248</v>
       </c>
       <c r="C299" s="83">
         <v>2630</v>
@@ -19700,7 +19732,7 @@
       <c r="F299" s="44"/>
       <c r="G299" s="44"/>
       <c r="H299" s="44" t="s">
-        <v>1251</v>
+        <v>1246</v>
       </c>
       <c r="I299" s="44" t="s">
         <v>148</v>
@@ -19711,7 +19743,7 @@
         <v>46238</v>
       </c>
       <c r="B300" s="45" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="C300" s="85">
         <v>1380</v>
@@ -19736,7 +19768,7 @@
         <v>46238</v>
       </c>
       <c r="B301" s="44" t="s">
-        <v>1255</v>
+        <v>1315</v>
       </c>
       <c r="C301" s="83">
         <v>12650</v>
@@ -19750,7 +19782,7 @@
       <c r="F301" s="44"/>
       <c r="G301" s="44"/>
       <c r="H301" s="44" t="s">
-        <v>1256</v>
+        <v>1250</v>
       </c>
       <c r="I301" s="44" t="s">
         <v>148</v>
@@ -19761,7 +19793,7 @@
         <v>46240</v>
       </c>
       <c r="B302" s="45" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="C302" s="85">
         <v>1000</v>
@@ -19771,7 +19803,7 @@
       <c r="F302" s="46"/>
       <c r="G302" s="46"/>
       <c r="H302" s="46" t="s">
-        <v>1262</v>
+        <v>1256</v>
       </c>
       <c r="I302" s="45" t="s">
         <v>148</v>
@@ -19792,7 +19824,7 @@
       <c r="F303" s="44"/>
       <c r="G303" s="44"/>
       <c r="H303" s="44" t="s">
-        <v>1293</v>
+        <v>1287</v>
       </c>
       <c r="I303" s="44" t="s">
         <v>356</v>
@@ -19803,7 +19835,7 @@
         <v>46243</v>
       </c>
       <c r="B304" s="45" t="s">
-        <v>1308</v>
+        <v>1302</v>
       </c>
       <c r="C304" s="85">
         <v>1380</v>
@@ -19813,44 +19845,86 @@
       <c r="F304" s="46"/>
       <c r="G304" s="46"/>
       <c r="H304" s="46" t="s">
-        <v>1309</v>
+        <v>1303</v>
       </c>
       <c r="I304" s="45" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="305" spans="1:9">
-      <c r="A305" s="82"/>
-      <c r="B305" s="44"/>
-      <c r="C305" s="83"/>
-      <c r="D305" s="44"/>
-      <c r="E305" s="44"/>
+    <row r="305" spans="1:9" ht="14">
+      <c r="A305" s="82">
+        <v>46243</v>
+      </c>
+      <c r="B305" s="44" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C305" s="83">
+        <v>1380</v>
+      </c>
+      <c r="D305" s="44" t="s">
+        <v>162</v>
+      </c>
+      <c r="E305" s="44" t="s">
+        <v>49</v>
+      </c>
       <c r="F305" s="44"/>
       <c r="G305" s="44"/>
-      <c r="H305" s="44"/>
-      <c r="I305" s="44"/>
-    </row>
-    <row r="306" spans="1:9">
-      <c r="A306" s="84"/>
-      <c r="B306" s="45"/>
-      <c r="C306" s="85"/>
-      <c r="D306" s="45"/>
-      <c r="E306" s="45"/>
+      <c r="H305" s="44" t="s">
+        <v>1305</v>
+      </c>
+      <c r="I305" s="44" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="306" spans="1:9" ht="14">
+      <c r="A306" s="84">
+        <v>46243</v>
+      </c>
+      <c r="B306" s="45" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C306" s="85">
+        <v>1250</v>
+      </c>
+      <c r="D306" s="45" t="s">
+        <v>162</v>
+      </c>
+      <c r="E306" s="45" t="s">
+        <v>49</v>
+      </c>
       <c r="F306" s="46"/>
       <c r="G306" s="46"/>
-      <c r="H306" s="46"/>
-      <c r="I306" s="45"/>
-    </row>
-    <row r="307" spans="1:9">
-      <c r="A307" s="82"/>
-      <c r="B307" s="44"/>
-      <c r="C307" s="83"/>
-      <c r="D307" s="44"/>
-      <c r="E307" s="44"/>
+      <c r="H306" s="46" t="s">
+        <v>1309</v>
+      </c>
+      <c r="I306" s="45" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="307" spans="1:9" ht="14">
+      <c r="A307" s="82">
+        <v>46243</v>
+      </c>
+      <c r="B307" s="44" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C307" s="83">
+        <v>5750</v>
+      </c>
+      <c r="D307" s="44" t="s">
+        <v>162</v>
+      </c>
+      <c r="E307" s="44" t="s">
+        <v>49</v>
+      </c>
       <c r="F307" s="44"/>
       <c r="G307" s="44"/>
-      <c r="H307" s="44"/>
-      <c r="I307" s="44"/>
+      <c r="H307" s="44" t="s">
+        <v>1317</v>
+      </c>
+      <c r="I307" s="44" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="308" spans="1:9">
       <c r="A308" s="84"/>
@@ -26716,7 +26790,7 @@
         <v>0</v>
       </c>
       <c r="L59" s="55" t="s">
-        <v>1304</v>
+        <v>1298</v>
       </c>
       <c r="M59" s="55"/>
       <c r="N59" s="55" t="s">
@@ -28260,7 +28334,7 @@
         <v>0</v>
       </c>
       <c r="L88" s="52" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="M88" s="52"/>
       <c r="N88" s="52" t="s">
@@ -28520,7 +28594,7 @@
         <v>472</v>
       </c>
       <c r="L93" s="55" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="M93" s="55"/>
       <c r="N93" s="52" t="s">
@@ -29536,7 +29610,7 @@
         <v>0</v>
       </c>
       <c r="L112" s="52" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="M112" s="52"/>
       <c r="N112" s="52" t="s">
@@ -29958,7 +30032,7 @@
         <v>3351.6266666666638</v>
       </c>
       <c r="L120" s="52" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="M120" s="52" t="s">
         <v>49</v>
@@ -29968,7 +30042,7 @@
       </c>
       <c r="O120" s="52"/>
       <c r="P120" s="52" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="Q120" s="52"/>
       <c r="R120" s="52"/>
@@ -32048,7 +32122,7 @@
         <v>0</v>
       </c>
       <c r="L147" s="55" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="M147" s="55"/>
       <c r="N147" s="55" t="s">
@@ -32100,7 +32174,7 @@
         <v>1004</v>
       </c>
       <c r="L148" s="52" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="M148" s="52"/>
       <c r="N148" s="52" t="s">
@@ -32152,7 +32226,7 @@
         <v>0</v>
       </c>
       <c r="L149" s="55" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="M149" s="55"/>
       <c r="N149" s="55" t="s">
@@ -32420,14 +32494,14 @@
         <v>949</v>
       </c>
       <c r="L154" s="52" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="M154" s="52"/>
       <c r="N154" s="52" t="s">
         <v>589</v>
       </c>
       <c r="O154" s="52" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="P154" s="52"/>
       <c r="Q154" s="52"/>
@@ -32474,14 +32548,14 @@
         <v>949</v>
       </c>
       <c r="L155" s="55" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="M155" s="55"/>
       <c r="N155" s="55" t="s">
         <v>589</v>
       </c>
       <c r="O155" s="55" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="P155" s="55"/>
       <c r="Q155" s="55"/>
@@ -32528,7 +32602,7 @@
         <v>1900</v>
       </c>
       <c r="L156" s="52" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="M156" s="52"/>
       <c r="N156" s="52" t="s">
@@ -32950,7 +33024,7 @@
         <v>0</v>
       </c>
       <c r="L164" s="52" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="M164" s="52"/>
       <c r="N164" s="52" t="s">
@@ -33376,7 +33450,7 @@
         <v>0</v>
       </c>
       <c r="L172" s="52" t="s">
-        <v>1292</v>
+        <v>1286</v>
       </c>
       <c r="M172" s="52"/>
       <c r="N172" s="52" t="s">
@@ -33510,10 +33584,10 @@
         <v>1250</v>
       </c>
       <c r="F175" s="64">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G175" s="64">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H175" s="63">
         <f t="shared" si="11"/>
@@ -33525,14 +33599,14 @@
       </c>
       <c r="J175" s="63">
         <f t="shared" si="9"/>
-        <v>3491.25</v>
+        <v>4189.5</v>
       </c>
       <c r="K175" s="63">
         <f t="shared" si="10"/>
-        <v>3491.25</v>
+        <v>2793</v>
       </c>
       <c r="L175" s="55" t="s">
-        <v>1102</v>
+        <v>1311</v>
       </c>
       <c r="M175" s="55"/>
       <c r="N175" s="55" t="s">
@@ -33540,7 +33614,7 @@
       </c>
       <c r="O175" s="55"/>
       <c r="P175" s="55" t="s">
-        <v>1101</v>
+        <v>1310</v>
       </c>
       <c r="Q175" s="55"/>
       <c r="R175" s="55"/>
@@ -33852,14 +33926,14 @@
         <v>2038</v>
       </c>
       <c r="L181" s="55" t="s">
-        <v>1302</v>
+        <v>1296</v>
       </c>
       <c r="M181" s="55"/>
       <c r="N181" s="55" t="s">
         <v>589</v>
       </c>
       <c r="O181" s="55" t="s">
-        <v>1303</v>
+        <v>1297</v>
       </c>
       <c r="P181" s="55" t="s">
         <v>954</v>
@@ -33959,7 +34033,7 @@
         <v>1676</v>
       </c>
       <c r="L183" s="55" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="M183" s="55"/>
       <c r="N183" s="55" t="s">
@@ -34011,7 +34085,7 @@
         <v>0</v>
       </c>
       <c r="L184" s="52" t="s">
-        <v>1254</v>
+        <v>1249</v>
       </c>
       <c r="M184" s="52"/>
       <c r="N184" s="52" t="s">
@@ -34215,7 +34289,7 @@
         <v>891</v>
       </c>
       <c r="L188" s="52" t="s">
-        <v>1258</v>
+        <v>1252</v>
       </c>
       <c r="M188" s="52"/>
       <c r="N188" s="52" t="s">
@@ -34267,7 +34341,7 @@
         <v>1782</v>
       </c>
       <c r="L189" s="55" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="M189" s="55"/>
       <c r="N189" s="55" t="s">
@@ -34275,7 +34349,7 @@
       </c>
       <c r="O189" s="55"/>
       <c r="P189" s="55" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="Q189" s="55"/>
       <c r="R189" s="55"/>
@@ -34321,7 +34395,7 @@
         <v>0</v>
       </c>
       <c r="L190" s="52" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="M190" s="52"/>
       <c r="N190" s="47" t="s">
@@ -34618,14 +34692,14 @@
         <v>3985</v>
       </c>
       <c r="L196" s="52" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="M196" s="52"/>
       <c r="N196" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P196" s="47" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="S196" s="47"/>
       <c r="T196" s="47"/>
@@ -34767,14 +34841,14 @@
         <v>1401</v>
       </c>
       <c r="L199" s="55" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="M199" s="55"/>
       <c r="N199" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P199" s="47" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="S199" s="47"/>
       <c r="T199" s="47"/>
@@ -34920,14 +34994,14 @@
         <v>940</v>
       </c>
       <c r="L202" s="52" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="M202" s="52"/>
       <c r="N202" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P202" s="47" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="S202" s="47"/>
       <c r="T202" s="47"/>
@@ -35022,14 +35096,14 @@
         <v>880</v>
       </c>
       <c r="L204" s="52" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="M204" s="52"/>
       <c r="N204" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P204" s="47" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="S204" s="47"/>
       <c r="T204" s="47"/>
@@ -35390,7 +35464,7 @@
         <v>1034</v>
       </c>
       <c r="B212" s="55" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="C212" s="55" t="s">
         <v>95</v>
@@ -35424,7 +35498,7 @@
         <v>13372.5</v>
       </c>
       <c r="L212" s="52" t="s">
-        <v>1257</v>
+        <v>1251</v>
       </c>
       <c r="M212" s="52"/>
       <c r="N212" s="47" t="s">
@@ -35438,7 +35512,7 @@
         <v>1035</v>
       </c>
       <c r="B213" s="52" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="C213" s="52" t="s">
         <v>95</v>
@@ -35472,14 +35546,14 @@
         <v>3330</v>
       </c>
       <c r="L213" s="55" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="M213" s="55"/>
       <c r="N213" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P213" s="47" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="S213" s="47"/>
       <c r="T213" s="47"/>
@@ -35489,7 +35563,7 @@
         <v>1036</v>
       </c>
       <c r="B214" s="52" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="C214" s="52" t="s">
         <v>95</v>
@@ -35528,7 +35602,7 @@
         <v>678</v>
       </c>
       <c r="P214" s="47" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="S214" s="47"/>
       <c r="T214" s="47"/>
@@ -35538,7 +35612,7 @@
         <v>1037</v>
       </c>
       <c r="B215" s="55" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="C215" s="55" t="s">
         <v>95</v>
@@ -35572,14 +35646,14 @@
         <v>2976</v>
       </c>
       <c r="L215" s="55" t="s">
-        <v>1247</v>
+        <v>1242</v>
       </c>
       <c r="M215" s="55"/>
       <c r="N215" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P215" s="47" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="S215" s="47"/>
       <c r="T215" s="47"/>
@@ -35623,14 +35697,14 @@
         <v>2880</v>
       </c>
       <c r="L216" s="52" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="M216" s="52"/>
       <c r="N216" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P216" s="47" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="S216" s="47"/>
       <c r="T216" s="47"/>
@@ -35640,7 +35714,7 @@
         <v>1039</v>
       </c>
       <c r="B217" s="55" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="C217" s="55" t="s">
         <v>95</v>
@@ -35674,14 +35748,14 @@
         <v>0</v>
       </c>
       <c r="L217" s="55" t="s">
-        <v>1301</v>
+        <v>1295</v>
       </c>
       <c r="M217" s="55"/>
       <c r="N217" s="47" t="s">
         <v>504</v>
       </c>
       <c r="P217" s="47" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="S217" s="47"/>
       <c r="T217" s="47"/>
@@ -35691,7 +35765,7 @@
         <v>1040</v>
       </c>
       <c r="B218" s="52" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="C218" s="52" t="s">
         <v>95</v>
@@ -35725,14 +35799,14 @@
         <v>828</v>
       </c>
       <c r="L218" s="52" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="M218" s="52"/>
       <c r="N218" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P218" s="47" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="S218" s="47"/>
       <c r="T218" s="47"/>
@@ -35742,7 +35816,7 @@
         <v>1041</v>
       </c>
       <c r="B219" s="55" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="C219" s="55" t="s">
         <v>95</v>
@@ -35776,14 +35850,14 @@
         <v>2283</v>
       </c>
       <c r="L219" s="55" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="M219" s="55"/>
       <c r="N219" s="47" t="s">
         <v>678</v>
       </c>
       <c r="P219" s="47" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="S219" s="47"/>
       <c r="T219" s="47"/>
@@ -35793,7 +35867,7 @@
         <v>1042</v>
       </c>
       <c r="B220" s="52" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="C220" s="52" t="s">
         <v>95</v>
@@ -35827,14 +35901,14 @@
         <v>3805</v>
       </c>
       <c r="L220" s="52" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="M220" s="52"/>
       <c r="N220" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P220" s="47" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="S220" s="47"/>
       <c r="T220" s="47"/>
@@ -35844,7 +35918,7 @@
         <v>1043</v>
       </c>
       <c r="B221" s="55" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="C221" s="55" t="s">
         <v>95</v>
@@ -35883,7 +35957,7 @@
         <v>678</v>
       </c>
       <c r="P221" s="47" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="S221" s="47"/>
       <c r="T221" s="47"/>
@@ -35893,7 +35967,7 @@
         <v>1044</v>
       </c>
       <c r="B222" s="52" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="C222" s="52" t="s">
         <v>96</v>
@@ -35932,7 +36006,7 @@
         <v>678</v>
       </c>
       <c r="P222" s="86" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="S222" s="47"/>
       <c r="T222" s="47"/>
@@ -35942,7 +36016,7 @@
         <v>1045</v>
       </c>
       <c r="B223" s="55" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="C223" s="55" t="s">
         <v>95</v>
@@ -35981,7 +36055,7 @@
         <v>678</v>
       </c>
       <c r="P223" s="86" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="S223" s="47"/>
       <c r="T223" s="47"/>
@@ -35991,7 +36065,7 @@
         <v>1046</v>
       </c>
       <c r="B224" s="52" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="C224" s="52" t="s">
         <v>95</v>
@@ -36025,14 +36099,14 @@
         <v>942</v>
       </c>
       <c r="L224" s="52" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
       <c r="M224" s="52"/>
       <c r="N224" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P224" s="86" t="s">
-        <v>1252</v>
+        <v>1247</v>
       </c>
       <c r="S224" s="47"/>
       <c r="T224" s="47"/>
@@ -36042,7 +36116,7 @@
         <v>1047</v>
       </c>
       <c r="B225" s="55" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="C225" s="55" t="s">
         <v>95</v>
@@ -36083,7 +36157,7 @@
         <v>504</v>
       </c>
       <c r="P225" s="86" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="S225" s="47"/>
       <c r="T225" s="47"/>
@@ -36093,7 +36167,7 @@
         <v>1048</v>
       </c>
       <c r="B226" s="52" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="C226" s="52" t="s">
         <v>95</v>
@@ -36132,17 +36206,17 @@
         <v>678</v>
       </c>
       <c r="P226" s="86" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="S226" s="47"/>
       <c r="T226" s="47"/>
     </row>
     <row r="227" spans="1:20" ht="17">
       <c r="A227" s="52" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="B227" s="55" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="C227" s="55" t="s">
         <v>95</v>
@@ -36176,24 +36250,24 @@
         <v>1338</v>
       </c>
       <c r="L227" s="55" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="M227" s="55"/>
       <c r="N227" s="47" t="s">
         <v>678</v>
       </c>
       <c r="P227" s="86" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="S227" s="47"/>
       <c r="T227" s="47"/>
     </row>
     <row r="228" spans="1:20" ht="17">
       <c r="A228" s="55" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="B228" s="52" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="C228" s="52" t="s">
         <v>95</v>
@@ -36232,17 +36306,17 @@
         <v>678</v>
       </c>
       <c r="P228" s="86" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="S228" s="47"/>
       <c r="T228" s="47"/>
     </row>
     <row r="229" spans="1:20" ht="17">
       <c r="A229" s="52" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="B229" s="55" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="C229" s="55" t="s">
         <v>95</v>
@@ -36281,17 +36355,17 @@
         <v>678</v>
       </c>
       <c r="P229" s="86" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="S229" s="47"/>
       <c r="T229" s="47"/>
     </row>
     <row r="230" spans="1:20" ht="17">
       <c r="A230" s="55" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="B230" s="52" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="C230" s="52" t="s">
         <v>95</v>
@@ -36325,24 +36399,24 @@
         <v>782</v>
       </c>
       <c r="L230" s="52" t="s">
-        <v>1298</v>
+        <v>1292</v>
       </c>
       <c r="M230" s="52"/>
       <c r="N230" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P230" s="86" t="s">
-        <v>1299</v>
+        <v>1293</v>
       </c>
       <c r="S230" s="47"/>
       <c r="T230" s="47"/>
     </row>
     <row r="231" spans="1:20" ht="17">
       <c r="A231" s="52" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="B231" s="55" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="C231" s="55" t="s">
         <v>95</v>
@@ -36383,17 +36457,17 @@
         <v>589</v>
       </c>
       <c r="P231" s="86" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="S231" s="47"/>
       <c r="T231" s="47"/>
     </row>
     <row r="232" spans="1:20" ht="17">
       <c r="A232" s="52" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="B232" s="52" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="C232" s="52" t="s">
         <v>95</v>
@@ -36432,17 +36506,17 @@
         <v>678</v>
       </c>
       <c r="P232" s="86" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="S232" s="47"/>
       <c r="T232" s="47"/>
     </row>
     <row r="233" spans="1:20" ht="17">
       <c r="A233" s="55" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="B233" s="55" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="C233" s="55" t="s">
         <v>95</v>
@@ -36476,24 +36550,24 @@
         <v>0</v>
       </c>
       <c r="L233" s="55" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
       <c r="M233" s="55"/>
       <c r="N233" s="47" t="s">
         <v>504</v>
       </c>
       <c r="P233" s="86" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="S233" s="47"/>
       <c r="T233" s="47"/>
     </row>
     <row r="234" spans="1:20" ht="17">
       <c r="A234" s="52" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="B234" s="52" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="C234" s="52" t="s">
         <v>95</v>
@@ -36527,24 +36601,24 @@
         <v>1048</v>
       </c>
       <c r="L234" s="52" t="s">
-        <v>1300</v>
+        <v>1294</v>
       </c>
       <c r="M234" s="52"/>
       <c r="N234" s="47" t="s">
         <v>678</v>
       </c>
       <c r="P234" s="86" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="S234" s="47"/>
       <c r="T234" s="47"/>
     </row>
     <row r="235" spans="1:20" ht="17">
       <c r="A235" s="55" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="B235" s="55" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="C235" s="55" t="s">
         <v>95</v>
@@ -36583,14 +36657,14 @@
         <v>678</v>
       </c>
       <c r="P235" s="86" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="S235" s="47"/>
       <c r="T235" s="47"/>
     </row>
     <row r="236" spans="1:20" ht="17">
       <c r="A236" s="52" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="B236" s="52" t="s">
         <v>510</v>
@@ -36605,10 +36679,10 @@
         <v>1380</v>
       </c>
       <c r="F236" s="66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G236" s="66">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H236" s="65">
         <f t="shared" si="15"/>
@@ -36620,29 +36694,31 @@
       </c>
       <c r="J236" s="65">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>912</v>
       </c>
       <c r="K236" s="65">
         <f t="shared" si="17"/>
-        <v>3648</v>
-      </c>
-      <c r="L236" s="52"/>
+        <v>2736</v>
+      </c>
+      <c r="L236" s="52" t="s">
+        <v>1306</v>
+      </c>
       <c r="M236" s="52"/>
       <c r="N236" s="47" t="s">
-        <v>678</v>
+        <v>589</v>
       </c>
       <c r="P236" s="86" t="s">
-        <v>1239</v>
+        <v>1307</v>
       </c>
       <c r="S236" s="47"/>
       <c r="T236" s="47"/>
     </row>
     <row r="237" spans="1:20" ht="17">
       <c r="A237" s="52" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="B237" s="55" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="C237" s="55" t="s">
         <v>95</v>
@@ -36676,24 +36752,24 @@
         <v>1468</v>
       </c>
       <c r="L237" s="55" t="s">
-        <v>1296</v>
+        <v>1290</v>
       </c>
       <c r="M237" s="55"/>
       <c r="N237" s="47" t="s">
         <v>678</v>
       </c>
       <c r="P237" s="86" t="s">
-        <v>1297</v>
+        <v>1291</v>
       </c>
       <c r="S237" s="47"/>
       <c r="T237" s="47"/>
     </row>
     <row r="238" spans="1:20" ht="17">
       <c r="A238" s="55" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="B238" s="52" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="C238" s="52" t="s">
         <v>95</v>
@@ -36727,24 +36803,24 @@
         <v>872</v>
       </c>
       <c r="L238" s="52" t="s">
-        <v>1295</v>
+        <v>1289</v>
       </c>
       <c r="M238" s="52"/>
       <c r="N238" s="47" t="s">
         <v>678</v>
       </c>
       <c r="P238" s="86" t="s">
-        <v>1294</v>
+        <v>1288</v>
       </c>
       <c r="S238" s="47"/>
       <c r="T238" s="47"/>
     </row>
     <row r="239" spans="1:20" ht="16">
       <c r="A239" s="55" t="s">
-        <v>1260</v>
+        <v>1254</v>
       </c>
       <c r="B239" s="55" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="C239" s="55" t="s">
         <v>95</v>
@@ -36778,7 +36854,7 @@
         <v>0</v>
       </c>
       <c r="L239" s="55" t="s">
-        <v>1261</v>
+        <v>1255</v>
       </c>
       <c r="M239" s="55"/>
       <c r="N239" s="47" t="s">
@@ -36790,10 +36866,10 @@
     </row>
     <row r="240" spans="1:20" ht="17">
       <c r="A240" s="52" t="s">
-        <v>1264</v>
+        <v>1258</v>
       </c>
       <c r="B240" s="52" t="s">
-        <v>1274</v>
+        <v>1268</v>
       </c>
       <c r="C240" s="52" t="s">
         <v>95</v>
@@ -36832,17 +36908,17 @@
         <v>678</v>
       </c>
       <c r="P240" s="86" t="s">
-        <v>1285</v>
+        <v>1279</v>
       </c>
       <c r="S240" s="47"/>
       <c r="T240" s="47"/>
     </row>
     <row r="241" spans="1:20" ht="17">
       <c r="A241" s="55" t="s">
-        <v>1265</v>
+        <v>1259</v>
       </c>
       <c r="B241" s="55" t="s">
-        <v>1283</v>
+        <v>1277</v>
       </c>
       <c r="C241" s="55" t="s">
         <v>95</v>
@@ -36876,7 +36952,7 @@
         <v>0</v>
       </c>
       <c r="L241" s="55" t="s">
-        <v>1284</v>
+        <v>1278</v>
       </c>
       <c r="M241" s="55"/>
       <c r="N241" s="47" t="s">
@@ -36890,10 +36966,10 @@
     </row>
     <row r="242" spans="1:20" ht="17">
       <c r="A242" s="52" t="s">
-        <v>1266</v>
+        <v>1260</v>
       </c>
       <c r="B242" s="52" t="s">
-        <v>1275</v>
+        <v>1269</v>
       </c>
       <c r="C242" s="52" t="s">
         <v>95</v>
@@ -36932,17 +37008,17 @@
         <v>678</v>
       </c>
       <c r="P242" s="86" t="s">
-        <v>1286</v>
+        <v>1280</v>
       </c>
       <c r="S242" s="47"/>
       <c r="T242" s="47"/>
     </row>
     <row r="243" spans="1:20" ht="17">
       <c r="A243" s="55" t="s">
-        <v>1267</v>
+        <v>1261</v>
       </c>
       <c r="B243" s="55" t="s">
-        <v>1276</v>
+        <v>1270</v>
       </c>
       <c r="C243" s="55" t="s">
         <v>95</v>
@@ -36983,17 +37059,17 @@
         <v>678</v>
       </c>
       <c r="P243" s="86" t="s">
-        <v>1287</v>
+        <v>1281</v>
       </c>
       <c r="S243" s="47"/>
       <c r="T243" s="47"/>
     </row>
     <row r="244" spans="1:20" ht="17">
       <c r="A244" s="52" t="s">
-        <v>1268</v>
+        <v>1262</v>
       </c>
       <c r="B244" s="52" t="s">
-        <v>1277</v>
+        <v>1271</v>
       </c>
       <c r="C244" s="52" t="s">
         <v>95</v>
@@ -37032,17 +37108,17 @@
         <v>678</v>
       </c>
       <c r="P244" s="86" t="s">
-        <v>1288</v>
+        <v>1282</v>
       </c>
       <c r="S244" s="47"/>
       <c r="T244" s="47"/>
     </row>
     <row r="245" spans="1:20" ht="17">
       <c r="A245" s="55" t="s">
-        <v>1269</v>
+        <v>1263</v>
       </c>
       <c r="B245" s="55" t="s">
-        <v>1278</v>
+        <v>1272</v>
       </c>
       <c r="C245" s="55" t="s">
         <v>95</v>
@@ -37081,17 +37157,17 @@
         <v>678</v>
       </c>
       <c r="P245" s="86" t="s">
-        <v>1289</v>
+        <v>1283</v>
       </c>
       <c r="S245" s="47"/>
       <c r="T245" s="47"/>
     </row>
     <row r="246" spans="1:20" ht="16">
       <c r="A246" s="52" t="s">
-        <v>1270</v>
+        <v>1264</v>
       </c>
       <c r="B246" s="52" t="s">
-        <v>1279</v>
+        <v>1273</v>
       </c>
       <c r="C246" s="52" t="s">
         <v>95</v>
@@ -37135,10 +37211,10 @@
     </row>
     <row r="247" spans="1:20" ht="17">
       <c r="A247" s="55" t="s">
-        <v>1271</v>
+        <v>1265</v>
       </c>
       <c r="B247" s="55" t="s">
-        <v>1280</v>
+        <v>1274</v>
       </c>
       <c r="C247" s="55" t="s">
         <v>95</v>
@@ -37177,17 +37253,17 @@
         <v>504</v>
       </c>
       <c r="P247" s="86" t="s">
-        <v>1290</v>
+        <v>1284</v>
       </c>
       <c r="S247" s="47"/>
       <c r="T247" s="47"/>
     </row>
     <row r="248" spans="1:20" ht="16">
       <c r="A248" s="52" t="s">
-        <v>1272</v>
+        <v>1266</v>
       </c>
       <c r="B248" s="52" t="s">
-        <v>1281</v>
+        <v>1275</v>
       </c>
       <c r="C248" s="52" t="s">
         <v>95</v>
@@ -37231,10 +37307,10 @@
     </row>
     <row r="249" spans="1:20" ht="17">
       <c r="A249" s="55" t="s">
-        <v>1273</v>
+        <v>1267</v>
       </c>
       <c r="B249" s="55" t="s">
-        <v>1282</v>
+        <v>1276</v>
       </c>
       <c r="C249" s="55" t="s">
         <v>95</v>
@@ -37273,7 +37349,7 @@
         <v>678</v>
       </c>
       <c r="P249" s="86" t="s">
-        <v>1291</v>
+        <v>1285</v>
       </c>
       <c r="S249" s="47"/>
       <c r="T249" s="47"/>
@@ -43518,15 +43594,15 @@
       </c>
       <c r="B8" s="9">
         <f>IFERROR(SUMIF(Purchases!$B:$B,$A8,Purchases!$C:$C),0)</f>
-        <v>261817</v>
+        <v>262387</v>
       </c>
       <c r="C8" s="9">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>188578</v>
+        <v>188768</v>
       </c>
       <c r="D8" s="9">
         <f>B8-C8</f>
-        <v>73239</v>
+        <v>73619</v>
       </c>
       <c r="E8" s="9">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A8,$A$3:$B$5,2,FALSE()),0)</f>
@@ -43534,7 +43610,7 @@
       </c>
       <c r="F8" s="9">
         <f>D8+E8</f>
-        <v>73239</v>
+        <v>73619</v>
       </c>
       <c r="G8" s="9">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A8,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A8,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A8,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A8,$B$13:$B$499,"Profit"),0)</f>
@@ -43542,7 +43618,7 @@
       </c>
       <c r="H8" s="73">
         <f>F8-G8</f>
-        <v>54935.66</v>
+        <v>55315.66</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="13.5" customHeight="1">
@@ -43555,11 +43631,11 @@
       </c>
       <c r="C9" s="11">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>188578</v>
+        <v>188768</v>
       </c>
       <c r="D9" s="11">
         <f>B9-C9</f>
-        <v>82739</v>
+        <v>82549</v>
       </c>
       <c r="E9" s="11">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A9,$A$3:$B$5,2,FALSE()),0)</f>
@@ -43567,7 +43643,7 @@
       </c>
       <c r="F9" s="11">
         <f>D9+E9</f>
-        <v>82739</v>
+        <v>82549</v>
       </c>
       <c r="G9" s="11">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A9,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A9,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A9,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A9,$B$13:$B$499,"Profit"),0)</f>
@@ -43575,7 +43651,7 @@
       </c>
       <c r="H9" s="74">
         <f>F9-G9</f>
-        <v>41099.67</v>
+        <v>40909.67</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="13.5" customHeight="1">
@@ -43588,11 +43664,11 @@
       </c>
       <c r="C10" s="9">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>188578</v>
+        <v>188768</v>
       </c>
       <c r="D10" s="9">
         <f>B10-C10</f>
-        <v>-155978</v>
+        <v>-156168</v>
       </c>
       <c r="E10" s="9">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A10,$A$3:$B$5,2,FALSE()),0)</f>
@@ -43600,7 +43676,7 @@
       </c>
       <c r="F10" s="9">
         <f>D10+E10</f>
-        <v>-155978</v>
+        <v>-156168</v>
       </c>
       <c r="G10" s="9">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A10,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A10,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A10,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A10,$B$13:$B$499,"Profit"),0)</f>
@@ -43608,7 +43684,7 @@
       </c>
       <c r="H10" s="73">
         <f>F10-G10</f>
-        <v>-96035.33</v>
+        <v>-96225.33</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="75" customFormat="1" ht="15.75" customHeight="1">
@@ -44025,7 +44101,7 @@
       </c>
       <c r="B4" s="9">
         <f>IFERROR(SUMIFS(Sales!$C:$C,Sales!$E:$E,$A4,Sales!$I:$I,"Completed"),0)</f>
-        <v>432799</v>
+        <v>441179</v>
       </c>
       <c r="C4" s="9">
         <f>VLOOKUP($A4,PartnerShares!$A$3:$B$5,2,FALSE())</f>
@@ -44033,11 +44109,11 @@
       </c>
       <c r="D4" s="9">
         <f>Summary!$B$4*C4</f>
-        <v>167017.73019999999</v>
+        <v>169811.62219999998</v>
       </c>
       <c r="E4" s="9">
         <f>B4-D4</f>
-        <v>265781.26980000001</v>
+        <v>271367.37780000002</v>
       </c>
       <c r="F4" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -44045,7 +44121,7 @@
       </c>
       <c r="G4" s="73">
         <f>E4+F4</f>
-        <v>128471.2438</v>
+        <v>134057.3518</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5" customHeight="1">
@@ -44062,11 +44138,11 @@
       </c>
       <c r="D5" s="11">
         <f>Summary!$B$4*C5</f>
-        <v>166917.53959999999</v>
+        <v>169709.7556</v>
       </c>
       <c r="E5" s="11">
         <f>B5-D5</f>
-        <v>-112293.53959999999</v>
+        <v>-115085.7556</v>
       </c>
       <c r="F5" s="11">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -44074,7 +44150,7 @@
       </c>
       <c r="G5" s="74">
         <f>E5+F5</f>
-        <v>-40706.497599999988</v>
+        <v>-43498.713600000003</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1">
@@ -44091,11 +44167,11 @@
       </c>
       <c r="D6" s="9">
         <f>Summary!$B$4*C6</f>
-        <v>167017.73019999999</v>
+        <v>169811.62219999998</v>
       </c>
       <c r="E6" s="9">
         <f>B6-D6</f>
-        <v>-154487.73019999999</v>
+        <v>-157281.62219999998</v>
       </c>
       <c r="F6" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -44103,7 +44179,7 @@
       </c>
       <c r="G6" s="73">
         <f>E6+F6</f>
-        <v>-88764.74619999998</v>
+        <v>-91558.638199999972</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="13.5" customHeight="1">

--- a/docs/Chiraath-Summary-Aug26.xlsx
+++ b/docs/Chiraath-Summary-Aug26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anooppremachandran/Desktop/CHIRAATH/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4DF1193-96AF-F04D-A734-C93F87366B10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54CC07C2-3DBB-6E48-9840-D321B9CE6E83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">INVENTORY!$A$1:$T$262</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Purchases!$A$1:$D$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Sales!$A$1:$I$303</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Sales!$A$1:$I$315</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3326" uniqueCount="1326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3342" uniqueCount="1326">
   <si>
     <t>Notes:</t>
   </si>
@@ -3406,9 +3406,6 @@
     <t xml:space="preserve">CHR-203 kalyani Blue/maroon </t>
   </si>
   <si>
-    <t>Bank of baroda customer 2</t>
-  </si>
-  <si>
     <t>Shylaja Bank</t>
   </si>
   <si>
@@ -3745,9 +3742,6 @@
     <t>Black/Silver</t>
   </si>
   <si>
-    <t>Black, Maroon, Violet, Rani Pink, Olive Green, Navy Blue</t>
-  </si>
-  <si>
     <t>Golden (Different Designs)</t>
   </si>
   <si>
@@ -3769,9 +3763,6 @@
     <t>CHR-182 (Yellow Linen Saree with Lotus, CHR-217 cream/gold with stars and paisley &amp; cream/gold with flowers - 1000 advance, 900 - pending</t>
   </si>
   <si>
-    <t>Parrot Green Banarasi - 6 pieces from bulk</t>
-  </si>
-  <si>
     <t>Asha Sandran</t>
   </si>
   <si>
@@ -3799,12 +3790,6 @@
     <t>Sheeba George, Soji Thomas, Jessy Joseph, Jeeja Anil ,Sanam, Geetha, Sushama Bhaskar, Divya Jacob, Baby Johny, Jayasree, Navya, Bindu Saji, Vanajakshi, Dison Jose, Akshitha, Bahuleyan, Urmila, Gincy Jibi, Razia Salim, Komalavalli</t>
   </si>
   <si>
-    <t>Parrot Green Banarasi - 11 pieces from bulk</t>
-  </si>
-  <si>
-    <t>1250 X 6, 1250 X 11</t>
-  </si>
-  <si>
     <t>Renju</t>
   </si>
   <si>
@@ -3820,9 +3805,6 @@
     <t>CHR-238 - Kerala</t>
   </si>
   <si>
-    <t>CHR-87 Red Salwar with Elephant print, CHR-58 Wine Red Salwar (2100 advance, 250 balance)</t>
-  </si>
-  <si>
     <t>CHR-239</t>
   </si>
   <si>
@@ -3910,9 +3892,6 @@
     <t>Revathi, Simi Sudhir, Aruna</t>
   </si>
   <si>
-    <t xml:space="preserve">Temple Design, CHR-240 New Kerala Golden Saree with flowers, CHR-242-Kerala Saree, CHR-230 - Jute Silk </t>
-  </si>
-  <si>
     <t>Pink, Black</t>
   </si>
   <si>
@@ -3937,18 +3916,12 @@
     <t>2 -return</t>
   </si>
   <si>
-    <t>Shinoob School - 1500(XXL), Niroop - XL</t>
-  </si>
-  <si>
     <t>M, L</t>
   </si>
   <si>
     <t>Sruthi (1300) - L, Bank of baroda customer - M, Niroop - XL</t>
   </si>
   <si>
-    <t>CHR-192 Small temple design, CHR-180 - Coffee Brown Cotton Salwar, CHR-58 wine red salwar, CHR-226 - Jet black semi jute</t>
-  </si>
-  <si>
     <t>CHR-212 - Purple, CHR-215 - Green and Maroon with golden design - 1000 advance, 750 pending</t>
   </si>
   <si>
@@ -3980,24 +3953,6 @@
   </si>
   <si>
     <t>DTDC parcel charges</t>
-  </si>
-  <si>
-    <t>Asha Binu (Haritha Karma Sena Bulk Order)</t>
-  </si>
-  <si>
-    <t>Asha Binu (Haritha Karma Sena Bulk - 6 pieces)</t>
-  </si>
-  <si>
-    <t>Asha Binu (Haritha Karma Sena Bulk - 11 pieces)</t>
-  </si>
-  <si>
-    <t>Asha Binu (Advance for Bulk 5 saree)</t>
-  </si>
-  <si>
-    <t>Parrot Green Banarasi - advance</t>
-  </si>
-  <si>
-    <t>CHR-243 Green leaf design</t>
   </si>
   <si>
     <t>Ranju Bank Staff (850)</t>
@@ -4041,6 +3996,51 @@
   </si>
   <si>
     <t>Cotton Saree Collections</t>
+  </si>
+  <si>
+    <t>CHR-241 - Net Kota, CHR-228 Jute Silk Navy Blue</t>
+  </si>
+  <si>
+    <t>Navy Blue - Neethu</t>
+  </si>
+  <si>
+    <t>Black, Maroon, Violet, Rani Pink, Olive Green</t>
+  </si>
+  <si>
+    <t>Temple Design, CHR-240 New Kerala Golden Saree with flowers, CHR-242-Kerala Saree, CHR-230 - Jute Silk  (Advance -2800)</t>
+  </si>
+  <si>
+    <t>Bank Account</t>
+  </si>
+  <si>
+    <t>CHR-192 Small temple design, CHR-180 - Coffee Brown Cotton Salwar,CHR-226 - Jet black semi jute</t>
+  </si>
+  <si>
+    <t>Prajisha (Construction Company)</t>
+  </si>
+  <si>
+    <t>CHR-87 Red Salwar with Elephant print, CHR-58 Wine Red Salwar, CHR-180 Coffee Brown Salwar(M) (2100 advance, 1350 balance)</t>
+  </si>
+  <si>
+    <t>Shinoob School - 1500(XXL), Niroop - XL, Prajisha(1100) - M</t>
+  </si>
+  <si>
+    <t>Asha Binu (Haritha Karma Sena)</t>
+  </si>
+  <si>
+    <t>Parrot Green Banarasi - 5 sarees</t>
+  </si>
+  <si>
+    <t>Parrot Green Banarasi - 6 sarees</t>
+  </si>
+  <si>
+    <t>Parrot Green Banarasi - 11 sarees</t>
+  </si>
+  <si>
+    <t>Rejitha Sijo</t>
+  </si>
+  <si>
+    <t>1250 X 6, 1250 X 11, 1250 X 5, 1250 x 5, 1250 X5</t>
   </si>
 </sst>
 </file>
@@ -4926,10 +4926,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>330</c:v>
+                  <c:v>347</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>98</c:v>
+                  <c:v>99</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>5</c:v>
@@ -5029,10 +5029,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>199</c:v>
+                  <c:v>182</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>52</c:v>
+                  <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>3</c:v>
@@ -5359,10 +5359,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>54964</c:v>
+                  <c:v>53945</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>144401.64666666664</c:v>
+                  <c:v>129583.14666666667</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>1062</c:v>
@@ -5698,7 +5698,7 @@
                   <c:v>102200</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>10141</c:v>
+                  <c:v>10461</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -5855,10 +5855,10 @@
                   <c:v>72885</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>63646</c:v>
+                  <c:v>62646</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>49819</c:v>
+                  <c:v>61468</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -6295,10 +6295,10 @@
                   <c:v>-26158</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-38554</c:v>
+                  <c:v>-39554</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>39678</c:v>
+                  <c:v>51007</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -6759,10 +6759,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>433</c:v>
+                  <c:v>451</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>296</c:v>
+                  <c:v>278</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7934,7 +7934,7 @@
       </c>
       <c r="B3" s="8">
         <f>SUM(Purchases!C:C)</f>
-        <v>566488</v>
+        <v>566808</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>42</v>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="B4" s="10">
         <f>SUMIFS(Sales!C:C, Sales!I:I, "Completed")</f>
-        <v>515323</v>
+        <v>528802</v>
       </c>
       <c r="E4" s="9" t="str">
         <f>PartnerShares!A3</f>
@@ -7966,7 +7966,7 @@
       </c>
       <c r="B5" s="12">
         <f>SUM(Sales!C:C)</f>
-        <v>541963</v>
+        <v>552612</v>
       </c>
       <c r="E5" s="11" t="str">
         <f>PartnerShares!A4</f>
@@ -7983,7 +7983,7 @@
       </c>
       <c r="B6" s="10">
         <f>B4-B3</f>
-        <v>-51165</v>
+        <v>-38006</v>
       </c>
       <c r="E6" s="9" t="str">
         <f>PartnerShares!A5</f>
@@ -8018,7 +8018,7 @@
       </c>
       <c r="B10" s="13">
         <f>PartnerShares!H8</f>
-        <v>55438.32666666666</v>
+        <v>55651.66</v>
       </c>
       <c r="C10" s="9"/>
     </row>
@@ -8028,7 +8028,7 @@
       </c>
       <c r="B11" s="14">
         <f>PartnerShares!H9</f>
-        <v>40848.336666666655</v>
+        <v>40741.67</v>
       </c>
       <c r="C11" s="11"/>
     </row>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="B12" s="13">
         <f>PartnerShares!H10</f>
-        <v>-96286.663333333345</v>
+        <v>-96393.33</v>
       </c>
       <c r="C12" s="9"/>
     </row>
@@ -8077,15 +8077,15 @@
       </c>
       <c r="B18" s="10">
         <f>PartnerShares!B8</f>
-        <v>262571</v>
+        <v>262891</v>
       </c>
       <c r="C18" s="10">
         <f>PartnerShares!C8</f>
-        <v>188829.33333333334</v>
+        <v>188936</v>
       </c>
       <c r="D18" s="10">
         <f>PartnerShares!D8</f>
-        <v>73741.666666666657</v>
+        <v>73955</v>
       </c>
       <c r="E18" s="10">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A18,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A18,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -8093,11 +8093,11 @@
       </c>
       <c r="F18" s="13">
         <f>D18-E18</f>
-        <v>55438.32666666666</v>
+        <v>55651.66</v>
       </c>
       <c r="G18" s="16" t="str">
         <f>IF(ROUND(F18,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F18),"#,##0"),IF(ROUND(F18,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F18),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹55,438</v>
+        <v>Receive ₹55,652</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="13.5" customHeight="1">
@@ -8111,11 +8111,11 @@
       </c>
       <c r="C19" s="12">
         <f>PartnerShares!C9</f>
-        <v>188829.33333333334</v>
+        <v>188936</v>
       </c>
       <c r="D19" s="12">
         <f>PartnerShares!D9</f>
-        <v>82487.666666666657</v>
+        <v>82381</v>
       </c>
       <c r="E19" s="12">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A19,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A19,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -8123,11 +8123,11 @@
       </c>
       <c r="F19" s="14">
         <f>D19-E19</f>
-        <v>40848.336666666655</v>
+        <v>40741.67</v>
       </c>
       <c r="G19" s="17" t="str">
         <f>IF(ROUND(F19,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F19),"#,##0"),IF(ROUND(F19,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F19),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹40,848</v>
+        <v>Receive ₹40,742</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="13.5" customHeight="1">
@@ -8141,11 +8141,11 @@
       </c>
       <c r="C20" s="10">
         <f>PartnerShares!C10</f>
-        <v>188829.33333333334</v>
+        <v>188936</v>
       </c>
       <c r="D20" s="10">
         <f>PartnerShares!D10</f>
-        <v>-156229.33333333334</v>
+        <v>-156336</v>
       </c>
       <c r="E20" s="10">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A20,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A20,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -8153,11 +8153,11 @@
       </c>
       <c r="F20" s="13">
         <f>D20-E20</f>
-        <v>-96286.663333333345</v>
+        <v>-96393.33</v>
       </c>
       <c r="G20" s="17" t="str">
         <f>IF(ROUND(F20,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F20),"#,##0"),IF(ROUND(F20,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F20),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹96,287</v>
+        <v>Pay ₹96,393</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.75" customHeight="1">
@@ -8195,15 +8195,15 @@
       </c>
       <c r="B26" s="10">
         <f>'Cash Pool'!B4</f>
-        <v>447169</v>
+        <v>460648</v>
       </c>
       <c r="C26" s="10">
         <f>'Cash Pool'!D4</f>
-        <v>171808.68819999998</v>
+        <v>176302.58679999999</v>
       </c>
       <c r="D26" s="10">
         <f>'Cash Pool'!E4</f>
-        <v>275360.31180000002</v>
+        <v>284345.41320000001</v>
       </c>
       <c r="E26" s="10">
         <f>'Cash Pool'!F4</f>
@@ -8211,11 +8211,11 @@
       </c>
       <c r="F26" s="13">
         <f>'Cash Pool'!G4</f>
-        <v>138050.28580000001</v>
+        <v>147035.3872</v>
       </c>
       <c r="G26" s="17" t="str">
         <f>IF(ROUND(F26,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F26),"#,##0"),IF(ROUND(F26,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F26),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹138,050</v>
+        <v>Pay ₹147,035</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="13.5" customHeight="1">
@@ -8229,11 +8229,11 @@
       </c>
       <c r="C27" s="12">
         <f>'Cash Pool'!D5</f>
-        <v>171705.62359999999</v>
+        <v>176196.82639999999</v>
       </c>
       <c r="D27" s="12">
         <f>'Cash Pool'!E5</f>
-        <v>-117081.62359999999</v>
+        <v>-121572.82639999999</v>
       </c>
       <c r="E27" s="12">
         <f>'Cash Pool'!F5</f>
@@ -8241,11 +8241,11 @@
       </c>
       <c r="F27" s="14">
         <f>'Cash Pool'!G5</f>
-        <v>-45494.58159999999</v>
+        <v>-49985.78439999999</v>
       </c>
       <c r="G27" s="18" t="str">
         <f>IF(ROUND(F27,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F27),"#,##0"),IF(ROUND(F27,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F27),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹45,495</v>
+        <v>Receive ₹49,986</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="13.5" customHeight="1">
@@ -8259,11 +8259,11 @@
       </c>
       <c r="C28" s="10">
         <f>'Cash Pool'!D6</f>
-        <v>171808.68819999998</v>
+        <v>176302.58679999999</v>
       </c>
       <c r="D28" s="10">
         <f>'Cash Pool'!E6</f>
-        <v>-159278.68819999998</v>
+        <v>-163772.58679999999</v>
       </c>
       <c r="E28" s="10">
         <f>'Cash Pool'!F6</f>
@@ -8271,11 +8271,11 @@
       </c>
       <c r="F28" s="13">
         <f>'Cash Pool'!G6</f>
-        <v>-93555.704199999964</v>
+        <v>-98049.602799999979</v>
       </c>
       <c r="G28" s="16" t="str">
         <f>IF(ROUND(F28,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F28),"#,##0"),IF(ROUND(F28,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F28),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹93,556</v>
+        <v>Receive ₹98,050</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.75" customHeight="1">
@@ -8387,7 +8387,7 @@
       </c>
       <c r="B3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46250</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1">
@@ -8396,14 +8396,14 @@
       </c>
       <c r="B5" s="21">
         <f>Summary!B3</f>
-        <v>566488</v>
+        <v>566808</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>69</v>
       </c>
       <c r="E5" s="21">
         <f>Summary!B4</f>
-        <v>515323</v>
+        <v>528802</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
@@ -8412,14 +8412,14 @@
       </c>
       <c r="B6" s="21">
         <f>Summary!B6</f>
-        <v>-51165</v>
+        <v>-38006</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>71</v>
       </c>
       <c r="E6" s="21">
         <f>SUMIFS(INVENTORY!K:K, INVENTORY!N:N, "&lt;&gt;Sold Out")</f>
-        <v>189556.84666666665</v>
+        <v>173719.34666666665</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1">
@@ -8459,7 +8459,7 @@
         <v>47311</v>
       </c>
       <c r="C10" s="21">
-        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$994,"MMM")=$A10)*(YEAR(Sales!$A$2:$A$994)=$B$7)*Sales!$C$2:$C$994),0)</f>
+        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$993,"MMM")=$A10)*(YEAR(Sales!$A$2:$A$993)=$B$7)*Sales!$C$2:$C$993),0)</f>
         <v>45448</v>
       </c>
       <c r="D10" s="21">
@@ -8471,7 +8471,7 @@
       </c>
       <c r="G10" s="21">
         <f>SUM(INVENTORY!F:F)</f>
-        <v>433</v>
+        <v>451</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1">
@@ -8483,7 +8483,7 @@
         <v>5152</v>
       </c>
       <c r="C11" s="27">
-        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$994,"MMM")=$A11)*(YEAR(Sales!$A$2:$A$994)=$B$7)*Sales!$C$2:$C$994),0)</f>
+        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$993,"MMM")=$A11)*(YEAR(Sales!$A$2:$A$993)=$B$7)*Sales!$C$2:$C$993),0)</f>
         <v>19089</v>
       </c>
       <c r="D11" s="27">
@@ -8495,7 +8495,7 @@
       </c>
       <c r="G11" s="27">
         <f>SUM(INVENTORY!G:G)</f>
-        <v>296</v>
+        <v>278</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
@@ -8507,7 +8507,7 @@
         <v>22172</v>
       </c>
       <c r="C12" s="21">
-        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$994,"MMM")=$A12)*(YEAR(Sales!$A$2:$A$994)=$B$7)*Sales!$C$2:$C$994),0)</f>
+        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$993,"MMM")=$A12)*(YEAR(Sales!$A$2:$A$993)=$B$7)*Sales!$C$2:$C$993),0)</f>
         <v>16248</v>
       </c>
       <c r="D12" s="21">
@@ -8524,7 +8524,7 @@
         <v>71002</v>
       </c>
       <c r="C13" s="27">
-        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$994,"MMM")=$A13)*(YEAR(Sales!$A$2:$A$994)=$B$7)*Sales!$C$2:$C$994),0)</f>
+        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$993,"MMM")=$A13)*(YEAR(Sales!$A$2:$A$993)=$B$7)*Sales!$C$2:$C$993),0)</f>
         <v>54177</v>
       </c>
       <c r="D13" s="27">
@@ -8541,7 +8541,7 @@
         <v>4449</v>
       </c>
       <c r="C14" s="21">
-        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$994,"MMM")=$A14)*(YEAR(Sales!$A$2:$A$994)=$B$7)*Sales!$C$2:$C$994),0)</f>
+        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$993,"MMM")=$A14)*(YEAR(Sales!$A$2:$A$993)=$B$7)*Sales!$C$2:$C$993),0)</f>
         <v>54624</v>
       </c>
       <c r="D14" s="21">
@@ -8558,7 +8558,7 @@
         <v>99043</v>
       </c>
       <c r="C15" s="27">
-        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$994,"MMM")=$A15)*(YEAR(Sales!$A$2:$A$994)=$B$7)*Sales!$C$2:$C$994),0)</f>
+        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$993,"MMM")=$A15)*(YEAR(Sales!$A$2:$A$993)=$B$7)*Sales!$C$2:$C$993),0)</f>
         <v>72885</v>
       </c>
       <c r="D15" s="27">
@@ -8575,12 +8575,12 @@
         <v>102200</v>
       </c>
       <c r="C16" s="21">
-        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$994,"MMM")=$A16)*(YEAR(Sales!$A$2:$A$994)=$B$7)*Sales!$C$2:$C$994),0)</f>
-        <v>63646</v>
+        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$993,"MMM")=$A16)*(YEAR(Sales!$A$2:$A$993)=$B$7)*Sales!$C$2:$C$993),0)</f>
+        <v>62646</v>
       </c>
       <c r="D16" s="21">
         <f t="shared" si="0"/>
-        <v>-38554</v>
+        <v>-39554</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1">
@@ -8589,15 +8589,15 @@
       </c>
       <c r="B17" s="27">
         <f>IFERROR(SUMPRODUCT((TEXT(Purchases!$A$2:$A$998,"MMM")=$A17)*(YEAR(Purchases!$A$2:$A$998)=$B$7)*Purchases!$C$2:$C$998),0)</f>
-        <v>10141</v>
+        <v>10461</v>
       </c>
       <c r="C17" s="27">
-        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$994,"MMM")=$A17)*(YEAR(Sales!$A$2:$A$994)=$B$7)*Sales!$C$2:$C$994),0)</f>
-        <v>49819</v>
+        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$993,"MMM")=$A17)*(YEAR(Sales!$A$2:$A$993)=$B$7)*Sales!$C$2:$C$993),0)</f>
+        <v>61468</v>
       </c>
       <c r="D17" s="27">
         <f t="shared" si="0"/>
-        <v>39678</v>
+        <v>51007</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1">
@@ -8609,7 +8609,7 @@
         <v>0</v>
       </c>
       <c r="C18" s="21">
-        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$994,"MMM")=$A18)*(YEAR(Sales!$A$2:$A$994)=$B$7)*Sales!$C$2:$C$994),0)</f>
+        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$993,"MMM")=$A18)*(YEAR(Sales!$A$2:$A$993)=$B$7)*Sales!$C$2:$C$993),0)</f>
         <v>0</v>
       </c>
       <c r="D18" s="21">
@@ -8626,7 +8626,7 @@
         <v>0</v>
       </c>
       <c r="C19" s="27">
-        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$994,"MMM")=$A19)*(YEAR(Sales!$A$2:$A$994)=$B$7)*Sales!$C$2:$C$994),0)</f>
+        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$993,"MMM")=$A19)*(YEAR(Sales!$A$2:$A$993)=$B$7)*Sales!$C$2:$C$993),0)</f>
         <v>0</v>
       </c>
       <c r="D19" s="27">
@@ -8643,7 +8643,7 @@
         <v>0</v>
       </c>
       <c r="C20" s="21">
-        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$994,"MMM")=$A20)*(YEAR(Sales!$A$2:$A$994)=$B$7)*Sales!$C$2:$C$994),0)</f>
+        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$993,"MMM")=$A20)*(YEAR(Sales!$A$2:$A$993)=$B$7)*Sales!$C$2:$C$993),0)</f>
         <v>0</v>
       </c>
       <c r="D20" s="21">
@@ -8660,7 +8660,7 @@
         <v>0</v>
       </c>
       <c r="C21" s="27">
-        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$994,"MMM")=$A21)*(YEAR(Sales!$A$2:$A$994)=$B$7)*Sales!$C$2:$C$994),0)</f>
+        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$993,"MMM")=$A21)*(YEAR(Sales!$A$2:$A$993)=$B$7)*Sales!$C$2:$C$993),0)</f>
         <v>0</v>
       </c>
       <c r="D21" s="27">
@@ -8691,18 +8691,18 @@
       </c>
       <c r="G47" s="30">
         <f>SUMIF(INVENTORY!C:C, F47, INVENTORY!F:F)</f>
-        <v>330</v>
+        <v>347</v>
       </c>
       <c r="H47" s="30">
         <f>SUMIF(INVENTORY!C:C, F47, INVENTORY!G:G)</f>
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="J47" s="30" t="s">
         <v>96</v>
       </c>
       <c r="K47" s="31">
         <f t="array" ref="K47">SUMPRODUCT((INVENTORY!$C$2:$C$476=J47)*(INVENTORY!$D$2:$D$476)*(INVENTORY!$G$2:$G$476))</f>
-        <v>54964</v>
+        <v>53945</v>
       </c>
     </row>
     <row r="48" spans="6:11" ht="15" customHeight="1">
@@ -8711,18 +8711,18 @@
       </c>
       <c r="G48" s="30">
         <f>SUMIF(INVENTORY!C:C, F48, INVENTORY!F:F)</f>
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H48" s="30">
         <f>SUMIF(INVENTORY!C:C, F48, INVENTORY!G:G)</f>
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J48" s="30" t="s">
         <v>95</v>
       </c>
       <c r="K48" s="31">
         <f t="array" ref="K48">SUMPRODUCT((INVENTORY!$C$2:$C$476=J48)*(INVENTORY!$D$2:$D$476)*(INVENTORY!$G$2:$G$476))</f>
-        <v>144401.64666666664</v>
+        <v>129583.14666666667</v>
       </c>
     </row>
     <row r="49" spans="5:12" ht="15" customHeight="1">
@@ -10165,7 +10165,7 @@
         <v>70</v>
       </c>
       <c r="D96" s="36" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="15" customHeight="1">
@@ -10179,7 +10179,7 @@
         <v>1375</v>
       </c>
       <c r="D97" s="39" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="15" customHeight="1">
@@ -10193,7 +10193,7 @@
         <v>189</v>
       </c>
       <c r="D98" s="36" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="15" customHeight="1">
@@ -10319,7 +10319,7 @@
         <v>570</v>
       </c>
       <c r="D107" s="39" t="s">
-        <v>1305</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="15" customHeight="1">
@@ -10337,10 +10337,18 @@
       </c>
     </row>
     <row r="109" spans="1:4" ht="15" customHeight="1">
-      <c r="A109" s="38"/>
-      <c r="B109" s="39"/>
-      <c r="C109" s="40"/>
-      <c r="D109" s="39"/>
+      <c r="A109" s="38">
+        <v>46249</v>
+      </c>
+      <c r="B109" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="C109" s="40">
+        <v>320</v>
+      </c>
+      <c r="D109" s="39" t="s">
+        <v>1296</v>
+      </c>
     </row>
     <row r="110" spans="1:4" ht="15" customHeight="1">
       <c r="A110" s="35"/>
@@ -12397,7 +12405,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:I329"/>
+  <dimension ref="A1:I328"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="10" style="42" customWidth="1"/>
@@ -18833,7 +18841,7 @@
       <c r="F261" s="46"/>
       <c r="G261" s="46"/>
       <c r="H261" s="46" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="I261" s="45" t="s">
         <v>148</v>
@@ -18894,7 +18902,7 @@
         <v>46206</v>
       </c>
       <c r="B264" s="44" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C264" s="83">
         <v>2500</v>
@@ -18908,7 +18916,7 @@
       <c r="F264" s="44"/>
       <c r="G264" s="44"/>
       <c r="H264" s="44" t="s">
-        <v>1296</v>
+        <v>1287</v>
       </c>
       <c r="I264" s="44" t="s">
         <v>356</v>
@@ -18933,7 +18941,7 @@
       <c r="F265" s="46"/>
       <c r="G265" s="46"/>
       <c r="H265" s="46" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="I265" s="45" t="s">
         <v>356</v>
@@ -18989,12 +18997,12 @@
         <v>148</v>
       </c>
     </row>
-    <row r="268" spans="1:9" ht="28">
+    <row r="268" spans="1:9" ht="42">
       <c r="A268" s="82">
         <v>46208</v>
       </c>
       <c r="B268" s="44" t="s">
-        <v>1115</v>
+        <v>1317</v>
       </c>
       <c r="C268" s="83">
         <v>2350</v>
@@ -19004,7 +19012,7 @@
       <c r="F268" s="44"/>
       <c r="G268" s="44"/>
       <c r="H268" s="44" t="s">
-        <v>1252</v>
+        <v>1318</v>
       </c>
       <c r="I268" s="44" t="s">
         <v>356</v>
@@ -19040,7 +19048,7 @@
         <v>46210</v>
       </c>
       <c r="B270" s="44" t="s">
-        <v>1306</v>
+        <v>1320</v>
       </c>
       <c r="C270" s="83">
         <v>3200</v>
@@ -19054,7 +19062,7 @@
       <c r="F270" s="44"/>
       <c r="G270" s="44"/>
       <c r="H270" s="44" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="I270" s="44" t="s">
         <v>148</v>
@@ -19065,7 +19073,7 @@
         <v>46211</v>
       </c>
       <c r="B271" s="45" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C271" s="85">
         <v>1380</v>
@@ -19079,7 +19087,7 @@
       <c r="F271" s="46"/>
       <c r="G271" s="46"/>
       <c r="H271" s="46" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="I271" s="45" t="s">
         <v>148</v>
@@ -19090,7 +19098,7 @@
         <v>46215</v>
       </c>
       <c r="B272" s="44" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="C272" s="83">
         <v>1380</v>
@@ -19115,7 +19123,7 @@
         <v>46215</v>
       </c>
       <c r="B273" s="45" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="C273" s="85">
         <v>699</v>
@@ -19154,7 +19162,7 @@
       <c r="F274" s="44"/>
       <c r="G274" s="44"/>
       <c r="H274" s="44" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="I274" s="44" t="s">
         <v>148</v>
@@ -19165,7 +19173,7 @@
         <v>46216</v>
       </c>
       <c r="B275" s="45" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="C275" s="85">
         <v>699</v>
@@ -19190,7 +19198,7 @@
         <v>46216</v>
       </c>
       <c r="B276" s="44" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="C276" s="83">
         <v>3000</v>
@@ -19204,7 +19212,7 @@
       <c r="F276" s="44"/>
       <c r="G276" s="44"/>
       <c r="H276" s="44" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="I276" s="44" t="s">
         <v>148</v>
@@ -19215,7 +19223,7 @@
         <v>46219</v>
       </c>
       <c r="B277" s="45" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="C277" s="85">
         <v>1380</v>
@@ -19279,7 +19287,7 @@
       <c r="F279" s="46"/>
       <c r="G279" s="46"/>
       <c r="H279" s="46" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="I279" s="45" t="s">
         <v>148</v>
@@ -19304,7 +19312,7 @@
       <c r="F280" s="44"/>
       <c r="G280" s="44"/>
       <c r="H280" s="44" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="I280" s="44" t="s">
         <v>148</v>
@@ -19329,7 +19337,7 @@
       <c r="F281" s="46"/>
       <c r="G281" s="46"/>
       <c r="H281" s="46" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="I281" s="45" t="s">
         <v>148</v>
@@ -19340,7 +19348,7 @@
         <v>46220</v>
       </c>
       <c r="B282" s="44" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="C282" s="83">
         <v>1500</v>
@@ -19354,7 +19362,7 @@
       <c r="F282" s="44"/>
       <c r="G282" s="44"/>
       <c r="H282" s="44" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="I282" s="44" t="s">
         <v>148</v>
@@ -19365,7 +19373,7 @@
         <v>46221</v>
       </c>
       <c r="B283" s="45" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="C283" s="85">
         <v>1100</v>
@@ -19379,7 +19387,7 @@
       <c r="F283" s="46"/>
       <c r="G283" s="46"/>
       <c r="H283" s="46" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="I283" s="45" t="s">
         <v>148</v>
@@ -19390,7 +19398,7 @@
         <v>46222</v>
       </c>
       <c r="B284" s="44" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="C284" s="83">
         <v>850</v>
@@ -19404,7 +19412,7 @@
       <c r="F284" s="44"/>
       <c r="G284" s="44"/>
       <c r="H284" s="44" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="I284" s="44" t="s">
         <v>148</v>
@@ -19415,7 +19423,7 @@
         <v>46222</v>
       </c>
       <c r="B285" s="45" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="C285" s="85">
         <v>1250</v>
@@ -19429,7 +19437,7 @@
       <c r="F285" s="46"/>
       <c r="G285" s="46"/>
       <c r="H285" s="46" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="I285" s="45" t="s">
         <v>148</v>
@@ -19440,7 +19448,7 @@
         <v>46222</v>
       </c>
       <c r="B286" s="44" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="C286" s="83">
         <v>700</v>
@@ -19465,7 +19473,7 @@
         <v>46222</v>
       </c>
       <c r="B287" s="45" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="C287" s="85">
         <v>699</v>
@@ -19490,7 +19498,7 @@
         <v>46223</v>
       </c>
       <c r="B288" s="44" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="C288" s="83">
         <v>1380</v>
@@ -19504,7 +19512,7 @@
       <c r="F288" s="44"/>
       <c r="G288" s="44"/>
       <c r="H288" s="44" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="I288" s="44" t="s">
         <v>148</v>
@@ -19515,7 +19523,7 @@
         <v>46224</v>
       </c>
       <c r="B289" s="45" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="C289" s="85">
         <v>1380</v>
@@ -19529,7 +19537,7 @@
       <c r="F289" s="46"/>
       <c r="G289" s="46"/>
       <c r="H289" s="46" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="I289" s="45" t="s">
         <v>148</v>
@@ -19540,7 +19548,7 @@
         <v>46224</v>
       </c>
       <c r="B290" s="44" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="C290" s="83">
         <v>1380</v>
@@ -19554,7 +19562,7 @@
       <c r="F290" s="44"/>
       <c r="G290" s="44"/>
       <c r="H290" s="44" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="I290" s="44" t="s">
         <v>148</v>
@@ -19579,7 +19587,7 @@
       <c r="F291" s="44"/>
       <c r="G291" s="44"/>
       <c r="H291" s="44" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="I291" s="44" t="s">
         <v>148</v>
@@ -19590,7 +19598,7 @@
         <v>46229</v>
       </c>
       <c r="B292" s="45" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="C292" s="85">
         <v>1900</v>
@@ -19600,7 +19608,7 @@
       <c r="F292" s="46"/>
       <c r="G292" s="46"/>
       <c r="H292" s="46" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="I292" s="45" t="s">
         <v>356</v>
@@ -19621,7 +19629,7 @@
       <c r="F293" s="44"/>
       <c r="G293" s="44"/>
       <c r="H293" s="44" t="s">
-        <v>1295</v>
+        <v>1286</v>
       </c>
       <c r="I293" s="44" t="s">
         <v>356</v>
@@ -19642,7 +19650,7 @@
       <c r="F294" s="46"/>
       <c r="G294" s="46"/>
       <c r="H294" s="46" t="s">
-        <v>1248</v>
+        <v>1243</v>
       </c>
       <c r="I294" s="45" t="s">
         <v>356</v>
@@ -19653,17 +19661,21 @@
         <v>46229</v>
       </c>
       <c r="B295" s="44" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="C295" s="83">
-        <v>4700</v>
-      </c>
-      <c r="D295" s="44"/>
-      <c r="E295" s="44"/>
+        <v>3700</v>
+      </c>
+      <c r="D295" s="44" t="s">
+        <v>1315</v>
+      </c>
+      <c r="E295" s="44" t="s">
+        <v>49</v>
+      </c>
       <c r="F295" s="44"/>
       <c r="G295" s="44"/>
       <c r="H295" s="44" t="s">
-        <v>1294</v>
+        <v>1316</v>
       </c>
       <c r="I295" s="44" t="s">
         <v>356</v>
@@ -19674,7 +19686,7 @@
         <v>46235</v>
       </c>
       <c r="B296" s="45" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
       <c r="C296" s="85">
         <v>1450</v>
@@ -19688,7 +19700,7 @@
       <c r="F296" s="46"/>
       <c r="G296" s="46"/>
       <c r="H296" s="46" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="I296" s="45" t="s">
         <v>148</v>
@@ -19699,7 +19711,7 @@
         <v>46236</v>
       </c>
       <c r="B297" s="44" t="s">
-        <v>1307</v>
+        <v>1320</v>
       </c>
       <c r="C297" s="83">
         <v>6900</v>
@@ -19713,7 +19725,7 @@
       <c r="F297" s="44"/>
       <c r="G297" s="44"/>
       <c r="H297" s="44" t="s">
-        <v>1235</v>
+        <v>1322</v>
       </c>
       <c r="I297" s="44" t="s">
         <v>148</v>
@@ -19724,7 +19736,7 @@
         <v>46236</v>
       </c>
       <c r="B298" s="45" t="s">
-        <v>1239</v>
+        <v>1236</v>
       </c>
       <c r="C298" s="85">
         <v>1479</v>
@@ -19738,7 +19750,7 @@
       <c r="F298" s="46"/>
       <c r="G298" s="46"/>
       <c r="H298" s="46" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="I298" s="45" t="s">
         <v>148</v>
@@ -19749,7 +19761,7 @@
         <v>46236</v>
       </c>
       <c r="B299" s="44" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="C299" s="83">
         <v>2630</v>
@@ -19763,7 +19775,7 @@
       <c r="F299" s="44"/>
       <c r="G299" s="44"/>
       <c r="H299" s="44" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="I299" s="44" t="s">
         <v>148</v>
@@ -19794,12 +19806,12 @@
         <v>148</v>
       </c>
     </row>
-    <row r="301" spans="1:9" ht="28">
+    <row r="301" spans="1:9" ht="14">
       <c r="A301" s="82">
         <v>46238</v>
       </c>
       <c r="B301" s="44" t="s">
-        <v>1308</v>
+        <v>1320</v>
       </c>
       <c r="C301" s="83">
         <v>12650</v>
@@ -19813,7 +19825,7 @@
       <c r="F301" s="44"/>
       <c r="G301" s="44"/>
       <c r="H301" s="44" t="s">
-        <v>1245</v>
+        <v>1323</v>
       </c>
       <c r="I301" s="44" t="s">
         <v>148</v>
@@ -19824,7 +19836,7 @@
         <v>46240</v>
       </c>
       <c r="B302" s="45" t="s">
-        <v>1239</v>
+        <v>1236</v>
       </c>
       <c r="C302" s="85">
         <v>1000</v>
@@ -19834,13 +19846,13 @@
       <c r="F302" s="46"/>
       <c r="G302" s="46"/>
       <c r="H302" s="46" t="s">
-        <v>1251</v>
+        <v>1246</v>
       </c>
       <c r="I302" s="45" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="303" spans="1:9" ht="28">
+    <row r="303" spans="1:9" ht="42">
       <c r="A303" s="82">
         <v>46241</v>
       </c>
@@ -19855,7 +19867,7 @@
       <c r="F303" s="44"/>
       <c r="G303" s="44"/>
       <c r="H303" s="44" t="s">
-        <v>1282</v>
+        <v>1314</v>
       </c>
       <c r="I303" s="44" t="s">
         <v>356</v>
@@ -19866,7 +19878,7 @@
         <v>46243</v>
       </c>
       <c r="B304" s="45" t="s">
-        <v>1297</v>
+        <v>1288</v>
       </c>
       <c r="C304" s="85">
         <v>1380</v>
@@ -19876,7 +19888,7 @@
       <c r="F304" s="46"/>
       <c r="G304" s="46"/>
       <c r="H304" s="46" t="s">
-        <v>1298</v>
+        <v>1289</v>
       </c>
       <c r="I304" s="45" t="s">
         <v>356</v>
@@ -19887,7 +19899,7 @@
         <v>46243</v>
       </c>
       <c r="B305" s="44" t="s">
-        <v>1299</v>
+        <v>1290</v>
       </c>
       <c r="C305" s="83">
         <v>1380</v>
@@ -19901,7 +19913,7 @@
       <c r="F305" s="44"/>
       <c r="G305" s="44"/>
       <c r="H305" s="44" t="s">
-        <v>1300</v>
+        <v>1291</v>
       </c>
       <c r="I305" s="44" t="s">
         <v>148</v>
@@ -19912,7 +19924,7 @@
         <v>46243</v>
       </c>
       <c r="B306" s="45" t="s">
-        <v>1303</v>
+        <v>1294</v>
       </c>
       <c r="C306" s="85">
         <v>1250</v>
@@ -19926,7 +19938,7 @@
       <c r="F306" s="46"/>
       <c r="G306" s="46"/>
       <c r="H306" s="46" t="s">
-        <v>1304</v>
+        <v>1295</v>
       </c>
       <c r="I306" s="45" t="s">
         <v>148</v>
@@ -19937,7 +19949,7 @@
         <v>46243</v>
       </c>
       <c r="B307" s="44" t="s">
-        <v>1309</v>
+        <v>1320</v>
       </c>
       <c r="C307" s="83">
         <v>5750</v>
@@ -19951,334 +19963,349 @@
       <c r="F307" s="44"/>
       <c r="G307" s="44"/>
       <c r="H307" s="44" t="s">
-        <v>1310</v>
+        <v>1321</v>
       </c>
       <c r="I307" s="44" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="308" spans="1:9" ht="14">
-      <c r="A308" s="84">
-        <v>46246</v>
-      </c>
-      <c r="B308" s="45" t="s">
-        <v>1180</v>
-      </c>
-      <c r="C308" s="85">
-        <v>850</v>
-      </c>
-      <c r="D308" s="45"/>
-      <c r="E308" s="45"/>
-      <c r="F308" s="46"/>
-      <c r="G308" s="46"/>
-      <c r="H308" s="46" t="s">
+      <c r="A308" s="82">
+        <v>46248</v>
+      </c>
+      <c r="B308" s="44" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C308" s="83">
+        <v>1380</v>
+      </c>
+      <c r="D308" s="44" t="s">
+        <v>162</v>
+      </c>
+      <c r="E308" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="F308" s="44"/>
+      <c r="G308" s="44"/>
+      <c r="H308" s="44" t="s">
+        <v>1299</v>
+      </c>
+      <c r="I308" s="44" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="309" spans="1:9" ht="14">
+      <c r="A309" s="84">
+        <v>46248</v>
+      </c>
+      <c r="B309" s="45" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C309" s="85">
+        <v>1380</v>
+      </c>
+      <c r="D309" s="45" t="s">
+        <v>162</v>
+      </c>
+      <c r="E309" s="45" t="s">
+        <v>49</v>
+      </c>
+      <c r="F309" s="46"/>
+      <c r="G309" s="46"/>
+      <c r="H309" s="46" t="s">
+        <v>1301</v>
+      </c>
+      <c r="I309" s="45" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="310" spans="1:9" ht="14">
+      <c r="A310" s="82">
+        <v>46250</v>
+      </c>
+      <c r="B310" s="44" t="s">
+        <v>329</v>
+      </c>
+      <c r="C310" s="83">
+        <v>1979</v>
+      </c>
+      <c r="D310" s="44" t="s">
+        <v>162</v>
+      </c>
+      <c r="E310" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="F310" s="44"/>
+      <c r="G310" s="44"/>
+      <c r="H310" s="44" t="s">
         <v>1311</v>
       </c>
-      <c r="I308" s="45" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="309" spans="1:9" ht="14">
-      <c r="A309" s="82">
-        <v>46248</v>
-      </c>
-      <c r="B309" s="44" t="s">
-        <v>1313</v>
-      </c>
-      <c r="C309" s="83">
-        <v>1380</v>
-      </c>
-      <c r="D309" s="44" t="s">
+      <c r="I310" s="44" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="311" spans="1:9" ht="14">
+      <c r="A311" s="84">
+        <v>46250</v>
+      </c>
+      <c r="B311" s="45" t="s">
+        <v>197</v>
+      </c>
+      <c r="C311" s="85">
+        <v>980</v>
+      </c>
+      <c r="D311" s="45" t="s">
         <v>162</v>
       </c>
-      <c r="E309" s="44" t="s">
+      <c r="E311" s="45" t="s">
         <v>49</v>
       </c>
-      <c r="F309" s="44"/>
-      <c r="G309" s="44"/>
-      <c r="H309" s="44" t="s">
-        <v>1314</v>
-      </c>
-      <c r="I309" s="44" t="s">
+      <c r="F311" s="46"/>
+      <c r="G311" s="46"/>
+      <c r="H311" s="46" t="s">
+        <v>1303</v>
+      </c>
+      <c r="I311" s="45" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="310" spans="1:9" ht="14">
-      <c r="A310" s="84">
-        <v>46248</v>
-      </c>
-      <c r="B310" s="45" t="s">
-        <v>1315</v>
-      </c>
-      <c r="C310" s="85">
-        <v>1380</v>
-      </c>
-      <c r="D310" s="45" t="s">
+    <row r="312" spans="1:9" ht="14">
+      <c r="A312" s="82">
+        <v>46250</v>
+      </c>
+      <c r="B312" s="44" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C312" s="83">
+        <v>2250</v>
+      </c>
+      <c r="D312" s="44" t="s">
         <v>162</v>
       </c>
-      <c r="E310" s="45" t="s">
+      <c r="E312" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="F310" s="46"/>
-      <c r="G310" s="46"/>
-      <c r="H310" s="46" t="s">
-        <v>1316</v>
-      </c>
-      <c r="I310" s="45" t="s">
+      <c r="F312" s="44"/>
+      <c r="G312" s="44"/>
+      <c r="H312" s="44" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I312" s="44" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="311" spans="1:9" ht="14">
-      <c r="A311" s="82">
-        <v>46250</v>
-      </c>
-      <c r="B311" s="44" t="s">
-        <v>329</v>
-      </c>
-      <c r="C311" s="83">
-        <v>980</v>
-      </c>
-      <c r="D311" s="44"/>
-      <c r="E311" s="44"/>
-      <c r="F311" s="44"/>
-      <c r="G311" s="44"/>
-      <c r="H311" s="44" t="s">
-        <v>1318</v>
-      </c>
-      <c r="I311" s="44" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="312" spans="1:9" ht="14">
-      <c r="A312" s="84">
-        <v>46250</v>
-      </c>
-      <c r="B312" s="45" t="s">
-        <v>197</v>
-      </c>
-      <c r="C312" s="85">
-        <v>980</v>
-      </c>
-      <c r="D312" s="45" t="s">
+    <row r="313" spans="1:9" ht="14">
+      <c r="A313" s="84">
+        <v>46252</v>
+      </c>
+      <c r="B313" s="45" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C313" s="85">
+        <v>5750</v>
+      </c>
+      <c r="D313" s="45" t="s">
         <v>162</v>
       </c>
-      <c r="E312" s="45" t="s">
+      <c r="E313" s="45" t="s">
         <v>49</v>
       </c>
-      <c r="F312" s="46"/>
-      <c r="G312" s="46"/>
-      <c r="H312" s="46" t="s">
-        <v>1318</v>
-      </c>
-      <c r="I312" s="45" t="s">
+      <c r="F313" s="46"/>
+      <c r="G313" s="46"/>
+      <c r="H313" s="46" t="s">
+        <v>1321</v>
+      </c>
+      <c r="I313" s="45" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="313" spans="1:9" ht="14">
-      <c r="A313" s="82">
-        <v>46250</v>
-      </c>
-      <c r="B313" s="44" t="s">
+    <row r="314" spans="1:9" ht="14">
+      <c r="A314" s="82">
+        <v>46252</v>
+      </c>
+      <c r="B314" s="44" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C314" s="83"/>
+      <c r="D314" s="44"/>
+      <c r="E314" s="44"/>
+      <c r="F314" s="44"/>
+      <c r="G314" s="44"/>
+      <c r="H314" s="44"/>
+      <c r="I314" s="44"/>
+    </row>
+    <row r="315" spans="1:9" ht="14">
+      <c r="A315" s="84">
+        <v>46252</v>
+      </c>
+      <c r="B315" s="45" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C315" s="85">
+        <v>5750</v>
+      </c>
+      <c r="D315" s="45" t="s">
+        <v>162</v>
+      </c>
+      <c r="E315" s="45" t="s">
+        <v>49</v>
+      </c>
+      <c r="F315" s="46"/>
+      <c r="G315" s="46"/>
+      <c r="H315" s="46" t="s">
         <v>1321</v>
       </c>
-      <c r="C313" s="83">
-        <v>2250</v>
-      </c>
-      <c r="D313" s="44" t="s">
-        <v>162</v>
-      </c>
-      <c r="E313" s="44" t="s">
-        <v>49</v>
-      </c>
-      <c r="F313" s="44"/>
-      <c r="G313" s="44"/>
-      <c r="H313" s="44" t="s">
-        <v>1323</v>
-      </c>
-      <c r="I313" s="44" t="s">
+      <c r="I315" s="45" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="314" spans="1:9">
-      <c r="A314" s="84"/>
-      <c r="B314" s="45"/>
-      <c r="C314" s="85"/>
-      <c r="D314" s="45"/>
-      <c r="E314" s="45"/>
-      <c r="F314" s="46"/>
-      <c r="G314" s="46"/>
-      <c r="H314" s="46"/>
-      <c r="I314" s="45"/>
-    </row>
-    <row r="315" spans="1:9">
-      <c r="A315" s="82"/>
-      <c r="B315" s="44"/>
-      <c r="C315" s="83"/>
-      <c r="D315" s="44"/>
-      <c r="E315" s="44"/>
-      <c r="F315" s="44"/>
-      <c r="G315" s="44"/>
-      <c r="H315" s="44"/>
-      <c r="I315" s="44"/>
-    </row>
     <row r="316" spans="1:9">
-      <c r="A316" s="84"/>
-      <c r="B316" s="45"/>
-      <c r="C316" s="85"/>
-      <c r="D316" s="45"/>
-      <c r="E316" s="45"/>
-      <c r="F316" s="46"/>
-      <c r="G316" s="46"/>
-      <c r="H316" s="46"/>
-      <c r="I316" s="45"/>
+      <c r="A316" s="82"/>
+      <c r="B316" s="44"/>
+      <c r="C316" s="83"/>
+      <c r="D316" s="44"/>
+      <c r="E316" s="44"/>
+      <c r="F316" s="44"/>
+      <c r="G316" s="44"/>
+      <c r="H316" s="44"/>
+      <c r="I316" s="44"/>
     </row>
     <row r="317" spans="1:9">
-      <c r="A317" s="82"/>
-      <c r="B317" s="44"/>
-      <c r="C317" s="83"/>
-      <c r="D317" s="44"/>
-      <c r="E317" s="44"/>
-      <c r="F317" s="44"/>
-      <c r="G317" s="44"/>
-      <c r="H317" s="44"/>
-      <c r="I317" s="44"/>
+      <c r="A317" s="84"/>
+      <c r="B317" s="45"/>
+      <c r="C317" s="85"/>
+      <c r="D317" s="45"/>
+      <c r="E317" s="45"/>
+      <c r="F317" s="46"/>
+      <c r="G317" s="46"/>
+      <c r="H317" s="46"/>
+      <c r="I317" s="45"/>
     </row>
     <row r="318" spans="1:9">
-      <c r="A318" s="84"/>
-      <c r="B318" s="45"/>
-      <c r="C318" s="85"/>
-      <c r="D318" s="45"/>
-      <c r="E318" s="45"/>
-      <c r="F318" s="46"/>
-      <c r="G318" s="46"/>
-      <c r="H318" s="46"/>
-      <c r="I318" s="45"/>
+      <c r="A318" s="82"/>
+      <c r="B318" s="44"/>
+      <c r="C318" s="83"/>
+      <c r="D318" s="44"/>
+      <c r="E318" s="44"/>
+      <c r="F318" s="44"/>
+      <c r="G318" s="44"/>
+      <c r="H318" s="44"/>
+      <c r="I318" s="44"/>
     </row>
     <row r="319" spans="1:9">
-      <c r="A319" s="82"/>
-      <c r="B319" s="44"/>
-      <c r="C319" s="83"/>
-      <c r="D319" s="44"/>
-      <c r="E319" s="44"/>
-      <c r="F319" s="44"/>
-      <c r="G319" s="44"/>
-      <c r="H319" s="44"/>
-      <c r="I319" s="44"/>
+      <c r="A319" s="84"/>
+      <c r="B319" s="45"/>
+      <c r="C319" s="85"/>
+      <c r="D319" s="45"/>
+      <c r="E319" s="45"/>
+      <c r="F319" s="46"/>
+      <c r="G319" s="46"/>
+      <c r="H319" s="46"/>
+      <c r="I319" s="45"/>
     </row>
     <row r="320" spans="1:9">
-      <c r="A320" s="84"/>
-      <c r="B320" s="45"/>
-      <c r="C320" s="85"/>
-      <c r="D320" s="45"/>
-      <c r="E320" s="45"/>
-      <c r="F320" s="46"/>
-      <c r="G320" s="46"/>
-      <c r="H320" s="46"/>
-      <c r="I320" s="45"/>
+      <c r="A320" s="82"/>
+      <c r="B320" s="44"/>
+      <c r="C320" s="83"/>
+      <c r="D320" s="44"/>
+      <c r="E320" s="44"/>
+      <c r="F320" s="44"/>
+      <c r="G320" s="44"/>
+      <c r="H320" s="44"/>
+      <c r="I320" s="44"/>
     </row>
     <row r="321" spans="1:9">
-      <c r="A321" s="82"/>
-      <c r="B321" s="44"/>
-      <c r="C321" s="83"/>
-      <c r="D321" s="44"/>
-      <c r="E321" s="44"/>
-      <c r="F321" s="44"/>
-      <c r="G321" s="44"/>
-      <c r="H321" s="44"/>
-      <c r="I321" s="44"/>
+      <c r="A321" s="84"/>
+      <c r="B321" s="45"/>
+      <c r="C321" s="85"/>
+      <c r="D321" s="45"/>
+      <c r="E321" s="45"/>
+      <c r="F321" s="46"/>
+      <c r="G321" s="46"/>
+      <c r="H321" s="46"/>
+      <c r="I321" s="45"/>
     </row>
     <row r="322" spans="1:9">
-      <c r="A322" s="84"/>
-      <c r="B322" s="45"/>
-      <c r="C322" s="85"/>
-      <c r="D322" s="45"/>
-      <c r="E322" s="45"/>
-      <c r="F322" s="46"/>
-      <c r="G322" s="46"/>
-      <c r="H322" s="46"/>
-      <c r="I322" s="45"/>
+      <c r="A322" s="82"/>
+      <c r="B322" s="44"/>
+      <c r="C322" s="83"/>
+      <c r="D322" s="44"/>
+      <c r="E322" s="44"/>
+      <c r="F322" s="44"/>
+      <c r="G322" s="44"/>
+      <c r="H322" s="44"/>
+      <c r="I322" s="44"/>
     </row>
     <row r="323" spans="1:9">
-      <c r="A323" s="82"/>
-      <c r="B323" s="44"/>
-      <c r="C323" s="83"/>
-      <c r="D323" s="44"/>
-      <c r="E323" s="44"/>
-      <c r="F323" s="44"/>
-      <c r="G323" s="44"/>
-      <c r="H323" s="44"/>
-      <c r="I323" s="44"/>
+      <c r="A323" s="84"/>
+      <c r="B323" s="45"/>
+      <c r="C323" s="85"/>
+      <c r="D323" s="45"/>
+      <c r="E323" s="45"/>
+      <c r="F323" s="46"/>
+      <c r="G323" s="46"/>
+      <c r="H323" s="46"/>
+      <c r="I323" s="45"/>
     </row>
     <row r="324" spans="1:9">
-      <c r="A324" s="84"/>
-      <c r="B324" s="45"/>
-      <c r="C324" s="85"/>
-      <c r="D324" s="45"/>
-      <c r="E324" s="45"/>
-      <c r="F324" s="46"/>
-      <c r="G324" s="46"/>
-      <c r="H324" s="46"/>
-      <c r="I324" s="45"/>
+      <c r="A324" s="82"/>
+      <c r="B324" s="44"/>
+      <c r="C324" s="83"/>
+      <c r="D324" s="44"/>
+      <c r="E324" s="44"/>
+      <c r="F324" s="44"/>
+      <c r="G324" s="44"/>
+      <c r="H324" s="44"/>
+      <c r="I324" s="44"/>
     </row>
     <row r="325" spans="1:9">
-      <c r="A325" s="82"/>
-      <c r="B325" s="44"/>
-      <c r="C325" s="83"/>
-      <c r="D325" s="44"/>
-      <c r="E325" s="44"/>
-      <c r="F325" s="44"/>
-      <c r="G325" s="44"/>
-      <c r="H325" s="44"/>
-      <c r="I325" s="44"/>
+      <c r="A325" s="84"/>
+      <c r="B325" s="45"/>
+      <c r="C325" s="85"/>
+      <c r="D325" s="45"/>
+      <c r="E325" s="45"/>
+      <c r="F325" s="46"/>
+      <c r="G325" s="46"/>
+      <c r="H325" s="46"/>
+      <c r="I325" s="45"/>
     </row>
     <row r="326" spans="1:9">
-      <c r="A326" s="84"/>
-      <c r="B326" s="45"/>
-      <c r="C326" s="85"/>
-      <c r="D326" s="45"/>
-      <c r="E326" s="45"/>
-      <c r="F326" s="46"/>
-      <c r="G326" s="46"/>
-      <c r="H326" s="46"/>
-      <c r="I326" s="45"/>
+      <c r="A326" s="82"/>
+      <c r="B326" s="44"/>
+      <c r="C326" s="83"/>
+      <c r="D326" s="44"/>
+      <c r="E326" s="44"/>
+      <c r="F326" s="44"/>
+      <c r="G326" s="44"/>
+      <c r="H326" s="44"/>
+      <c r="I326" s="44"/>
     </row>
     <row r="327" spans="1:9">
-      <c r="A327" s="82"/>
-      <c r="B327" s="44"/>
-      <c r="C327" s="83"/>
-      <c r="D327" s="44"/>
-      <c r="E327" s="44"/>
-      <c r="F327" s="44"/>
-      <c r="G327" s="44"/>
-      <c r="H327" s="44"/>
-      <c r="I327" s="44"/>
+      <c r="A327" s="84"/>
+      <c r="B327" s="45"/>
+      <c r="C327" s="85"/>
+      <c r="D327" s="45"/>
+      <c r="E327" s="45"/>
+      <c r="F327" s="46"/>
+      <c r="G327" s="46"/>
+      <c r="H327" s="46"/>
+      <c r="I327" s="45"/>
     </row>
     <row r="328" spans="1:9">
-      <c r="A328" s="84"/>
-      <c r="B328" s="45"/>
-      <c r="C328" s="85"/>
-      <c r="D328" s="45"/>
-      <c r="E328" s="45"/>
-      <c r="F328" s="46"/>
-      <c r="G328" s="46"/>
-      <c r="H328" s="46"/>
-      <c r="I328" s="45"/>
-    </row>
-    <row r="329" spans="1:9">
-      <c r="A329" s="82"/>
-      <c r="B329" s="44"/>
-      <c r="C329" s="83"/>
-      <c r="D329" s="44"/>
-      <c r="E329" s="44"/>
-      <c r="F329" s="44"/>
-      <c r="G329" s="44"/>
-      <c r="H329" s="44"/>
-      <c r="I329" s="44"/>
+      <c r="A328" s="82"/>
+      <c r="B328" s="44"/>
+      <c r="C328" s="83"/>
+      <c r="D328" s="44"/>
+      <c r="E328" s="44"/>
+      <c r="F328" s="44"/>
+      <c r="G328" s="44"/>
+      <c r="H328" s="44"/>
+      <c r="I328" s="44"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I303" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <autoFilter ref="A1:I315" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1258" xr:uid="{00000000-0002-0000-0400-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1257" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"Ordered,Pending,Completed,Cancelled"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -26897,7 +26924,7 @@
         <v>0</v>
       </c>
       <c r="L59" s="55" t="s">
-        <v>1293</v>
+        <v>1285</v>
       </c>
       <c r="M59" s="55"/>
       <c r="N59" s="55" t="s">
@@ -28441,7 +28468,7 @@
         <v>0</v>
       </c>
       <c r="L88" s="52" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="M88" s="52"/>
       <c r="N88" s="52" t="s">
@@ -28701,7 +28728,7 @@
         <v>472</v>
       </c>
       <c r="L93" s="55" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="M93" s="55"/>
       <c r="N93" s="52" t="s">
@@ -30139,7 +30166,7 @@
         <v>3351.6266666666638</v>
       </c>
       <c r="L120" s="52" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="M120" s="52" t="s">
         <v>49</v>
@@ -30149,7 +30176,7 @@
       </c>
       <c r="O120" s="52"/>
       <c r="P120" s="52" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="Q120" s="52"/>
       <c r="R120" s="52"/>
@@ -32229,7 +32256,7 @@
         <v>0</v>
       </c>
       <c r="L147" s="55" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="M147" s="55"/>
       <c r="N147" s="55" t="s">
@@ -32281,7 +32308,7 @@
         <v>1004</v>
       </c>
       <c r="L148" s="52" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="M148" s="52"/>
       <c r="N148" s="52" t="s">
@@ -32333,7 +32360,7 @@
         <v>0</v>
       </c>
       <c r="L149" s="55" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="M149" s="55"/>
       <c r="N149" s="55" t="s">
@@ -32655,7 +32682,7 @@
         <v>949</v>
       </c>
       <c r="L155" s="55" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="M155" s="55"/>
       <c r="N155" s="55" t="s">
@@ -33131,7 +33158,7 @@
         <v>0</v>
       </c>
       <c r="L164" s="52" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="M164" s="52"/>
       <c r="N164" s="52" t="s">
@@ -33557,7 +33584,7 @@
         <v>0</v>
       </c>
       <c r="L172" s="52" t="s">
-        <v>1281</v>
+        <v>1275</v>
       </c>
       <c r="M172" s="52"/>
       <c r="N172" s="52" t="s">
@@ -33713,7 +33740,7 @@
         <v>2793</v>
       </c>
       <c r="L175" s="55" t="s">
-        <v>1322</v>
+        <v>1307</v>
       </c>
       <c r="M175" s="55"/>
       <c r="N175" s="55" t="s">
@@ -33721,7 +33748,7 @@
       </c>
       <c r="O175" s="55"/>
       <c r="P175" s="55" t="s">
-        <v>1320</v>
+        <v>1305</v>
       </c>
       <c r="Q175" s="55"/>
       <c r="R175" s="55"/>
@@ -34011,10 +34038,10 @@
         <v>1499</v>
       </c>
       <c r="F181" s="64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G181" s="64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H181" s="63">
         <f t="shared" si="11"/>
@@ -34026,21 +34053,21 @@
       </c>
       <c r="J181" s="63">
         <f t="shared" si="9"/>
-        <v>2038</v>
+        <v>3057</v>
       </c>
       <c r="K181" s="63">
         <f t="shared" si="10"/>
-        <v>2038</v>
+        <v>1019</v>
       </c>
       <c r="L181" s="55" t="s">
-        <v>1291</v>
+        <v>1319</v>
       </c>
       <c r="M181" s="55"/>
       <c r="N181" s="55" t="s">
         <v>589</v>
       </c>
       <c r="O181" s="55" t="s">
-        <v>1292</v>
+        <v>1284</v>
       </c>
       <c r="P181" s="55" t="s">
         <v>954</v>
@@ -34140,7 +34167,7 @@
         <v>1676</v>
       </c>
       <c r="L183" s="55" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="M183" s="55"/>
       <c r="N183" s="55" t="s">
@@ -34192,7 +34219,7 @@
         <v>0</v>
       </c>
       <c r="L184" s="52" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="M184" s="52"/>
       <c r="N184" s="52" t="s">
@@ -34324,10 +34351,10 @@
         <v>1380</v>
       </c>
       <c r="F187" s="64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G187" s="64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H187" s="63">
         <f t="shared" si="12"/>
@@ -34339,16 +34366,18 @@
       </c>
       <c r="J187" s="63">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>891</v>
       </c>
       <c r="K187" s="63">
         <f t="shared" si="10"/>
-        <v>1782</v>
-      </c>
-      <c r="L187" s="55"/>
+        <v>891</v>
+      </c>
+      <c r="L187" s="55" t="s">
+        <v>1324</v>
+      </c>
       <c r="M187" s="55"/>
       <c r="N187" s="55" t="s">
-        <v>678</v>
+        <v>589</v>
       </c>
       <c r="O187" s="55"/>
       <c r="P187" s="55"/>
@@ -34396,7 +34425,7 @@
         <v>891</v>
       </c>
       <c r="L188" s="52" t="s">
-        <v>1247</v>
+        <v>1242</v>
       </c>
       <c r="M188" s="52"/>
       <c r="N188" s="52" t="s">
@@ -34448,7 +34477,7 @@
         <v>1782</v>
       </c>
       <c r="L189" s="55" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="M189" s="55"/>
       <c r="N189" s="55" t="s">
@@ -34456,7 +34485,7 @@
       </c>
       <c r="O189" s="55"/>
       <c r="P189" s="55" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="Q189" s="55"/>
       <c r="R189" s="55"/>
@@ -34502,7 +34531,7 @@
         <v>0</v>
       </c>
       <c r="L190" s="52" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="M190" s="52"/>
       <c r="N190" s="47" t="s">
@@ -34665,7 +34694,7 @@
         <v>982</v>
       </c>
       <c r="B194" s="52" t="s">
-        <v>1325</v>
+        <v>1310</v>
       </c>
       <c r="C194" s="52" t="s">
         <v>95</v>
@@ -34699,14 +34728,14 @@
         <v>6320</v>
       </c>
       <c r="L194" s="52" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="M194" s="52"/>
       <c r="N194" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P194" s="47" t="s">
-        <v>1324</v>
+        <v>1309</v>
       </c>
       <c r="S194" s="47"/>
       <c r="T194" s="47"/>
@@ -34899,14 +34928,14 @@
         <v>1401</v>
       </c>
       <c r="L198" s="55" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="M198" s="55"/>
       <c r="N198" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P198" s="47" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="S198" s="47"/>
       <c r="T198" s="47"/>
@@ -35052,14 +35081,14 @@
         <v>940</v>
       </c>
       <c r="L201" s="52" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="M201" s="52"/>
       <c r="N201" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P201" s="47" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="S201" s="47"/>
       <c r="T201" s="47"/>
@@ -35534,10 +35563,10 @@
         <v>1380</v>
       </c>
       <c r="F211" s="66">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="G211" s="66">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H211" s="65">
         <f t="shared" si="12"/>
@@ -35549,18 +35578,18 @@
       </c>
       <c r="J211" s="65">
         <f t="shared" si="13"/>
-        <v>15155.5</v>
+        <v>28528</v>
       </c>
       <c r="K211" s="65">
         <f t="shared" si="14"/>
-        <v>13372.5</v>
+        <v>0</v>
       </c>
       <c r="L211" s="52" t="s">
-        <v>1246</v>
+        <v>1325</v>
       </c>
       <c r="M211" s="52"/>
       <c r="N211" s="47" t="s">
-        <v>589</v>
+        <v>504</v>
       </c>
       <c r="S211" s="47"/>
       <c r="T211" s="47"/>
@@ -35570,7 +35599,7 @@
         <v>1031</v>
       </c>
       <c r="B212" s="52" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="C212" s="52" t="s">
         <v>95</v>
@@ -35604,14 +35633,14 @@
         <v>3330</v>
       </c>
       <c r="L212" s="55" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="M212" s="55"/>
       <c r="N212" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P212" s="47" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="S212" s="47"/>
       <c r="T212" s="47"/>
@@ -35621,7 +35650,7 @@
         <v>1032</v>
       </c>
       <c r="B213" s="52" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="C213" s="52" t="s">
         <v>95</v>
@@ -35660,7 +35689,7 @@
         <v>678</v>
       </c>
       <c r="P213" s="47" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="S213" s="47"/>
       <c r="T213" s="47"/>
@@ -35670,7 +35699,7 @@
         <v>1033</v>
       </c>
       <c r="B214" s="55" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="C214" s="55" t="s">
         <v>95</v>
@@ -35704,14 +35733,14 @@
         <v>2976</v>
       </c>
       <c r="L214" s="55" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="M214" s="55"/>
       <c r="N214" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P214" s="47" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="S214" s="47"/>
       <c r="T214" s="47"/>
@@ -35755,14 +35784,14 @@
         <v>2880</v>
       </c>
       <c r="L215" s="52" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="M215" s="52"/>
       <c r="N215" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P215" s="47" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="S215" s="47"/>
       <c r="T215" s="47"/>
@@ -35772,7 +35801,7 @@
         <v>1035</v>
       </c>
       <c r="B216" s="55" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="C216" s="55" t="s">
         <v>95</v>
@@ -35806,14 +35835,14 @@
         <v>0</v>
       </c>
       <c r="L216" s="55" t="s">
-        <v>1290</v>
+        <v>1283</v>
       </c>
       <c r="M216" s="55"/>
       <c r="N216" s="47" t="s">
         <v>504</v>
       </c>
       <c r="P216" s="47" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="S216" s="47"/>
       <c r="T216" s="47"/>
@@ -35823,7 +35852,7 @@
         <v>1036</v>
       </c>
       <c r="B217" s="52" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="C217" s="52" t="s">
         <v>95</v>
@@ -35857,14 +35886,14 @@
         <v>828</v>
       </c>
       <c r="L217" s="52" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="M217" s="52"/>
       <c r="N217" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P217" s="47" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="S217" s="47"/>
       <c r="T217" s="47"/>
@@ -35874,7 +35903,7 @@
         <v>1037</v>
       </c>
       <c r="B218" s="55" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="C218" s="55" t="s">
         <v>95</v>
@@ -35908,14 +35937,14 @@
         <v>2283</v>
       </c>
       <c r="L218" s="55" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="M218" s="55"/>
       <c r="N218" s="47" t="s">
         <v>678</v>
       </c>
       <c r="P218" s="47" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="S218" s="47"/>
       <c r="T218" s="47"/>
@@ -35925,7 +35954,7 @@
         <v>1038</v>
       </c>
       <c r="B219" s="52" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="C219" s="52" t="s">
         <v>95</v>
@@ -35959,14 +35988,14 @@
         <v>3805</v>
       </c>
       <c r="L219" s="52" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="M219" s="52"/>
       <c r="N219" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P219" s="47" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="S219" s="47"/>
       <c r="T219" s="47"/>
@@ -35976,7 +36005,7 @@
         <v>1039</v>
       </c>
       <c r="B220" s="55" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="C220" s="55" t="s">
         <v>95</v>
@@ -36015,7 +36044,7 @@
         <v>678</v>
       </c>
       <c r="P220" s="47" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="S220" s="47"/>
       <c r="T220" s="47"/>
@@ -36025,7 +36054,7 @@
         <v>1040</v>
       </c>
       <c r="B221" s="52" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="C221" s="52" t="s">
         <v>96</v>
@@ -36064,7 +36093,7 @@
         <v>678</v>
       </c>
       <c r="P221" s="86" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="S221" s="47"/>
       <c r="T221" s="47"/>
@@ -36074,7 +36103,7 @@
         <v>1041</v>
       </c>
       <c r="B222" s="55" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="C222" s="55" t="s">
         <v>95</v>
@@ -36113,7 +36142,7 @@
         <v>678</v>
       </c>
       <c r="P222" s="86" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="S222" s="47"/>
       <c r="T222" s="47"/>
@@ -36123,7 +36152,7 @@
         <v>1042</v>
       </c>
       <c r="B223" s="52" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="C223" s="52" t="s">
         <v>95</v>
@@ -36157,14 +36186,14 @@
         <v>942</v>
       </c>
       <c r="L223" s="52" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
       <c r="M223" s="52"/>
       <c r="N223" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P223" s="86" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
       <c r="S223" s="47"/>
       <c r="T223" s="47"/>
@@ -36174,7 +36203,7 @@
         <v>1043</v>
       </c>
       <c r="B224" s="55" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="C224" s="55" t="s">
         <v>95</v>
@@ -36215,7 +36244,7 @@
         <v>504</v>
       </c>
       <c r="P224" s="86" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="S224" s="47"/>
       <c r="T224" s="47"/>
@@ -36225,7 +36254,7 @@
         <v>1044</v>
       </c>
       <c r="B225" s="52" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="C225" s="52" t="s">
         <v>95</v>
@@ -36264,17 +36293,17 @@
         <v>678</v>
       </c>
       <c r="P225" s="86" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="S225" s="47"/>
       <c r="T225" s="47"/>
     </row>
     <row r="226" spans="1:20" ht="17">
       <c r="A226" s="52" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="B226" s="55" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="C226" s="55" t="s">
         <v>95</v>
@@ -36308,24 +36337,24 @@
         <v>1338</v>
       </c>
       <c r="L226" s="55" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="M226" s="55"/>
       <c r="N226" s="47" t="s">
         <v>678</v>
       </c>
       <c r="P226" s="86" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="S226" s="47"/>
       <c r="T226" s="47"/>
     </row>
     <row r="227" spans="1:20" ht="17">
       <c r="A227" s="55" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="B227" s="52" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="C227" s="52" t="s">
         <v>95</v>
@@ -36364,17 +36393,17 @@
         <v>678</v>
       </c>
       <c r="P227" s="86" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="S227" s="47"/>
       <c r="T227" s="47"/>
     </row>
     <row r="228" spans="1:20" ht="17">
       <c r="A228" s="52" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="B228" s="55" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="C228" s="55" t="s">
         <v>95</v>
@@ -36386,10 +36415,10 @@
         <v>999</v>
       </c>
       <c r="F228" s="64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G228" s="64">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H228" s="63">
         <f t="shared" si="15"/>
@@ -36401,29 +36430,31 @@
       </c>
       <c r="J228" s="63">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>555</v>
       </c>
       <c r="K228" s="63">
         <f t="shared" si="17"/>
-        <v>3330</v>
-      </c>
-      <c r="L228" s="55"/>
+        <v>2775</v>
+      </c>
+      <c r="L228" s="55" t="s">
+        <v>1312</v>
+      </c>
       <c r="M228" s="55"/>
       <c r="N228" s="47" t="s">
-        <v>678</v>
+        <v>589</v>
       </c>
       <c r="P228" s="86" t="s">
-        <v>1227</v>
+        <v>1313</v>
       </c>
       <c r="S228" s="47"/>
       <c r="T228" s="47"/>
     </row>
     <row r="229" spans="1:20" ht="17">
       <c r="A229" s="55" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="B229" s="52" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="C229" s="52" t="s">
         <v>95</v>
@@ -36457,24 +36488,24 @@
         <v>782</v>
       </c>
       <c r="L229" s="52" t="s">
-        <v>1287</v>
+        <v>1280</v>
       </c>
       <c r="M229" s="52"/>
       <c r="N229" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P229" s="86" t="s">
-        <v>1288</v>
+        <v>1281</v>
       </c>
       <c r="S229" s="47"/>
       <c r="T229" s="47"/>
     </row>
     <row r="230" spans="1:20" ht="17">
       <c r="A230" s="52" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="B230" s="55" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="C230" s="55" t="s">
         <v>95</v>
@@ -36515,17 +36546,17 @@
         <v>589</v>
       </c>
       <c r="P230" s="86" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="S230" s="47"/>
       <c r="T230" s="47"/>
     </row>
     <row r="231" spans="1:20" ht="17">
       <c r="A231" s="52" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="B231" s="52" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C231" s="52" t="s">
         <v>95</v>
@@ -36564,17 +36595,17 @@
         <v>678</v>
       </c>
       <c r="P231" s="86" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="S231" s="47"/>
       <c r="T231" s="47"/>
     </row>
     <row r="232" spans="1:20" ht="17">
       <c r="A232" s="55" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="B232" s="55" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="C232" s="55" t="s">
         <v>95</v>
@@ -36608,24 +36639,24 @@
         <v>0</v>
       </c>
       <c r="L232" s="55" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="M232" s="55"/>
       <c r="N232" s="47" t="s">
         <v>504</v>
       </c>
       <c r="P232" s="86" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="S232" s="47"/>
       <c r="T232" s="47"/>
     </row>
     <row r="233" spans="1:20" ht="17">
       <c r="A233" s="52" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="B233" s="52" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="C233" s="52" t="s">
         <v>95</v>
@@ -36659,24 +36690,24 @@
         <v>1048</v>
       </c>
       <c r="L233" s="52" t="s">
-        <v>1289</v>
+        <v>1282</v>
       </c>
       <c r="M233" s="52"/>
       <c r="N233" s="47" t="s">
         <v>678</v>
       </c>
       <c r="P233" s="86" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="S233" s="47"/>
       <c r="T233" s="47"/>
     </row>
     <row r="234" spans="1:20" ht="17">
       <c r="A234" s="55" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="B234" s="55" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="C234" s="55" t="s">
         <v>95</v>
@@ -36710,21 +36741,21 @@
         <v>891</v>
       </c>
       <c r="L234" s="55" t="s">
-        <v>1317</v>
+        <v>1302</v>
       </c>
       <c r="M234" s="55"/>
       <c r="N234" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P234" s="86" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="S234" s="47"/>
       <c r="T234" s="47"/>
     </row>
     <row r="235" spans="1:20" ht="17">
       <c r="A235" s="52" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="B235" s="52" t="s">
         <v>510</v>
@@ -36761,24 +36792,24 @@
         <v>2736</v>
       </c>
       <c r="L235" s="52" t="s">
-        <v>1301</v>
+        <v>1292</v>
       </c>
       <c r="M235" s="52"/>
       <c r="N235" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P235" s="86" t="s">
-        <v>1302</v>
+        <v>1293</v>
       </c>
       <c r="S235" s="47"/>
       <c r="T235" s="47"/>
     </row>
     <row r="236" spans="1:20" ht="17">
       <c r="A236" s="52" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="B236" s="55" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="C236" s="55" t="s">
         <v>95</v>
@@ -36812,24 +36843,24 @@
         <v>1468</v>
       </c>
       <c r="L236" s="55" t="s">
-        <v>1285</v>
+        <v>1278</v>
       </c>
       <c r="M236" s="55"/>
       <c r="N236" s="47" t="s">
         <v>678</v>
       </c>
       <c r="P236" s="86" t="s">
-        <v>1286</v>
+        <v>1279</v>
       </c>
       <c r="S236" s="47"/>
       <c r="T236" s="47"/>
     </row>
     <row r="237" spans="1:20" ht="17">
       <c r="A237" s="55" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B237" s="52" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="C237" s="52" t="s">
         <v>95</v>
@@ -36863,24 +36894,24 @@
         <v>872</v>
       </c>
       <c r="L237" s="52" t="s">
-        <v>1284</v>
+        <v>1277</v>
       </c>
       <c r="M237" s="52"/>
       <c r="N237" s="47" t="s">
         <v>678</v>
       </c>
       <c r="P237" s="86" t="s">
-        <v>1283</v>
+        <v>1276</v>
       </c>
       <c r="S237" s="47"/>
       <c r="T237" s="47"/>
     </row>
     <row r="238" spans="1:20" ht="16">
       <c r="A238" s="55" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="B238" s="55" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="C238" s="55" t="s">
         <v>95</v>
@@ -36914,7 +36945,7 @@
         <v>0</v>
       </c>
       <c r="L238" s="55" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
       <c r="M238" s="55"/>
       <c r="N238" s="47" t="s">
@@ -36926,10 +36957,10 @@
     </row>
     <row r="239" spans="1:20" ht="17">
       <c r="A239" s="52" t="s">
-        <v>1253</v>
+        <v>1247</v>
       </c>
       <c r="B239" s="52" t="s">
-        <v>1263</v>
+        <v>1257</v>
       </c>
       <c r="C239" s="52" t="s">
         <v>95</v>
@@ -36968,17 +36999,17 @@
         <v>678</v>
       </c>
       <c r="P239" s="86" t="s">
-        <v>1274</v>
+        <v>1268</v>
       </c>
       <c r="S239" s="47"/>
       <c r="T239" s="47"/>
     </row>
     <row r="240" spans="1:20" ht="17">
       <c r="A240" s="55" t="s">
-        <v>1254</v>
+        <v>1248</v>
       </c>
       <c r="B240" s="55" t="s">
-        <v>1272</v>
+        <v>1266</v>
       </c>
       <c r="C240" s="55" t="s">
         <v>95</v>
@@ -37012,7 +37043,7 @@
         <v>0</v>
       </c>
       <c r="L240" s="55" t="s">
-        <v>1273</v>
+        <v>1267</v>
       </c>
       <c r="M240" s="55"/>
       <c r="N240" s="47" t="s">
@@ -37026,10 +37057,10 @@
     </row>
     <row r="241" spans="1:20" ht="17">
       <c r="A241" s="52" t="s">
-        <v>1255</v>
+        <v>1249</v>
       </c>
       <c r="B241" s="52" t="s">
-        <v>1264</v>
+        <v>1258</v>
       </c>
       <c r="C241" s="52" t="s">
         <v>95</v>
@@ -37063,24 +37094,24 @@
         <v>1124</v>
       </c>
       <c r="L241" s="52" t="s">
-        <v>1319</v>
+        <v>1304</v>
       </c>
       <c r="M241" s="52"/>
       <c r="N241" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P241" s="86" t="s">
-        <v>1275</v>
+        <v>1269</v>
       </c>
       <c r="S241" s="47"/>
       <c r="T241" s="47"/>
     </row>
     <row r="242" spans="1:20" ht="17">
       <c r="A242" s="55" t="s">
-        <v>1256</v>
+        <v>1250</v>
       </c>
       <c r="B242" s="55" t="s">
-        <v>1265</v>
+        <v>1259</v>
       </c>
       <c r="C242" s="55" t="s">
         <v>95</v>
@@ -37121,17 +37152,17 @@
         <v>678</v>
       </c>
       <c r="P242" s="86" t="s">
-        <v>1276</v>
+        <v>1270</v>
       </c>
       <c r="S242" s="47"/>
       <c r="T242" s="47"/>
     </row>
     <row r="243" spans="1:20" ht="17">
       <c r="A243" s="52" t="s">
-        <v>1257</v>
+        <v>1251</v>
       </c>
       <c r="B243" s="52" t="s">
-        <v>1266</v>
+        <v>1260</v>
       </c>
       <c r="C243" s="52" t="s">
         <v>95</v>
@@ -37165,24 +37196,24 @@
         <v>545</v>
       </c>
       <c r="L243" s="52" t="s">
-        <v>1312</v>
+        <v>1297</v>
       </c>
       <c r="M243" s="52"/>
       <c r="N243" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P243" s="86" t="s">
-        <v>1277</v>
+        <v>1271</v>
       </c>
       <c r="S243" s="47"/>
       <c r="T243" s="47"/>
     </row>
     <row r="244" spans="1:20" ht="17">
       <c r="A244" s="55" t="s">
-        <v>1258</v>
+        <v>1252</v>
       </c>
       <c r="B244" s="55" t="s">
-        <v>1267</v>
+        <v>1261</v>
       </c>
       <c r="C244" s="55" t="s">
         <v>95</v>
@@ -37221,17 +37252,17 @@
         <v>678</v>
       </c>
       <c r="P244" s="86" t="s">
-        <v>1278</v>
+        <v>1272</v>
       </c>
       <c r="S244" s="47"/>
       <c r="T244" s="47"/>
     </row>
     <row r="245" spans="1:20" ht="16">
       <c r="A245" s="52" t="s">
-        <v>1259</v>
+        <v>1253</v>
       </c>
       <c r="B245" s="52" t="s">
-        <v>1268</v>
+        <v>1262</v>
       </c>
       <c r="C245" s="52" t="s">
         <v>95</v>
@@ -37275,10 +37306,10 @@
     </row>
     <row r="246" spans="1:20" ht="17">
       <c r="A246" s="55" t="s">
-        <v>1260</v>
+        <v>1254</v>
       </c>
       <c r="B246" s="55" t="s">
-        <v>1269</v>
+        <v>1263</v>
       </c>
       <c r="C246" s="55" t="s">
         <v>95</v>
@@ -37317,17 +37348,17 @@
         <v>504</v>
       </c>
       <c r="P246" s="86" t="s">
-        <v>1279</v>
+        <v>1273</v>
       </c>
       <c r="S246" s="47"/>
       <c r="T246" s="47"/>
     </row>
     <row r="247" spans="1:20" ht="16">
       <c r="A247" s="52" t="s">
-        <v>1261</v>
+        <v>1255</v>
       </c>
       <c r="B247" s="52" t="s">
-        <v>1270</v>
+        <v>1264</v>
       </c>
       <c r="C247" s="52" t="s">
         <v>95</v>
@@ -37371,10 +37402,10 @@
     </row>
     <row r="248" spans="1:20" ht="17">
       <c r="A248" s="55" t="s">
-        <v>1262</v>
+        <v>1256</v>
       </c>
       <c r="B248" s="55" t="s">
-        <v>1271</v>
+        <v>1265</v>
       </c>
       <c r="C248" s="55" t="s">
         <v>95</v>
@@ -37413,7 +37444,7 @@
         <v>678</v>
       </c>
       <c r="P248" s="86" t="s">
-        <v>1280</v>
+        <v>1274</v>
       </c>
       <c r="S248" s="47"/>
       <c r="T248" s="47"/>
@@ -43658,15 +43689,15 @@
       </c>
       <c r="B8" s="9">
         <f>IFERROR(SUMIF(Purchases!$B:$B,$A8,Purchases!$C:$C),0)</f>
-        <v>262571</v>
+        <v>262891</v>
       </c>
       <c r="C8" s="9">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>188829.33333333334</v>
+        <v>188936</v>
       </c>
       <c r="D8" s="9">
         <f>B8-C8</f>
-        <v>73741.666666666657</v>
+        <v>73955</v>
       </c>
       <c r="E8" s="9">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A8,$A$3:$B$5,2,FALSE()),0)</f>
@@ -43674,7 +43705,7 @@
       </c>
       <c r="F8" s="9">
         <f>D8+E8</f>
-        <v>73741.666666666657</v>
+        <v>73955</v>
       </c>
       <c r="G8" s="9">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A8,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A8,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A8,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A8,$B$13:$B$499,"Profit"),0)</f>
@@ -43682,7 +43713,7 @@
       </c>
       <c r="H8" s="73">
         <f>F8-G8</f>
-        <v>55438.32666666666</v>
+        <v>55651.66</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="13.5" customHeight="1">
@@ -43695,11 +43726,11 @@
       </c>
       <c r="C9" s="11">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>188829.33333333334</v>
+        <v>188936</v>
       </c>
       <c r="D9" s="11">
         <f>B9-C9</f>
-        <v>82487.666666666657</v>
+        <v>82381</v>
       </c>
       <c r="E9" s="11">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A9,$A$3:$B$5,2,FALSE()),0)</f>
@@ -43707,7 +43738,7 @@
       </c>
       <c r="F9" s="11">
         <f>D9+E9</f>
-        <v>82487.666666666657</v>
+        <v>82381</v>
       </c>
       <c r="G9" s="11">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A9,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A9,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A9,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A9,$B$13:$B$499,"Profit"),0)</f>
@@ -43715,7 +43746,7 @@
       </c>
       <c r="H9" s="74">
         <f>F9-G9</f>
-        <v>40848.336666666655</v>
+        <v>40741.67</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="13.5" customHeight="1">
@@ -43728,11 +43759,11 @@
       </c>
       <c r="C10" s="9">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>188829.33333333334</v>
+        <v>188936</v>
       </c>
       <c r="D10" s="9">
         <f>B10-C10</f>
-        <v>-156229.33333333334</v>
+        <v>-156336</v>
       </c>
       <c r="E10" s="9">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A10,$A$3:$B$5,2,FALSE()),0)</f>
@@ -43740,7 +43771,7 @@
       </c>
       <c r="F10" s="9">
         <f>D10+E10</f>
-        <v>-156229.33333333334</v>
+        <v>-156336</v>
       </c>
       <c r="G10" s="9">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A10,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A10,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A10,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A10,$B$13:$B$499,"Profit"),0)</f>
@@ -43748,7 +43779,7 @@
       </c>
       <c r="H10" s="73">
         <f>F10-G10</f>
-        <v>-96286.663333333345</v>
+        <v>-96393.33</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="75" customFormat="1" ht="15.75" customHeight="1">
@@ -44165,7 +44196,7 @@
       </c>
       <c r="B4" s="9">
         <f>IFERROR(SUMIFS(Sales!$C:$C,Sales!$E:$E,$A4,Sales!$I:$I,"Completed"),0)</f>
-        <v>447169</v>
+        <v>460648</v>
       </c>
       <c r="C4" s="9">
         <f>VLOOKUP($A4,PartnerShares!$A$3:$B$5,2,FALSE())</f>
@@ -44173,11 +44204,11 @@
       </c>
       <c r="D4" s="9">
         <f>Summary!$B$4*C4</f>
-        <v>171808.68819999998</v>
+        <v>176302.58679999999</v>
       </c>
       <c r="E4" s="9">
         <f>B4-D4</f>
-        <v>275360.31180000002</v>
+        <v>284345.41320000001</v>
       </c>
       <c r="F4" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -44185,7 +44216,7 @@
       </c>
       <c r="G4" s="73">
         <f>E4+F4</f>
-        <v>138050.28580000001</v>
+        <v>147035.3872</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5" customHeight="1">
@@ -44202,11 +44233,11 @@
       </c>
       <c r="D5" s="11">
         <f>Summary!$B$4*C5</f>
-        <v>171705.62359999999</v>
+        <v>176196.82639999999</v>
       </c>
       <c r="E5" s="11">
         <f>B5-D5</f>
-        <v>-117081.62359999999</v>
+        <v>-121572.82639999999</v>
       </c>
       <c r="F5" s="11">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -44214,7 +44245,7 @@
       </c>
       <c r="G5" s="74">
         <f>E5+F5</f>
-        <v>-45494.58159999999</v>
+        <v>-49985.78439999999</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1">
@@ -44231,11 +44262,11 @@
       </c>
       <c r="D6" s="9">
         <f>Summary!$B$4*C6</f>
-        <v>171808.68819999998</v>
+        <v>176302.58679999999</v>
       </c>
       <c r="E6" s="9">
         <f>B6-D6</f>
-        <v>-159278.68819999998</v>
+        <v>-163772.58679999999</v>
       </c>
       <c r="F6" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -44243,7 +44274,7 @@
       </c>
       <c r="G6" s="73">
         <f>E6+F6</f>
-        <v>-93555.704199999964</v>
+        <v>-98049.602799999979</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="13.5" customHeight="1">

--- a/docs/Chiraath-Summary-Aug26.xlsx
+++ b/docs/Chiraath-Summary-Aug26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anooppremachandran/Desktop/CHIRAATH/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54CC07C2-3DBB-6E48-9840-D321B9CE6E83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F5DA603-7CD1-944E-ACA5-37C93750C159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3342" uniqueCount="1326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3356" uniqueCount="1331">
   <si>
     <t>Notes:</t>
   </si>
@@ -3316,12 +3316,6 @@
     <t>Nishida friend - 1400 - checks/floral + kathakali</t>
   </si>
   <si>
-    <t>Navy/blue &amp; maroon/grey - Navya</t>
-  </si>
-  <si>
-    <t>Green/Navy, Red/maroon, Dark green/Navy</t>
-  </si>
-  <si>
     <t>Cotton 2-piece set with blue floral prints-M (CHR-156), Short Kurti(CHR-151)-L, Dusty Rose Salwar(CHR-77)-L, Chanderis Silk Saree(Yellow-CHR-119), Matka - Lavender/Violet(CHR-174), Chikku Maroon new design(CHR-188)</t>
   </si>
   <si>
@@ -3449,12 +3443,6 @@
     <t>Gincy Jibi</t>
   </si>
   <si>
-    <t>Green/maroon - Rajitha Teacher,  chikku green - Razia Salim, Rust Orange/Coffee Brown - Nishida, Chikku Maroon(1200) - Nishida, Komalavalli - Red/green, peacock blue/navy - returned, mustard/blue - girija(1200)</t>
-  </si>
-  <si>
-    <t>Golden yellow &amp; green triangle, Red &amp; Green</t>
-  </si>
-  <si>
     <t>mustard/blue CHR-188</t>
   </si>
   <si>
@@ -3619,12 +3607,6 @@
     <t>Green and maroon, deep purple and dark green, blue and dark green, rose pink and olive green, Red</t>
   </si>
   <si>
-    <t>Latha - Red, Shylaja - Purple, Jisha - Red</t>
-  </si>
-  <si>
-    <t>Yellow/Orange(4), Green, Blue</t>
-  </si>
-  <si>
     <t>CHR-111 white cotton salwar, Banarasi golden yellow blue</t>
   </si>
   <si>
@@ -3760,9 +3742,6 @@
     <t>CHR-214 - Yellow/Blue Chanderi Silk</t>
   </si>
   <si>
-    <t>CHR-182 (Yellow Linen Saree with Lotus, CHR-217 cream/gold with stars and paisley &amp; cream/gold with flowers - 1000 advance, 900 - pending</t>
-  </si>
-  <si>
     <t>Asha Sandran</t>
   </si>
   <si>
@@ -3791,9 +3770,6 @@
   </si>
   <si>
     <t>Renju</t>
-  </si>
-  <si>
-    <t>CHR-212 - Red, CHR-214 - Yellow/Blue Chanderi Silk - 1380 advance for the returned saree, 920 pending</t>
   </si>
   <si>
     <t>CHR-238</t>
@@ -4041,6 +4017,45 @@
   </si>
   <si>
     <t>1250 X 6, 1250 X 11, 1250 X 5, 1250 x 5, 1250 X5</t>
+  </si>
+  <si>
+    <t>CHR-212 - Red, CHR-214 - Yellow/Blue Chanderi Silk</t>
+  </si>
+  <si>
+    <t>CHR-182 (Yellow Linen Saree with Lotus, CHR-217 cream/gold with stars and paisley &amp; cream/gold with flowers, CHR-212 Green elephant print - 1600 advance, 1150 - pending</t>
+  </si>
+  <si>
+    <t>Latha - Red, Shylaja - Purple, Jisha - Red, Bank staff - Green</t>
+  </si>
+  <si>
+    <t>Yellow/Orange(4), Blue</t>
+  </si>
+  <si>
+    <t>Green/maroon - Rajitha Teacher,  chikku green - Razia Salim, Rust Orange/Coffee Brown - Nishida, Chikku Maroon(1200) - Nishida, Komalavalli - Red/green, peacock blue/navy - returned, mustard/blue - girija(1200), Suma - Golden yellow &amp; green triangle</t>
+  </si>
+  <si>
+    <t>Suma Bank</t>
+  </si>
+  <si>
+    <t>CHR-188 - Banarasi yellow triangle</t>
+  </si>
+  <si>
+    <t>Red &amp; Green</t>
+  </si>
+  <si>
+    <t>Sangeetha Prasad</t>
+  </si>
+  <si>
+    <t>CHR-199 - Tissue Dark Green/navy</t>
+  </si>
+  <si>
+    <t>Navy/blue &amp; maroon/grey - Navya, Sangeetha - Dark green/Navy</t>
+  </si>
+  <si>
+    <t>Green/Navy, Red/maroon</t>
+  </si>
+  <si>
+    <t>CHR-186 - Banarasi Silk (Golden Yellow Green)</t>
   </si>
 </sst>
 </file>
@@ -4926,7 +4941,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>347</c:v>
+                  <c:v>350</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>99</c:v>
@@ -5029,7 +5044,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>182</c:v>
+                  <c:v>179</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>51</c:v>
@@ -5362,7 +5377,7 @@
                   <c:v>53945</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>129583.14666666667</c:v>
+                  <c:v>127271.14666666667</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>1062</c:v>
@@ -5855,10 +5870,10 @@
                   <c:v>72885</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>62646</c:v>
+                  <c:v>63426</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>61468</c:v>
+                  <c:v>65478</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -6295,10 +6310,10 @@
                   <c:v>-26158</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-39554</c:v>
+                  <c:v>-38774</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>51007</c:v>
+                  <c:v>55017</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -6759,10 +6774,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>451</c:v>
+                  <c:v>454</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>278</c:v>
+                  <c:v>275</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7949,7 +7964,7 @@
       </c>
       <c r="B4" s="10">
         <f>SUMIFS(Sales!C:C, Sales!I:I, "Completed")</f>
-        <v>528802</v>
+        <v>537362</v>
       </c>
       <c r="E4" s="9" t="str">
         <f>PartnerShares!A3</f>
@@ -7966,7 +7981,7 @@
       </c>
       <c r="B5" s="12">
         <f>SUM(Sales!C:C)</f>
-        <v>552612</v>
+        <v>557402</v>
       </c>
       <c r="E5" s="11" t="str">
         <f>PartnerShares!A4</f>
@@ -7983,7 +7998,7 @@
       </c>
       <c r="B6" s="10">
         <f>B4-B3</f>
-        <v>-38006</v>
+        <v>-29446</v>
       </c>
       <c r="E6" s="9" t="str">
         <f>PartnerShares!A5</f>
@@ -8195,15 +8210,15 @@
       </c>
       <c r="B26" s="10">
         <f>'Cash Pool'!B4</f>
-        <v>460648</v>
+        <v>469208</v>
       </c>
       <c r="C26" s="10">
         <f>'Cash Pool'!D4</f>
-        <v>176302.58679999999</v>
+        <v>179156.4908</v>
       </c>
       <c r="D26" s="10">
         <f>'Cash Pool'!E4</f>
-        <v>284345.41320000001</v>
+        <v>290051.50919999997</v>
       </c>
       <c r="E26" s="10">
         <f>'Cash Pool'!F4</f>
@@ -8211,11 +8226,11 @@
       </c>
       <c r="F26" s="13">
         <f>'Cash Pool'!G4</f>
-        <v>147035.3872</v>
+        <v>152741.48319999996</v>
       </c>
       <c r="G26" s="17" t="str">
         <f>IF(ROUND(F26,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F26),"#,##0"),IF(ROUND(F26,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F26),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹147,035</v>
+        <v>Pay ₹152,741</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="13.5" customHeight="1">
@@ -8229,11 +8244,11 @@
       </c>
       <c r="C27" s="12">
         <f>'Cash Pool'!D5</f>
-        <v>176196.82639999999</v>
+        <v>179049.0184</v>
       </c>
       <c r="D27" s="12">
         <f>'Cash Pool'!E5</f>
-        <v>-121572.82639999999</v>
+        <v>-124425.0184</v>
       </c>
       <c r="E27" s="12">
         <f>'Cash Pool'!F5</f>
@@ -8241,11 +8256,11 @@
       </c>
       <c r="F27" s="14">
         <f>'Cash Pool'!G5</f>
-        <v>-49985.78439999999</v>
+        <v>-52837.9764</v>
       </c>
       <c r="G27" s="18" t="str">
         <f>IF(ROUND(F27,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F27),"#,##0"),IF(ROUND(F27,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F27),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹49,986</v>
+        <v>Receive ₹52,838</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="13.5" customHeight="1">
@@ -8259,11 +8274,11 @@
       </c>
       <c r="C28" s="10">
         <f>'Cash Pool'!D6</f>
-        <v>176302.58679999999</v>
+        <v>179156.4908</v>
       </c>
       <c r="D28" s="10">
         <f>'Cash Pool'!E6</f>
-        <v>-163772.58679999999</v>
+        <v>-166626.4908</v>
       </c>
       <c r="E28" s="10">
         <f>'Cash Pool'!F6</f>
@@ -8271,11 +8286,11 @@
       </c>
       <c r="F28" s="13">
         <f>'Cash Pool'!G6</f>
-        <v>-98049.602799999979</v>
+        <v>-100903.50679999999</v>
       </c>
       <c r="G28" s="16" t="str">
         <f>IF(ROUND(F28,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F28),"#,##0"),IF(ROUND(F28,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F28),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹98,050</v>
+        <v>Receive ₹100,904</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.75" customHeight="1">
@@ -8387,7 +8402,7 @@
       </c>
       <c r="B3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46252</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1">
@@ -8403,7 +8418,7 @@
       </c>
       <c r="E5" s="21">
         <f>Summary!B4</f>
-        <v>528802</v>
+        <v>537362</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
@@ -8412,14 +8427,14 @@
       </c>
       <c r="B6" s="21">
         <f>Summary!B6</f>
-        <v>-38006</v>
+        <v>-29446</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>71</v>
       </c>
       <c r="E6" s="21">
         <f>SUMIFS(INVENTORY!K:K, INVENTORY!N:N, "&lt;&gt;Sold Out")</f>
-        <v>173719.34666666665</v>
+        <v>171407.34666666665</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1">
@@ -8471,7 +8486,7 @@
       </c>
       <c r="G10" s="21">
         <f>SUM(INVENTORY!F:F)</f>
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1">
@@ -8495,7 +8510,7 @@
       </c>
       <c r="G11" s="27">
         <f>SUM(INVENTORY!G:G)</f>
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
@@ -8576,11 +8591,11 @@
       </c>
       <c r="C16" s="21">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$993,"MMM")=$A16)*(YEAR(Sales!$A$2:$A$993)=$B$7)*Sales!$C$2:$C$993),0)</f>
-        <v>62646</v>
+        <v>63426</v>
       </c>
       <c r="D16" s="21">
         <f t="shared" si="0"/>
-        <v>-39554</v>
+        <v>-38774</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1">
@@ -8593,11 +8608,11 @@
       </c>
       <c r="C17" s="27">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$993,"MMM")=$A17)*(YEAR(Sales!$A$2:$A$993)=$B$7)*Sales!$C$2:$C$993),0)</f>
-        <v>61468</v>
+        <v>65478</v>
       </c>
       <c r="D17" s="27">
         <f t="shared" si="0"/>
-        <v>51007</v>
+        <v>55017</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1">
@@ -8691,11 +8706,11 @@
       </c>
       <c r="G47" s="30">
         <f>SUMIF(INVENTORY!C:C, F47, INVENTORY!F:F)</f>
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="H47" s="30">
         <f>SUMIF(INVENTORY!C:C, F47, INVENTORY!G:G)</f>
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="J47" s="30" t="s">
         <v>96</v>
@@ -8722,7 +8737,7 @@
       </c>
       <c r="K48" s="31">
         <f t="array" ref="K48">SUMPRODUCT((INVENTORY!$C$2:$C$476=J48)*(INVENTORY!$D$2:$D$476)*(INVENTORY!$G$2:$G$476))</f>
-        <v>129583.14666666667</v>
+        <v>127271.14666666667</v>
       </c>
     </row>
     <row r="49" spans="5:12" ht="15" customHeight="1">
@@ -10095,7 +10110,7 @@
         <v>28526</v>
       </c>
       <c r="D91" s="39" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="15" customHeight="1">
@@ -10165,7 +10180,7 @@
         <v>70</v>
       </c>
       <c r="D96" s="36" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="15" customHeight="1">
@@ -10179,7 +10194,7 @@
         <v>1375</v>
       </c>
       <c r="D97" s="39" t="s">
-        <v>1133</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="15" customHeight="1">
@@ -10193,7 +10208,7 @@
         <v>189</v>
       </c>
       <c r="D98" s="36" t="s">
-        <v>1134</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="15" customHeight="1">
@@ -10319,7 +10334,7 @@
         <v>570</v>
       </c>
       <c r="D107" s="39" t="s">
-        <v>1296</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="15" customHeight="1">
@@ -10347,7 +10362,7 @@
         <v>320</v>
       </c>
       <c r="D109" s="39" t="s">
-        <v>1296</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="15" customHeight="1">
@@ -17720,7 +17735,7 @@
       <c r="F216" s="46"/>
       <c r="G216" s="46"/>
       <c r="H216" s="46" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="I216" s="45" t="s">
         <v>148</v>
@@ -18577,7 +18592,7 @@
         <v>46201</v>
       </c>
       <c r="B251" s="45" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="C251" s="85">
         <v>1380</v>
@@ -18702,7 +18717,7 @@
         <v>46203</v>
       </c>
       <c r="B256" s="44" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="C256" s="83">
         <v>950</v>
@@ -18716,7 +18731,7 @@
       <c r="F256" s="44"/>
       <c r="G256" s="44"/>
       <c r="H256" s="44" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="I256" s="44" t="s">
         <v>148</v>
@@ -18727,7 +18742,7 @@
         <v>46204</v>
       </c>
       <c r="B257" s="45" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="C257" s="85">
         <v>699</v>
@@ -18741,7 +18756,7 @@
       <c r="F257" s="46"/>
       <c r="G257" s="46"/>
       <c r="H257" s="46" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="I257" s="45" t="s">
         <v>148</v>
@@ -18752,7 +18767,7 @@
         <v>46205</v>
       </c>
       <c r="B258" s="44" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="C258" s="83">
         <v>1500</v>
@@ -18766,7 +18781,7 @@
       <c r="F258" s="44"/>
       <c r="G258" s="44"/>
       <c r="H258" s="44" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="I258" s="44" t="s">
         <v>148</v>
@@ -18777,7 +18792,7 @@
         <v>46205</v>
       </c>
       <c r="B259" s="45" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="C259" s="85">
         <v>1200</v>
@@ -18791,7 +18806,7 @@
       <c r="F259" s="46"/>
       <c r="G259" s="46"/>
       <c r="H259" s="46" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="I259" s="45" t="s">
         <v>148</v>
@@ -18802,7 +18817,7 @@
         <v>46205</v>
       </c>
       <c r="B260" s="44" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="C260" s="83">
         <v>1500</v>
@@ -18816,7 +18831,7 @@
       <c r="F260" s="44"/>
       <c r="G260" s="44"/>
       <c r="H260" s="44" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="I260" s="44" t="s">
         <v>148</v>
@@ -18827,7 +18842,7 @@
         <v>46205</v>
       </c>
       <c r="B261" s="45" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="C261" s="85">
         <v>2600</v>
@@ -18841,7 +18856,7 @@
       <c r="F261" s="46"/>
       <c r="G261" s="46"/>
       <c r="H261" s="46" t="s">
-        <v>1187</v>
+        <v>1181</v>
       </c>
       <c r="I261" s="45" t="s">
         <v>148</v>
@@ -18852,7 +18867,7 @@
         <v>46206</v>
       </c>
       <c r="B262" s="44" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="C262" s="83">
         <v>1380</v>
@@ -18877,7 +18892,7 @@
         <v>46206</v>
       </c>
       <c r="B263" s="45" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="C263" s="85">
         <v>1380</v>
@@ -18902,7 +18917,7 @@
         <v>46206</v>
       </c>
       <c r="B264" s="44" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="C264" s="83">
         <v>2500</v>
@@ -18916,7 +18931,7 @@
       <c r="F264" s="44"/>
       <c r="G264" s="44"/>
       <c r="H264" s="44" t="s">
-        <v>1287</v>
+        <v>1279</v>
       </c>
       <c r="I264" s="44" t="s">
         <v>356</v>
@@ -18927,7 +18942,7 @@
         <v>46206</v>
       </c>
       <c r="B265" s="45" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="C265" s="85">
         <v>1300</v>
@@ -18941,7 +18956,7 @@
       <c r="F265" s="46"/>
       <c r="G265" s="46"/>
       <c r="H265" s="46" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="I265" s="45" t="s">
         <v>356</v>
@@ -18952,7 +18967,7 @@
         <v>46206</v>
       </c>
       <c r="B266" s="44" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="C266" s="83">
         <v>1380</v>
@@ -18966,7 +18981,7 @@
       <c r="F266" s="44"/>
       <c r="G266" s="44"/>
       <c r="H266" s="44" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="I266" s="44" t="s">
         <v>148</v>
@@ -18991,7 +19006,7 @@
       <c r="F267" s="46"/>
       <c r="G267" s="46"/>
       <c r="H267" s="46" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="I267" s="45" t="s">
         <v>148</v>
@@ -19002,7 +19017,7 @@
         <v>46208</v>
       </c>
       <c r="B268" s="44" t="s">
-        <v>1317</v>
+        <v>1309</v>
       </c>
       <c r="C268" s="83">
         <v>2350</v>
@@ -19012,7 +19027,7 @@
       <c r="F268" s="44"/>
       <c r="G268" s="44"/>
       <c r="H268" s="44" t="s">
-        <v>1318</v>
+        <v>1310</v>
       </c>
       <c r="I268" s="44" t="s">
         <v>356</v>
@@ -19023,7 +19038,7 @@
         <v>46209</v>
       </c>
       <c r="B269" s="45" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="C269" s="85">
         <v>1100</v>
@@ -19037,7 +19052,7 @@
       <c r="F269" s="46"/>
       <c r="G269" s="46"/>
       <c r="H269" s="46" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="I269" s="45" t="s">
         <v>148</v>
@@ -19048,7 +19063,7 @@
         <v>46210</v>
       </c>
       <c r="B270" s="44" t="s">
-        <v>1320</v>
+        <v>1312</v>
       </c>
       <c r="C270" s="83">
         <v>3200</v>
@@ -19062,7 +19077,7 @@
       <c r="F270" s="44"/>
       <c r="G270" s="44"/>
       <c r="H270" s="44" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="I270" s="44" t="s">
         <v>148</v>
@@ -19073,7 +19088,7 @@
         <v>46211</v>
       </c>
       <c r="B271" s="45" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="C271" s="85">
         <v>1380</v>
@@ -19087,7 +19102,7 @@
       <c r="F271" s="46"/>
       <c r="G271" s="46"/>
       <c r="H271" s="46" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="I271" s="45" t="s">
         <v>148</v>
@@ -19098,7 +19113,7 @@
         <v>46215</v>
       </c>
       <c r="B272" s="44" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="C272" s="83">
         <v>1380</v>
@@ -19123,7 +19138,7 @@
         <v>46215</v>
       </c>
       <c r="B273" s="45" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="C273" s="85">
         <v>699</v>
@@ -19137,7 +19152,7 @@
       <c r="F273" s="46"/>
       <c r="G273" s="46"/>
       <c r="H273" s="46" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="I273" s="45" t="s">
         <v>148</v>
@@ -19162,7 +19177,7 @@
       <c r="F274" s="44"/>
       <c r="G274" s="44"/>
       <c r="H274" s="44" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="I274" s="44" t="s">
         <v>148</v>
@@ -19173,7 +19188,7 @@
         <v>46216</v>
       </c>
       <c r="B275" s="45" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="C275" s="85">
         <v>699</v>
@@ -19187,7 +19202,7 @@
       <c r="F275" s="46"/>
       <c r="G275" s="46"/>
       <c r="H275" s="46" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="I275" s="45" t="s">
         <v>148</v>
@@ -19198,7 +19213,7 @@
         <v>46216</v>
       </c>
       <c r="B276" s="44" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="C276" s="83">
         <v>3000</v>
@@ -19212,7 +19227,7 @@
       <c r="F276" s="44"/>
       <c r="G276" s="44"/>
       <c r="H276" s="44" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="I276" s="44" t="s">
         <v>148</v>
@@ -19223,7 +19238,7 @@
         <v>46219</v>
       </c>
       <c r="B277" s="45" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="C277" s="85">
         <v>1380</v>
@@ -19287,7 +19302,7 @@
       <c r="F279" s="46"/>
       <c r="G279" s="46"/>
       <c r="H279" s="46" t="s">
-        <v>1131</v>
+        <v>1127</v>
       </c>
       <c r="I279" s="45" t="s">
         <v>148</v>
@@ -19312,7 +19327,7 @@
       <c r="F280" s="44"/>
       <c r="G280" s="44"/>
       <c r="H280" s="44" t="s">
-        <v>1137</v>
+        <v>1133</v>
       </c>
       <c r="I280" s="44" t="s">
         <v>148</v>
@@ -19337,7 +19352,7 @@
       <c r="F281" s="46"/>
       <c r="G281" s="46"/>
       <c r="H281" s="46" t="s">
-        <v>1141</v>
+        <v>1137</v>
       </c>
       <c r="I281" s="45" t="s">
         <v>148</v>
@@ -19348,7 +19363,7 @@
         <v>46220</v>
       </c>
       <c r="B282" s="44" t="s">
-        <v>1151</v>
+        <v>1147</v>
       </c>
       <c r="C282" s="83">
         <v>1500</v>
@@ -19362,7 +19377,7 @@
       <c r="F282" s="44"/>
       <c r="G282" s="44"/>
       <c r="H282" s="44" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="I282" s="44" t="s">
         <v>148</v>
@@ -19373,7 +19388,7 @@
         <v>46221</v>
       </c>
       <c r="B283" s="45" t="s">
-        <v>1155</v>
+        <v>1151</v>
       </c>
       <c r="C283" s="85">
         <v>1100</v>
@@ -19387,7 +19402,7 @@
       <c r="F283" s="46"/>
       <c r="G283" s="46"/>
       <c r="H283" s="46" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="I283" s="45" t="s">
         <v>148</v>
@@ -19398,7 +19413,7 @@
         <v>46222</v>
       </c>
       <c r="B284" s="44" t="s">
-        <v>1157</v>
+        <v>1153</v>
       </c>
       <c r="C284" s="83">
         <v>850</v>
@@ -19412,7 +19427,7 @@
       <c r="F284" s="44"/>
       <c r="G284" s="44"/>
       <c r="H284" s="44" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
       <c r="I284" s="44" t="s">
         <v>148</v>
@@ -19423,7 +19438,7 @@
         <v>46222</v>
       </c>
       <c r="B285" s="45" t="s">
-        <v>1159</v>
+        <v>1155</v>
       </c>
       <c r="C285" s="85">
         <v>1250</v>
@@ -19437,7 +19452,7 @@
       <c r="F285" s="46"/>
       <c r="G285" s="46"/>
       <c r="H285" s="46" t="s">
-        <v>1160</v>
+        <v>1156</v>
       </c>
       <c r="I285" s="45" t="s">
         <v>148</v>
@@ -19448,7 +19463,7 @@
         <v>46222</v>
       </c>
       <c r="B286" s="44" t="s">
-        <v>1162</v>
+        <v>1158</v>
       </c>
       <c r="C286" s="83">
         <v>700</v>
@@ -19473,7 +19488,7 @@
         <v>46222</v>
       </c>
       <c r="B287" s="45" t="s">
-        <v>1163</v>
+        <v>1159</v>
       </c>
       <c r="C287" s="85">
         <v>699</v>
@@ -19498,7 +19513,7 @@
         <v>46223</v>
       </c>
       <c r="B288" s="44" t="s">
-        <v>1166</v>
+        <v>1162</v>
       </c>
       <c r="C288" s="83">
         <v>1380</v>
@@ -19512,7 +19527,7 @@
       <c r="F288" s="44"/>
       <c r="G288" s="44"/>
       <c r="H288" s="44" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="I288" s="44" t="s">
         <v>148</v>
@@ -19523,7 +19538,7 @@
         <v>46224</v>
       </c>
       <c r="B289" s="45" t="s">
-        <v>1169</v>
+        <v>1165</v>
       </c>
       <c r="C289" s="85">
         <v>1380</v>
@@ -19537,7 +19552,7 @@
       <c r="F289" s="46"/>
       <c r="G289" s="46"/>
       <c r="H289" s="46" t="s">
-        <v>1172</v>
+        <v>1168</v>
       </c>
       <c r="I289" s="45" t="s">
         <v>148</v>
@@ -19548,7 +19563,7 @@
         <v>46224</v>
       </c>
       <c r="B290" s="44" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="C290" s="83">
         <v>1380</v>
@@ -19562,7 +19577,7 @@
       <c r="F290" s="44"/>
       <c r="G290" s="44"/>
       <c r="H290" s="44" t="s">
-        <v>1173</v>
+        <v>1169</v>
       </c>
       <c r="I290" s="44" t="s">
         <v>148</v>
@@ -19587,7 +19602,7 @@
       <c r="F291" s="44"/>
       <c r="G291" s="44"/>
       <c r="H291" s="44" t="s">
-        <v>1176</v>
+        <v>1172</v>
       </c>
       <c r="I291" s="44" t="s">
         <v>148</v>
@@ -19598,17 +19613,17 @@
         <v>46229</v>
       </c>
       <c r="B292" s="45" t="s">
-        <v>1179</v>
+        <v>1175</v>
       </c>
       <c r="C292" s="85">
-        <v>1900</v>
+        <v>2750</v>
       </c>
       <c r="D292" s="45"/>
       <c r="E292" s="45"/>
       <c r="F292" s="46"/>
       <c r="G292" s="46"/>
       <c r="H292" s="46" t="s">
-        <v>1232</v>
+        <v>1319</v>
       </c>
       <c r="I292" s="45" t="s">
         <v>356</v>
@@ -19629,31 +19644,35 @@
       <c r="F293" s="44"/>
       <c r="G293" s="44"/>
       <c r="H293" s="44" t="s">
-        <v>1286</v>
+        <v>1278</v>
       </c>
       <c r="I293" s="44" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="294" spans="1:9" ht="28">
+    <row r="294" spans="1:9" ht="14">
       <c r="A294" s="84">
         <v>46229</v>
       </c>
       <c r="B294" s="45" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="C294" s="85">
-        <v>2300</v>
-      </c>
-      <c r="D294" s="45"/>
-      <c r="E294" s="45"/>
+        <v>2230</v>
+      </c>
+      <c r="D294" s="45" t="s">
+        <v>162</v>
+      </c>
+      <c r="E294" s="45" t="s">
+        <v>49</v>
+      </c>
       <c r="F294" s="46"/>
       <c r="G294" s="46"/>
       <c r="H294" s="46" t="s">
-        <v>1243</v>
+        <v>1318</v>
       </c>
       <c r="I294" s="45" t="s">
-        <v>356</v>
+        <v>148</v>
       </c>
     </row>
     <row r="295" spans="1:9" ht="28">
@@ -19661,13 +19680,13 @@
         <v>46229</v>
       </c>
       <c r="B295" s="44" t="s">
-        <v>1190</v>
+        <v>1184</v>
       </c>
       <c r="C295" s="83">
         <v>3700</v>
       </c>
       <c r="D295" s="44" t="s">
-        <v>1315</v>
+        <v>1307</v>
       </c>
       <c r="E295" s="44" t="s">
         <v>49</v>
@@ -19675,10 +19694,10 @@
       <c r="F295" s="44"/>
       <c r="G295" s="44"/>
       <c r="H295" s="44" t="s">
-        <v>1316</v>
+        <v>1308</v>
       </c>
       <c r="I295" s="44" t="s">
-        <v>356</v>
+        <v>148</v>
       </c>
     </row>
     <row r="296" spans="1:9" ht="14">
@@ -19686,7 +19705,7 @@
         <v>46235</v>
       </c>
       <c r="B296" s="45" t="s">
-        <v>1233</v>
+        <v>1226</v>
       </c>
       <c r="C296" s="85">
         <v>1450</v>
@@ -19700,7 +19719,7 @@
       <c r="F296" s="46"/>
       <c r="G296" s="46"/>
       <c r="H296" s="46" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
       <c r="I296" s="45" t="s">
         <v>148</v>
@@ -19711,7 +19730,7 @@
         <v>46236</v>
       </c>
       <c r="B297" s="44" t="s">
-        <v>1320</v>
+        <v>1312</v>
       </c>
       <c r="C297" s="83">
         <v>6900</v>
@@ -19725,7 +19744,7 @@
       <c r="F297" s="44"/>
       <c r="G297" s="44"/>
       <c r="H297" s="44" t="s">
-        <v>1322</v>
+        <v>1314</v>
       </c>
       <c r="I297" s="44" t="s">
         <v>148</v>
@@ -19736,7 +19755,7 @@
         <v>46236</v>
       </c>
       <c r="B298" s="45" t="s">
-        <v>1236</v>
+        <v>1229</v>
       </c>
       <c r="C298" s="85">
         <v>1479</v>
@@ -19750,7 +19769,7 @@
       <c r="F298" s="46"/>
       <c r="G298" s="46"/>
       <c r="H298" s="46" t="s">
-        <v>1235</v>
+        <v>1228</v>
       </c>
       <c r="I298" s="45" t="s">
         <v>148</v>
@@ -19761,7 +19780,7 @@
         <v>46236</v>
       </c>
       <c r="B299" s="44" t="s">
-        <v>1240</v>
+        <v>1233</v>
       </c>
       <c r="C299" s="83">
         <v>2630</v>
@@ -19775,7 +19794,7 @@
       <c r="F299" s="44"/>
       <c r="G299" s="44"/>
       <c r="H299" s="44" t="s">
-        <v>1238</v>
+        <v>1231</v>
       </c>
       <c r="I299" s="44" t="s">
         <v>148</v>
@@ -19786,7 +19805,7 @@
         <v>46238</v>
       </c>
       <c r="B300" s="45" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="C300" s="85">
         <v>1380</v>
@@ -19811,7 +19830,7 @@
         <v>46238</v>
       </c>
       <c r="B301" s="44" t="s">
-        <v>1320</v>
+        <v>1312</v>
       </c>
       <c r="C301" s="83">
         <v>12650</v>
@@ -19825,7 +19844,7 @@
       <c r="F301" s="44"/>
       <c r="G301" s="44"/>
       <c r="H301" s="44" t="s">
-        <v>1323</v>
+        <v>1315</v>
       </c>
       <c r="I301" s="44" t="s">
         <v>148</v>
@@ -19836,7 +19855,7 @@
         <v>46240</v>
       </c>
       <c r="B302" s="45" t="s">
-        <v>1236</v>
+        <v>1229</v>
       </c>
       <c r="C302" s="85">
         <v>1000</v>
@@ -19846,7 +19865,7 @@
       <c r="F302" s="46"/>
       <c r="G302" s="46"/>
       <c r="H302" s="46" t="s">
-        <v>1246</v>
+        <v>1238</v>
       </c>
       <c r="I302" s="45" t="s">
         <v>148</v>
@@ -19867,7 +19886,7 @@
       <c r="F303" s="44"/>
       <c r="G303" s="44"/>
       <c r="H303" s="44" t="s">
-        <v>1314</v>
+        <v>1306</v>
       </c>
       <c r="I303" s="44" t="s">
         <v>356</v>
@@ -19878,7 +19897,7 @@
         <v>46243</v>
       </c>
       <c r="B304" s="45" t="s">
-        <v>1288</v>
+        <v>1280</v>
       </c>
       <c r="C304" s="85">
         <v>1380</v>
@@ -19888,7 +19907,7 @@
       <c r="F304" s="46"/>
       <c r="G304" s="46"/>
       <c r="H304" s="46" t="s">
-        <v>1289</v>
+        <v>1281</v>
       </c>
       <c r="I304" s="45" t="s">
         <v>356</v>
@@ -19899,7 +19918,7 @@
         <v>46243</v>
       </c>
       <c r="B305" s="44" t="s">
-        <v>1290</v>
+        <v>1282</v>
       </c>
       <c r="C305" s="83">
         <v>1380</v>
@@ -19913,7 +19932,7 @@
       <c r="F305" s="44"/>
       <c r="G305" s="44"/>
       <c r="H305" s="44" t="s">
-        <v>1291</v>
+        <v>1283</v>
       </c>
       <c r="I305" s="44" t="s">
         <v>148</v>
@@ -19924,7 +19943,7 @@
         <v>46243</v>
       </c>
       <c r="B306" s="45" t="s">
-        <v>1294</v>
+        <v>1286</v>
       </c>
       <c r="C306" s="85">
         <v>1250</v>
@@ -19938,7 +19957,7 @@
       <c r="F306" s="46"/>
       <c r="G306" s="46"/>
       <c r="H306" s="46" t="s">
-        <v>1295</v>
+        <v>1287</v>
       </c>
       <c r="I306" s="45" t="s">
         <v>148</v>
@@ -19949,7 +19968,7 @@
         <v>46243</v>
       </c>
       <c r="B307" s="44" t="s">
-        <v>1320</v>
+        <v>1312</v>
       </c>
       <c r="C307" s="83">
         <v>5750</v>
@@ -19963,7 +19982,7 @@
       <c r="F307" s="44"/>
       <c r="G307" s="44"/>
       <c r="H307" s="44" t="s">
-        <v>1321</v>
+        <v>1313</v>
       </c>
       <c r="I307" s="44" t="s">
         <v>148</v>
@@ -19974,7 +19993,7 @@
         <v>46248</v>
       </c>
       <c r="B308" s="44" t="s">
-        <v>1298</v>
+        <v>1290</v>
       </c>
       <c r="C308" s="83">
         <v>1380</v>
@@ -19988,7 +20007,7 @@
       <c r="F308" s="44"/>
       <c r="G308" s="44"/>
       <c r="H308" s="44" t="s">
-        <v>1299</v>
+        <v>1291</v>
       </c>
       <c r="I308" s="44" t="s">
         <v>148</v>
@@ -19999,7 +20018,7 @@
         <v>46248</v>
       </c>
       <c r="B309" s="45" t="s">
-        <v>1300</v>
+        <v>1292</v>
       </c>
       <c r="C309" s="85">
         <v>1380</v>
@@ -20013,7 +20032,7 @@
       <c r="F309" s="46"/>
       <c r="G309" s="46"/>
       <c r="H309" s="46" t="s">
-        <v>1301</v>
+        <v>1293</v>
       </c>
       <c r="I309" s="45" t="s">
         <v>148</v>
@@ -20038,7 +20057,7 @@
       <c r="F310" s="44"/>
       <c r="G310" s="44"/>
       <c r="H310" s="44" t="s">
-        <v>1311</v>
+        <v>1303</v>
       </c>
       <c r="I310" s="44" t="s">
         <v>148</v>
@@ -20063,7 +20082,7 @@
       <c r="F311" s="46"/>
       <c r="G311" s="46"/>
       <c r="H311" s="46" t="s">
-        <v>1303</v>
+        <v>1295</v>
       </c>
       <c r="I311" s="45" t="s">
         <v>148</v>
@@ -20074,7 +20093,7 @@
         <v>46250</v>
       </c>
       <c r="B312" s="44" t="s">
-        <v>1306</v>
+        <v>1298</v>
       </c>
       <c r="C312" s="83">
         <v>2250</v>
@@ -20088,7 +20107,7 @@
       <c r="F312" s="44"/>
       <c r="G312" s="44"/>
       <c r="H312" s="44" t="s">
-        <v>1308</v>
+        <v>1300</v>
       </c>
       <c r="I312" s="44" t="s">
         <v>148</v>
@@ -20099,7 +20118,7 @@
         <v>46252</v>
       </c>
       <c r="B313" s="45" t="s">
-        <v>1320</v>
+        <v>1312</v>
       </c>
       <c r="C313" s="85">
         <v>5750</v>
@@ -20113,7 +20132,7 @@
       <c r="F313" s="46"/>
       <c r="G313" s="46"/>
       <c r="H313" s="46" t="s">
-        <v>1321</v>
+        <v>1313</v>
       </c>
       <c r="I313" s="45" t="s">
         <v>148</v>
@@ -20124,22 +20143,32 @@
         <v>46252</v>
       </c>
       <c r="B314" s="44" t="s">
-        <v>1324</v>
-      </c>
-      <c r="C314" s="83"/>
-      <c r="D314" s="44"/>
-      <c r="E314" s="44"/>
+        <v>1316</v>
+      </c>
+      <c r="C314" s="83">
+        <v>1380</v>
+      </c>
+      <c r="D314" s="44" t="s">
+        <v>162</v>
+      </c>
+      <c r="E314" s="44" t="s">
+        <v>49</v>
+      </c>
       <c r="F314" s="44"/>
       <c r="G314" s="44"/>
-      <c r="H314" s="44"/>
-      <c r="I314" s="44"/>
+      <c r="H314" s="44" t="s">
+        <v>1330</v>
+      </c>
+      <c r="I314" s="44" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="315" spans="1:9" ht="14">
       <c r="A315" s="84">
         <v>46252</v>
       </c>
       <c r="B315" s="45" t="s">
-        <v>1320</v>
+        <v>1312</v>
       </c>
       <c r="C315" s="85">
         <v>5750</v>
@@ -20153,33 +20182,57 @@
       <c r="F315" s="46"/>
       <c r="G315" s="46"/>
       <c r="H315" s="46" t="s">
-        <v>1321</v>
+        <v>1313</v>
       </c>
       <c r="I315" s="45" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="316" spans="1:9">
-      <c r="A316" s="82"/>
-      <c r="B316" s="44"/>
-      <c r="C316" s="83"/>
+    <row r="316" spans="1:9" ht="14">
+      <c r="A316" s="82">
+        <v>46252</v>
+      </c>
+      <c r="B316" s="44" t="s">
+        <v>1323</v>
+      </c>
+      <c r="C316" s="83">
+        <v>1380</v>
+      </c>
       <c r="D316" s="44"/>
       <c r="E316" s="44"/>
       <c r="F316" s="44"/>
       <c r="G316" s="44"/>
-      <c r="H316" s="44"/>
-      <c r="I316" s="44"/>
-    </row>
-    <row r="317" spans="1:9">
-      <c r="A317" s="84"/>
-      <c r="B317" s="45"/>
-      <c r="C317" s="85"/>
-      <c r="D317" s="45"/>
-      <c r="E317" s="45"/>
+      <c r="H316" s="44" t="s">
+        <v>1324</v>
+      </c>
+      <c r="I316" s="44" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="317" spans="1:9" ht="14">
+      <c r="A317" s="84">
+        <v>46252</v>
+      </c>
+      <c r="B317" s="45" t="s">
+        <v>1326</v>
+      </c>
+      <c r="C317" s="85">
+        <v>1250</v>
+      </c>
+      <c r="D317" s="45" t="s">
+        <v>162</v>
+      </c>
+      <c r="E317" s="45" t="s">
+        <v>49</v>
+      </c>
       <c r="F317" s="46"/>
       <c r="G317" s="46"/>
-      <c r="H317" s="46"/>
-      <c r="I317" s="45"/>
+      <c r="H317" s="46" t="s">
+        <v>1327</v>
+      </c>
+      <c r="I317" s="45" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="318" spans="1:9">
       <c r="A318" s="82"/>
@@ -26924,7 +26977,7 @@
         <v>0</v>
       </c>
       <c r="L59" s="55" t="s">
-        <v>1285</v>
+        <v>1277</v>
       </c>
       <c r="M59" s="55"/>
       <c r="N59" s="55" t="s">
@@ -28468,7 +28521,7 @@
         <v>0</v>
       </c>
       <c r="L88" s="52" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="M88" s="52"/>
       <c r="N88" s="52" t="s">
@@ -28728,7 +28781,7 @@
         <v>472</v>
       </c>
       <c r="L93" s="55" t="s">
-        <v>1170</v>
+        <v>1166</v>
       </c>
       <c r="M93" s="55"/>
       <c r="N93" s="52" t="s">
@@ -29744,7 +29797,7 @@
         <v>0</v>
       </c>
       <c r="L112" s="52" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="M112" s="52"/>
       <c r="N112" s="52" t="s">
@@ -30166,7 +30219,7 @@
         <v>3351.6266666666638</v>
       </c>
       <c r="L120" s="52" t="s">
-        <v>1164</v>
+        <v>1160</v>
       </c>
       <c r="M120" s="52" t="s">
         <v>49</v>
@@ -30176,7 +30229,7 @@
       </c>
       <c r="O120" s="52"/>
       <c r="P120" s="52" t="s">
-        <v>1165</v>
+        <v>1161</v>
       </c>
       <c r="Q120" s="52"/>
       <c r="R120" s="52"/>
@@ -32256,7 +32309,7 @@
         <v>0</v>
       </c>
       <c r="L147" s="55" t="s">
-        <v>1161</v>
+        <v>1157</v>
       </c>
       <c r="M147" s="55"/>
       <c r="N147" s="55" t="s">
@@ -32308,7 +32361,7 @@
         <v>1004</v>
       </c>
       <c r="L148" s="52" t="s">
-        <v>1135</v>
+        <v>1131</v>
       </c>
       <c r="M148" s="52"/>
       <c r="N148" s="52" t="s">
@@ -32360,7 +32413,7 @@
         <v>0</v>
       </c>
       <c r="L149" s="55" t="s">
-        <v>1136</v>
+        <v>1132</v>
       </c>
       <c r="M149" s="55"/>
       <c r="N149" s="55" t="s">
@@ -32628,14 +32681,14 @@
         <v>949</v>
       </c>
       <c r="L154" s="52" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="M154" s="52"/>
       <c r="N154" s="52" t="s">
         <v>589</v>
       </c>
       <c r="O154" s="52" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="P154" s="52"/>
       <c r="Q154" s="52"/>
@@ -32682,14 +32735,14 @@
         <v>949</v>
       </c>
       <c r="L155" s="55" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="M155" s="55"/>
       <c r="N155" s="55" t="s">
         <v>589</v>
       </c>
       <c r="O155" s="55" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="P155" s="55"/>
       <c r="Q155" s="55"/>
@@ -32736,7 +32789,7 @@
         <v>1900</v>
       </c>
       <c r="L156" s="52" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="M156" s="52"/>
       <c r="N156" s="52" t="s">
@@ -33158,7 +33211,7 @@
         <v>0</v>
       </c>
       <c r="L164" s="52" t="s">
-        <v>1140</v>
+        <v>1136</v>
       </c>
       <c r="M164" s="52"/>
       <c r="N164" s="52" t="s">
@@ -33264,7 +33317,7 @@
         <v>1212</v>
       </c>
       <c r="L166" s="52" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="M166" s="52"/>
       <c r="N166" s="52" t="s">
@@ -33272,7 +33325,7 @@
       </c>
       <c r="O166" s="52"/>
       <c r="P166" s="52" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="Q166" s="52"/>
       <c r="R166" s="52"/>
@@ -33584,7 +33637,7 @@
         <v>0</v>
       </c>
       <c r="L172" s="52" t="s">
-        <v>1275</v>
+        <v>1267</v>
       </c>
       <c r="M172" s="52"/>
       <c r="N172" s="52" t="s">
@@ -33740,7 +33793,7 @@
         <v>2793</v>
       </c>
       <c r="L175" s="55" t="s">
-        <v>1307</v>
+        <v>1299</v>
       </c>
       <c r="M175" s="55"/>
       <c r="N175" s="55" t="s">
@@ -33748,7 +33801,7 @@
       </c>
       <c r="O175" s="55"/>
       <c r="P175" s="55" t="s">
-        <v>1305</v>
+        <v>1297</v>
       </c>
       <c r="Q175" s="55"/>
       <c r="R175" s="55"/>
@@ -34060,14 +34113,14 @@
         <v>1019</v>
       </c>
       <c r="L181" s="55" t="s">
-        <v>1319</v>
+        <v>1311</v>
       </c>
       <c r="M181" s="55"/>
       <c r="N181" s="55" t="s">
         <v>589</v>
       </c>
       <c r="O181" s="55" t="s">
-        <v>1284</v>
+        <v>1276</v>
       </c>
       <c r="P181" s="55" t="s">
         <v>954</v>
@@ -34167,7 +34220,7 @@
         <v>1676</v>
       </c>
       <c r="L183" s="55" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="M183" s="55"/>
       <c r="N183" s="55" t="s">
@@ -34219,7 +34272,7 @@
         <v>0</v>
       </c>
       <c r="L184" s="52" t="s">
-        <v>1241</v>
+        <v>1234</v>
       </c>
       <c r="M184" s="52"/>
       <c r="N184" s="52" t="s">
@@ -34373,7 +34426,7 @@
         <v>891</v>
       </c>
       <c r="L187" s="55" t="s">
-        <v>1324</v>
+        <v>1316</v>
       </c>
       <c r="M187" s="55"/>
       <c r="N187" s="55" t="s">
@@ -34425,7 +34478,7 @@
         <v>891</v>
       </c>
       <c r="L188" s="52" t="s">
-        <v>1242</v>
+        <v>1235</v>
       </c>
       <c r="M188" s="52"/>
       <c r="N188" s="52" t="s">
@@ -34438,7 +34491,7 @@
       <c r="S188" s="52"/>
       <c r="T188" s="52"/>
     </row>
-    <row r="189" spans="1:20" ht="52" customHeight="1">
+    <row r="189" spans="1:20" ht="63" customHeight="1">
       <c r="A189" s="55" t="s">
         <v>970</v>
       </c>
@@ -34455,10 +34508,10 @@
         <v>1380</v>
       </c>
       <c r="F189" s="64">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G189" s="64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H189" s="63">
         <f t="shared" si="12"/>
@@ -34470,14 +34523,14 @@
       </c>
       <c r="J189" s="63">
         <f t="shared" si="9"/>
-        <v>5346</v>
+        <v>6237</v>
       </c>
       <c r="K189" s="63">
         <f t="shared" si="10"/>
-        <v>1782</v>
+        <v>891</v>
       </c>
       <c r="L189" s="55" t="s">
-        <v>1129</v>
+        <v>1322</v>
       </c>
       <c r="M189" s="55"/>
       <c r="N189" s="55" t="s">
@@ -34485,7 +34538,7 @@
       </c>
       <c r="O189" s="55"/>
       <c r="P189" s="55" t="s">
-        <v>1130</v>
+        <v>1325</v>
       </c>
       <c r="Q189" s="55"/>
       <c r="R189" s="55"/>
@@ -34531,7 +34584,7 @@
         <v>0</v>
       </c>
       <c r="L190" s="52" t="s">
-        <v>1171</v>
+        <v>1167</v>
       </c>
       <c r="M190" s="52"/>
       <c r="N190" s="47" t="s">
@@ -34694,7 +34747,7 @@
         <v>982</v>
       </c>
       <c r="B194" s="52" t="s">
-        <v>1310</v>
+        <v>1302</v>
       </c>
       <c r="C194" s="52" t="s">
         <v>95</v>
@@ -34728,14 +34781,14 @@
         <v>6320</v>
       </c>
       <c r="L194" s="52" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
       <c r="M194" s="52"/>
       <c r="N194" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P194" s="47" t="s">
-        <v>1309</v>
+        <v>1301</v>
       </c>
       <c r="S194" s="47"/>
       <c r="T194" s="47"/>
@@ -34928,14 +34981,14 @@
         <v>1401</v>
       </c>
       <c r="L198" s="55" t="s">
-        <v>1188</v>
+        <v>1182</v>
       </c>
       <c r="M198" s="55"/>
       <c r="N198" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P198" s="47" t="s">
-        <v>1189</v>
+        <v>1183</v>
       </c>
       <c r="S198" s="47"/>
       <c r="T198" s="47"/>
@@ -34957,10 +35010,10 @@
         <v>1350</v>
       </c>
       <c r="F199" s="66">
+        <v>3</v>
+      </c>
+      <c r="G199" s="66">
         <v>2</v>
-      </c>
-      <c r="G199" s="66">
-        <v>3</v>
       </c>
       <c r="H199" s="65">
         <f t="shared" si="12"/>
@@ -34972,21 +35025,21 @@
       </c>
       <c r="J199" s="65">
         <f t="shared" si="13"/>
-        <v>1732</v>
+        <v>2598</v>
       </c>
       <c r="K199" s="65">
         <f t="shared" si="14"/>
-        <v>2598</v>
+        <v>1732</v>
       </c>
       <c r="L199" s="52" t="s">
-        <v>1085</v>
+        <v>1328</v>
       </c>
       <c r="M199" s="52"/>
       <c r="N199" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P199" s="47" t="s">
-        <v>1086</v>
+        <v>1329</v>
       </c>
       <c r="S199" s="47"/>
       <c r="T199" s="47"/>
@@ -35081,14 +35134,14 @@
         <v>940</v>
       </c>
       <c r="L201" s="52" t="s">
-        <v>1153</v>
+        <v>1149</v>
       </c>
       <c r="M201" s="52"/>
       <c r="N201" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P201" s="47" t="s">
-        <v>1154</v>
+        <v>1150</v>
       </c>
       <c r="S201" s="47"/>
       <c r="T201" s="47"/>
@@ -35183,14 +35236,14 @@
         <v>880</v>
       </c>
       <c r="L203" s="52" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="M203" s="52"/>
       <c r="N203" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P203" s="47" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="S203" s="47"/>
       <c r="T203" s="47"/>
@@ -35551,7 +35604,7 @@
         <v>1030</v>
       </c>
       <c r="B211" s="55" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="C211" s="55" t="s">
         <v>95</v>
@@ -35585,7 +35638,7 @@
         <v>0</v>
       </c>
       <c r="L211" s="52" t="s">
-        <v>1325</v>
+        <v>1317</v>
       </c>
       <c r="M211" s="52"/>
       <c r="N211" s="47" t="s">
@@ -35599,7 +35652,7 @@
         <v>1031</v>
       </c>
       <c r="B212" s="52" t="s">
-        <v>1138</v>
+        <v>1134</v>
       </c>
       <c r="C212" s="52" t="s">
         <v>95</v>
@@ -35611,10 +35664,10 @@
         <v>850</v>
       </c>
       <c r="F212" s="64">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G212" s="64">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H212" s="63">
         <f t="shared" si="12"/>
@@ -35626,21 +35679,21 @@
       </c>
       <c r="J212" s="63">
         <f t="shared" si="13"/>
-        <v>1665</v>
+        <v>2220</v>
       </c>
       <c r="K212" s="63">
         <f t="shared" si="14"/>
-        <v>3330</v>
+        <v>2775</v>
       </c>
       <c r="L212" s="55" t="s">
-        <v>1185</v>
+        <v>1320</v>
       </c>
       <c r="M212" s="55"/>
       <c r="N212" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P212" s="47" t="s">
-        <v>1186</v>
+        <v>1321</v>
       </c>
       <c r="S212" s="47"/>
       <c r="T212" s="47"/>
@@ -35650,7 +35703,7 @@
         <v>1032</v>
       </c>
       <c r="B213" s="52" t="s">
-        <v>1142</v>
+        <v>1138</v>
       </c>
       <c r="C213" s="52" t="s">
         <v>95</v>
@@ -35689,7 +35742,7 @@
         <v>678</v>
       </c>
       <c r="P213" s="47" t="s">
-        <v>1143</v>
+        <v>1139</v>
       </c>
       <c r="S213" s="47"/>
       <c r="T213" s="47"/>
@@ -35699,7 +35752,7 @@
         <v>1033</v>
       </c>
       <c r="B214" s="55" t="s">
-        <v>1144</v>
+        <v>1140</v>
       </c>
       <c r="C214" s="55" t="s">
         <v>95</v>
@@ -35733,14 +35786,14 @@
         <v>2976</v>
       </c>
       <c r="L214" s="55" t="s">
-        <v>1234</v>
+        <v>1227</v>
       </c>
       <c r="M214" s="55"/>
       <c r="N214" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P214" s="47" t="s">
-        <v>1145</v>
+        <v>1141</v>
       </c>
       <c r="S214" s="47"/>
       <c r="T214" s="47"/>
@@ -35784,14 +35837,14 @@
         <v>2880</v>
       </c>
       <c r="L215" s="52" t="s">
-        <v>1183</v>
+        <v>1179</v>
       </c>
       <c r="M215" s="52"/>
       <c r="N215" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P215" s="47" t="s">
-        <v>1184</v>
+        <v>1180</v>
       </c>
       <c r="S215" s="47"/>
       <c r="T215" s="47"/>
@@ -35801,7 +35854,7 @@
         <v>1035</v>
       </c>
       <c r="B216" s="55" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
       <c r="C216" s="55" t="s">
         <v>95</v>
@@ -35835,14 +35888,14 @@
         <v>0</v>
       </c>
       <c r="L216" s="55" t="s">
-        <v>1283</v>
+        <v>1275</v>
       </c>
       <c r="M216" s="55"/>
       <c r="N216" s="47" t="s">
         <v>504</v>
       </c>
       <c r="P216" s="47" t="s">
-        <v>1147</v>
+        <v>1143</v>
       </c>
       <c r="S216" s="47"/>
       <c r="T216" s="47"/>
@@ -35852,7 +35905,7 @@
         <v>1036</v>
       </c>
       <c r="B217" s="52" t="s">
-        <v>1148</v>
+        <v>1144</v>
       </c>
       <c r="C217" s="52" t="s">
         <v>95</v>
@@ -35886,14 +35939,14 @@
         <v>828</v>
       </c>
       <c r="L217" s="52" t="s">
-        <v>1181</v>
+        <v>1177</v>
       </c>
       <c r="M217" s="52"/>
       <c r="N217" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P217" s="47" t="s">
-        <v>1182</v>
+        <v>1178</v>
       </c>
       <c r="S217" s="47"/>
       <c r="T217" s="47"/>
@@ -35903,7 +35956,7 @@
         <v>1037</v>
       </c>
       <c r="B218" s="55" t="s">
-        <v>1149</v>
+        <v>1145</v>
       </c>
       <c r="C218" s="55" t="s">
         <v>95</v>
@@ -35937,14 +35990,14 @@
         <v>2283</v>
       </c>
       <c r="L218" s="55" t="s">
-        <v>1192</v>
+        <v>1186</v>
       </c>
       <c r="M218" s="55"/>
       <c r="N218" s="47" t="s">
         <v>678</v>
       </c>
       <c r="P218" s="47" t="s">
-        <v>1191</v>
+        <v>1185</v>
       </c>
       <c r="S218" s="47"/>
       <c r="T218" s="47"/>
@@ -35954,7 +36007,7 @@
         <v>1038</v>
       </c>
       <c r="B219" s="52" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="C219" s="52" t="s">
         <v>95</v>
@@ -35988,14 +36041,14 @@
         <v>3805</v>
       </c>
       <c r="L219" s="52" t="s">
-        <v>1177</v>
+        <v>1173</v>
       </c>
       <c r="M219" s="52"/>
       <c r="N219" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P219" s="47" t="s">
-        <v>1178</v>
+        <v>1174</v>
       </c>
       <c r="S219" s="47"/>
       <c r="T219" s="47"/>
@@ -36005,7 +36058,7 @@
         <v>1039</v>
       </c>
       <c r="B220" s="55" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="C220" s="55" t="s">
         <v>95</v>
@@ -36044,7 +36097,7 @@
         <v>678</v>
       </c>
       <c r="P220" s="47" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="S220" s="47"/>
       <c r="T220" s="47"/>
@@ -36054,7 +36107,7 @@
         <v>1040</v>
       </c>
       <c r="B221" s="52" t="s">
-        <v>1193</v>
+        <v>1187</v>
       </c>
       <c r="C221" s="52" t="s">
         <v>96</v>
@@ -36093,7 +36146,7 @@
         <v>678</v>
       </c>
       <c r="P221" s="86" t="s">
-        <v>1220</v>
+        <v>1214</v>
       </c>
       <c r="S221" s="47"/>
       <c r="T221" s="47"/>
@@ -36103,7 +36156,7 @@
         <v>1041</v>
       </c>
       <c r="B222" s="55" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="C222" s="55" t="s">
         <v>95</v>
@@ -36142,7 +36195,7 @@
         <v>678</v>
       </c>
       <c r="P222" s="86" t="s">
-        <v>1221</v>
+        <v>1215</v>
       </c>
       <c r="S222" s="47"/>
       <c r="T222" s="47"/>
@@ -36152,7 +36205,7 @@
         <v>1042</v>
       </c>
       <c r="B223" s="52" t="s">
-        <v>1195</v>
+        <v>1189</v>
       </c>
       <c r="C223" s="52" t="s">
         <v>95</v>
@@ -36186,14 +36239,14 @@
         <v>942</v>
       </c>
       <c r="L223" s="52" t="s">
-        <v>1237</v>
+        <v>1230</v>
       </c>
       <c r="M223" s="52"/>
       <c r="N223" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P223" s="86" t="s">
-        <v>1239</v>
+        <v>1232</v>
       </c>
       <c r="S223" s="47"/>
       <c r="T223" s="47"/>
@@ -36203,7 +36256,7 @@
         <v>1043</v>
       </c>
       <c r="B224" s="55" t="s">
-        <v>1196</v>
+        <v>1190</v>
       </c>
       <c r="C224" s="55" t="s">
         <v>95</v>
@@ -36244,7 +36297,7 @@
         <v>504</v>
       </c>
       <c r="P224" s="86" t="s">
-        <v>1222</v>
+        <v>1216</v>
       </c>
       <c r="S224" s="47"/>
       <c r="T224" s="47"/>
@@ -36254,7 +36307,7 @@
         <v>1044</v>
       </c>
       <c r="B225" s="52" t="s">
-        <v>1197</v>
+        <v>1191</v>
       </c>
       <c r="C225" s="52" t="s">
         <v>95</v>
@@ -36293,17 +36346,17 @@
         <v>678</v>
       </c>
       <c r="P225" s="86" t="s">
-        <v>1223</v>
+        <v>1217</v>
       </c>
       <c r="S225" s="47"/>
       <c r="T225" s="47"/>
     </row>
     <row r="226" spans="1:20" ht="17">
       <c r="A226" s="52" t="s">
-        <v>1208</v>
+        <v>1202</v>
       </c>
       <c r="B226" s="55" t="s">
-        <v>1198</v>
+        <v>1192</v>
       </c>
       <c r="C226" s="55" t="s">
         <v>95</v>
@@ -36337,24 +36390,24 @@
         <v>1338</v>
       </c>
       <c r="L226" s="55" t="s">
-        <v>1190</v>
+        <v>1184</v>
       </c>
       <c r="M226" s="55"/>
       <c r="N226" s="47" t="s">
         <v>678</v>
       </c>
       <c r="P226" s="86" t="s">
-        <v>1224</v>
+        <v>1218</v>
       </c>
       <c r="S226" s="47"/>
       <c r="T226" s="47"/>
     </row>
     <row r="227" spans="1:20" ht="17">
       <c r="A227" s="55" t="s">
-        <v>1209</v>
+        <v>1203</v>
       </c>
       <c r="B227" s="52" t="s">
-        <v>1199</v>
+        <v>1193</v>
       </c>
       <c r="C227" s="52" t="s">
         <v>95</v>
@@ -36393,17 +36446,17 @@
         <v>678</v>
       </c>
       <c r="P227" s="86" t="s">
-        <v>1225</v>
+        <v>1219</v>
       </c>
       <c r="S227" s="47"/>
       <c r="T227" s="47"/>
     </row>
     <row r="228" spans="1:20" ht="17">
       <c r="A228" s="52" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="B228" s="55" t="s">
-        <v>1200</v>
+        <v>1194</v>
       </c>
       <c r="C228" s="55" t="s">
         <v>95</v>
@@ -36437,24 +36490,24 @@
         <v>2775</v>
       </c>
       <c r="L228" s="55" t="s">
-        <v>1312</v>
+        <v>1304</v>
       </c>
       <c r="M228" s="55"/>
       <c r="N228" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P228" s="86" t="s">
-        <v>1313</v>
+        <v>1305</v>
       </c>
       <c r="S228" s="47"/>
       <c r="T228" s="47"/>
     </row>
     <row r="229" spans="1:20" ht="17">
       <c r="A229" s="55" t="s">
-        <v>1211</v>
+        <v>1205</v>
       </c>
       <c r="B229" s="52" t="s">
-        <v>1201</v>
+        <v>1195</v>
       </c>
       <c r="C229" s="52" t="s">
         <v>95</v>
@@ -36488,24 +36541,24 @@
         <v>782</v>
       </c>
       <c r="L229" s="52" t="s">
-        <v>1280</v>
+        <v>1272</v>
       </c>
       <c r="M229" s="52"/>
       <c r="N229" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P229" s="86" t="s">
-        <v>1281</v>
+        <v>1273</v>
       </c>
       <c r="S229" s="47"/>
       <c r="T229" s="47"/>
     </row>
     <row r="230" spans="1:20" ht="17">
       <c r="A230" s="52" t="s">
-        <v>1212</v>
+        <v>1206</v>
       </c>
       <c r="B230" s="55" t="s">
-        <v>1200</v>
+        <v>1194</v>
       </c>
       <c r="C230" s="55" t="s">
         <v>95</v>
@@ -36546,17 +36599,17 @@
         <v>589</v>
       </c>
       <c r="P230" s="86" t="s">
-        <v>1226</v>
+        <v>1220</v>
       </c>
       <c r="S230" s="47"/>
       <c r="T230" s="47"/>
     </row>
     <row r="231" spans="1:20" ht="17">
       <c r="A231" s="52" t="s">
-        <v>1213</v>
+        <v>1207</v>
       </c>
       <c r="B231" s="52" t="s">
-        <v>1202</v>
+        <v>1196</v>
       </c>
       <c r="C231" s="52" t="s">
         <v>95</v>
@@ -36595,17 +36648,17 @@
         <v>678</v>
       </c>
       <c r="P231" s="86" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="S231" s="47"/>
       <c r="T231" s="47"/>
     </row>
     <row r="232" spans="1:20" ht="17">
       <c r="A232" s="55" t="s">
-        <v>1214</v>
+        <v>1208</v>
       </c>
       <c r="B232" s="55" t="s">
-        <v>1203</v>
+        <v>1197</v>
       </c>
       <c r="C232" s="55" t="s">
         <v>95</v>
@@ -36639,24 +36692,24 @@
         <v>0</v>
       </c>
       <c r="L232" s="55" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="M232" s="55"/>
       <c r="N232" s="47" t="s">
         <v>504</v>
       </c>
       <c r="P232" s="86" t="s">
-        <v>1227</v>
+        <v>1221</v>
       </c>
       <c r="S232" s="47"/>
       <c r="T232" s="47"/>
     </row>
     <row r="233" spans="1:20" ht="17">
       <c r="A233" s="52" t="s">
-        <v>1215</v>
+        <v>1209</v>
       </c>
       <c r="B233" s="52" t="s">
-        <v>1204</v>
+        <v>1198</v>
       </c>
       <c r="C233" s="52" t="s">
         <v>95</v>
@@ -36690,24 +36743,24 @@
         <v>1048</v>
       </c>
       <c r="L233" s="52" t="s">
-        <v>1282</v>
+        <v>1274</v>
       </c>
       <c r="M233" s="52"/>
       <c r="N233" s="47" t="s">
         <v>678</v>
       </c>
       <c r="P233" s="86" t="s">
-        <v>1228</v>
+        <v>1222</v>
       </c>
       <c r="S233" s="47"/>
       <c r="T233" s="47"/>
     </row>
     <row r="234" spans="1:20" ht="17">
       <c r="A234" s="55" t="s">
-        <v>1216</v>
+        <v>1210</v>
       </c>
       <c r="B234" s="55" t="s">
-        <v>1205</v>
+        <v>1199</v>
       </c>
       <c r="C234" s="55" t="s">
         <v>95</v>
@@ -36741,21 +36794,21 @@
         <v>891</v>
       </c>
       <c r="L234" s="55" t="s">
-        <v>1302</v>
+        <v>1294</v>
       </c>
       <c r="M234" s="55"/>
       <c r="N234" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P234" s="86" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="S234" s="47"/>
       <c r="T234" s="47"/>
     </row>
     <row r="235" spans="1:20" ht="17">
       <c r="A235" s="52" t="s">
-        <v>1217</v>
+        <v>1211</v>
       </c>
       <c r="B235" s="52" t="s">
         <v>510</v>
@@ -36792,24 +36845,24 @@
         <v>2736</v>
       </c>
       <c r="L235" s="52" t="s">
-        <v>1292</v>
+        <v>1284</v>
       </c>
       <c r="M235" s="52"/>
       <c r="N235" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P235" s="86" t="s">
-        <v>1293</v>
+        <v>1285</v>
       </c>
       <c r="S235" s="47"/>
       <c r="T235" s="47"/>
     </row>
     <row r="236" spans="1:20" ht="17">
       <c r="A236" s="52" t="s">
-        <v>1218</v>
+        <v>1212</v>
       </c>
       <c r="B236" s="55" t="s">
-        <v>1206</v>
+        <v>1200</v>
       </c>
       <c r="C236" s="55" t="s">
         <v>95</v>
@@ -36843,24 +36896,24 @@
         <v>1468</v>
       </c>
       <c r="L236" s="55" t="s">
-        <v>1278</v>
+        <v>1270</v>
       </c>
       <c r="M236" s="55"/>
       <c r="N236" s="47" t="s">
         <v>678</v>
       </c>
       <c r="P236" s="86" t="s">
-        <v>1279</v>
+        <v>1271</v>
       </c>
       <c r="S236" s="47"/>
       <c r="T236" s="47"/>
     </row>
     <row r="237" spans="1:20" ht="17">
       <c r="A237" s="55" t="s">
-        <v>1219</v>
+        <v>1213</v>
       </c>
       <c r="B237" s="52" t="s">
-        <v>1207</v>
+        <v>1201</v>
       </c>
       <c r="C237" s="52" t="s">
         <v>95</v>
@@ -36894,24 +36947,24 @@
         <v>872</v>
       </c>
       <c r="L237" s="52" t="s">
-        <v>1277</v>
+        <v>1269</v>
       </c>
       <c r="M237" s="52"/>
       <c r="N237" s="47" t="s">
         <v>678</v>
       </c>
       <c r="P237" s="86" t="s">
-        <v>1276</v>
+        <v>1268</v>
       </c>
       <c r="S237" s="47"/>
       <c r="T237" s="47"/>
     </row>
     <row r="238" spans="1:20" ht="16">
       <c r="A238" s="55" t="s">
-        <v>1244</v>
+        <v>1236</v>
       </c>
       <c r="B238" s="55" t="s">
-        <v>1203</v>
+        <v>1197</v>
       </c>
       <c r="C238" s="55" t="s">
         <v>95</v>
@@ -36945,7 +36998,7 @@
         <v>0</v>
       </c>
       <c r="L238" s="55" t="s">
-        <v>1245</v>
+        <v>1237</v>
       </c>
       <c r="M238" s="55"/>
       <c r="N238" s="47" t="s">
@@ -36957,10 +37010,10 @@
     </row>
     <row r="239" spans="1:20" ht="17">
       <c r="A239" s="52" t="s">
-        <v>1247</v>
+        <v>1239</v>
       </c>
       <c r="B239" s="52" t="s">
-        <v>1257</v>
+        <v>1249</v>
       </c>
       <c r="C239" s="52" t="s">
         <v>95</v>
@@ -36999,17 +37052,17 @@
         <v>678</v>
       </c>
       <c r="P239" s="86" t="s">
-        <v>1268</v>
+        <v>1260</v>
       </c>
       <c r="S239" s="47"/>
       <c r="T239" s="47"/>
     </row>
     <row r="240" spans="1:20" ht="17">
       <c r="A240" s="55" t="s">
-        <v>1248</v>
+        <v>1240</v>
       </c>
       <c r="B240" s="55" t="s">
-        <v>1266</v>
+        <v>1258</v>
       </c>
       <c r="C240" s="55" t="s">
         <v>95</v>
@@ -37043,7 +37096,7 @@
         <v>0</v>
       </c>
       <c r="L240" s="55" t="s">
-        <v>1267</v>
+        <v>1259</v>
       </c>
       <c r="M240" s="55"/>
       <c r="N240" s="47" t="s">
@@ -37057,10 +37110,10 @@
     </row>
     <row r="241" spans="1:20" ht="17">
       <c r="A241" s="52" t="s">
-        <v>1249</v>
+        <v>1241</v>
       </c>
       <c r="B241" s="52" t="s">
-        <v>1258</v>
+        <v>1250</v>
       </c>
       <c r="C241" s="52" t="s">
         <v>95</v>
@@ -37094,24 +37147,24 @@
         <v>1124</v>
       </c>
       <c r="L241" s="52" t="s">
-        <v>1304</v>
+        <v>1296</v>
       </c>
       <c r="M241" s="52"/>
       <c r="N241" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P241" s="86" t="s">
-        <v>1269</v>
+        <v>1261</v>
       </c>
       <c r="S241" s="47"/>
       <c r="T241" s="47"/>
     </row>
     <row r="242" spans="1:20" ht="17">
       <c r="A242" s="55" t="s">
-        <v>1250</v>
+        <v>1242</v>
       </c>
       <c r="B242" s="55" t="s">
-        <v>1259</v>
+        <v>1251</v>
       </c>
       <c r="C242" s="55" t="s">
         <v>95</v>
@@ -37152,17 +37205,17 @@
         <v>678</v>
       </c>
       <c r="P242" s="86" t="s">
-        <v>1270</v>
+        <v>1262</v>
       </c>
       <c r="S242" s="47"/>
       <c r="T242" s="47"/>
     </row>
     <row r="243" spans="1:20" ht="17">
       <c r="A243" s="52" t="s">
-        <v>1251</v>
+        <v>1243</v>
       </c>
       <c r="B243" s="52" t="s">
-        <v>1260</v>
+        <v>1252</v>
       </c>
       <c r="C243" s="52" t="s">
         <v>95</v>
@@ -37196,24 +37249,24 @@
         <v>545</v>
       </c>
       <c r="L243" s="52" t="s">
-        <v>1297</v>
+        <v>1289</v>
       </c>
       <c r="M243" s="52"/>
       <c r="N243" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P243" s="86" t="s">
-        <v>1271</v>
+        <v>1263</v>
       </c>
       <c r="S243" s="47"/>
       <c r="T243" s="47"/>
     </row>
     <row r="244" spans="1:20" ht="17">
       <c r="A244" s="55" t="s">
-        <v>1252</v>
+        <v>1244</v>
       </c>
       <c r="B244" s="55" t="s">
-        <v>1261</v>
+        <v>1253</v>
       </c>
       <c r="C244" s="55" t="s">
         <v>95</v>
@@ -37252,17 +37305,17 @@
         <v>678</v>
       </c>
       <c r="P244" s="86" t="s">
-        <v>1272</v>
+        <v>1264</v>
       </c>
       <c r="S244" s="47"/>
       <c r="T244" s="47"/>
     </row>
     <row r="245" spans="1:20" ht="16">
       <c r="A245" s="52" t="s">
-        <v>1253</v>
+        <v>1245</v>
       </c>
       <c r="B245" s="52" t="s">
-        <v>1262</v>
+        <v>1254</v>
       </c>
       <c r="C245" s="52" t="s">
         <v>95</v>
@@ -37306,10 +37359,10 @@
     </row>
     <row r="246" spans="1:20" ht="17">
       <c r="A246" s="55" t="s">
-        <v>1254</v>
+        <v>1246</v>
       </c>
       <c r="B246" s="55" t="s">
-        <v>1263</v>
+        <v>1255</v>
       </c>
       <c r="C246" s="55" t="s">
         <v>95</v>
@@ -37348,17 +37401,17 @@
         <v>504</v>
       </c>
       <c r="P246" s="86" t="s">
-        <v>1273</v>
+        <v>1265</v>
       </c>
       <c r="S246" s="47"/>
       <c r="T246" s="47"/>
     </row>
     <row r="247" spans="1:20" ht="16">
       <c r="A247" s="52" t="s">
-        <v>1255</v>
+        <v>1247</v>
       </c>
       <c r="B247" s="52" t="s">
-        <v>1264</v>
+        <v>1256</v>
       </c>
       <c r="C247" s="52" t="s">
         <v>95</v>
@@ -37402,10 +37455,10 @@
     </row>
     <row r="248" spans="1:20" ht="17">
       <c r="A248" s="55" t="s">
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="B248" s="55" t="s">
-        <v>1265</v>
+        <v>1257</v>
       </c>
       <c r="C248" s="55" t="s">
         <v>95</v>
@@ -37444,7 +37497,7 @@
         <v>678</v>
       </c>
       <c r="P248" s="86" t="s">
-        <v>1274</v>
+        <v>1266</v>
       </c>
       <c r="S248" s="47"/>
       <c r="T248" s="47"/>
@@ -44196,7 +44249,7 @@
       </c>
       <c r="B4" s="9">
         <f>IFERROR(SUMIFS(Sales!$C:$C,Sales!$E:$E,$A4,Sales!$I:$I,"Completed"),0)</f>
-        <v>460648</v>
+        <v>469208</v>
       </c>
       <c r="C4" s="9">
         <f>VLOOKUP($A4,PartnerShares!$A$3:$B$5,2,FALSE())</f>
@@ -44204,11 +44257,11 @@
       </c>
       <c r="D4" s="9">
         <f>Summary!$B$4*C4</f>
-        <v>176302.58679999999</v>
+        <v>179156.4908</v>
       </c>
       <c r="E4" s="9">
         <f>B4-D4</f>
-        <v>284345.41320000001</v>
+        <v>290051.50919999997</v>
       </c>
       <c r="F4" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -44216,7 +44269,7 @@
       </c>
       <c r="G4" s="73">
         <f>E4+F4</f>
-        <v>147035.3872</v>
+        <v>152741.48319999996</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5" customHeight="1">
@@ -44233,11 +44286,11 @@
       </c>
       <c r="D5" s="11">
         <f>Summary!$B$4*C5</f>
-        <v>176196.82639999999</v>
+        <v>179049.0184</v>
       </c>
       <c r="E5" s="11">
         <f>B5-D5</f>
-        <v>-121572.82639999999</v>
+        <v>-124425.0184</v>
       </c>
       <c r="F5" s="11">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -44245,7 +44298,7 @@
       </c>
       <c r="G5" s="74">
         <f>E5+F5</f>
-        <v>-49985.78439999999</v>
+        <v>-52837.9764</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1">
@@ -44262,11 +44315,11 @@
       </c>
       <c r="D6" s="9">
         <f>Summary!$B$4*C6</f>
-        <v>176302.58679999999</v>
+        <v>179156.4908</v>
       </c>
       <c r="E6" s="9">
         <f>B6-D6</f>
-        <v>-163772.58679999999</v>
+        <v>-166626.4908</v>
       </c>
       <c r="F6" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -44274,7 +44327,7 @@
       </c>
       <c r="G6" s="73">
         <f>E6+F6</f>
-        <v>-98049.602799999979</v>
+        <v>-100903.50679999999</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="13.5" customHeight="1">

--- a/docs/Chiraath-Summary-Aug26.xlsx
+++ b/docs/Chiraath-Summary-Aug26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anooppremachandran/Desktop/CHIRAATH/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F5DA603-7CD1-944E-ACA5-37C93750C159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63805685-D5E2-F64D-8AAE-58F5C469B1FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3356" uniqueCount="1331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3381" uniqueCount="1339">
   <si>
     <t>Notes:</t>
   </si>
@@ -3094,12 +3094,6 @@
     <t>Matka Saree Collections</t>
   </si>
   <si>
-    <t>Navya - Black Orange</t>
-  </si>
-  <si>
-    <t>Black/pink, black/orange, violet/bottle green</t>
-  </si>
-  <si>
     <t>CHR-205</t>
   </si>
   <si>
@@ -3326,12 +3320,6 @@
   </si>
   <si>
     <t>CHR-165 (Chocolate Brown)</t>
-  </si>
-  <si>
-    <t>Chocolate Brown - Albert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Violet, Bottle Green  </t>
   </si>
   <si>
     <t>Irene Anna Reji</t>
@@ -3601,9 +3589,6 @@
     <t>Cream/gold with leaves, cream/gold with flowers</t>
   </si>
   <si>
-    <t>Shylaja - Green and maroon with golden design</t>
-  </si>
-  <si>
     <t>Green and maroon, deep purple and dark green, blue and dark green, rose pink and olive green, Red</t>
   </si>
   <si>
@@ -3715,9 +3700,6 @@
     <t>Brown</t>
   </si>
   <si>
-    <t>Black, Wine</t>
-  </si>
-  <si>
     <t>Jet Black</t>
   </si>
   <si>
@@ -3898,9 +3880,6 @@
     <t>Sruthi (1300) - L, Bank of baroda customer - M, Niroop - XL</t>
   </si>
   <si>
-    <t>CHR-212 - Purple, CHR-215 - Green and Maroon with golden design - 1000 advance, 750 pending</t>
-  </si>
-  <si>
     <t>CHR-153 (XXL)-Cotton whine 3 piece salwar, CHR-155 (XXL) -Cotton black 3 piece salwar, CHR-51(XXL)-Mul cotton floral salwar  - 1000 advance, 1500 pending</t>
   </si>
   <si>
@@ -3914,12 +3893,6 @@
   </si>
   <si>
     <t>CHR-235-Silk Saree - Yellow/Black</t>
-  </si>
-  <si>
-    <t>Dr.Reshna - Yellow/Black</t>
-  </si>
-  <si>
-    <t>Pink with Silver Butas, Black/Red, Wine/Green</t>
   </si>
   <si>
     <t>Nisha Shaju</t>
@@ -4025,12 +3998,6 @@
     <t>CHR-182 (Yellow Linen Saree with Lotus, CHR-217 cream/gold with stars and paisley &amp; cream/gold with flowers, CHR-212 Green elephant print - 1600 advance, 1150 - pending</t>
   </si>
   <si>
-    <t>Latha - Red, Shylaja - Purple, Jisha - Red, Bank staff - Green</t>
-  </si>
-  <si>
-    <t>Yellow/Orange(4), Blue</t>
-  </si>
-  <si>
     <t>Green/maroon - Rajitha Teacher,  chikku green - Razia Salim, Rust Orange/Coffee Brown - Nishida, Chikku Maroon(1200) - Nishida, Komalavalli - Red/green, peacock blue/navy - returned, mustard/blue - girija(1200), Suma - Golden yellow &amp; green triangle</t>
   </si>
   <si>
@@ -4056,6 +4023,63 @@
   </si>
   <si>
     <t>CHR-186 - Banarasi Silk (Golden Yellow Green)</t>
+  </si>
+  <si>
+    <t>Courier charges</t>
+  </si>
+  <si>
+    <t>Chocolate Brown - Albert, Green - Said</t>
+  </si>
+  <si>
+    <t>Violet</t>
+  </si>
+  <si>
+    <t>CHR-165 - Checked Green, CHR-204 - Black/Pink</t>
+  </si>
+  <si>
+    <t>Navya - Black Orange, Saida - Black Pink</t>
+  </si>
+  <si>
+    <t>Violet/bottle green</t>
+  </si>
+  <si>
+    <t>CHR-212 Yellow/Orange</t>
+  </si>
+  <si>
+    <t>Latha - Red, Shylaja - Purple, Jisha - Red, Bank staff - Green, Rajna - Yellow/Orange</t>
+  </si>
+  <si>
+    <t>Yellow/Orange(2), Blue</t>
+  </si>
+  <si>
+    <t>CHR-212 - Purple, CHR-235 - Black Red - 1000 advance, 750 pending</t>
+  </si>
+  <si>
+    <t>Dr.Reshna - Yellow/Black, Shylaja - Black/Red</t>
+  </si>
+  <si>
+    <t>Pink with Silver Butas,  Wine/Green</t>
+  </si>
+  <si>
+    <t>Tennish</t>
+  </si>
+  <si>
+    <t>CHR-225 Black Tusshar</t>
+  </si>
+  <si>
+    <t>Tennish - Black Tussar</t>
+  </si>
+  <si>
+    <t>Wine</t>
+  </si>
+  <si>
+    <t>Hima BS</t>
+  </si>
+  <si>
+    <t>120 count mul cotton</t>
+  </si>
+  <si>
+    <t>Hima B S</t>
   </si>
 </sst>
 </file>
@@ -4941,7 +4965,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>350</c:v>
+                  <c:v>355</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>99</c:v>
@@ -5044,7 +5068,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>179</c:v>
+                  <c:v>173</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>51</c:v>
@@ -5377,7 +5401,7 @@
                   <c:v>53945</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>127271.14666666667</c:v>
+                  <c:v>122683.14666666667</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>1062</c:v>
@@ -5870,10 +5894,10 @@
                   <c:v>72885</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>63426</c:v>
+                  <c:v>63906</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>65478</c:v>
+                  <c:v>72908</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -6310,10 +6334,10 @@
                   <c:v>-26158</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-38774</c:v>
+                  <c:v>-38294</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>55017</c:v>
+                  <c:v>62447</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -6774,10 +6798,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>454</c:v>
+                  <c:v>459</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>275</c:v>
+                  <c:v>269</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7964,7 +7988,7 @@
       </c>
       <c r="B4" s="10">
         <f>SUMIFS(Sales!C:C, Sales!I:I, "Completed")</f>
-        <v>537362</v>
+        <v>541092</v>
       </c>
       <c r="E4" s="9" t="str">
         <f>PartnerShares!A3</f>
@@ -7981,7 +8005,7 @@
       </c>
       <c r="B5" s="12">
         <f>SUM(Sales!C:C)</f>
-        <v>557402</v>
+        <v>565312</v>
       </c>
       <c r="E5" s="11" t="str">
         <f>PartnerShares!A4</f>
@@ -7998,7 +8022,7 @@
       </c>
       <c r="B6" s="10">
         <f>B4-B3</f>
-        <v>-29446</v>
+        <v>-25716</v>
       </c>
       <c r="E6" s="9" t="str">
         <f>PartnerShares!A5</f>
@@ -8210,15 +8234,15 @@
       </c>
       <c r="B26" s="10">
         <f>'Cash Pool'!B4</f>
-        <v>469208</v>
+        <v>472938</v>
       </c>
       <c r="C26" s="10">
         <f>'Cash Pool'!D4</f>
-        <v>179156.4908</v>
+        <v>180400.07279999999</v>
       </c>
       <c r="D26" s="10">
         <f>'Cash Pool'!E4</f>
-        <v>290051.50919999997</v>
+        <v>292537.92720000003</v>
       </c>
       <c r="E26" s="10">
         <f>'Cash Pool'!F4</f>
@@ -8226,11 +8250,11 @@
       </c>
       <c r="F26" s="13">
         <f>'Cash Pool'!G4</f>
-        <v>152741.48319999996</v>
+        <v>155227.90120000002</v>
       </c>
       <c r="G26" s="17" t="str">
         <f>IF(ROUND(F26,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F26),"#,##0"),IF(ROUND(F26,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F26),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹152,741</v>
+        <v>Pay ₹155,228</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="13.5" customHeight="1">
@@ -8244,11 +8268,11 @@
       </c>
       <c r="C27" s="12">
         <f>'Cash Pool'!D5</f>
-        <v>179049.0184</v>
+        <v>180291.85440000001</v>
       </c>
       <c r="D27" s="12">
         <f>'Cash Pool'!E5</f>
-        <v>-124425.0184</v>
+        <v>-125667.85440000001</v>
       </c>
       <c r="E27" s="12">
         <f>'Cash Pool'!F5</f>
@@ -8256,11 +8280,11 @@
       </c>
       <c r="F27" s="14">
         <f>'Cash Pool'!G5</f>
-        <v>-52837.9764</v>
+        <v>-54080.81240000001</v>
       </c>
       <c r="G27" s="18" t="str">
         <f>IF(ROUND(F27,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F27),"#,##0"),IF(ROUND(F27,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F27),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹52,838</v>
+        <v>Receive ₹54,081</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="13.5" customHeight="1">
@@ -8274,11 +8298,11 @@
       </c>
       <c r="C28" s="10">
         <f>'Cash Pool'!D6</f>
-        <v>179156.4908</v>
+        <v>180400.07279999999</v>
       </c>
       <c r="D28" s="10">
         <f>'Cash Pool'!E6</f>
-        <v>-166626.4908</v>
+        <v>-167870.07279999999</v>
       </c>
       <c r="E28" s="10">
         <f>'Cash Pool'!F6</f>
@@ -8286,11 +8310,11 @@
       </c>
       <c r="F28" s="13">
         <f>'Cash Pool'!G6</f>
-        <v>-100903.50679999999</v>
+        <v>-102147.08879999998</v>
       </c>
       <c r="G28" s="16" t="str">
         <f>IF(ROUND(F28,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F28),"#,##0"),IF(ROUND(F28,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F28),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹100,904</v>
+        <v>Receive ₹102,147</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.75" customHeight="1">
@@ -8402,7 +8426,7 @@
       </c>
       <c r="B3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46253</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1">
@@ -8418,7 +8442,7 @@
       </c>
       <c r="E5" s="21">
         <f>Summary!B4</f>
-        <v>537362</v>
+        <v>541092</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
@@ -8427,14 +8451,14 @@
       </c>
       <c r="B6" s="21">
         <f>Summary!B6</f>
-        <v>-29446</v>
+        <v>-25716</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>71</v>
       </c>
       <c r="E6" s="21">
         <f>SUMIFS(INVENTORY!K:K, INVENTORY!N:N, "&lt;&gt;Sold Out")</f>
-        <v>171407.34666666665</v>
+        <v>168031.34666666665</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1">
@@ -8486,7 +8510,7 @@
       </c>
       <c r="G10" s="21">
         <f>SUM(INVENTORY!F:F)</f>
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1">
@@ -8510,7 +8534,7 @@
       </c>
       <c r="G11" s="27">
         <f>SUM(INVENTORY!G:G)</f>
-        <v>275</v>
+        <v>269</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
@@ -8591,11 +8615,11 @@
       </c>
       <c r="C16" s="21">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$993,"MMM")=$A16)*(YEAR(Sales!$A$2:$A$993)=$B$7)*Sales!$C$2:$C$993),0)</f>
-        <v>63426</v>
+        <v>63906</v>
       </c>
       <c r="D16" s="21">
         <f t="shared" si="0"/>
-        <v>-38774</v>
+        <v>-38294</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1">
@@ -8608,11 +8632,11 @@
       </c>
       <c r="C17" s="27">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$993,"MMM")=$A17)*(YEAR(Sales!$A$2:$A$993)=$B$7)*Sales!$C$2:$C$993),0)</f>
-        <v>65478</v>
+        <v>72908</v>
       </c>
       <c r="D17" s="27">
         <f t="shared" si="0"/>
-        <v>55017</v>
+        <v>62447</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1">
@@ -8706,11 +8730,11 @@
       </c>
       <c r="G47" s="30">
         <f>SUMIF(INVENTORY!C:C, F47, INVENTORY!F:F)</f>
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="H47" s="30">
         <f>SUMIF(INVENTORY!C:C, F47, INVENTORY!G:G)</f>
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="J47" s="30" t="s">
         <v>96</v>
@@ -8737,7 +8761,7 @@
       </c>
       <c r="K48" s="31">
         <f t="array" ref="K48">SUMPRODUCT((INVENTORY!$C$2:$C$476=J48)*(INVENTORY!$D$2:$D$476)*(INVENTORY!$G$2:$G$476))</f>
-        <v>127271.14666666667</v>
+        <v>122683.14666666667</v>
       </c>
     </row>
     <row r="49" spans="5:12" ht="15" customHeight="1">
@@ -10110,7 +10134,7 @@
         <v>28526</v>
       </c>
       <c r="D91" s="39" t="s">
-        <v>1098</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="15" customHeight="1">
@@ -10180,7 +10204,7 @@
         <v>70</v>
       </c>
       <c r="D96" s="36" t="s">
-        <v>1128</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="15" customHeight="1">
@@ -10194,7 +10218,7 @@
         <v>1375</v>
       </c>
       <c r="D97" s="39" t="s">
-        <v>1129</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="15" customHeight="1">
@@ -10208,7 +10232,7 @@
         <v>189</v>
       </c>
       <c r="D98" s="36" t="s">
-        <v>1130</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="15" customHeight="1">
@@ -10334,7 +10358,7 @@
         <v>570</v>
       </c>
       <c r="D107" s="39" t="s">
-        <v>1288</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="15" customHeight="1">
@@ -10362,7 +10386,7 @@
         <v>320</v>
       </c>
       <c r="D109" s="39" t="s">
-        <v>1288</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="15" customHeight="1">
@@ -17735,7 +17759,7 @@
       <c r="F216" s="46"/>
       <c r="G216" s="46"/>
       <c r="H216" s="46" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="I216" s="45" t="s">
         <v>148</v>
@@ -18560,7 +18584,7 @@
       <c r="F249" s="46"/>
       <c r="G249" s="46"/>
       <c r="H249" s="46" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="I249" s="45" t="s">
         <v>148</v>
@@ -18581,7 +18605,7 @@
       <c r="F250" s="44"/>
       <c r="G250" s="44"/>
       <c r="H250" s="44" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="I250" s="44" t="s">
         <v>356</v>
@@ -18592,7 +18616,7 @@
         <v>46201</v>
       </c>
       <c r="B251" s="45" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="C251" s="85">
         <v>1380</v>
@@ -18617,7 +18641,7 @@
         <v>46201</v>
       </c>
       <c r="B252" s="44" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="C252" s="83">
         <v>699</v>
@@ -18631,7 +18655,7 @@
       <c r="F252" s="44"/>
       <c r="G252" s="44"/>
       <c r="H252" s="44" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="I252" s="44" t="s">
         <v>148</v>
@@ -18642,7 +18666,7 @@
         <v>46201</v>
       </c>
       <c r="B253" s="45" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="C253" s="85">
         <v>699</v>
@@ -18656,7 +18680,7 @@
       <c r="F253" s="46"/>
       <c r="G253" s="46"/>
       <c r="H253" s="46" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="I253" s="45" t="s">
         <v>148</v>
@@ -18667,7 +18691,7 @@
         <v>46201</v>
       </c>
       <c r="B254" s="44" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="C254" s="83">
         <v>699</v>
@@ -18681,7 +18705,7 @@
       <c r="F254" s="44"/>
       <c r="G254" s="44"/>
       <c r="H254" s="44" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="I254" s="44" t="s">
         <v>148</v>
@@ -18706,7 +18730,7 @@
       <c r="F255" s="46"/>
       <c r="G255" s="46"/>
       <c r="H255" s="46" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="I255" s="45" t="s">
         <v>148</v>
@@ -18717,7 +18741,7 @@
         <v>46203</v>
       </c>
       <c r="B256" s="44" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="C256" s="83">
         <v>950</v>
@@ -18731,7 +18755,7 @@
       <c r="F256" s="44"/>
       <c r="G256" s="44"/>
       <c r="H256" s="44" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="I256" s="44" t="s">
         <v>148</v>
@@ -18742,7 +18766,7 @@
         <v>46204</v>
       </c>
       <c r="B257" s="45" t="s">
-        <v>1091</v>
+        <v>1087</v>
       </c>
       <c r="C257" s="85">
         <v>699</v>
@@ -18756,7 +18780,7 @@
       <c r="F257" s="46"/>
       <c r="G257" s="46"/>
       <c r="H257" s="46" t="s">
-        <v>1092</v>
+        <v>1088</v>
       </c>
       <c r="I257" s="45" t="s">
         <v>148</v>
@@ -18767,7 +18791,7 @@
         <v>46205</v>
       </c>
       <c r="B258" s="44" t="s">
-        <v>1093</v>
+        <v>1089</v>
       </c>
       <c r="C258" s="83">
         <v>1500</v>
@@ -18781,7 +18805,7 @@
       <c r="F258" s="44"/>
       <c r="G258" s="44"/>
       <c r="H258" s="44" t="s">
-        <v>1094</v>
+        <v>1090</v>
       </c>
       <c r="I258" s="44" t="s">
         <v>148</v>
@@ -18792,7 +18816,7 @@
         <v>46205</v>
       </c>
       <c r="B259" s="45" t="s">
-        <v>1093</v>
+        <v>1089</v>
       </c>
       <c r="C259" s="85">
         <v>1200</v>
@@ -18806,7 +18830,7 @@
       <c r="F259" s="46"/>
       <c r="G259" s="46"/>
       <c r="H259" s="46" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="I259" s="45" t="s">
         <v>148</v>
@@ -18817,7 +18841,7 @@
         <v>46205</v>
       </c>
       <c r="B260" s="44" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="C260" s="83">
         <v>1500</v>
@@ -18831,7 +18855,7 @@
       <c r="F260" s="44"/>
       <c r="G260" s="44"/>
       <c r="H260" s="44" t="s">
-        <v>1096</v>
+        <v>1092</v>
       </c>
       <c r="I260" s="44" t="s">
         <v>148</v>
@@ -18842,7 +18866,7 @@
         <v>46205</v>
       </c>
       <c r="B261" s="45" t="s">
-        <v>1100</v>
+        <v>1096</v>
       </c>
       <c r="C261" s="85">
         <v>2600</v>
@@ -18856,7 +18880,7 @@
       <c r="F261" s="46"/>
       <c r="G261" s="46"/>
       <c r="H261" s="46" t="s">
-        <v>1181</v>
+        <v>1176</v>
       </c>
       <c r="I261" s="45" t="s">
         <v>148</v>
@@ -18867,7 +18891,7 @@
         <v>46206</v>
       </c>
       <c r="B262" s="44" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
       <c r="C262" s="83">
         <v>1380</v>
@@ -18892,7 +18916,7 @@
         <v>46206</v>
       </c>
       <c r="B263" s="45" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="C263" s="85">
         <v>1380</v>
@@ -18917,7 +18941,7 @@
         <v>46206</v>
       </c>
       <c r="B264" s="44" t="s">
-        <v>1113</v>
+        <v>1109</v>
       </c>
       <c r="C264" s="83">
         <v>2500</v>
@@ -18931,7 +18955,7 @@
       <c r="F264" s="44"/>
       <c r="G264" s="44"/>
       <c r="H264" s="44" t="s">
-        <v>1279</v>
+        <v>1272</v>
       </c>
       <c r="I264" s="44" t="s">
         <v>356</v>
@@ -18942,7 +18966,7 @@
         <v>46206</v>
       </c>
       <c r="B265" s="45" t="s">
-        <v>1106</v>
+        <v>1102</v>
       </c>
       <c r="C265" s="85">
         <v>1300</v>
@@ -18956,7 +18980,7 @@
       <c r="F265" s="46"/>
       <c r="G265" s="46"/>
       <c r="H265" s="46" t="s">
-        <v>1118</v>
+        <v>1114</v>
       </c>
       <c r="I265" s="45" t="s">
         <v>356</v>
@@ -18967,7 +18991,7 @@
         <v>46206</v>
       </c>
       <c r="B266" s="44" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="C266" s="83">
         <v>1380</v>
@@ -18981,7 +19005,7 @@
       <c r="F266" s="44"/>
       <c r="G266" s="44"/>
       <c r="H266" s="44" t="s">
-        <v>1107</v>
+        <v>1103</v>
       </c>
       <c r="I266" s="44" t="s">
         <v>148</v>
@@ -19006,7 +19030,7 @@
       <c r="F267" s="46"/>
       <c r="G267" s="46"/>
       <c r="H267" s="46" t="s">
-        <v>1108</v>
+        <v>1104</v>
       </c>
       <c r="I267" s="45" t="s">
         <v>148</v>
@@ -19017,7 +19041,7 @@
         <v>46208</v>
       </c>
       <c r="B268" s="44" t="s">
-        <v>1309</v>
+        <v>1300</v>
       </c>
       <c r="C268" s="83">
         <v>2350</v>
@@ -19027,7 +19051,7 @@
       <c r="F268" s="44"/>
       <c r="G268" s="44"/>
       <c r="H268" s="44" t="s">
-        <v>1310</v>
+        <v>1301</v>
       </c>
       <c r="I268" s="44" t="s">
         <v>356</v>
@@ -19038,7 +19062,7 @@
         <v>46209</v>
       </c>
       <c r="B269" s="45" t="s">
-        <v>1111</v>
+        <v>1107</v>
       </c>
       <c r="C269" s="85">
         <v>1100</v>
@@ -19052,7 +19076,7 @@
       <c r="F269" s="46"/>
       <c r="G269" s="46"/>
       <c r="H269" s="46" t="s">
-        <v>1112</v>
+        <v>1108</v>
       </c>
       <c r="I269" s="45" t="s">
         <v>148</v>
@@ -19063,7 +19087,7 @@
         <v>46210</v>
       </c>
       <c r="B270" s="44" t="s">
-        <v>1312</v>
+        <v>1303</v>
       </c>
       <c r="C270" s="83">
         <v>3200</v>
@@ -19077,7 +19101,7 @@
       <c r="F270" s="44"/>
       <c r="G270" s="44"/>
       <c r="H270" s="44" t="s">
-        <v>1115</v>
+        <v>1111</v>
       </c>
       <c r="I270" s="44" t="s">
         <v>148</v>
@@ -19088,7 +19112,7 @@
         <v>46211</v>
       </c>
       <c r="B271" s="45" t="s">
-        <v>1116</v>
+        <v>1112</v>
       </c>
       <c r="C271" s="85">
         <v>1380</v>
@@ -19102,7 +19126,7 @@
       <c r="F271" s="46"/>
       <c r="G271" s="46"/>
       <c r="H271" s="46" t="s">
-        <v>1117</v>
+        <v>1113</v>
       </c>
       <c r="I271" s="45" t="s">
         <v>148</v>
@@ -19113,7 +19137,7 @@
         <v>46215</v>
       </c>
       <c r="B272" s="44" t="s">
-        <v>1119</v>
+        <v>1115</v>
       </c>
       <c r="C272" s="83">
         <v>1380</v>
@@ -19138,7 +19162,7 @@
         <v>46215</v>
       </c>
       <c r="B273" s="45" t="s">
-        <v>1120</v>
+        <v>1116</v>
       </c>
       <c r="C273" s="85">
         <v>699</v>
@@ -19152,7 +19176,7 @@
       <c r="F273" s="46"/>
       <c r="G273" s="46"/>
       <c r="H273" s="46" t="s">
-        <v>1092</v>
+        <v>1088</v>
       </c>
       <c r="I273" s="45" t="s">
         <v>148</v>
@@ -19177,7 +19201,7 @@
       <c r="F274" s="44"/>
       <c r="G274" s="44"/>
       <c r="H274" s="44" t="s">
-        <v>1122</v>
+        <v>1118</v>
       </c>
       <c r="I274" s="44" t="s">
         <v>148</v>
@@ -19188,7 +19212,7 @@
         <v>46216</v>
       </c>
       <c r="B275" s="45" t="s">
-        <v>1123</v>
+        <v>1119</v>
       </c>
       <c r="C275" s="85">
         <v>699</v>
@@ -19202,7 +19226,7 @@
       <c r="F275" s="46"/>
       <c r="G275" s="46"/>
       <c r="H275" s="46" t="s">
-        <v>1092</v>
+        <v>1088</v>
       </c>
       <c r="I275" s="45" t="s">
         <v>148</v>
@@ -19213,7 +19237,7 @@
         <v>46216</v>
       </c>
       <c r="B276" s="44" t="s">
-        <v>1125</v>
+        <v>1121</v>
       </c>
       <c r="C276" s="83">
         <v>3000</v>
@@ -19227,7 +19251,7 @@
       <c r="F276" s="44"/>
       <c r="G276" s="44"/>
       <c r="H276" s="44" t="s">
-        <v>1124</v>
+        <v>1120</v>
       </c>
       <c r="I276" s="44" t="s">
         <v>148</v>
@@ -19238,7 +19262,7 @@
         <v>46219</v>
       </c>
       <c r="B277" s="45" t="s">
-        <v>1126</v>
+        <v>1122</v>
       </c>
       <c r="C277" s="85">
         <v>1380</v>
@@ -19302,7 +19326,7 @@
       <c r="F279" s="46"/>
       <c r="G279" s="46"/>
       <c r="H279" s="46" t="s">
-        <v>1127</v>
+        <v>1123</v>
       </c>
       <c r="I279" s="45" t="s">
         <v>148</v>
@@ -19327,7 +19351,7 @@
       <c r="F280" s="44"/>
       <c r="G280" s="44"/>
       <c r="H280" s="44" t="s">
-        <v>1133</v>
+        <v>1129</v>
       </c>
       <c r="I280" s="44" t="s">
         <v>148</v>
@@ -19352,7 +19376,7 @@
       <c r="F281" s="46"/>
       <c r="G281" s="46"/>
       <c r="H281" s="46" t="s">
-        <v>1137</v>
+        <v>1133</v>
       </c>
       <c r="I281" s="45" t="s">
         <v>148</v>
@@ -19363,7 +19387,7 @@
         <v>46220</v>
       </c>
       <c r="B282" s="44" t="s">
-        <v>1147</v>
+        <v>1143</v>
       </c>
       <c r="C282" s="83">
         <v>1500</v>
@@ -19377,7 +19401,7 @@
       <c r="F282" s="44"/>
       <c r="G282" s="44"/>
       <c r="H282" s="44" t="s">
-        <v>1148</v>
+        <v>1144</v>
       </c>
       <c r="I282" s="44" t="s">
         <v>148</v>
@@ -19388,7 +19412,7 @@
         <v>46221</v>
       </c>
       <c r="B283" s="45" t="s">
-        <v>1151</v>
+        <v>1147</v>
       </c>
       <c r="C283" s="85">
         <v>1100</v>
@@ -19402,7 +19426,7 @@
       <c r="F283" s="46"/>
       <c r="G283" s="46"/>
       <c r="H283" s="46" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="I283" s="45" t="s">
         <v>148</v>
@@ -19413,7 +19437,7 @@
         <v>46222</v>
       </c>
       <c r="B284" s="44" t="s">
-        <v>1153</v>
+        <v>1149</v>
       </c>
       <c r="C284" s="83">
         <v>850</v>
@@ -19427,7 +19451,7 @@
       <c r="F284" s="44"/>
       <c r="G284" s="44"/>
       <c r="H284" s="44" t="s">
-        <v>1154</v>
+        <v>1150</v>
       </c>
       <c r="I284" s="44" t="s">
         <v>148</v>
@@ -19438,7 +19462,7 @@
         <v>46222</v>
       </c>
       <c r="B285" s="45" t="s">
-        <v>1155</v>
+        <v>1151</v>
       </c>
       <c r="C285" s="85">
         <v>1250</v>
@@ -19452,7 +19476,7 @@
       <c r="F285" s="46"/>
       <c r="G285" s="46"/>
       <c r="H285" s="46" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="I285" s="45" t="s">
         <v>148</v>
@@ -19463,7 +19487,7 @@
         <v>46222</v>
       </c>
       <c r="B286" s="44" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
       <c r="C286" s="83">
         <v>700</v>
@@ -19488,7 +19512,7 @@
         <v>46222</v>
       </c>
       <c r="B287" s="45" t="s">
-        <v>1159</v>
+        <v>1155</v>
       </c>
       <c r="C287" s="85">
         <v>699</v>
@@ -19513,7 +19537,7 @@
         <v>46223</v>
       </c>
       <c r="B288" s="44" t="s">
-        <v>1162</v>
+        <v>1158</v>
       </c>
       <c r="C288" s="83">
         <v>1380</v>
@@ -19527,7 +19551,7 @@
       <c r="F288" s="44"/>
       <c r="G288" s="44"/>
       <c r="H288" s="44" t="s">
-        <v>1163</v>
+        <v>1159</v>
       </c>
       <c r="I288" s="44" t="s">
         <v>148</v>
@@ -19538,7 +19562,7 @@
         <v>46224</v>
       </c>
       <c r="B289" s="45" t="s">
-        <v>1165</v>
+        <v>1161</v>
       </c>
       <c r="C289" s="85">
         <v>1380</v>
@@ -19552,7 +19576,7 @@
       <c r="F289" s="46"/>
       <c r="G289" s="46"/>
       <c r="H289" s="46" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="I289" s="45" t="s">
         <v>148</v>
@@ -19563,7 +19587,7 @@
         <v>46224</v>
       </c>
       <c r="B290" s="44" t="s">
-        <v>1164</v>
+        <v>1160</v>
       </c>
       <c r="C290" s="83">
         <v>1380</v>
@@ -19577,7 +19601,7 @@
       <c r="F290" s="44"/>
       <c r="G290" s="44"/>
       <c r="H290" s="44" t="s">
-        <v>1169</v>
+        <v>1165</v>
       </c>
       <c r="I290" s="44" t="s">
         <v>148</v>
@@ -19602,7 +19626,7 @@
       <c r="F291" s="44"/>
       <c r="G291" s="44"/>
       <c r="H291" s="44" t="s">
-        <v>1172</v>
+        <v>1168</v>
       </c>
       <c r="I291" s="44" t="s">
         <v>148</v>
@@ -19613,7 +19637,7 @@
         <v>46229</v>
       </c>
       <c r="B292" s="45" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="C292" s="85">
         <v>2750</v>
@@ -19623,7 +19647,7 @@
       <c r="F292" s="46"/>
       <c r="G292" s="46"/>
       <c r="H292" s="46" t="s">
-        <v>1319</v>
+        <v>1310</v>
       </c>
       <c r="I292" s="45" t="s">
         <v>356</v>
@@ -19637,14 +19661,14 @@
         <v>293</v>
       </c>
       <c r="C293" s="83">
-        <v>1750</v>
+        <v>2230</v>
       </c>
       <c r="D293" s="44"/>
       <c r="E293" s="44"/>
       <c r="F293" s="44"/>
       <c r="G293" s="44"/>
       <c r="H293" s="44" t="s">
-        <v>1278</v>
+        <v>1329</v>
       </c>
       <c r="I293" s="44" t="s">
         <v>356</v>
@@ -19655,7 +19679,7 @@
         <v>46229</v>
       </c>
       <c r="B294" s="45" t="s">
-        <v>1100</v>
+        <v>1096</v>
       </c>
       <c r="C294" s="85">
         <v>2230</v>
@@ -19669,7 +19693,7 @@
       <c r="F294" s="46"/>
       <c r="G294" s="46"/>
       <c r="H294" s="46" t="s">
-        <v>1318</v>
+        <v>1309</v>
       </c>
       <c r="I294" s="45" t="s">
         <v>148</v>
@@ -19680,13 +19704,13 @@
         <v>46229</v>
       </c>
       <c r="B295" s="44" t="s">
-        <v>1184</v>
+        <v>1179</v>
       </c>
       <c r="C295" s="83">
         <v>3700</v>
       </c>
       <c r="D295" s="44" t="s">
-        <v>1307</v>
+        <v>1298</v>
       </c>
       <c r="E295" s="44" t="s">
         <v>49</v>
@@ -19694,7 +19718,7 @@
       <c r="F295" s="44"/>
       <c r="G295" s="44"/>
       <c r="H295" s="44" t="s">
-        <v>1308</v>
+        <v>1299</v>
       </c>
       <c r="I295" s="44" t="s">
         <v>148</v>
@@ -19705,7 +19729,7 @@
         <v>46235</v>
       </c>
       <c r="B296" s="45" t="s">
-        <v>1226</v>
+        <v>1220</v>
       </c>
       <c r="C296" s="85">
         <v>1450</v>
@@ -19719,7 +19743,7 @@
       <c r="F296" s="46"/>
       <c r="G296" s="46"/>
       <c r="H296" s="46" t="s">
-        <v>1225</v>
+        <v>1219</v>
       </c>
       <c r="I296" s="45" t="s">
         <v>148</v>
@@ -19730,7 +19754,7 @@
         <v>46236</v>
       </c>
       <c r="B297" s="44" t="s">
-        <v>1312</v>
+        <v>1303</v>
       </c>
       <c r="C297" s="83">
         <v>6900</v>
@@ -19744,7 +19768,7 @@
       <c r="F297" s="44"/>
       <c r="G297" s="44"/>
       <c r="H297" s="44" t="s">
-        <v>1314</v>
+        <v>1305</v>
       </c>
       <c r="I297" s="44" t="s">
         <v>148</v>
@@ -19755,7 +19779,7 @@
         <v>46236</v>
       </c>
       <c r="B298" s="45" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="C298" s="85">
         <v>1479</v>
@@ -19769,7 +19793,7 @@
       <c r="F298" s="46"/>
       <c r="G298" s="46"/>
       <c r="H298" s="46" t="s">
-        <v>1228</v>
+        <v>1222</v>
       </c>
       <c r="I298" s="45" t="s">
         <v>148</v>
@@ -19780,7 +19804,7 @@
         <v>46236</v>
       </c>
       <c r="B299" s="44" t="s">
-        <v>1233</v>
+        <v>1227</v>
       </c>
       <c r="C299" s="83">
         <v>2630</v>
@@ -19794,7 +19818,7 @@
       <c r="F299" s="44"/>
       <c r="G299" s="44"/>
       <c r="H299" s="44" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
       <c r="I299" s="44" t="s">
         <v>148</v>
@@ -19805,7 +19829,7 @@
         <v>46238</v>
       </c>
       <c r="B300" s="45" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="C300" s="85">
         <v>1380</v>
@@ -19830,7 +19854,7 @@
         <v>46238</v>
       </c>
       <c r="B301" s="44" t="s">
-        <v>1312</v>
+        <v>1303</v>
       </c>
       <c r="C301" s="83">
         <v>12650</v>
@@ -19844,7 +19868,7 @@
       <c r="F301" s="44"/>
       <c r="G301" s="44"/>
       <c r="H301" s="44" t="s">
-        <v>1315</v>
+        <v>1306</v>
       </c>
       <c r="I301" s="44" t="s">
         <v>148</v>
@@ -19855,7 +19879,7 @@
         <v>46240</v>
       </c>
       <c r="B302" s="45" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="C302" s="85">
         <v>1000</v>
@@ -19865,7 +19889,7 @@
       <c r="F302" s="46"/>
       <c r="G302" s="46"/>
       <c r="H302" s="46" t="s">
-        <v>1238</v>
+        <v>1232</v>
       </c>
       <c r="I302" s="45" t="s">
         <v>148</v>
@@ -19886,7 +19910,7 @@
       <c r="F303" s="44"/>
       <c r="G303" s="44"/>
       <c r="H303" s="44" t="s">
-        <v>1306</v>
+        <v>1297</v>
       </c>
       <c r="I303" s="44" t="s">
         <v>356</v>
@@ -19897,7 +19921,7 @@
         <v>46243</v>
       </c>
       <c r="B304" s="45" t="s">
-        <v>1280</v>
+        <v>1273</v>
       </c>
       <c r="C304" s="85">
         <v>1380</v>
@@ -19907,7 +19931,7 @@
       <c r="F304" s="46"/>
       <c r="G304" s="46"/>
       <c r="H304" s="46" t="s">
-        <v>1281</v>
+        <v>1274</v>
       </c>
       <c r="I304" s="45" t="s">
         <v>356</v>
@@ -19918,7 +19942,7 @@
         <v>46243</v>
       </c>
       <c r="B305" s="44" t="s">
-        <v>1282</v>
+        <v>1275</v>
       </c>
       <c r="C305" s="83">
         <v>1380</v>
@@ -19932,7 +19956,7 @@
       <c r="F305" s="44"/>
       <c r="G305" s="44"/>
       <c r="H305" s="44" t="s">
-        <v>1283</v>
+        <v>1276</v>
       </c>
       <c r="I305" s="44" t="s">
         <v>148</v>
@@ -19943,7 +19967,7 @@
         <v>46243</v>
       </c>
       <c r="B306" s="45" t="s">
-        <v>1286</v>
+        <v>1277</v>
       </c>
       <c r="C306" s="85">
         <v>1250</v>
@@ -19957,7 +19981,7 @@
       <c r="F306" s="46"/>
       <c r="G306" s="46"/>
       <c r="H306" s="46" t="s">
-        <v>1287</v>
+        <v>1278</v>
       </c>
       <c r="I306" s="45" t="s">
         <v>148</v>
@@ -19968,7 +19992,7 @@
         <v>46243</v>
       </c>
       <c r="B307" s="44" t="s">
-        <v>1312</v>
+        <v>1303</v>
       </c>
       <c r="C307" s="83">
         <v>5750</v>
@@ -19982,7 +20006,7 @@
       <c r="F307" s="44"/>
       <c r="G307" s="44"/>
       <c r="H307" s="44" t="s">
-        <v>1313</v>
+        <v>1304</v>
       </c>
       <c r="I307" s="44" t="s">
         <v>148</v>
@@ -19993,7 +20017,7 @@
         <v>46248</v>
       </c>
       <c r="B308" s="44" t="s">
-        <v>1290</v>
+        <v>1281</v>
       </c>
       <c r="C308" s="83">
         <v>1380</v>
@@ -20007,7 +20031,7 @@
       <c r="F308" s="44"/>
       <c r="G308" s="44"/>
       <c r="H308" s="44" t="s">
-        <v>1291</v>
+        <v>1282</v>
       </c>
       <c r="I308" s="44" t="s">
         <v>148</v>
@@ -20018,7 +20042,7 @@
         <v>46248</v>
       </c>
       <c r="B309" s="45" t="s">
-        <v>1292</v>
+        <v>1283</v>
       </c>
       <c r="C309" s="85">
         <v>1380</v>
@@ -20032,7 +20056,7 @@
       <c r="F309" s="46"/>
       <c r="G309" s="46"/>
       <c r="H309" s="46" t="s">
-        <v>1293</v>
+        <v>1284</v>
       </c>
       <c r="I309" s="45" t="s">
         <v>148</v>
@@ -20057,7 +20081,7 @@
       <c r="F310" s="44"/>
       <c r="G310" s="44"/>
       <c r="H310" s="44" t="s">
-        <v>1303</v>
+        <v>1294</v>
       </c>
       <c r="I310" s="44" t="s">
         <v>148</v>
@@ -20082,7 +20106,7 @@
       <c r="F311" s="46"/>
       <c r="G311" s="46"/>
       <c r="H311" s="46" t="s">
-        <v>1295</v>
+        <v>1286</v>
       </c>
       <c r="I311" s="45" t="s">
         <v>148</v>
@@ -20093,7 +20117,7 @@
         <v>46250</v>
       </c>
       <c r="B312" s="44" t="s">
-        <v>1298</v>
+        <v>1289</v>
       </c>
       <c r="C312" s="83">
         <v>2250</v>
@@ -20107,7 +20131,7 @@
       <c r="F312" s="44"/>
       <c r="G312" s="44"/>
       <c r="H312" s="44" t="s">
-        <v>1300</v>
+        <v>1291</v>
       </c>
       <c r="I312" s="44" t="s">
         <v>148</v>
@@ -20118,7 +20142,7 @@
         <v>46252</v>
       </c>
       <c r="B313" s="45" t="s">
-        <v>1312</v>
+        <v>1303</v>
       </c>
       <c r="C313" s="85">
         <v>5750</v>
@@ -20132,7 +20156,7 @@
       <c r="F313" s="46"/>
       <c r="G313" s="46"/>
       <c r="H313" s="46" t="s">
-        <v>1313</v>
+        <v>1304</v>
       </c>
       <c r="I313" s="45" t="s">
         <v>148</v>
@@ -20143,7 +20167,7 @@
         <v>46252</v>
       </c>
       <c r="B314" s="44" t="s">
-        <v>1316</v>
+        <v>1307</v>
       </c>
       <c r="C314" s="83">
         <v>1380</v>
@@ -20157,7 +20181,7 @@
       <c r="F314" s="44"/>
       <c r="G314" s="44"/>
       <c r="H314" s="44" t="s">
-        <v>1330</v>
+        <v>1319</v>
       </c>
       <c r="I314" s="44" t="s">
         <v>148</v>
@@ -20168,7 +20192,7 @@
         <v>46252</v>
       </c>
       <c r="B315" s="45" t="s">
-        <v>1312</v>
+        <v>1303</v>
       </c>
       <c r="C315" s="85">
         <v>5750</v>
@@ -20182,7 +20206,7 @@
       <c r="F315" s="46"/>
       <c r="G315" s="46"/>
       <c r="H315" s="46" t="s">
-        <v>1313</v>
+        <v>1304</v>
       </c>
       <c r="I315" s="45" t="s">
         <v>148</v>
@@ -20193,7 +20217,7 @@
         <v>46252</v>
       </c>
       <c r="B316" s="44" t="s">
-        <v>1323</v>
+        <v>1312</v>
       </c>
       <c r="C316" s="83">
         <v>1380</v>
@@ -20203,7 +20227,7 @@
       <c r="F316" s="44"/>
       <c r="G316" s="44"/>
       <c r="H316" s="44" t="s">
-        <v>1324</v>
+        <v>1313</v>
       </c>
       <c r="I316" s="44" t="s">
         <v>356</v>
@@ -20214,7 +20238,7 @@
         <v>46252</v>
       </c>
       <c r="B317" s="45" t="s">
-        <v>1326</v>
+        <v>1315</v>
       </c>
       <c r="C317" s="85">
         <v>1250</v>
@@ -20228,66 +20252,134 @@
       <c r="F317" s="46"/>
       <c r="G317" s="46"/>
       <c r="H317" s="46" t="s">
-        <v>1327</v>
+        <v>1316</v>
       </c>
       <c r="I317" s="45" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="318" spans="1:9">
-      <c r="A318" s="82"/>
-      <c r="B318" s="44"/>
-      <c r="C318" s="83"/>
-      <c r="D318" s="44"/>
-      <c r="E318" s="44"/>
+    <row r="318" spans="1:9" ht="14">
+      <c r="A318" s="82">
+        <v>46257</v>
+      </c>
+      <c r="B318" s="44" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C318" s="83">
+        <v>1780</v>
+      </c>
+      <c r="D318" s="44" t="s">
+        <v>162</v>
+      </c>
+      <c r="E318" s="44" t="s">
+        <v>49</v>
+      </c>
       <c r="F318" s="44"/>
       <c r="G318" s="44"/>
-      <c r="H318" s="44"/>
-      <c r="I318" s="44"/>
-    </row>
-    <row r="319" spans="1:9">
-      <c r="A319" s="84"/>
-      <c r="B319" s="45"/>
-      <c r="C319" s="85"/>
-      <c r="D319" s="45"/>
+      <c r="H318" s="44" t="s">
+        <v>1320</v>
+      </c>
+      <c r="I318" s="44" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="319" spans="1:9" ht="14">
+      <c r="A319" s="84">
+        <v>46257</v>
+      </c>
+      <c r="B319" s="45" t="s">
+        <v>175</v>
+      </c>
+      <c r="C319" s="85">
+        <v>2200</v>
+      </c>
+      <c r="D319" s="45" t="s">
+        <v>162</v>
+      </c>
       <c r="E319" s="45"/>
       <c r="F319" s="46"/>
       <c r="G319" s="46"/>
-      <c r="H319" s="46"/>
-      <c r="I319" s="45"/>
-    </row>
-    <row r="320" spans="1:9">
-      <c r="A320" s="82"/>
-      <c r="B320" s="44"/>
-      <c r="C320" s="83"/>
-      <c r="D320" s="44"/>
-      <c r="E320" s="44"/>
+      <c r="H319" s="46" t="s">
+        <v>1323</v>
+      </c>
+      <c r="I319" s="45" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="320" spans="1:9" ht="14">
+      <c r="A320" s="82">
+        <v>46257</v>
+      </c>
+      <c r="B320" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="C320" s="83">
+        <v>700</v>
+      </c>
+      <c r="D320" s="44" t="s">
+        <v>162</v>
+      </c>
+      <c r="E320" s="44" t="s">
+        <v>49</v>
+      </c>
       <c r="F320" s="44"/>
       <c r="G320" s="44"/>
-      <c r="H320" s="44"/>
-      <c r="I320" s="44"/>
-    </row>
-    <row r="321" spans="1:9">
-      <c r="A321" s="84"/>
-      <c r="B321" s="45"/>
-      <c r="C321" s="85"/>
-      <c r="D321" s="45"/>
-      <c r="E321" s="45"/>
+      <c r="H320" s="44" t="s">
+        <v>1326</v>
+      </c>
+      <c r="I320" s="44" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="321" spans="1:9" ht="14">
+      <c r="A321" s="84">
+        <v>46257</v>
+      </c>
+      <c r="B321" s="45" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C321" s="85">
+        <v>1500</v>
+      </c>
+      <c r="D321" s="45" t="s">
+        <v>162</v>
+      </c>
+      <c r="E321" s="45" t="s">
+        <v>49</v>
+      </c>
       <c r="F321" s="46"/>
       <c r="G321" s="46"/>
-      <c r="H321" s="46"/>
-      <c r="I321" s="45"/>
-    </row>
-    <row r="322" spans="1:9">
-      <c r="A322" s="82"/>
-      <c r="B322" s="44"/>
-      <c r="C322" s="83"/>
-      <c r="D322" s="44"/>
-      <c r="E322" s="44"/>
+      <c r="H321" s="46" t="s">
+        <v>1333</v>
+      </c>
+      <c r="I321" s="45" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="322" spans="1:9" ht="14">
+      <c r="A322" s="82">
+        <v>46258</v>
+      </c>
+      <c r="B322" s="44" t="s">
+        <v>1336</v>
+      </c>
+      <c r="C322" s="83">
+        <v>1250</v>
+      </c>
+      <c r="D322" s="44" t="s">
+        <v>162</v>
+      </c>
+      <c r="E322" s="44" t="s">
+        <v>49</v>
+      </c>
       <c r="F322" s="44"/>
       <c r="G322" s="44"/>
-      <c r="H322" s="44"/>
-      <c r="I322" s="44"/>
+      <c r="H322" s="44" t="s">
+        <v>1337</v>
+      </c>
+      <c r="I322" s="44" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="323" spans="1:9">
       <c r="A323" s="84"/>
@@ -26977,7 +27069,7 @@
         <v>0</v>
       </c>
       <c r="L59" s="55" t="s">
-        <v>1277</v>
+        <v>1271</v>
       </c>
       <c r="M59" s="55"/>
       <c r="N59" s="55" t="s">
@@ -28521,7 +28613,7 @@
         <v>0</v>
       </c>
       <c r="L88" s="52" t="s">
-        <v>1114</v>
+        <v>1110</v>
       </c>
       <c r="M88" s="52"/>
       <c r="N88" s="52" t="s">
@@ -28781,7 +28873,7 @@
         <v>472</v>
       </c>
       <c r="L93" s="55" t="s">
-        <v>1166</v>
+        <v>1162</v>
       </c>
       <c r="M93" s="55"/>
       <c r="N93" s="52" t="s">
@@ -29797,7 +29889,7 @@
         <v>0</v>
       </c>
       <c r="L112" s="52" t="s">
-        <v>1100</v>
+        <v>1096</v>
       </c>
       <c r="M112" s="52"/>
       <c r="N112" s="52" t="s">
@@ -30219,7 +30311,7 @@
         <v>3351.6266666666638</v>
       </c>
       <c r="L120" s="52" t="s">
-        <v>1160</v>
+        <v>1156</v>
       </c>
       <c r="M120" s="52" t="s">
         <v>49</v>
@@ -30229,7 +30321,7 @@
       </c>
       <c r="O120" s="52"/>
       <c r="P120" s="52" t="s">
-        <v>1161</v>
+        <v>1157</v>
       </c>
       <c r="Q120" s="52"/>
       <c r="R120" s="52"/>
@@ -31327,7 +31419,7 @@
         <v>0</v>
       </c>
       <c r="L128" s="52" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="M128" s="52"/>
       <c r="N128" s="52" t="s">
@@ -32309,7 +32401,7 @@
         <v>0</v>
       </c>
       <c r="L147" s="55" t="s">
-        <v>1157</v>
+        <v>1153</v>
       </c>
       <c r="M147" s="55"/>
       <c r="N147" s="55" t="s">
@@ -32361,7 +32453,7 @@
         <v>1004</v>
       </c>
       <c r="L148" s="52" t="s">
-        <v>1131</v>
+        <v>1127</v>
       </c>
       <c r="M148" s="52"/>
       <c r="N148" s="52" t="s">
@@ -32413,7 +32505,7 @@
         <v>0</v>
       </c>
       <c r="L149" s="55" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="M149" s="55"/>
       <c r="N149" s="55" t="s">
@@ -32681,14 +32773,14 @@
         <v>949</v>
       </c>
       <c r="L154" s="52" t="s">
-        <v>1104</v>
+        <v>1100</v>
       </c>
       <c r="M154" s="52"/>
       <c r="N154" s="52" t="s">
         <v>589</v>
       </c>
       <c r="O154" s="52" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="P154" s="52"/>
       <c r="Q154" s="52"/>
@@ -32735,14 +32827,14 @@
         <v>949</v>
       </c>
       <c r="L155" s="55" t="s">
-        <v>1121</v>
+        <v>1117</v>
       </c>
       <c r="M155" s="55"/>
       <c r="N155" s="55" t="s">
         <v>589</v>
       </c>
       <c r="O155" s="55" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="P155" s="55"/>
       <c r="Q155" s="55"/>
@@ -32789,7 +32881,7 @@
         <v>1900</v>
       </c>
       <c r="L156" s="52" t="s">
-        <v>1105</v>
+        <v>1101</v>
       </c>
       <c r="M156" s="52"/>
       <c r="N156" s="52" t="s">
@@ -33211,7 +33303,7 @@
         <v>0</v>
       </c>
       <c r="L164" s="52" t="s">
-        <v>1136</v>
+        <v>1132</v>
       </c>
       <c r="M164" s="52"/>
       <c r="N164" s="52" t="s">
@@ -33295,10 +33387,10 @@
         <v>950</v>
       </c>
       <c r="F166" s="66">
+        <v>2</v>
+      </c>
+      <c r="G166" s="66">
         <v>1</v>
-      </c>
-      <c r="G166" s="66">
-        <v>2</v>
       </c>
       <c r="H166" s="65">
         <f t="shared" si="11"/>
@@ -33310,22 +33402,22 @@
       </c>
       <c r="J166" s="65">
         <f t="shared" si="9"/>
-        <v>606</v>
+        <v>1212</v>
       </c>
       <c r="K166" s="65">
         <f t="shared" si="10"/>
-        <v>1212</v>
+        <v>606</v>
       </c>
       <c r="L166" s="52" t="s">
-        <v>1089</v>
+        <v>1321</v>
       </c>
       <c r="M166" s="52"/>
       <c r="N166" s="52" t="s">
-        <v>504</v>
+        <v>589</v>
       </c>
       <c r="O166" s="52"/>
       <c r="P166" s="52" t="s">
-        <v>1090</v>
+        <v>1322</v>
       </c>
       <c r="Q166" s="52"/>
       <c r="R166" s="52"/>
@@ -33637,7 +33729,7 @@
         <v>0</v>
       </c>
       <c r="L172" s="52" t="s">
-        <v>1267</v>
+        <v>1261</v>
       </c>
       <c r="M172" s="52"/>
       <c r="N172" s="52" t="s">
@@ -33793,7 +33885,7 @@
         <v>2793</v>
       </c>
       <c r="L175" s="55" t="s">
-        <v>1299</v>
+        <v>1290</v>
       </c>
       <c r="M175" s="55"/>
       <c r="N175" s="55" t="s">
@@ -33801,7 +33893,7 @@
       </c>
       <c r="O175" s="55"/>
       <c r="P175" s="55" t="s">
-        <v>1297</v>
+        <v>1288</v>
       </c>
       <c r="Q175" s="55"/>
       <c r="R175" s="55"/>
@@ -34113,14 +34205,14 @@
         <v>1019</v>
       </c>
       <c r="L181" s="55" t="s">
-        <v>1311</v>
+        <v>1302</v>
       </c>
       <c r="M181" s="55"/>
       <c r="N181" s="55" t="s">
         <v>589</v>
       </c>
       <c r="O181" s="55" t="s">
-        <v>1276</v>
+        <v>1270</v>
       </c>
       <c r="P181" s="55" t="s">
         <v>954</v>
@@ -34220,7 +34312,7 @@
         <v>1676</v>
       </c>
       <c r="L183" s="55" t="s">
-        <v>1176</v>
+        <v>1172</v>
       </c>
       <c r="M183" s="55"/>
       <c r="N183" s="55" t="s">
@@ -34272,7 +34364,7 @@
         <v>0</v>
       </c>
       <c r="L184" s="52" t="s">
-        <v>1234</v>
+        <v>1228</v>
       </c>
       <c r="M184" s="52"/>
       <c r="N184" s="52" t="s">
@@ -34426,7 +34518,7 @@
         <v>891</v>
       </c>
       <c r="L187" s="55" t="s">
-        <v>1316</v>
+        <v>1307</v>
       </c>
       <c r="M187" s="55"/>
       <c r="N187" s="55" t="s">
@@ -34478,7 +34570,7 @@
         <v>891</v>
       </c>
       <c r="L188" s="52" t="s">
-        <v>1235</v>
+        <v>1229</v>
       </c>
       <c r="M188" s="52"/>
       <c r="N188" s="52" t="s">
@@ -34530,7 +34622,7 @@
         <v>891</v>
       </c>
       <c r="L189" s="55" t="s">
-        <v>1322</v>
+        <v>1311</v>
       </c>
       <c r="M189" s="55"/>
       <c r="N189" s="55" t="s">
@@ -34538,7 +34630,7 @@
       </c>
       <c r="O189" s="55"/>
       <c r="P189" s="55" t="s">
-        <v>1325</v>
+        <v>1314</v>
       </c>
       <c r="Q189" s="55"/>
       <c r="R189" s="55"/>
@@ -34584,7 +34676,7 @@
         <v>0</v>
       </c>
       <c r="L190" s="52" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="M190" s="52"/>
       <c r="N190" s="47" t="s">
@@ -34681,14 +34773,14 @@
         <v>1616</v>
       </c>
       <c r="L192" s="52" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="M192" s="52"/>
       <c r="N192" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P192" s="47" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="S192" s="47"/>
       <c r="T192" s="47"/>
@@ -34747,7 +34839,7 @@
         <v>982</v>
       </c>
       <c r="B194" s="52" t="s">
-        <v>1302</v>
+        <v>1293</v>
       </c>
       <c r="C194" s="52" t="s">
         <v>95</v>
@@ -34781,14 +34873,14 @@
         <v>6320</v>
       </c>
       <c r="L194" s="52" t="s">
-        <v>1135</v>
+        <v>1131</v>
       </c>
       <c r="M194" s="52"/>
       <c r="N194" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P194" s="47" t="s">
-        <v>1301</v>
+        <v>1292</v>
       </c>
       <c r="S194" s="47"/>
       <c r="T194" s="47"/>
@@ -34981,14 +35073,14 @@
         <v>1401</v>
       </c>
       <c r="L198" s="55" t="s">
-        <v>1182</v>
+        <v>1177</v>
       </c>
       <c r="M198" s="55"/>
       <c r="N198" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P198" s="47" t="s">
-        <v>1183</v>
+        <v>1178</v>
       </c>
       <c r="S198" s="47"/>
       <c r="T198" s="47"/>
@@ -35032,14 +35124,14 @@
         <v>1732</v>
       </c>
       <c r="L199" s="52" t="s">
-        <v>1328</v>
+        <v>1317</v>
       </c>
       <c r="M199" s="52"/>
       <c r="N199" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P199" s="47" t="s">
-        <v>1329</v>
+        <v>1318</v>
       </c>
       <c r="S199" s="47"/>
       <c r="T199" s="47"/>
@@ -35134,14 +35226,14 @@
         <v>940</v>
       </c>
       <c r="L201" s="52" t="s">
-        <v>1149</v>
+        <v>1145</v>
       </c>
       <c r="M201" s="52"/>
       <c r="N201" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P201" s="47" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="S201" s="47"/>
       <c r="T201" s="47"/>
@@ -35236,14 +35328,14 @@
         <v>880</v>
       </c>
       <c r="L203" s="52" t="s">
-        <v>1110</v>
+        <v>1106</v>
       </c>
       <c r="M203" s="52"/>
       <c r="N203" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P203" s="47" t="s">
-        <v>1109</v>
+        <v>1105</v>
       </c>
       <c r="S203" s="47"/>
       <c r="T203" s="47"/>
@@ -35265,10 +35357,10 @@
         <v>1250</v>
       </c>
       <c r="F204" s="64">
+        <v>2</v>
+      </c>
+      <c r="G204" s="64">
         <v>1</v>
-      </c>
-      <c r="G204" s="64">
-        <v>2</v>
       </c>
       <c r="H204" s="63">
         <f t="shared" si="12"/>
@@ -35280,31 +35372,31 @@
       </c>
       <c r="J204" s="63">
         <f t="shared" si="13"/>
-        <v>761</v>
+        <v>1522</v>
       </c>
       <c r="K204" s="63">
         <f t="shared" si="14"/>
-        <v>1522</v>
+        <v>761</v>
       </c>
       <c r="L204" s="55" t="s">
-        <v>1011</v>
+        <v>1324</v>
       </c>
       <c r="M204" s="55"/>
       <c r="N204" s="47" t="s">
-        <v>678</v>
+        <v>589</v>
       </c>
       <c r="P204" s="47" t="s">
-        <v>1012</v>
+        <v>1325</v>
       </c>
       <c r="S204" s="47"/>
       <c r="T204" s="47"/>
     </row>
     <row r="205" spans="1:20" ht="15" customHeight="1">
       <c r="A205" s="52" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="B205" s="52" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="C205" s="52" t="s">
         <v>95</v>
@@ -35345,17 +35437,17 @@
         <v>504</v>
       </c>
       <c r="P205" s="47" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="S205" s="47"/>
       <c r="T205" s="47"/>
     </row>
     <row r="206" spans="1:20" ht="15" customHeight="1">
       <c r="A206" s="55" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="B206" s="55" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="C206" s="55" t="s">
         <v>95</v>
@@ -35389,24 +35481,24 @@
         <v>3312</v>
       </c>
       <c r="L206" s="55" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="M206" s="55"/>
       <c r="N206" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P206" s="47" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="S206" s="47"/>
       <c r="T206" s="47"/>
     </row>
     <row r="207" spans="1:20" ht="30" customHeight="1">
       <c r="A207" s="52" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="B207" s="52" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="C207" s="52" t="s">
         <v>95</v>
@@ -35445,17 +35537,17 @@
         <v>678</v>
       </c>
       <c r="P207" s="47" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="S207" s="47"/>
       <c r="T207" s="47"/>
     </row>
     <row r="208" spans="1:20" ht="15" customHeight="1">
       <c r="A208" s="55" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="B208" s="52" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="C208" s="52" t="s">
         <v>95</v>
@@ -35489,24 +35581,24 @@
         <v>982</v>
       </c>
       <c r="L208" s="55" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="M208" s="55"/>
       <c r="N208" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P208" s="47" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="S208" s="47"/>
       <c r="T208" s="47"/>
     </row>
     <row r="209" spans="1:20" ht="15" customHeight="1">
       <c r="A209" s="52" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="B209" s="55" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="C209" s="55" t="s">
         <v>95</v>
@@ -35545,14 +35637,14 @@
         <v>678</v>
       </c>
       <c r="P209" s="47" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="S209" s="47"/>
       <c r="T209" s="47"/>
     </row>
     <row r="210" spans="1:20" ht="15" customHeight="1">
       <c r="A210" s="55" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="B210" s="52" t="s">
         <v>901</v>
@@ -35594,17 +35686,17 @@
         <v>678</v>
       </c>
       <c r="P210" s="47" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="S210" s="47"/>
       <c r="T210" s="47"/>
     </row>
     <row r="211" spans="1:20" ht="15" customHeight="1">
       <c r="A211" s="52" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="B211" s="55" t="s">
-        <v>1099</v>
+        <v>1095</v>
       </c>
       <c r="C211" s="55" t="s">
         <v>95</v>
@@ -35638,7 +35730,7 @@
         <v>0</v>
       </c>
       <c r="L211" s="52" t="s">
-        <v>1317</v>
+        <v>1308</v>
       </c>
       <c r="M211" s="52"/>
       <c r="N211" s="47" t="s">
@@ -35649,10 +35741,10 @@
     </row>
     <row r="212" spans="1:20" ht="15" customHeight="1">
       <c r="A212" s="55" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="B212" s="52" t="s">
-        <v>1134</v>
+        <v>1130</v>
       </c>
       <c r="C212" s="52" t="s">
         <v>95</v>
@@ -35664,14 +35756,14 @@
         <v>850</v>
       </c>
       <c r="F212" s="64">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G212" s="64">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H212" s="63">
         <f t="shared" si="12"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I212" s="63">
         <f>IF(D212&lt;&gt;"",D212,IFERROR(E212/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
@@ -35679,31 +35771,31 @@
       </c>
       <c r="J212" s="63">
         <f t="shared" si="13"/>
-        <v>2220</v>
+        <v>2775</v>
       </c>
       <c r="K212" s="63">
         <f t="shared" si="14"/>
-        <v>2775</v>
+        <v>1665</v>
       </c>
       <c r="L212" s="55" t="s">
-        <v>1320</v>
+        <v>1327</v>
       </c>
       <c r="M212" s="55"/>
       <c r="N212" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P212" s="47" t="s">
-        <v>1321</v>
+        <v>1328</v>
       </c>
       <c r="S212" s="47"/>
       <c r="T212" s="47"/>
     </row>
     <row r="213" spans="1:20" ht="15" customHeight="1">
       <c r="A213" s="52" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="B213" s="52" t="s">
-        <v>1138</v>
+        <v>1134</v>
       </c>
       <c r="C213" s="52" t="s">
         <v>95</v>
@@ -35715,10 +35807,10 @@
         <v>1250</v>
       </c>
       <c r="F213" s="66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G213" s="66">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H213" s="65">
         <f t="shared" si="12"/>
@@ -35730,29 +35822,31 @@
       </c>
       <c r="J213" s="65">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>835</v>
       </c>
       <c r="K213" s="65">
         <f t="shared" si="14"/>
-        <v>4175</v>
-      </c>
-      <c r="L213" s="52"/>
+        <v>3340</v>
+      </c>
+      <c r="L213" s="52" t="s">
+        <v>1338</v>
+      </c>
       <c r="M213" s="52"/>
       <c r="N213" s="47" t="s">
-        <v>678</v>
+        <v>589</v>
       </c>
       <c r="P213" s="47" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
       <c r="S213" s="47"/>
       <c r="T213" s="47"/>
     </row>
     <row r="214" spans="1:20" ht="15" customHeight="1">
       <c r="A214" s="55" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="B214" s="55" t="s">
-        <v>1140</v>
+        <v>1136</v>
       </c>
       <c r="C214" s="55" t="s">
         <v>95</v>
@@ -35786,21 +35880,21 @@
         <v>2976</v>
       </c>
       <c r="L214" s="55" t="s">
-        <v>1227</v>
+        <v>1221</v>
       </c>
       <c r="M214" s="55"/>
       <c r="N214" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P214" s="47" t="s">
-        <v>1141</v>
+        <v>1137</v>
       </c>
       <c r="S214" s="47"/>
       <c r="T214" s="47"/>
     </row>
     <row r="215" spans="1:20" ht="30">
       <c r="A215" s="52" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="B215" s="52" t="s">
         <v>994</v>
@@ -35815,10 +35909,10 @@
         <v>899</v>
       </c>
       <c r="F215" s="66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G215" s="66">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H215" s="65">
         <f t="shared" si="12"/>
@@ -35830,31 +35924,29 @@
       </c>
       <c r="J215" s="65">
         <f t="shared" si="13"/>
-        <v>576</v>
+        <v>0</v>
       </c>
       <c r="K215" s="65">
         <f t="shared" si="14"/>
-        <v>2880</v>
-      </c>
-      <c r="L215" s="52" t="s">
-        <v>1179</v>
-      </c>
+        <v>3456</v>
+      </c>
+      <c r="L215" s="52"/>
       <c r="M215" s="52"/>
       <c r="N215" s="47" t="s">
-        <v>589</v>
+        <v>678</v>
       </c>
       <c r="P215" s="47" t="s">
-        <v>1180</v>
+        <v>1175</v>
       </c>
       <c r="S215" s="47"/>
       <c r="T215" s="47"/>
     </row>
     <row r="216" spans="1:20" ht="15" customHeight="1">
       <c r="A216" s="55" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="B216" s="55" t="s">
-        <v>1142</v>
+        <v>1138</v>
       </c>
       <c r="C216" s="55" t="s">
         <v>95</v>
@@ -35888,24 +35980,24 @@
         <v>0</v>
       </c>
       <c r="L216" s="55" t="s">
-        <v>1275</v>
+        <v>1269</v>
       </c>
       <c r="M216" s="55"/>
       <c r="N216" s="47" t="s">
         <v>504</v>
       </c>
       <c r="P216" s="47" t="s">
-        <v>1143</v>
+        <v>1139</v>
       </c>
       <c r="S216" s="47"/>
       <c r="T216" s="47"/>
     </row>
     <row r="217" spans="1:20" ht="15">
       <c r="A217" s="52" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B217" s="52" t="s">
-        <v>1144</v>
+        <v>1140</v>
       </c>
       <c r="C217" s="52" t="s">
         <v>95</v>
@@ -35939,24 +36031,24 @@
         <v>828</v>
       </c>
       <c r="L217" s="52" t="s">
-        <v>1177</v>
+        <v>1173</v>
       </c>
       <c r="M217" s="52"/>
       <c r="N217" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P217" s="47" t="s">
-        <v>1178</v>
+        <v>1174</v>
       </c>
       <c r="S217" s="47"/>
       <c r="T217" s="47"/>
     </row>
     <row r="218" spans="1:20" ht="15" customHeight="1">
       <c r="A218" s="55" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="B218" s="55" t="s">
-        <v>1145</v>
+        <v>1141</v>
       </c>
       <c r="C218" s="55" t="s">
         <v>95</v>
@@ -35990,24 +36082,24 @@
         <v>2283</v>
       </c>
       <c r="L218" s="55" t="s">
-        <v>1186</v>
+        <v>1181</v>
       </c>
       <c r="M218" s="55"/>
       <c r="N218" s="47" t="s">
         <v>678</v>
       </c>
       <c r="P218" s="47" t="s">
-        <v>1185</v>
+        <v>1180</v>
       </c>
       <c r="S218" s="47"/>
       <c r="T218" s="47"/>
     </row>
     <row r="219" spans="1:20" ht="15">
       <c r="A219" s="52" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="B219" s="52" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
       <c r="C219" s="52" t="s">
         <v>95</v>
@@ -36041,24 +36133,24 @@
         <v>3805</v>
       </c>
       <c r="L219" s="52" t="s">
-        <v>1173</v>
+        <v>1169</v>
       </c>
       <c r="M219" s="52"/>
       <c r="N219" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P219" s="47" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="S219" s="47"/>
       <c r="T219" s="47"/>
     </row>
     <row r="220" spans="1:20" ht="15" customHeight="1">
       <c r="A220" s="55" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="B220" s="55" t="s">
-        <v>1170</v>
+        <v>1166</v>
       </c>
       <c r="C220" s="55" t="s">
         <v>95</v>
@@ -36097,17 +36189,17 @@
         <v>678</v>
       </c>
       <c r="P220" s="47" t="s">
-        <v>1171</v>
+        <v>1167</v>
       </c>
       <c r="S220" s="47"/>
       <c r="T220" s="47"/>
     </row>
     <row r="221" spans="1:20" ht="17">
       <c r="A221" s="52" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="B221" s="52" t="s">
-        <v>1187</v>
+        <v>1182</v>
       </c>
       <c r="C221" s="52" t="s">
         <v>96</v>
@@ -36146,17 +36238,17 @@
         <v>678</v>
       </c>
       <c r="P221" s="86" t="s">
-        <v>1214</v>
+        <v>1209</v>
       </c>
       <c r="S221" s="47"/>
       <c r="T221" s="47"/>
     </row>
     <row r="222" spans="1:20" ht="15" customHeight="1">
       <c r="A222" s="55" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="B222" s="55" t="s">
-        <v>1188</v>
+        <v>1183</v>
       </c>
       <c r="C222" s="55" t="s">
         <v>95</v>
@@ -36195,17 +36287,17 @@
         <v>678</v>
       </c>
       <c r="P222" s="86" t="s">
-        <v>1215</v>
+        <v>1210</v>
       </c>
       <c r="S222" s="47"/>
       <c r="T222" s="47"/>
     </row>
     <row r="223" spans="1:20" ht="15" customHeight="1">
       <c r="A223" s="52" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="B223" s="52" t="s">
-        <v>1189</v>
+        <v>1184</v>
       </c>
       <c r="C223" s="52" t="s">
         <v>95</v>
@@ -36239,24 +36331,24 @@
         <v>942</v>
       </c>
       <c r="L223" s="52" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="M223" s="52"/>
       <c r="N223" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P223" s="86" t="s">
-        <v>1232</v>
+        <v>1226</v>
       </c>
       <c r="S223" s="47"/>
       <c r="T223" s="47"/>
     </row>
     <row r="224" spans="1:20" ht="15" customHeight="1">
       <c r="A224" s="55" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="B224" s="55" t="s">
-        <v>1190</v>
+        <v>1185</v>
       </c>
       <c r="C224" s="55" t="s">
         <v>95</v>
@@ -36297,17 +36389,17 @@
         <v>504</v>
       </c>
       <c r="P224" s="86" t="s">
-        <v>1216</v>
+        <v>1211</v>
       </c>
       <c r="S224" s="47"/>
       <c r="T224" s="47"/>
     </row>
     <row r="225" spans="1:20" ht="15" customHeight="1">
       <c r="A225" s="52" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="B225" s="52" t="s">
-        <v>1191</v>
+        <v>1186</v>
       </c>
       <c r="C225" s="52" t="s">
         <v>95</v>
@@ -36319,10 +36411,10 @@
         <v>1500</v>
       </c>
       <c r="F225" s="66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G225" s="66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H225" s="65">
         <f t="shared" si="12"/>
@@ -36334,29 +36426,31 @@
       </c>
       <c r="J225" s="65">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>940</v>
       </c>
       <c r="K225" s="65">
         <f t="shared" si="14"/>
-        <v>1880</v>
-      </c>
-      <c r="L225" s="52"/>
+        <v>940</v>
+      </c>
+      <c r="L225" s="52" t="s">
+        <v>1334</v>
+      </c>
       <c r="M225" s="52"/>
       <c r="N225" s="47" t="s">
-        <v>678</v>
+        <v>589</v>
       </c>
       <c r="P225" s="86" t="s">
-        <v>1217</v>
+        <v>1335</v>
       </c>
       <c r="S225" s="47"/>
       <c r="T225" s="47"/>
     </row>
     <row r="226" spans="1:20" ht="17">
       <c r="A226" s="52" t="s">
-        <v>1202</v>
+        <v>1197</v>
       </c>
       <c r="B226" s="55" t="s">
-        <v>1192</v>
+        <v>1187</v>
       </c>
       <c r="C226" s="55" t="s">
         <v>95</v>
@@ -36390,24 +36484,24 @@
         <v>1338</v>
       </c>
       <c r="L226" s="55" t="s">
-        <v>1184</v>
+        <v>1179</v>
       </c>
       <c r="M226" s="55"/>
       <c r="N226" s="47" t="s">
         <v>678</v>
       </c>
       <c r="P226" s="86" t="s">
-        <v>1218</v>
+        <v>1212</v>
       </c>
       <c r="S226" s="47"/>
       <c r="T226" s="47"/>
     </row>
     <row r="227" spans="1:20" ht="17">
       <c r="A227" s="55" t="s">
-        <v>1203</v>
+        <v>1198</v>
       </c>
       <c r="B227" s="52" t="s">
-        <v>1193</v>
+        <v>1188</v>
       </c>
       <c r="C227" s="52" t="s">
         <v>95</v>
@@ -36446,17 +36540,17 @@
         <v>678</v>
       </c>
       <c r="P227" s="86" t="s">
-        <v>1219</v>
+        <v>1213</v>
       </c>
       <c r="S227" s="47"/>
       <c r="T227" s="47"/>
     </row>
     <row r="228" spans="1:20" ht="17">
       <c r="A228" s="52" t="s">
-        <v>1204</v>
+        <v>1199</v>
       </c>
       <c r="B228" s="55" t="s">
-        <v>1194</v>
+        <v>1189</v>
       </c>
       <c r="C228" s="55" t="s">
         <v>95</v>
@@ -36490,24 +36584,24 @@
         <v>2775</v>
       </c>
       <c r="L228" s="55" t="s">
-        <v>1304</v>
+        <v>1295</v>
       </c>
       <c r="M228" s="55"/>
       <c r="N228" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P228" s="86" t="s">
-        <v>1305</v>
+        <v>1296</v>
       </c>
       <c r="S228" s="47"/>
       <c r="T228" s="47"/>
     </row>
     <row r="229" spans="1:20" ht="17">
       <c r="A229" s="55" t="s">
-        <v>1205</v>
+        <v>1200</v>
       </c>
       <c r="B229" s="52" t="s">
-        <v>1195</v>
+        <v>1190</v>
       </c>
       <c r="C229" s="52" t="s">
         <v>95</v>
@@ -36541,24 +36635,24 @@
         <v>782</v>
       </c>
       <c r="L229" s="52" t="s">
-        <v>1272</v>
+        <v>1266</v>
       </c>
       <c r="M229" s="52"/>
       <c r="N229" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P229" s="86" t="s">
-        <v>1273</v>
+        <v>1267</v>
       </c>
       <c r="S229" s="47"/>
       <c r="T229" s="47"/>
     </row>
     <row r="230" spans="1:20" ht="17">
       <c r="A230" s="52" t="s">
-        <v>1206</v>
+        <v>1201</v>
       </c>
       <c r="B230" s="55" t="s">
-        <v>1194</v>
+        <v>1189</v>
       </c>
       <c r="C230" s="55" t="s">
         <v>95</v>
@@ -36599,17 +36693,17 @@
         <v>589</v>
       </c>
       <c r="P230" s="86" t="s">
-        <v>1220</v>
+        <v>1214</v>
       </c>
       <c r="S230" s="47"/>
       <c r="T230" s="47"/>
     </row>
     <row r="231" spans="1:20" ht="17">
       <c r="A231" s="52" t="s">
-        <v>1207</v>
+        <v>1202</v>
       </c>
       <c r="B231" s="52" t="s">
-        <v>1196</v>
+        <v>1191</v>
       </c>
       <c r="C231" s="52" t="s">
         <v>95</v>
@@ -36648,17 +36742,17 @@
         <v>678</v>
       </c>
       <c r="P231" s="86" t="s">
-        <v>1171</v>
+        <v>1167</v>
       </c>
       <c r="S231" s="47"/>
       <c r="T231" s="47"/>
     </row>
     <row r="232" spans="1:20" ht="17">
       <c r="A232" s="55" t="s">
-        <v>1208</v>
+        <v>1203</v>
       </c>
       <c r="B232" s="55" t="s">
-        <v>1197</v>
+        <v>1192</v>
       </c>
       <c r="C232" s="55" t="s">
         <v>95</v>
@@ -36692,24 +36786,24 @@
         <v>0</v>
       </c>
       <c r="L232" s="55" t="s">
-        <v>1224</v>
+        <v>1218</v>
       </c>
       <c r="M232" s="55"/>
       <c r="N232" s="47" t="s">
         <v>504</v>
       </c>
       <c r="P232" s="86" t="s">
-        <v>1221</v>
+        <v>1215</v>
       </c>
       <c r="S232" s="47"/>
       <c r="T232" s="47"/>
     </row>
     <row r="233" spans="1:20" ht="17">
       <c r="A233" s="52" t="s">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="B233" s="52" t="s">
-        <v>1198</v>
+        <v>1193</v>
       </c>
       <c r="C233" s="52" t="s">
         <v>95</v>
@@ -36743,24 +36837,24 @@
         <v>1048</v>
       </c>
       <c r="L233" s="52" t="s">
-        <v>1274</v>
+        <v>1268</v>
       </c>
       <c r="M233" s="52"/>
       <c r="N233" s="47" t="s">
         <v>678</v>
       </c>
       <c r="P233" s="86" t="s">
-        <v>1222</v>
+        <v>1216</v>
       </c>
       <c r="S233" s="47"/>
       <c r="T233" s="47"/>
     </row>
     <row r="234" spans="1:20" ht="17">
       <c r="A234" s="55" t="s">
-        <v>1210</v>
+        <v>1205</v>
       </c>
       <c r="B234" s="55" t="s">
-        <v>1199</v>
+        <v>1194</v>
       </c>
       <c r="C234" s="55" t="s">
         <v>95</v>
@@ -36794,21 +36888,21 @@
         <v>891</v>
       </c>
       <c r="L234" s="55" t="s">
-        <v>1294</v>
+        <v>1285</v>
       </c>
       <c r="M234" s="55"/>
       <c r="N234" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P234" s="86" t="s">
-        <v>1223</v>
+        <v>1217</v>
       </c>
       <c r="S234" s="47"/>
       <c r="T234" s="47"/>
     </row>
     <row r="235" spans="1:20" ht="17">
       <c r="A235" s="52" t="s">
-        <v>1211</v>
+        <v>1206</v>
       </c>
       <c r="B235" s="52" t="s">
         <v>510</v>
@@ -36823,10 +36917,10 @@
         <v>1380</v>
       </c>
       <c r="F235" s="66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G235" s="66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H235" s="65">
         <f t="shared" si="15"/>
@@ -36838,31 +36932,31 @@
       </c>
       <c r="J235" s="65">
         <f t="shared" si="16"/>
-        <v>912</v>
+        <v>1824</v>
       </c>
       <c r="K235" s="65">
         <f t="shared" si="17"/>
-        <v>2736</v>
+        <v>1824</v>
       </c>
       <c r="L235" s="52" t="s">
-        <v>1284</v>
+        <v>1330</v>
       </c>
       <c r="M235" s="52"/>
       <c r="N235" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P235" s="86" t="s">
-        <v>1285</v>
+        <v>1331</v>
       </c>
       <c r="S235" s="47"/>
       <c r="T235" s="47"/>
     </row>
     <row r="236" spans="1:20" ht="17">
       <c r="A236" s="52" t="s">
-        <v>1212</v>
+        <v>1207</v>
       </c>
       <c r="B236" s="55" t="s">
-        <v>1200</v>
+        <v>1195</v>
       </c>
       <c r="C236" s="55" t="s">
         <v>95</v>
@@ -36896,24 +36990,24 @@
         <v>1468</v>
       </c>
       <c r="L236" s="55" t="s">
-        <v>1270</v>
+        <v>1264</v>
       </c>
       <c r="M236" s="55"/>
       <c r="N236" s="47" t="s">
         <v>678</v>
       </c>
       <c r="P236" s="86" t="s">
-        <v>1271</v>
+        <v>1265</v>
       </c>
       <c r="S236" s="47"/>
       <c r="T236" s="47"/>
     </row>
     <row r="237" spans="1:20" ht="17">
       <c r="A237" s="55" t="s">
-        <v>1213</v>
+        <v>1208</v>
       </c>
       <c r="B237" s="52" t="s">
-        <v>1201</v>
+        <v>1196</v>
       </c>
       <c r="C237" s="52" t="s">
         <v>95</v>
@@ -36947,24 +37041,24 @@
         <v>872</v>
       </c>
       <c r="L237" s="52" t="s">
-        <v>1269</v>
+        <v>1263</v>
       </c>
       <c r="M237" s="52"/>
       <c r="N237" s="47" t="s">
         <v>678</v>
       </c>
       <c r="P237" s="86" t="s">
-        <v>1268</v>
+        <v>1262</v>
       </c>
       <c r="S237" s="47"/>
       <c r="T237" s="47"/>
     </row>
     <row r="238" spans="1:20" ht="16">
       <c r="A238" s="55" t="s">
-        <v>1236</v>
+        <v>1230</v>
       </c>
       <c r="B238" s="55" t="s">
-        <v>1197</v>
+        <v>1192</v>
       </c>
       <c r="C238" s="55" t="s">
         <v>95</v>
@@ -36998,7 +37092,7 @@
         <v>0</v>
       </c>
       <c r="L238" s="55" t="s">
-        <v>1237</v>
+        <v>1231</v>
       </c>
       <c r="M238" s="55"/>
       <c r="N238" s="47" t="s">
@@ -37010,10 +37104,10 @@
     </row>
     <row r="239" spans="1:20" ht="17">
       <c r="A239" s="52" t="s">
-        <v>1239</v>
+        <v>1233</v>
       </c>
       <c r="B239" s="52" t="s">
-        <v>1249</v>
+        <v>1243</v>
       </c>
       <c r="C239" s="52" t="s">
         <v>95</v>
@@ -37052,17 +37146,17 @@
         <v>678</v>
       </c>
       <c r="P239" s="86" t="s">
-        <v>1260</v>
+        <v>1254</v>
       </c>
       <c r="S239" s="47"/>
       <c r="T239" s="47"/>
     </row>
     <row r="240" spans="1:20" ht="17">
       <c r="A240" s="55" t="s">
-        <v>1240</v>
+        <v>1234</v>
       </c>
       <c r="B240" s="55" t="s">
-        <v>1258</v>
+        <v>1252</v>
       </c>
       <c r="C240" s="55" t="s">
         <v>95</v>
@@ -37096,7 +37190,7 @@
         <v>0</v>
       </c>
       <c r="L240" s="55" t="s">
-        <v>1259</v>
+        <v>1253</v>
       </c>
       <c r="M240" s="55"/>
       <c r="N240" s="47" t="s">
@@ -37110,10 +37204,10 @@
     </row>
     <row r="241" spans="1:20" ht="17">
       <c r="A241" s="52" t="s">
-        <v>1241</v>
+        <v>1235</v>
       </c>
       <c r="B241" s="52" t="s">
-        <v>1250</v>
+        <v>1244</v>
       </c>
       <c r="C241" s="52" t="s">
         <v>95</v>
@@ -37147,24 +37241,24 @@
         <v>1124</v>
       </c>
       <c r="L241" s="52" t="s">
-        <v>1296</v>
+        <v>1287</v>
       </c>
       <c r="M241" s="52"/>
       <c r="N241" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P241" s="86" t="s">
-        <v>1261</v>
+        <v>1255</v>
       </c>
       <c r="S241" s="47"/>
       <c r="T241" s="47"/>
     </row>
     <row r="242" spans="1:20" ht="17">
       <c r="A242" s="55" t="s">
-        <v>1242</v>
+        <v>1236</v>
       </c>
       <c r="B242" s="55" t="s">
-        <v>1251</v>
+        <v>1245</v>
       </c>
       <c r="C242" s="55" t="s">
         <v>95</v>
@@ -37205,17 +37299,17 @@
         <v>678</v>
       </c>
       <c r="P242" s="86" t="s">
-        <v>1262</v>
+        <v>1256</v>
       </c>
       <c r="S242" s="47"/>
       <c r="T242" s="47"/>
     </row>
     <row r="243" spans="1:20" ht="17">
       <c r="A243" s="52" t="s">
-        <v>1243</v>
+        <v>1237</v>
       </c>
       <c r="B243" s="52" t="s">
-        <v>1252</v>
+        <v>1246</v>
       </c>
       <c r="C243" s="52" t="s">
         <v>95</v>
@@ -37249,24 +37343,24 @@
         <v>545</v>
       </c>
       <c r="L243" s="52" t="s">
-        <v>1289</v>
+        <v>1280</v>
       </c>
       <c r="M243" s="52"/>
       <c r="N243" s="47" t="s">
         <v>589</v>
       </c>
       <c r="P243" s="86" t="s">
-        <v>1263</v>
+        <v>1257</v>
       </c>
       <c r="S243" s="47"/>
       <c r="T243" s="47"/>
     </row>
     <row r="244" spans="1:20" ht="17">
       <c r="A244" s="55" t="s">
-        <v>1244</v>
+        <v>1238</v>
       </c>
       <c r="B244" s="55" t="s">
-        <v>1253</v>
+        <v>1247</v>
       </c>
       <c r="C244" s="55" t="s">
         <v>95</v>
@@ -37305,17 +37399,17 @@
         <v>678</v>
       </c>
       <c r="P244" s="86" t="s">
-        <v>1264</v>
+        <v>1258</v>
       </c>
       <c r="S244" s="47"/>
       <c r="T244" s="47"/>
     </row>
     <row r="245" spans="1:20" ht="16">
       <c r="A245" s="52" t="s">
-        <v>1245</v>
+        <v>1239</v>
       </c>
       <c r="B245" s="52" t="s">
-        <v>1254</v>
+        <v>1248</v>
       </c>
       <c r="C245" s="52" t="s">
         <v>95</v>
@@ -37359,10 +37453,10 @@
     </row>
     <row r="246" spans="1:20" ht="17">
       <c r="A246" s="55" t="s">
-        <v>1246</v>
+        <v>1240</v>
       </c>
       <c r="B246" s="55" t="s">
-        <v>1255</v>
+        <v>1249</v>
       </c>
       <c r="C246" s="55" t="s">
         <v>95</v>
@@ -37401,17 +37495,17 @@
         <v>504</v>
       </c>
       <c r="P246" s="86" t="s">
-        <v>1265</v>
+        <v>1259</v>
       </c>
       <c r="S246" s="47"/>
       <c r="T246" s="47"/>
     </row>
     <row r="247" spans="1:20" ht="16">
       <c r="A247" s="52" t="s">
-        <v>1247</v>
+        <v>1241</v>
       </c>
       <c r="B247" s="52" t="s">
-        <v>1256</v>
+        <v>1250</v>
       </c>
       <c r="C247" s="52" t="s">
         <v>95</v>
@@ -37455,10 +37549,10 @@
     </row>
     <row r="248" spans="1:20" ht="17">
       <c r="A248" s="55" t="s">
-        <v>1248</v>
+        <v>1242</v>
       </c>
       <c r="B248" s="55" t="s">
-        <v>1257</v>
+        <v>1251</v>
       </c>
       <c r="C248" s="55" t="s">
         <v>95</v>
@@ -37497,7 +37591,7 @@
         <v>678</v>
       </c>
       <c r="P248" s="86" t="s">
-        <v>1266</v>
+        <v>1260</v>
       </c>
       <c r="S248" s="47"/>
       <c r="T248" s="47"/>
@@ -43674,7 +43768,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="15" customHeight="1">
       <c r="A1" s="88" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="B1" s="88"/>
     </row>
@@ -43683,7 +43777,7 @@
         <v>42</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="13.5" customHeight="1">
@@ -43715,25 +43809,25 @@
         <v>42</v>
       </c>
       <c r="B7" s="71" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C7" s="71" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D7" s="71" t="s">
         <v>1047</v>
       </c>
-      <c r="C7" s="71" t="s">
+      <c r="E7" s="71" t="s">
         <v>1048</v>
       </c>
-      <c r="D7" s="71" t="s">
+      <c r="F7" s="71" t="s">
         <v>1049</v>
       </c>
-      <c r="E7" s="71" t="s">
+      <c r="G7" s="71" t="s">
         <v>1050</v>
       </c>
-      <c r="F7" s="71" t="s">
+      <c r="H7" s="71" t="s">
         <v>1051</v>
-      </c>
-      <c r="G7" s="71" t="s">
-        <v>1052</v>
-      </c>
-      <c r="H7" s="71" t="s">
-        <v>1053</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="13.5" customHeight="1">
@@ -43837,7 +43931,7 @@
     </row>
     <row r="12" spans="1:8" s="75" customFormat="1" ht="15.75" customHeight="1">
       <c r="A12" s="89" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="B12" s="89"/>
       <c r="C12" s="89"/>
@@ -43850,13 +43944,13 @@
         <v>98</v>
       </c>
       <c r="B13" s="71" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C13" s="71" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D13" s="71" t="s">
         <v>1055</v>
-      </c>
-      <c r="C13" s="71" t="s">
-        <v>1056</v>
-      </c>
-      <c r="D13" s="71" t="s">
-        <v>1057</v>
       </c>
       <c r="E13" s="71" t="s">
         <v>99</v>
@@ -43870,7 +43964,7 @@
         <v>45952</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>51</v>
@@ -43888,7 +43982,7 @@
         <v>45952</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>51</v>
@@ -43942,7 +44036,7 @@
         <v>45970</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>50</v>
@@ -43960,7 +44054,7 @@
         <v>45970</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>50</v>
@@ -43978,7 +44072,7 @@
         <v>45973</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>50</v>
@@ -43996,7 +44090,7 @@
         <v>45973</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>49</v>
@@ -44014,7 +44108,7 @@
         <v>46058</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>51</v>
@@ -44050,7 +44144,7 @@
         <v>46059</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>49</v>
@@ -44086,7 +44180,7 @@
         <v>46093</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>50</v>
@@ -44104,7 +44198,7 @@
         <v>46093</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="C27" s="11" t="s">
         <v>51</v>
@@ -44187,7 +44281,7 @@
     </row>
     <row r="58" spans="2:2" ht="13.5" customHeight="1">
       <c r="B58" s="6" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
     </row>
   </sheetData>
@@ -44217,7 +44311,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="13.5" customHeight="1">
       <c r="A1" s="78" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="72" customFormat="1" ht="13.5" customHeight="1">
@@ -44225,22 +44319,22 @@
         <v>42</v>
       </c>
       <c r="B3" s="71" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C3" s="71" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D3" s="71" t="s">
+        <v>1060</v>
+      </c>
+      <c r="E3" s="71" t="s">
         <v>1061</v>
       </c>
-      <c r="C3" s="71" t="s">
-        <v>1046</v>
-      </c>
-      <c r="D3" s="71" t="s">
+      <c r="F3" s="71" t="s">
         <v>1062</v>
       </c>
-      <c r="E3" s="71" t="s">
+      <c r="G3" s="71" t="s">
         <v>1063</v>
-      </c>
-      <c r="F3" s="71" t="s">
-        <v>1064</v>
-      </c>
-      <c r="G3" s="71" t="s">
-        <v>1065</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="13.5" customHeight="1">
@@ -44249,7 +44343,7 @@
       </c>
       <c r="B4" s="9">
         <f>IFERROR(SUMIFS(Sales!$C:$C,Sales!$E:$E,$A4,Sales!$I:$I,"Completed"),0)</f>
-        <v>469208</v>
+        <v>472938</v>
       </c>
       <c r="C4" s="9">
         <f>VLOOKUP($A4,PartnerShares!$A$3:$B$5,2,FALSE())</f>
@@ -44257,11 +44351,11 @@
       </c>
       <c r="D4" s="9">
         <f>Summary!$B$4*C4</f>
-        <v>179156.4908</v>
+        <v>180400.07279999999</v>
       </c>
       <c r="E4" s="9">
         <f>B4-D4</f>
-        <v>290051.50919999997</v>
+        <v>292537.92720000003</v>
       </c>
       <c r="F4" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -44269,7 +44363,7 @@
       </c>
       <c r="G4" s="73">
         <f>E4+F4</f>
-        <v>152741.48319999996</v>
+        <v>155227.90120000002</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5" customHeight="1">
@@ -44286,11 +44380,11 @@
       </c>
       <c r="D5" s="11">
         <f>Summary!$B$4*C5</f>
-        <v>179049.0184</v>
+        <v>180291.85440000001</v>
       </c>
       <c r="E5" s="11">
         <f>B5-D5</f>
-        <v>-124425.0184</v>
+        <v>-125667.85440000001</v>
       </c>
       <c r="F5" s="11">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -44298,7 +44392,7 @@
       </c>
       <c r="G5" s="74">
         <f>E5+F5</f>
-        <v>-52837.9764</v>
+        <v>-54080.81240000001</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1">
@@ -44315,11 +44409,11 @@
       </c>
       <c r="D6" s="9">
         <f>Summary!$B$4*C6</f>
-        <v>179156.4908</v>
+        <v>180400.07279999999</v>
       </c>
       <c r="E6" s="9">
         <f>B6-D6</f>
-        <v>-166626.4908</v>
+        <v>-167870.07279999999</v>
       </c>
       <c r="F6" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -44327,7 +44421,7 @@
       </c>
       <c r="G6" s="73">
         <f>E6+F6</f>
-        <v>-100903.50679999999</v>
+        <v>-102147.08879999998</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="13.5" customHeight="1">
@@ -44337,27 +44431,27 @@
     </row>
     <row r="10" spans="1:7" ht="13.5" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="13.5" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="13.5" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="13.5" customHeight="1">
       <c r="A14" s="6" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Chiraath-Summary-Aug26.xlsx
+++ b/docs/Chiraath-Summary-Aug26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anooppremachandran/Desktop/CHIRAATH/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63805685-D5E2-F64D-8AAE-58F5C469B1FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAD0F0D8-6843-AD42-B565-17AC8A3C5383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3381" uniqueCount="1339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3418" uniqueCount="1355">
   <si>
     <t>Notes:</t>
   </si>
@@ -4080,6 +4080,54 @@
   </si>
   <si>
     <t>Hima B S</t>
+  </si>
+  <si>
+    <t>Kuthanpully</t>
+  </si>
+  <si>
+    <t>CHR-249</t>
+  </si>
+  <si>
+    <t>CHR-250</t>
+  </si>
+  <si>
+    <t>Purple with silver zari</t>
+  </si>
+  <si>
+    <t>Peacock blue/Royal blue, Purple/Pink, Lime Green/Wine Purple</t>
+  </si>
+  <si>
+    <t>426363 Churidar Set</t>
+  </si>
+  <si>
+    <t>L, XL, XXL</t>
+  </si>
+  <si>
+    <t>CHR-251</t>
+  </si>
+  <si>
+    <t>425677 Churidar Set</t>
+  </si>
+  <si>
+    <t>M, L, XL, XXL</t>
+  </si>
+  <si>
+    <t>CHR-252</t>
+  </si>
+  <si>
+    <t>417278 Churidar Set</t>
+  </si>
+  <si>
+    <t>CHR-253</t>
+  </si>
+  <si>
+    <t>424938 Churidar Set</t>
+  </si>
+  <si>
+    <t>Soft Silk Saree Collection (Kuthanpully)</t>
+  </si>
+  <si>
+    <t>Semi Silk (Kuthanpully)</t>
   </si>
 </sst>
 </file>
@@ -4091,7 +4139,7 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4322,6 +4370,13 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <strike/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -4437,7 +4492,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4677,6 +4732,21 @@
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5068,10 +5138,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>173</c:v>
+                  <c:v>177</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>51</c:v>
+                  <c:v>65</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>3</c:v>
@@ -5398,10 +5468,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>53945</c:v>
+                  <c:v>69573</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>122683.14666666667</c:v>
+                  <c:v>125729.14666666667</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>1062</c:v>
@@ -5737,7 +5807,7 @@
                   <c:v>102200</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>10461</c:v>
+                  <c:v>45517</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -5897,7 +5967,7 @@
                   <c:v>63906</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>72908</c:v>
+                  <c:v>72808</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -6337,7 +6407,7 @@
                   <c:v>-38294</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>62447</c:v>
+                  <c:v>27291</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -7958,7 +8028,7 @@
     <col min="4" max="4" width="30.1640625" style="6" customWidth="1"/>
     <col min="5" max="5" width="22.1640625" style="6" customWidth="1"/>
     <col min="6" max="6" width="31.1640625" style="6" customWidth="1"/>
-    <col min="7" max="7" width="14.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" style="6" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="8.83203125" style="6"/>
   </cols>
   <sheetData>
@@ -7973,7 +8043,7 @@
       </c>
       <c r="B3" s="8">
         <f>SUM(Purchases!C:C)</f>
-        <v>566808</v>
+        <v>601864</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>42</v>
@@ -7988,7 +8058,7 @@
       </c>
       <c r="B4" s="10">
         <f>SUMIFS(Sales!C:C, Sales!I:I, "Completed")</f>
-        <v>541092</v>
+        <v>544692</v>
       </c>
       <c r="E4" s="9" t="str">
         <f>PartnerShares!A3</f>
@@ -8005,7 +8075,7 @@
       </c>
       <c r="B5" s="12">
         <f>SUM(Sales!C:C)</f>
-        <v>565312</v>
+        <v>565212</v>
       </c>
       <c r="E5" s="11" t="str">
         <f>PartnerShares!A4</f>
@@ -8022,7 +8092,7 @@
       </c>
       <c r="B6" s="10">
         <f>B4-B3</f>
-        <v>-25716</v>
+        <v>-57172</v>
       </c>
       <c r="E6" s="9" t="str">
         <f>PartnerShares!A5</f>
@@ -8057,7 +8127,7 @@
       </c>
       <c r="B10" s="13">
         <f>PartnerShares!H8</f>
-        <v>55651.66</v>
+        <v>44016.32666666666</v>
       </c>
       <c r="C10" s="9"/>
     </row>
@@ -8067,7 +8137,7 @@
       </c>
       <c r="B11" s="14">
         <f>PartnerShares!H9</f>
-        <v>40741.67</v>
+        <v>64062.336666666655</v>
       </c>
       <c r="C11" s="11"/>
     </row>
@@ -8077,7 +8147,7 @@
       </c>
       <c r="B12" s="13">
         <f>PartnerShares!H10</f>
-        <v>-96393.33</v>
+        <v>-108078.66333333334</v>
       </c>
       <c r="C12" s="9"/>
     </row>
@@ -8116,15 +8186,15 @@
       </c>
       <c r="B18" s="10">
         <f>PartnerShares!B8</f>
-        <v>262891</v>
+        <v>262941</v>
       </c>
       <c r="C18" s="10">
         <f>PartnerShares!C8</f>
-        <v>188936</v>
+        <v>200621.33333333334</v>
       </c>
       <c r="D18" s="10">
         <f>PartnerShares!D8</f>
-        <v>73955</v>
+        <v>62319.666666666657</v>
       </c>
       <c r="E18" s="10">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A18,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A18,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -8132,11 +8202,11 @@
       </c>
       <c r="F18" s="13">
         <f>D18-E18</f>
-        <v>55651.66</v>
+        <v>44016.32666666666</v>
       </c>
       <c r="G18" s="16" t="str">
         <f>IF(ROUND(F18,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F18),"#,##0"),IF(ROUND(F18,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F18),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹55,652</v>
+        <v>Receive ₹44,016</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="13.5" customHeight="1">
@@ -8146,15 +8216,15 @@
       </c>
       <c r="B19" s="12">
         <f>PartnerShares!B9</f>
-        <v>271317</v>
+        <v>306323</v>
       </c>
       <c r="C19" s="12">
         <f>PartnerShares!C9</f>
-        <v>188936</v>
+        <v>200621.33333333334</v>
       </c>
       <c r="D19" s="12">
         <f>PartnerShares!D9</f>
-        <v>82381</v>
+        <v>105701.66666666666</v>
       </c>
       <c r="E19" s="12">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A19,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A19,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -8162,11 +8232,11 @@
       </c>
       <c r="F19" s="14">
         <f>D19-E19</f>
-        <v>40741.67</v>
+        <v>64062.336666666655</v>
       </c>
       <c r="G19" s="17" t="str">
         <f>IF(ROUND(F19,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F19),"#,##0"),IF(ROUND(F19,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F19),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹40,742</v>
+        <v>Receive ₹64,062</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="13.5" customHeight="1">
@@ -8180,11 +8250,11 @@
       </c>
       <c r="C20" s="10">
         <f>PartnerShares!C10</f>
-        <v>188936</v>
+        <v>200621.33333333334</v>
       </c>
       <c r="D20" s="10">
         <f>PartnerShares!D10</f>
-        <v>-156336</v>
+        <v>-168021.33333333334</v>
       </c>
       <c r="E20" s="10">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A20,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A20,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -8192,11 +8262,11 @@
       </c>
       <c r="F20" s="13">
         <f>D20-E20</f>
-        <v>-96393.33</v>
+        <v>-108078.66333333334</v>
       </c>
       <c r="G20" s="17" t="str">
         <f>IF(ROUND(F20,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F20),"#,##0"),IF(ROUND(F20,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F20),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹96,393</v>
+        <v>Pay ₹108,079</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.75" customHeight="1">
@@ -8234,15 +8304,15 @@
       </c>
       <c r="B26" s="10">
         <f>'Cash Pool'!B4</f>
-        <v>472938</v>
+        <v>476538</v>
       </c>
       <c r="C26" s="10">
         <f>'Cash Pool'!D4</f>
-        <v>180400.07279999999</v>
+        <v>181600.31279999999</v>
       </c>
       <c r="D26" s="10">
         <f>'Cash Pool'!E4</f>
-        <v>292537.92720000003</v>
+        <v>294937.68720000004</v>
       </c>
       <c r="E26" s="10">
         <f>'Cash Pool'!F4</f>
@@ -8250,11 +8320,11 @@
       </c>
       <c r="F26" s="13">
         <f>'Cash Pool'!G4</f>
-        <v>155227.90120000002</v>
+        <v>157627.66120000003</v>
       </c>
       <c r="G26" s="17" t="str">
         <f>IF(ROUND(F26,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F26),"#,##0"),IF(ROUND(F26,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F26),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹155,228</v>
+        <v>Pay ₹157,628</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="13.5" customHeight="1">
@@ -8268,11 +8338,11 @@
       </c>
       <c r="C27" s="12">
         <f>'Cash Pool'!D5</f>
-        <v>180291.85440000001</v>
+        <v>181491.3744</v>
       </c>
       <c r="D27" s="12">
         <f>'Cash Pool'!E5</f>
-        <v>-125667.85440000001</v>
+        <v>-126867.3744</v>
       </c>
       <c r="E27" s="12">
         <f>'Cash Pool'!F5</f>
@@ -8280,11 +8350,11 @@
       </c>
       <c r="F27" s="14">
         <f>'Cash Pool'!G5</f>
-        <v>-54080.81240000001</v>
+        <v>-55280.332399999999</v>
       </c>
       <c r="G27" s="18" t="str">
         <f>IF(ROUND(F27,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F27),"#,##0"),IF(ROUND(F27,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F27),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹54,081</v>
+        <v>Receive ₹55,280</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="13.5" customHeight="1">
@@ -8298,11 +8368,11 @@
       </c>
       <c r="C28" s="10">
         <f>'Cash Pool'!D6</f>
-        <v>180400.07279999999</v>
+        <v>181600.31279999999</v>
       </c>
       <c r="D28" s="10">
         <f>'Cash Pool'!E6</f>
-        <v>-167870.07279999999</v>
+        <v>-169070.31279999999</v>
       </c>
       <c r="E28" s="10">
         <f>'Cash Pool'!F6</f>
@@ -8310,11 +8380,11 @@
       </c>
       <c r="F28" s="13">
         <f>'Cash Pool'!G6</f>
-        <v>-102147.08879999998</v>
+        <v>-103347.32879999997</v>
       </c>
       <c r="G28" s="16" t="str">
         <f>IF(ROUND(F28,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F28),"#,##0"),IF(ROUND(F28,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F28),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹102,147</v>
+        <v>Receive ₹103,347</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.75" customHeight="1">
@@ -8426,7 +8496,7 @@
       </c>
       <c r="B3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1">
@@ -8435,14 +8505,14 @@
       </c>
       <c r="B5" s="21">
         <f>Summary!B3</f>
-        <v>566808</v>
+        <v>601864</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>69</v>
       </c>
       <c r="E5" s="21">
         <f>Summary!B4</f>
-        <v>541092</v>
+        <v>544692</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
@@ -8451,14 +8521,14 @@
       </c>
       <c r="B6" s="21">
         <f>Summary!B6</f>
-        <v>-25716</v>
+        <v>-57172</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>71</v>
       </c>
       <c r="E6" s="21">
         <f>SUMIFS(INVENTORY!K:K, INVENTORY!N:N, "&lt;&gt;Sold Out")</f>
-        <v>168031.34666666665</v>
+        <v>186705.34666666665</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1">
@@ -8628,15 +8698,15 @@
       </c>
       <c r="B17" s="27">
         <f>IFERROR(SUMPRODUCT((TEXT(Purchases!$A$2:$A$998,"MMM")=$A17)*(YEAR(Purchases!$A$2:$A$998)=$B$7)*Purchases!$C$2:$C$998),0)</f>
-        <v>10461</v>
+        <v>45517</v>
       </c>
       <c r="C17" s="27">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$993,"MMM")=$A17)*(YEAR(Sales!$A$2:$A$993)=$B$7)*Sales!$C$2:$C$993),0)</f>
-        <v>72908</v>
+        <v>72808</v>
       </c>
       <c r="D17" s="27">
         <f t="shared" si="0"/>
-        <v>62447</v>
+        <v>27291</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1">
@@ -8734,14 +8804,14 @@
       </c>
       <c r="H47" s="30">
         <f>SUMIF(INVENTORY!C:C, F47, INVENTORY!G:G)</f>
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="J47" s="30" t="s">
         <v>96</v>
       </c>
       <c r="K47" s="31">
         <f t="array" ref="K47">SUMPRODUCT((INVENTORY!$C$2:$C$476=J47)*(INVENTORY!$D$2:$D$476)*(INVENTORY!$G$2:$G$476))</f>
-        <v>53945</v>
+        <v>69573</v>
       </c>
     </row>
     <row r="48" spans="6:11" ht="15" customHeight="1">
@@ -8754,14 +8824,14 @@
       </c>
       <c r="H48" s="30">
         <f>SUMIF(INVENTORY!C:C, F48, INVENTORY!G:G)</f>
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="J48" s="30" t="s">
         <v>95</v>
       </c>
       <c r="K48" s="31">
         <f t="array" ref="K48">SUMPRODUCT((INVENTORY!$C$2:$C$476=J48)*(INVENTORY!$D$2:$D$476)*(INVENTORY!$G$2:$G$476))</f>
-        <v>122683.14666666667</v>
+        <v>125729.14666666667</v>
       </c>
     </row>
     <row r="49" spans="5:12" ht="15" customHeight="1">
@@ -10390,22 +10460,46 @@
       </c>
     </row>
     <row r="110" spans="1:4" ht="15" customHeight="1">
-      <c r="A110" s="35"/>
-      <c r="B110" s="36"/>
-      <c r="C110" s="37"/>
-      <c r="D110" s="36"/>
+      <c r="A110" s="35">
+        <v>46259</v>
+      </c>
+      <c r="B110" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="C110" s="37">
+        <v>3046</v>
+      </c>
+      <c r="D110" s="36" t="s">
+        <v>1339</v>
+      </c>
     </row>
     <row r="111" spans="1:4" ht="15" customHeight="1">
-      <c r="A111" s="38"/>
-      <c r="B111" s="39"/>
-      <c r="C111" s="40"/>
-      <c r="D111" s="39"/>
+      <c r="A111" s="38">
+        <v>46262</v>
+      </c>
+      <c r="B111" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="C111" s="40">
+        <v>50</v>
+      </c>
+      <c r="D111" s="39" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="112" spans="1:4" ht="15" customHeight="1">
-      <c r="A112" s="35"/>
-      <c r="B112" s="36"/>
-      <c r="C112" s="37"/>
-      <c r="D112" s="36"/>
+      <c r="A112" s="35">
+        <v>46262</v>
+      </c>
+      <c r="B112" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="C112" s="37">
+        <v>31960</v>
+      </c>
+      <c r="D112" s="36" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="113" spans="1:4" ht="15" customHeight="1">
       <c r="A113" s="38"/>
@@ -20291,19 +20385,21 @@
         <v>175</v>
       </c>
       <c r="C319" s="85">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="D319" s="45" t="s">
         <v>162</v>
       </c>
-      <c r="E319" s="45"/>
+      <c r="E319" s="45" t="s">
+        <v>49</v>
+      </c>
       <c r="F319" s="46"/>
       <c r="G319" s="46"/>
       <c r="H319" s="46" t="s">
         <v>1323</v>
       </c>
       <c r="I319" s="45" t="s">
-        <v>356</v>
+        <v>148</v>
       </c>
     </row>
     <row r="320" spans="1:9" ht="14">
@@ -20353,7 +20449,7 @@
         <v>1333</v>
       </c>
       <c r="I321" s="45" t="s">
-        <v>356</v>
+        <v>148</v>
       </c>
     </row>
     <row r="322" spans="1:9" ht="14">
@@ -37202,7 +37298,7 @@
       <c r="S240" s="47"/>
       <c r="T240" s="47"/>
     </row>
-    <row r="241" spans="1:20" ht="17">
+    <row r="241" spans="1:246" ht="17">
       <c r="A241" s="52" t="s">
         <v>1235</v>
       </c>
@@ -37253,7 +37349,7 @@
       <c r="S241" s="47"/>
       <c r="T241" s="47"/>
     </row>
-    <row r="242" spans="1:20" ht="17">
+    <row r="242" spans="1:246" ht="17">
       <c r="A242" s="55" t="s">
         <v>1236</v>
       </c>
@@ -37304,7 +37400,7 @@
       <c r="S242" s="47"/>
       <c r="T242" s="47"/>
     </row>
-    <row r="243" spans="1:20" ht="17">
+    <row r="243" spans="1:246" ht="17">
       <c r="A243" s="52" t="s">
         <v>1237</v>
       </c>
@@ -37355,7 +37451,7 @@
       <c r="S243" s="47"/>
       <c r="T243" s="47"/>
     </row>
-    <row r="244" spans="1:20" ht="17">
+    <row r="244" spans="1:246" ht="17">
       <c r="A244" s="55" t="s">
         <v>1238</v>
       </c>
@@ -37404,7 +37500,7 @@
       <c r="S244" s="47"/>
       <c r="T244" s="47"/>
     </row>
-    <row r="245" spans="1:20" ht="16">
+    <row r="245" spans="1:246" ht="16">
       <c r="A245" s="52" t="s">
         <v>1239</v>
       </c>
@@ -37451,58 +37547,282 @@
       <c r="S245" s="47"/>
       <c r="T245" s="47"/>
     </row>
-    <row r="246" spans="1:20" ht="17">
-      <c r="A246" s="55" t="s">
+    <row r="246" spans="1:246" s="62" customFormat="1" ht="17">
+      <c r="A246" s="90" t="s">
         <v>1240</v>
       </c>
-      <c r="B246" s="55" t="s">
+      <c r="B246" s="90" t="s">
         <v>1249</v>
       </c>
-      <c r="C246" s="55" t="s">
+      <c r="C246" s="90" t="s">
         <v>95</v>
       </c>
-      <c r="D246" s="56">
+      <c r="D246" s="91">
         <v>629</v>
       </c>
-      <c r="E246" s="56"/>
-      <c r="F246" s="64">
+      <c r="E246" s="91"/>
+      <c r="F246" s="92">
         <v>0</v>
       </c>
-      <c r="G246" s="64">
+      <c r="G246" s="92">
         <v>0</v>
       </c>
-      <c r="H246" s="63">
+      <c r="H246" s="93">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="I246" s="63">
+      <c r="I246" s="93">
         <f>IF(D246&lt;&gt;"",D246,IFERROR(E246/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
         <v>629</v>
       </c>
-      <c r="J246" s="63">
+      <c r="J246" s="93">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="K246" s="63">
+      <c r="K246" s="93">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="L246" s="55" t="s">
+      <c r="L246" s="90" t="s">
         <v>608</v>
       </c>
-      <c r="M246" s="55"/>
-      <c r="N246" s="47" t="s">
+      <c r="M246" s="90"/>
+      <c r="N246" s="62" t="s">
         <v>504</v>
       </c>
-      <c r="P246" s="86" t="s">
+      <c r="P246" s="94" t="s">
         <v>1259</v>
       </c>
-      <c r="S246" s="47"/>
-      <c r="T246" s="47"/>
-    </row>
-    <row r="247" spans="1:20" ht="16">
+      <c r="U246" s="61"/>
+      <c r="V246" s="61"/>
+      <c r="W246" s="61"/>
+      <c r="X246" s="61"/>
+      <c r="Y246" s="61"/>
+      <c r="Z246" s="61"/>
+      <c r="AA246" s="61"/>
+      <c r="AB246" s="61"/>
+      <c r="AC246" s="61"/>
+      <c r="AD246" s="61"/>
+      <c r="AE246" s="61"/>
+      <c r="AF246" s="61"/>
+      <c r="AG246" s="61"/>
+      <c r="AH246" s="61"/>
+      <c r="AI246" s="61"/>
+      <c r="AJ246" s="61"/>
+      <c r="AK246" s="61"/>
+      <c r="AL246" s="61"/>
+      <c r="AM246" s="61"/>
+      <c r="AN246" s="61"/>
+      <c r="AO246" s="61"/>
+      <c r="AP246" s="61"/>
+      <c r="AQ246" s="61"/>
+      <c r="AR246" s="61"/>
+      <c r="AS246" s="61"/>
+      <c r="AT246" s="61"/>
+      <c r="AU246" s="61"/>
+      <c r="AV246" s="61"/>
+      <c r="AW246" s="61"/>
+      <c r="AX246" s="61"/>
+      <c r="AY246" s="61"/>
+      <c r="AZ246" s="61"/>
+      <c r="BA246" s="61"/>
+      <c r="BB246" s="61"/>
+      <c r="BC246" s="61"/>
+      <c r="BD246" s="61"/>
+      <c r="BE246" s="61"/>
+      <c r="BF246" s="61"/>
+      <c r="BG246" s="61"/>
+      <c r="BH246" s="61"/>
+      <c r="BI246" s="61"/>
+      <c r="BJ246" s="61"/>
+      <c r="BK246" s="61"/>
+      <c r="BL246" s="61"/>
+      <c r="BM246" s="61"/>
+      <c r="BN246" s="61"/>
+      <c r="BO246" s="61"/>
+      <c r="BP246" s="61"/>
+      <c r="BQ246" s="61"/>
+      <c r="BR246" s="61"/>
+      <c r="BS246" s="61"/>
+      <c r="BT246" s="61"/>
+      <c r="BU246" s="61"/>
+      <c r="BV246" s="61"/>
+      <c r="BW246" s="61"/>
+      <c r="BX246" s="61"/>
+      <c r="BY246" s="61"/>
+      <c r="BZ246" s="61"/>
+      <c r="CA246" s="61"/>
+      <c r="CB246" s="61"/>
+      <c r="CC246" s="61"/>
+      <c r="CD246" s="61"/>
+      <c r="CE246" s="61"/>
+      <c r="CF246" s="61"/>
+      <c r="CG246" s="61"/>
+      <c r="CH246" s="61"/>
+      <c r="CI246" s="61"/>
+      <c r="CJ246" s="61"/>
+      <c r="CK246" s="61"/>
+      <c r="CL246" s="61"/>
+      <c r="CM246" s="61"/>
+      <c r="CN246" s="61"/>
+      <c r="CO246" s="61"/>
+      <c r="CP246" s="61"/>
+      <c r="CQ246" s="61"/>
+      <c r="CR246" s="61"/>
+      <c r="CS246" s="61"/>
+      <c r="CT246" s="61"/>
+      <c r="CU246" s="61"/>
+      <c r="CV246" s="61"/>
+      <c r="CW246" s="61"/>
+      <c r="CX246" s="61"/>
+      <c r="CY246" s="61"/>
+      <c r="CZ246" s="61"/>
+      <c r="DA246" s="61"/>
+      <c r="DB246" s="61"/>
+      <c r="DC246" s="61"/>
+      <c r="DD246" s="61"/>
+      <c r="DE246" s="61"/>
+      <c r="DF246" s="61"/>
+      <c r="DG246" s="61"/>
+      <c r="DH246" s="61"/>
+      <c r="DI246" s="61"/>
+      <c r="DJ246" s="61"/>
+      <c r="DK246" s="61"/>
+      <c r="DL246" s="61"/>
+      <c r="DM246" s="61"/>
+      <c r="DN246" s="61"/>
+      <c r="DO246" s="61"/>
+      <c r="DP246" s="61"/>
+      <c r="DQ246" s="61"/>
+      <c r="DR246" s="61"/>
+      <c r="DS246" s="61"/>
+      <c r="DT246" s="61"/>
+      <c r="DU246" s="61"/>
+      <c r="DV246" s="61"/>
+      <c r="DW246" s="61"/>
+      <c r="DX246" s="61"/>
+      <c r="DY246" s="61"/>
+      <c r="DZ246" s="61"/>
+      <c r="EA246" s="61"/>
+      <c r="EB246" s="61"/>
+      <c r="EC246" s="61"/>
+      <c r="ED246" s="61"/>
+      <c r="EE246" s="61"/>
+      <c r="EF246" s="61"/>
+      <c r="EG246" s="61"/>
+      <c r="EH246" s="61"/>
+      <c r="EI246" s="61"/>
+      <c r="EJ246" s="61"/>
+      <c r="EK246" s="61"/>
+      <c r="EL246" s="61"/>
+      <c r="EM246" s="61"/>
+      <c r="EN246" s="61"/>
+      <c r="EO246" s="61"/>
+      <c r="EP246" s="61"/>
+      <c r="EQ246" s="61"/>
+      <c r="ER246" s="61"/>
+      <c r="ES246" s="61"/>
+      <c r="ET246" s="61"/>
+      <c r="EU246" s="61"/>
+      <c r="EV246" s="61"/>
+      <c r="EW246" s="61"/>
+      <c r="EX246" s="61"/>
+      <c r="EY246" s="61"/>
+      <c r="EZ246" s="61"/>
+      <c r="FA246" s="61"/>
+      <c r="FB246" s="61"/>
+      <c r="FC246" s="61"/>
+      <c r="FD246" s="61"/>
+      <c r="FE246" s="61"/>
+      <c r="FF246" s="61"/>
+      <c r="FG246" s="61"/>
+      <c r="FH246" s="61"/>
+      <c r="FI246" s="61"/>
+      <c r="FJ246" s="61"/>
+      <c r="FK246" s="61"/>
+      <c r="FL246" s="61"/>
+      <c r="FM246" s="61"/>
+      <c r="FN246" s="61"/>
+      <c r="FO246" s="61"/>
+      <c r="FP246" s="61"/>
+      <c r="FQ246" s="61"/>
+      <c r="FR246" s="61"/>
+      <c r="FS246" s="61"/>
+      <c r="FT246" s="61"/>
+      <c r="FU246" s="61"/>
+      <c r="FV246" s="61"/>
+      <c r="FW246" s="61"/>
+      <c r="FX246" s="61"/>
+      <c r="FY246" s="61"/>
+      <c r="FZ246" s="61"/>
+      <c r="GA246" s="61"/>
+      <c r="GB246" s="61"/>
+      <c r="GC246" s="61"/>
+      <c r="GD246" s="61"/>
+      <c r="GE246" s="61"/>
+      <c r="GF246" s="61"/>
+      <c r="GG246" s="61"/>
+      <c r="GH246" s="61"/>
+      <c r="GI246" s="61"/>
+      <c r="GJ246" s="61"/>
+      <c r="GK246" s="61"/>
+      <c r="GL246" s="61"/>
+      <c r="GM246" s="61"/>
+      <c r="GN246" s="61"/>
+      <c r="GO246" s="61"/>
+      <c r="GP246" s="61"/>
+      <c r="GQ246" s="61"/>
+      <c r="GR246" s="61"/>
+      <c r="GS246" s="61"/>
+      <c r="GT246" s="61"/>
+      <c r="GU246" s="61"/>
+      <c r="GV246" s="61"/>
+      <c r="GW246" s="61"/>
+      <c r="GX246" s="61"/>
+      <c r="GY246" s="61"/>
+      <c r="GZ246" s="61"/>
+      <c r="HA246" s="61"/>
+      <c r="HB246" s="61"/>
+      <c r="HC246" s="61"/>
+      <c r="HD246" s="61"/>
+      <c r="HE246" s="61"/>
+      <c r="HF246" s="61"/>
+      <c r="HG246" s="61"/>
+      <c r="HH246" s="61"/>
+      <c r="HI246" s="61"/>
+      <c r="HJ246" s="61"/>
+      <c r="HK246" s="61"/>
+      <c r="HL246" s="61"/>
+      <c r="HM246" s="61"/>
+      <c r="HN246" s="61"/>
+      <c r="HO246" s="61"/>
+      <c r="HP246" s="61"/>
+      <c r="HQ246" s="61"/>
+      <c r="HR246" s="61"/>
+      <c r="HS246" s="61"/>
+      <c r="HT246" s="61"/>
+      <c r="HU246" s="61"/>
+      <c r="HV246" s="61"/>
+      <c r="HW246" s="61"/>
+      <c r="HX246" s="61"/>
+      <c r="HY246" s="61"/>
+      <c r="HZ246" s="61"/>
+      <c r="IA246" s="61"/>
+      <c r="IB246" s="61"/>
+      <c r="IC246" s="61"/>
+      <c r="ID246" s="61"/>
+      <c r="IE246" s="61"/>
+      <c r="IF246" s="61"/>
+      <c r="IG246" s="61"/>
+      <c r="IH246" s="61"/>
+      <c r="II246" s="61"/>
+      <c r="IJ246" s="61"/>
+      <c r="IK246" s="61"/>
+      <c r="IL246" s="61"/>
+    </row>
+    <row r="247" spans="1:246" ht="16">
       <c r="A247" s="52" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="B247" s="52" t="s">
         <v>1250</v>
@@ -37547,9 +37867,9 @@
       <c r="S247" s="47"/>
       <c r="T247" s="47"/>
     </row>
-    <row r="248" spans="1:20" ht="17">
+    <row r="248" spans="1:246" ht="17">
       <c r="A248" s="55" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="B248" s="55" t="s">
         <v>1251</v>
@@ -37596,12 +37916,22 @@
       <c r="S248" s="47"/>
       <c r="T248" s="47"/>
     </row>
-    <row r="249" spans="1:20" ht="16">
-      <c r="A249" s="52"/>
-      <c r="B249" s="52"/>
-      <c r="C249" s="52"/>
-      <c r="D249" s="53"/>
-      <c r="E249" s="53"/>
+    <row r="249" spans="1:246" ht="17">
+      <c r="A249" s="52" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B249" s="52" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C249" s="52" t="s">
+        <v>95</v>
+      </c>
+      <c r="D249" s="53">
+        <v>882</v>
+      </c>
+      <c r="E249" s="53">
+        <v>1380</v>
+      </c>
       <c r="F249" s="66">
         <v>0</v>
       </c>
@@ -37614,7 +37944,7 @@
       </c>
       <c r="I249" s="65">
         <f>IF(D249&lt;&gt;"",D249,IFERROR(E249/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
-        <v>0</v>
+        <v>882</v>
       </c>
       <c r="J249" s="65">
         <f t="shared" si="19"/>
@@ -37622,33 +37952,48 @@
       </c>
       <c r="K249" s="65">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>2646</v>
       </c>
       <c r="L249" s="52"/>
       <c r="M249" s="52"/>
-      <c r="P249" s="86"/>
+      <c r="N249" s="47" t="s">
+        <v>678</v>
+      </c>
+      <c r="P249" s="86" t="s">
+        <v>1343</v>
+      </c>
       <c r="S249" s="47"/>
       <c r="T249" s="47"/>
     </row>
-    <row r="250" spans="1:20" ht="16">
-      <c r="A250" s="55"/>
-      <c r="B250" s="55"/>
-      <c r="C250" s="55"/>
-      <c r="D250" s="56"/>
-      <c r="E250" s="56"/>
+    <row r="250" spans="1:246" ht="17">
+      <c r="A250" s="55" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B250" s="55" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C250" s="55" t="s">
+        <v>95</v>
+      </c>
+      <c r="D250" s="56">
+        <v>400</v>
+      </c>
+      <c r="E250" s="56">
+        <v>699</v>
+      </c>
       <c r="F250" s="64">
         <v>0</v>
       </c>
       <c r="G250" s="64">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H250" s="63">
         <f t="shared" si="18"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I250" s="63">
         <f>IF(D250&lt;&gt;"",D250,IFERROR(E250/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="J250" s="63">
         <f t="shared" si="19"/>
@@ -37656,19 +38001,32 @@
       </c>
       <c r="K250" s="63">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="L250" s="55"/>
       <c r="M250" s="55"/>
-      <c r="P250" s="86"/>
+      <c r="N250" s="47" t="s">
+        <v>678</v>
+      </c>
+      <c r="P250" s="86" t="s">
+        <v>1342</v>
+      </c>
       <c r="S250" s="47"/>
       <c r="T250" s="47"/>
     </row>
-    <row r="251" spans="1:20" ht="16">
-      <c r="A251" s="52"/>
-      <c r="B251" s="52"/>
-      <c r="C251" s="52"/>
-      <c r="D251" s="53"/>
+    <row r="251" spans="1:246" ht="16">
+      <c r="A251" s="52" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B251" s="52" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C251" s="52" t="s">
+        <v>96</v>
+      </c>
+      <c r="D251" s="53">
+        <v>1090</v>
+      </c>
       <c r="E251" s="53"/>
       <c r="F251" s="66">
         <v>0</v>
@@ -37682,7 +38040,7 @@
       </c>
       <c r="I251" s="65">
         <f>IF(D251&lt;&gt;"",D251,IFERROR(E251/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
-        <v>0</v>
+        <v>1090</v>
       </c>
       <c r="J251" s="65">
         <f t="shared" si="19"/>
@@ -37690,33 +38048,47 @@
       </c>
       <c r="K251" s="65">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>3270</v>
       </c>
       <c r="L251" s="52"/>
       <c r="M251" s="52"/>
+      <c r="N251" s="47" t="s">
+        <v>678</v>
+      </c>
+      <c r="O251" s="47" t="s">
+        <v>1345</v>
+      </c>
       <c r="P251" s="86"/>
       <c r="S251" s="47"/>
       <c r="T251" s="47"/>
     </row>
-    <row r="252" spans="1:20" ht="16">
-      <c r="A252" s="55"/>
-      <c r="B252" s="55"/>
-      <c r="C252" s="55"/>
-      <c r="D252" s="56"/>
+    <row r="252" spans="1:246" ht="16">
+      <c r="A252" s="55" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B252" s="55" t="s">
+        <v>1347</v>
+      </c>
+      <c r="C252" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="D252" s="56">
+        <v>1049</v>
+      </c>
       <c r="E252" s="56"/>
       <c r="F252" s="64">
         <v>0</v>
       </c>
       <c r="G252" s="64">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H252" s="63">
         <f t="shared" si="18"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I252" s="63">
         <f>IF(D252&lt;&gt;"",D252,IFERROR(E252/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
-        <v>0</v>
+        <v>1049</v>
       </c>
       <c r="J252" s="63">
         <f t="shared" si="19"/>
@@ -37724,33 +38096,47 @@
       </c>
       <c r="K252" s="63">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>4196</v>
       </c>
       <c r="L252" s="55"/>
       <c r="M252" s="55"/>
+      <c r="N252" s="47" t="s">
+        <v>678</v>
+      </c>
+      <c r="O252" s="47" t="s">
+        <v>1348</v>
+      </c>
       <c r="P252" s="86"/>
       <c r="S252" s="47"/>
       <c r="T252" s="47"/>
     </row>
-    <row r="253" spans="1:20" ht="16">
-      <c r="A253" s="52"/>
-      <c r="B253" s="52"/>
-      <c r="C253" s="52"/>
-      <c r="D253" s="53"/>
+    <row r="253" spans="1:246" ht="16">
+      <c r="A253" s="52" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B253" s="52" t="s">
+        <v>1350</v>
+      </c>
+      <c r="C253" s="52" t="s">
+        <v>96</v>
+      </c>
+      <c r="D253" s="53">
+        <v>1049</v>
+      </c>
       <c r="E253" s="53"/>
       <c r="F253" s="66">
         <v>0</v>
       </c>
       <c r="G253" s="66">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H253" s="65">
         <f t="shared" si="18"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I253" s="65">
         <f>IF(D253&lt;&gt;"",D253,IFERROR(E253/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
-        <v>0</v>
+        <v>1049</v>
       </c>
       <c r="J253" s="65">
         <f t="shared" si="19"/>
@@ -37758,19 +38144,33 @@
       </c>
       <c r="K253" s="65">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>4196</v>
       </c>
       <c r="L253" s="52"/>
       <c r="M253" s="52"/>
+      <c r="N253" s="47" t="s">
+        <v>678</v>
+      </c>
+      <c r="O253" s="47" t="s">
+        <v>1348</v>
+      </c>
       <c r="P253" s="86"/>
       <c r="S253" s="47"/>
       <c r="T253" s="47"/>
     </row>
-    <row r="254" spans="1:20" ht="16">
-      <c r="A254" s="55"/>
-      <c r="B254" s="55"/>
-      <c r="C254" s="55"/>
-      <c r="D254" s="56"/>
+    <row r="254" spans="1:246" ht="16">
+      <c r="A254" s="55" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B254" s="55" t="s">
+        <v>1352</v>
+      </c>
+      <c r="C254" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="D254" s="56">
+        <v>1322</v>
+      </c>
       <c r="E254" s="56"/>
       <c r="F254" s="64">
         <v>0</v>
@@ -37784,7 +38184,7 @@
       </c>
       <c r="I254" s="63">
         <f>IF(D254&lt;&gt;"",D254,IFERROR(E254/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
-        <v>0</v>
+        <v>1322</v>
       </c>
       <c r="J254" s="63">
         <f t="shared" si="19"/>
@@ -37792,15 +38192,21 @@
       </c>
       <c r="K254" s="63">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>3966</v>
       </c>
       <c r="L254" s="55"/>
       <c r="M254" s="55"/>
+      <c r="N254" s="47" t="s">
+        <v>678</v>
+      </c>
+      <c r="O254" s="47" t="s">
+        <v>1345</v>
+      </c>
       <c r="P254" s="86"/>
       <c r="S254" s="47"/>
       <c r="T254" s="47"/>
     </row>
-    <row r="255" spans="1:20" ht="16">
+    <row r="255" spans="1:246" ht="16">
       <c r="A255" s="52"/>
       <c r="B255" s="52"/>
       <c r="C255" s="52"/>
@@ -37834,7 +38240,7 @@
       <c r="S255" s="47"/>
       <c r="T255" s="47"/>
     </row>
-    <row r="256" spans="1:20" ht="16">
+    <row r="256" spans="1:246" ht="16">
       <c r="A256" s="55"/>
       <c r="B256" s="55"/>
       <c r="C256" s="55"/>
@@ -43836,15 +44242,15 @@
       </c>
       <c r="B8" s="9">
         <f>IFERROR(SUMIF(Purchases!$B:$B,$A8,Purchases!$C:$C),0)</f>
-        <v>262891</v>
+        <v>262941</v>
       </c>
       <c r="C8" s="9">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>188936</v>
+        <v>200621.33333333334</v>
       </c>
       <c r="D8" s="9">
         <f>B8-C8</f>
-        <v>73955</v>
+        <v>62319.666666666657</v>
       </c>
       <c r="E8" s="9">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A8,$A$3:$B$5,2,FALSE()),0)</f>
@@ -43852,7 +44258,7 @@
       </c>
       <c r="F8" s="9">
         <f>D8+E8</f>
-        <v>73955</v>
+        <v>62319.666666666657</v>
       </c>
       <c r="G8" s="9">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A8,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A8,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A8,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A8,$B$13:$B$499,"Profit"),0)</f>
@@ -43860,7 +44266,7 @@
       </c>
       <c r="H8" s="73">
         <f>F8-G8</f>
-        <v>55651.66</v>
+        <v>44016.32666666666</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="13.5" customHeight="1">
@@ -43869,15 +44275,15 @@
       </c>
       <c r="B9" s="11">
         <f>IFERROR(SUMIF(Purchases!$B:$B,$A9,Purchases!$C:$C),0)</f>
-        <v>271317</v>
+        <v>306323</v>
       </c>
       <c r="C9" s="11">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>188936</v>
+        <v>200621.33333333334</v>
       </c>
       <c r="D9" s="11">
         <f>B9-C9</f>
-        <v>82381</v>
+        <v>105701.66666666666</v>
       </c>
       <c r="E9" s="11">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A9,$A$3:$B$5,2,FALSE()),0)</f>
@@ -43885,7 +44291,7 @@
       </c>
       <c r="F9" s="11">
         <f>D9+E9</f>
-        <v>82381</v>
+        <v>105701.66666666666</v>
       </c>
       <c r="G9" s="11">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A9,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A9,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A9,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A9,$B$13:$B$499,"Profit"),0)</f>
@@ -43893,7 +44299,7 @@
       </c>
       <c r="H9" s="74">
         <f>F9-G9</f>
-        <v>40741.67</v>
+        <v>64062.336666666655</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="13.5" customHeight="1">
@@ -43906,11 +44312,11 @@
       </c>
       <c r="C10" s="9">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>188936</v>
+        <v>200621.33333333334</v>
       </c>
       <c r="D10" s="9">
         <f>B10-C10</f>
-        <v>-156336</v>
+        <v>-168021.33333333334</v>
       </c>
       <c r="E10" s="9">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A10,$A$3:$B$5,2,FALSE()),0)</f>
@@ -43918,7 +44324,7 @@
       </c>
       <c r="F10" s="9">
         <f>D10+E10</f>
-        <v>-156336</v>
+        <v>-168021.33333333334</v>
       </c>
       <c r="G10" s="9">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A10,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A10,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A10,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A10,$B$13:$B$499,"Profit"),0)</f>
@@ -43926,7 +44332,7 @@
       </c>
       <c r="H10" s="73">
         <f>F10-G10</f>
-        <v>-96393.33</v>
+        <v>-108078.66333333334</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="75" customFormat="1" ht="15.75" customHeight="1">
@@ -44343,7 +44749,7 @@
       </c>
       <c r="B4" s="9">
         <f>IFERROR(SUMIFS(Sales!$C:$C,Sales!$E:$E,$A4,Sales!$I:$I,"Completed"),0)</f>
-        <v>472938</v>
+        <v>476538</v>
       </c>
       <c r="C4" s="9">
         <f>VLOOKUP($A4,PartnerShares!$A$3:$B$5,2,FALSE())</f>
@@ -44351,11 +44757,11 @@
       </c>
       <c r="D4" s="9">
         <f>Summary!$B$4*C4</f>
-        <v>180400.07279999999</v>
+        <v>181600.31279999999</v>
       </c>
       <c r="E4" s="9">
         <f>B4-D4</f>
-        <v>292537.92720000003</v>
+        <v>294937.68720000004</v>
       </c>
       <c r="F4" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -44363,7 +44769,7 @@
       </c>
       <c r="G4" s="73">
         <f>E4+F4</f>
-        <v>155227.90120000002</v>
+        <v>157627.66120000003</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5" customHeight="1">
@@ -44380,11 +44786,11 @@
       </c>
       <c r="D5" s="11">
         <f>Summary!$B$4*C5</f>
-        <v>180291.85440000001</v>
+        <v>181491.3744</v>
       </c>
       <c r="E5" s="11">
         <f>B5-D5</f>
-        <v>-125667.85440000001</v>
+        <v>-126867.3744</v>
       </c>
       <c r="F5" s="11">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -44392,7 +44798,7 @@
       </c>
       <c r="G5" s="74">
         <f>E5+F5</f>
-        <v>-54080.81240000001</v>
+        <v>-55280.332399999999</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1">
@@ -44409,11 +44815,11 @@
       </c>
       <c r="D6" s="9">
         <f>Summary!$B$4*C6</f>
-        <v>180400.07279999999</v>
+        <v>181600.31279999999</v>
       </c>
       <c r="E6" s="9">
         <f>B6-D6</f>
-        <v>-167870.07279999999</v>
+        <v>-169070.31279999999</v>
       </c>
       <c r="F6" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -44421,7 +44827,7 @@
       </c>
       <c r="G6" s="73">
         <f>E6+F6</f>
-        <v>-102147.08879999998</v>
+        <v>-103347.32879999997</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="13.5" customHeight="1">
